--- a/evolution/unigrams_concat.xlsx
+++ b/evolution/unigrams_concat.xlsx
@@ -425,483 +425,514 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>All Tokens</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Distinct Token Count</t>
+          <t>1970s</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tokens Appearing Once</t>
+          <t>1980s</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Count (Once)</t>
+          <t>1990s</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tokens Appearing &gt;1 Time</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Count (&gt;1 Time)</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Total Token Count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Verification (Once + Multi)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Min Frequency</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>25% Frequency</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Median Frequency</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>75% Frequency</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Max Frequency</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Mean Frequency</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Std Frequency</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Skew Frequency</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Kurt Frequency</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Decade</t>
+          <t>2020s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>['behavior', 'self', 'children', 'training', 'ss', 'treatment', 'procedures', 'baseline', 'assessment', 'sensory', 'behavioral', 'use', 'design', 'response', 'data', 'multiple', 'recording', 'effects', 'results', 'therapy', 'time', 'behaviors', 'subject', 'procedure', 'extra', 'wk', 'interval', 'measures', 'generalization', 'reliability', 'sharing', 'maintenance', 'reinforcement', 'positive', 'tongue', 'smoking', 'level', 'experiment', 'groups', 'monitoring', 'compliance', 'analysis', 'demand', 'assessed', 'activity', 'drinking', 'device', 'setting', 'technology', 'mean', 'programming', 'using', 'play', 'responding', 'observed', 'social', 'stimulation', 'agreement', 'replication', 'control', 'used', 'reinforcers', 'high', 'type', 'modeling', 'different', 'taste', 'comments', 'physical', 'applied', 'sessions', 'variables', 'increase', 'asthma', 'appropriate', 'observer', 'recorded', 'relaxation', 'significantly', 'change', 'instructions', 'maintained', 'frequency', 'low', 'function', 'students', 'probabilities', 'errors', 'components', 'paradigm', 'studies', 'modification', 'human', 'group', 'subjects', 'decreased', 'tablets', '2nd', '1st', 'mirror', 'thrust', 'techniques', 'prosocial', 'attention', 'retarded', 'feedback', 'bias', 'program', 'alcoholic', 'comparison', 'classroom', 'tv', 'produced', 'verbal', 'demonstrated', 'times', 'manipulation', 'characteristics', 'follow', 'taught', 'previous', 'experience', 'methods', 'partial', 'vivo', 'game', 'involved', 'conversation', 'study', 'cost', 'individual', 'recordings', 'observational', 'reviewed', 'discussed', 'chronic', 'durable', 'operant', 'interactions', 'stereotyped', 'settings', 'research', 'interobserver', 'case', 'single', 'rate', 'introduced', 'pulmonary', 'apparatus', 'controlled', 'auditory', 'examined', 'associated', 'ippb', 'including', 'scale', 'assertion', 'risk', 'areas', 'producing', 'following', 'extinction', 'reduction', 'significant', 'involving', 'food', 'urine', 'disruptive', 'effectiveness', 'vitamin', 'complexity', 'artifact', 'sources', 'problems', 'influence', 'designs', 'functional', 'reversal', 'role', 'implemented', 'article', 'stimulatory', 'terms', 'concept', 'occurred', 'girls', 'modifying', 'living', 'daily', 'contingent', 'interresponse', 'observation', 'momentary', 'sampling', 'stimulus', 'conditioning', 'development', 'effective', 'old', 'yr', '10', 'simulated', 'circuit', 'period', 'free', 'durability', 'extensive', 'observers', 'duration', 'parameters', 'did', 'share', 'resulted', 'computer', 'area', 'trained', 'instructional', 'good', 'randomly', 'males', 'vs', 'interpreted', 'sequentially', 'additional', 'component', 'negative', 'min', 'tension', 'changes', 'pattern', 'instructed', 'decrease', 'sip', 'intersip', 'package', 'cigarette', 'therapeutic', 'given', 'making', 'changing', 'video', 'likely', 'usually', 'maintaining', 'heterosocially', 'anxious', 'college', 'analog', 'heterosocial', 'competence', 'contextual', 'multivariate', 'received', 'followed', 'generalize', 'magnitude', 'slightly', 'teaching', 'just', 'verbally', 'physically', 'approaches', 'closed', 'useful', 'long', 'preschool', 'evaluation', 'judged', 'boy', 'returned', 'increased', 'experiments', 'biomotometer', 'male', 'token', 'length', 'continuous', 'variance', 'durations', 'degree', 'relationship', 'television', 'special', 'generalized', 'class', 'criterion', 'plus', 'providing', 'flavored', 'tablet', 'record', 'circumstances', 'similar', 'media', 'pathological', 'environment', 'autistic', 'difference', 'application', 'learned', 'presence', 'intervention', 'employed', 'according', 'profoundly', 'staff', 'girl', 'later', 'showed', 'differential', 'collection', 'occurrence', 'computed', 'comparing', 'basis', 'phenazopyridine', 'provided', 'taking', 'technique', 'measurement', 'strong', 'indirect', 'child', 'preferred', 'reinforcer', 'systematically', 'removed', 'eliminated', 'reactivity', 'eliminating', 'traditional', 'aba', 'filters', 'systematic', 'detection', 'linked', 'visual', 'consequences', 'gains', 'status', 'new', 'absence', 'identified', 'served', 'variety', 'report', 'assessing', 'presented', 'requiring', 'medicine', 'videotapes', 'consisted', 'rating', 'comprehensive', 'skills', 'female', 'videotaped', 'analyses', 'revealed', 'highly', 'situations', 'assigned', 'dating', 'investigated', 'rates', 'heart', 'breathing', 'pressure', 'responses', 'skill', 'schizophrenics', 'stimuli', 'mechanics', 'potential', 'symptomatic', 'benefits', 'severely', 'asthmatic', '14', 'rested', 'quietly', 'finally', 'relaxing', 'previously', 'manner', 'far', 'definitive', 'cumulatively', 'format', 'females', 'patients', 'ups', 'indicated', 'near', 'levels', 'graphed', 'functions', 'implications', 'selection', 'devices', 'intermittent', 'delivers', 'bronchodilator', 'medication', 'lungs', 'youngsters', 'repeated', 'script', 'lung', 'failed', 'substantiate', 'preliminary', 'findings', 'clinically', 'meaningful', 'equipment', 'monitored', 'extent', 'muscle', 'tended', 'confirm', 'attainment', 'relaxed', 'states', '30', 'intervals', 'frontales', 'muscles', 'respiration', 'skin', 'temperature', 'conductance', 'unobtrusive', 'simple', 'prerequisites', 'assertiveness', 'improved', 'improvements', 'increasingly', 'complex', 'underassertive', 'undergraduate', 'client', 'weekly', 'personality', 'inventory', 'playing', 'brief', 'univariate', '16', 'dependent', 'reports', 'affected', 'phobic', 'illustrates', 'comprehensively', 'questionaires', 'responded', 'loud', 'taped', 'conversed', 'confederate', 'differences', 'contexual', 'designed', 'specifically', 'containing', 'drug', 'produces', 'bright', 'red', 'orange', 'journals', 'respect', 'tendency', 'assess', 'day', 'regimen', 'variation', 'tracer', 'topography', 'consumption', 'advantages', 'disadvantages', 'recently', 'published', 'based', 'appearing', 'functioning', 'feasible', 'profitable', 'classification', 'include', 'traditionally', 'measured', 'substance', 'taken', 'saliency', 'asking', 'flavor', 'ingested', 'end', '50', 'participated', 'reasonable', 'alternatives', 'present', 'nature', '72', '40', 'noncompliant', 'non', 'frequencies', 'differed', 'category', 'vocalization', 'main', 'coefficients', 'similarity', 'appear', 'discoloration', 'requested', 'indicate', 'discolorations', 'predicted', 'scheduled', 'sequence', 'categories', 'conducted', 'ended', 'generalizable', 'increases', 'greater', 'marked', 'improvement', 'independent', 'possibilities', 'concerning', 'specific', 'invivo', 'simultaneous', 'facilitating', 'generalizability', 'immediately', 'implementation', 'despite', 'lack', 'vice', 'versa', 'methodological', 'suggestion', 'studying', 'remaining', 'continued', 'returning', 'portion', 'deposit', 'preset', 'met', 'superior', 'treating', 'interventions', 'provide', 'desirable', 'alternative', 'intrusive', 'surgical', 'mechanical', 'objective', 'substantiated', 'pre', 'post', 'evaluations', 'occupational', 'therapists', 'means', 'attempting', 'modify', '11', 'active', 'withdrawn', 'hypoactive', 'trials', 'thrusters', 'history', 'noncompliance', 'biofeedback', 'electronic', 'simultaneously', 'provides', 'combination', 'material', 'recommended', 'greatly', 'restricted', 'substituted', 'possible', 'delinquents', 'correctional', 'institution', 'unbiased', 'ratio', 'sum', 'researchers', 'estimate', 'magnitudes', 'unable', 'choose', 'covariance', 'parameter', 'varying', 'altered', 'accuracies', 'measure', 'approach', 'yielded', 'facilitation', 'instrument', 'developed', 'stimulate', 'animal', 'generated', 'series', 'models', 'tokens', 'delivered', 'evening', 'peers', 'individuals', 'interfere', 'acquisition', 'access', 'chewing', 'compared', 'favorably', 'obtained', 'persons', 'like', 'carried', 'card', 'gently', 'pushing', 'mouth', 'spoon', 'substantial', 'decreases', 'expulsion', 'large', 'delinquent', 'drooling', 'observable', 'modified', 'mealtime', 'consisting', 'presentation', 'punishment', 'schedules', 'original', 'noncontingent', 'distinct', 'required', 'deficits', 'reviewers', 'external', 'effectively', 'public', 'school', 'personnel', 'continuously', 'ii', 'affecting', 'influential', 'mouthing', 'supppression', 'typically', 'achieved', 'aversive', 'quickly', 'teachers', 'administered', 'vibratory', 'withdrawal', 'virtually', 'nonoccurrence', 'stereotypic', 'hyperventilation', 'repeatedly', 'suppression', 'doesnt', 'written', 'hartmann', '1977', 'majority', 'argument', 'reflects', 'tradition', 'dental', 'malocclusion', 'articulation', 'difficulty', 'eating', 'excessive', 'comment', 'reliable', 'communities', 'spastic', 'cerebral', 'palsy', 'reverse', 'swallowing', 'neuromuscular', 'disorders', 'restraints', 'illustrate', 'instance', 'programmed', 'predictable', 'lawful', 'fashion', 'natural', 'theory', 'problem', 'solving', 'gained', 'flight', 'morass', 'psychology', 'danger', 'eventually', 'nongeneral', 'reviewer', 'opinion', 'distinctiveness', 'health', 'success', 'basic', 'turning', 'away', 'weak', 'ability', 'discover', 'powerful', 'effect', 'direct', 'deliberate', 'departure', 'prime', 'goal', 'generality', 'detected', 'discipline', 'deliberately', 'codes', 'behaviorial', 'observations', 'expectancies', 'recommendations', 'minimizing', 'factors', 'better', 'spuriously', 'affect', 'evidence', 'pertaining', 'various', 'interpretation', 'included', 'drift', 'frequently', 'focused', 'computing', 'credence', 'accorded', 'estimates', 'method', 'presupposes', 'abandonment', 'swamping', 'arguments', 'abcs', 'rely', 'influenced', 'diverse', 'literature', 'identify', 'proprioceptive', 'usual', 'tactics', 'hinge', 'assiging', 'implicit', 'correspondingly', 'appeared', 'relatively', 'principles', 'adaptive', 'spontaneous', 'developmentally', 'disabled', 'attempt', 'consequence', 'designated', 'phase', 'selectively', 'toys', 'kind', 'extinguished', 'toy', 'know', 'advent', 'statistical', 'evaluating', 'invites', 'reintroduced', 'result', 'removing', 'explained', 'prior', 'trend', 'expectancy', 'unknown', 'temporal', 'events', 'process', 'performing', 'bed', 'higher', 'aware', 'expected', 'expectations', 'outcome', 'account', 'appears', 'contribute', 'suggested', 'orientation', 'abandoned', 'awareness', 'having', 'observe', 'explicit', 'moderately', 'minor', 'considered', 'centiles', 'probability', 'substantive', 'types', 'experimental', 'potency', 'alcohol', 'mix', 'drinks', 'rapidly', 'inhalation', 'session', 'direction', 'interrelationships', 'evaluated', 'inpatient', 'permitted', 'drink', 'beverages', 'room', 'involvement', 'manual', 'number', 'cigarettes', 'smoked', 'posttreatment', 'mo', 'alcoholics', 'multivariable', 'spouses', 'selected', 'days', 'economy', 'discount', 'coupons', 'spouse', 'automated', 'transduction', 'sheltered', 'workshop', 'inexpensive', 'presenting', 'blurred', 'repertoires', 'ecology', 'disturbed', 'greeting', 'reduce', 'portable', 'attending', 'videotape', 'interviewing', 'nurses', 'experimenters', 'reflected', 'impact', 'patient', 'played', 'target', 'treated', 'train', 'eye', 'fixation', 'facial', 'posturing', 'diaphragmatic', 'relief', 'symptoms', 'interaction', 'receiving', 'information', 'completed', 'battery', 'standard', 'paper', 'pencil', 'coding', 'checks', 'especially', 'phases', 'pretreatment', 'competent', 'neutral', 'studied', 'population', 'smallpox', 'eradication', 'relative', 'teacher', 'formation', 'university', 'digitek', 'clinical', 'educational', 'current', 'science', 'versus', 'fixed', 'nontime', 'telling']</t>
+          <t>Total Word Count</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>944</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>['stimuli', 'mechanics', 'potential', 'symptomatic', 'benefits', 'severely', 'asthmatic', '14', 'rested', 'quietly', 'finally', 'relaxing', 'previously', 'manner', 'far', 'definitive', 'cumulatively', 'format', 'females', 'patients', 'ups', 'indicated', 'near', 'levels', 'graphed', 'functions', 'implications', 'selection', 'devices', 'intermittent', 'delivers', 'bronchodilator', 'medication', 'lungs', 'youngsters', 'repeated', 'script', 'lung', 'failed', 'substantiate', 'preliminary', 'findings', 'clinically', 'meaningful', 'equipment', 'monitored', 'extent', 'muscle', 'tended', 'confirm', 'attainment', 'relaxed', 'states', '30', 'intervals', 'frontales', 'muscles', 'respiration', 'skin', 'temperature', 'conductance', 'unobtrusive', 'simple', 'prerequisites', 'assertiveness', 'improved', 'improvements', 'increasingly', 'complex', 'underassertive', 'undergraduate', 'client', 'weekly', 'personality', 'inventory', 'playing', 'brief', 'univariate', '16', 'dependent', 'reports', 'affected', 'phobic', 'illustrates', 'comprehensively', 'questionaires', 'responded', 'loud', 'taped', 'conversed', 'confederate', 'differences', 'contexual', 'designed', 'specifically', 'containing', 'drug', 'produces', 'bright', 'red', 'orange', 'journals', 'respect', 'tendency', 'assess', 'day', 'regimen', 'variation', 'tracer', 'topography', 'consumption', 'advantages', 'disadvantages', 'recently', 'published', 'based', 'appearing', 'functioning', 'feasible', 'profitable', 'classification', 'include', 'traditionally', 'measured', 'substance', 'taken', 'saliency', 'asking', 'flavor', 'ingested', 'end', '50', 'participated', 'reasonable', 'alternatives', 'present', 'nature', '72', '40', 'noncompliant', 'non', 'frequencies', 'differed', 'category', 'vocalization', 'main', 'coefficients', 'similarity', 'appear', 'discoloration', 'requested', 'indicate', 'discolorations', 'predicted', 'scheduled', 'sequence', 'categories', 'conducted', 'ended', 'generalizable', 'increases', 'greater', 'marked', 'improvement', 'independent', 'possibilities', 'concerning', 'specific', 'invivo', 'simultaneous', 'facilitating', 'generalizability', 'immediately', 'implementation', 'despite', 'lack', 'vice', 'versa', 'methodological', 'suggestion', 'studying', 'remaining', 'continued', 'returning', 'portion', 'deposit', 'preset', 'met', 'superior', 'treating', 'interventions', 'provide', 'desirable', 'alternative', 'intrusive', 'surgical', 'mechanical', 'objective', 'substantiated', 'pre', 'post', 'evaluations', 'occupational', 'therapists', 'means', 'attempting', 'modify', '11', 'active', 'withdrawn', 'hypoactive', 'trials', 'thrusters', 'history', 'noncompliance', 'biofeedback', 'electronic', 'simultaneously', 'provides', 'combination', 'material', 'recommended', 'greatly', 'restricted', 'substituted', 'possible', 'delinquents', 'correctional', 'institution', 'unbiased', 'ratio', 'sum', 'researchers', 'estimate', 'magnitudes', 'unable', 'choose', 'covariance', 'parameter', 'varying', 'altered', 'accuracies', 'measure', 'approach', 'yielded', 'facilitation', 'instrument', 'developed', 'stimulate', 'animal', 'generated', 'series', 'models', 'tokens', 'delivered', 'evening', 'peers', 'individuals', 'interfere', 'acquisition', 'access', 'chewing', 'compared', 'favorably', 'obtained', 'persons', 'like', 'carried', 'card', 'gently', 'pushing', 'mouth', 'spoon', 'substantial', 'decreases', 'expulsion', 'large', 'delinquent', 'drooling', 'observable', 'modified', 'mealtime', 'consisting', 'presentation', 'punishment', 'schedules', 'original', 'noncontingent', 'distinct', 'required', 'deficits', 'reviewers', 'external', 'effectively', 'public', 'school', 'personnel', 'continuously', 'ii', 'affecting', 'influential', 'mouthing', 'supppression', 'typically', 'achieved', 'aversive', 'quickly', 'teachers', 'administered', 'vibratory', 'withdrawal', 'virtually', 'nonoccurrence', 'stereotypic', 'hyperventilation', 'repeatedly', 'suppression', 'doesnt', 'written', 'hartmann', '1977', 'majority', 'argument', 'reflects', 'tradition', 'dental', 'malocclusion', 'articulation', 'difficulty', 'eating', 'excessive', 'comment', 'reliable', 'communities', 'spastic', 'cerebral', 'palsy', 'reverse', 'swallowing', 'neuromuscular', 'disorders', 'restraints', 'illustrate', 'instance', 'programmed', 'predictable', 'lawful', 'fashion', 'natural', 'theory', 'problem', 'solving', 'gained', 'flight', 'morass', 'psychology', 'danger', 'eventually', 'nongeneral', 'reviewer', 'opinion', 'distinctiveness', 'health', 'success', 'basic', 'turning', 'away', 'weak', 'ability', 'discover', 'powerful', 'effect', 'direct', 'deliberate', 'departure', 'prime', 'goal', 'generality', 'detected', 'discipline', 'deliberately', 'codes', 'behaviorial', 'observations', 'expectancies', 'recommendations', 'minimizing', 'factors', 'better', 'spuriously', 'affect', 'evidence', 'pertaining', 'various', 'interpretation', 'included', 'drift', 'frequently', 'focused', 'computing', 'credence', 'accorded', 'estimates', 'method', 'presupposes', 'abandonment', 'swamping', 'arguments', 'abcs', 'rely', 'influenced', 'diverse', 'literature', 'identify', 'proprioceptive', 'usual', 'tactics', 'hinge', 'assiging', 'implicit', 'correspondingly', 'appeared', 'relatively', 'principles', 'adaptive', 'spontaneous', 'developmentally', 'disabled', 'attempt', 'consequence', 'designated', 'phase', 'selectively', 'toys', 'kind', 'extinguished', 'toy', 'know', 'advent', 'statistical', 'evaluating', 'invites', 'reintroduced', 'result', 'removing', 'explained', 'prior', 'trend', 'expectancy', 'unknown', 'temporal', 'events', 'process', 'performing', 'bed', 'higher', 'aware', 'expected', 'expectations', 'outcome', 'account', 'appears', 'contribute', 'suggested', 'orientation', 'abandoned', 'awareness', 'having', 'observe', 'explicit', 'moderately', 'minor', 'considered', 'centiles', 'probability', 'substantive', 'types', 'experimental', 'potency', 'alcohol', 'mix', 'drinks', 'rapidly', 'inhalation', 'session', 'direction', 'interrelationships', 'evaluated', 'inpatient', 'permitted', 'drink', 'beverages', 'room', 'involvement', 'manual', 'number', 'cigarettes', 'smoked', 'posttreatment', 'mo', 'alcoholics', 'multivariable', 'spouses', 'selected', 'days', 'economy', 'discount', 'coupons', 'spouse', 'automated', 'transduction', 'sheltered', 'workshop', 'inexpensive', 'presenting', 'blurred', 'repertoires', 'ecology', 'disturbed', 'greeting', 'reduce', 'portable', 'attending', 'videotape', 'interviewing', 'nurses', 'experimenters', 'reflected', 'impact', 'patient', 'played', 'target', 'treated', 'train', 'eye', 'fixation', 'facial', 'posturing', 'diaphragmatic', 'relief', 'symptoms', 'interaction', 'receiving', 'information', 'completed', 'battery', 'standard', 'paper', 'pencil', 'coding', 'checks', 'especially', 'phases', 'pretreatment', 'competent', 'neutral', 'studied', 'population', 'smallpox', 'eradication', 'relative', 'teacher', 'formation', 'university', 'digitek', 'clinical', 'educational', 'current', 'science', 'versus', 'fixed', 'nontime', 'telling']</t>
-        </is>
+        <v>2149</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4542</v>
       </c>
       <c r="D2" t="n">
-        <v>573</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>['behavior', 'self', 'children', 'training', 'ss', 'treatment', 'procedures', 'baseline', 'assessment', 'sensory', 'behavioral', 'use', 'design', 'response', 'data', 'multiple', 'recording', 'effects', 'results', 'therapy', 'time', 'behaviors', 'subject', 'procedure', 'extra', 'wk', 'interval', 'measures', 'generalization', 'reliability', 'sharing', 'maintenance', 'reinforcement', 'positive', 'tongue', 'smoking', 'level', 'experiment', 'groups', 'monitoring', 'compliance', 'analysis', 'demand', 'assessed', 'activity', 'drinking', 'device', 'setting', 'technology', 'mean', 'programming', 'using', 'play', 'responding', 'observed', 'social', 'stimulation', 'agreement', 'replication', 'control', 'used', 'reinforcers', 'high', 'type', 'modeling', 'different', 'taste', 'comments', 'physical', 'applied', 'sessions', 'variables', 'increase', 'asthma', 'appropriate', 'observer', 'recorded', 'relaxation', 'significantly', 'change', 'instructions', 'maintained', 'frequency', 'low', 'function', 'students', 'probabilities', 'errors', 'components', 'paradigm', 'studies', 'modification', 'human', 'group', 'subjects', 'decreased', 'tablets', '2nd', '1st', 'mirror', 'thrust', 'techniques', 'prosocial', 'attention', 'retarded', 'feedback', 'bias', 'program', 'alcoholic', 'comparison', 'classroom', 'tv', 'produced', 'verbal', 'demonstrated', 'times', 'manipulation', 'characteristics', 'follow', 'taught', 'previous', 'experience', 'methods', 'partial', 'vivo', 'game', 'involved', 'conversation', 'study', 'cost', 'individual', 'recordings', 'observational', 'reviewed', 'discussed', 'chronic', 'durable', 'operant', 'interactions', 'stereotyped', 'settings', 'research', 'interobserver', 'case', 'single', 'rate', 'introduced', 'pulmonary', 'apparatus', 'controlled', 'auditory', 'examined', 'associated', 'ippb', 'including', 'scale', 'assertion', 'risk', 'areas', 'producing', 'following', 'extinction', 'reduction', 'significant', 'involving', 'food', 'urine', 'disruptive', 'effectiveness', 'vitamin', 'complexity', 'artifact', 'sources', 'problems', 'influence', 'designs', 'functional', 'reversal', 'role', 'implemented', 'article', 'stimulatory', 'terms', 'concept', 'occurred', 'girls', 'modifying', 'living', 'daily', 'contingent', 'interresponse', 'observation', 'momentary', 'sampling', 'stimulus', 'conditioning', 'development', 'effective', 'old', 'yr', '10', 'simulated', 'circuit', 'period', 'free', 'durability', 'extensive', 'observers', 'duration', 'parameters', 'did', 'share', 'resulted', 'computer', 'area', 'trained', 'instructional', 'good', 'randomly', 'males', 'vs', 'interpreted', 'sequentially', 'additional', 'component', 'negative', 'min', 'tension', 'changes', 'pattern', 'instructed', 'decrease', 'sip', 'intersip', 'package', 'cigarette', 'therapeutic', 'given', 'making', 'changing', 'video', 'likely', 'usually', 'maintaining', 'heterosocially', 'anxious', 'college', 'analog', 'heterosocial', 'competence', 'contextual', 'multivariate', 'received', 'followed', 'generalize', 'magnitude', 'slightly', 'teaching', 'just', 'verbally', 'physically', 'approaches', 'closed', 'useful', 'long', 'preschool', 'evaluation', 'judged', 'boy', 'returned', 'increased', 'experiments', 'biomotometer', 'male', 'token', 'length', 'continuous', 'variance', 'durations', 'degree', 'relationship', 'television', 'special', 'generalized', 'class', 'criterion', 'plus', 'providing', 'flavored', 'tablet', 'record', 'circumstances', 'similar', 'media', 'pathological', 'environment', 'autistic', 'difference', 'application', 'learned', 'presence', 'intervention', 'employed', 'according', 'profoundly', 'staff', 'girl', 'later', 'showed', 'differential', 'collection', 'occurrence', 'computed', 'comparing', 'basis', 'phenazopyridine', 'provided', 'taking', 'technique', 'measurement', 'strong', 'indirect', 'child', 'preferred', 'reinforcer', 'systematically', 'removed', 'eliminated', 'reactivity', 'eliminating', 'traditional', 'aba', 'filters', 'systematic', 'detection', 'linked', 'visual', 'consequences', 'gains', 'status', 'new', 'absence', 'identified', 'served', 'variety', 'report', 'assessing', 'presented', 'requiring', 'medicine', 'videotapes', 'consisted', 'rating', 'comprehensive', 'skills', 'female', 'videotaped', 'analyses', 'revealed', 'highly', 'situations', 'assigned', 'dating', 'investigated', 'rates', 'heart', 'breathing', 'pressure', 'responses', 'skill', 'schizophrenics']</t>
-        </is>
+        <v>21306</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41419</v>
       </c>
       <c r="F2" t="n">
-        <v>371</v>
+        <v>150661</v>
       </c>
       <c r="G2" t="n">
-        <v>2149</v>
-      </c>
-      <c r="H2" t="n">
-        <v>944</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.276483050847458</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.864719004971168</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5.34819296219609</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>46.17321095884201</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1970s</t>
-        </is>
+        <v>203870</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>['behavior', 'subjects', 'children', 'design', 'training', 'treatment', 'behavioral', 'generalization', 'baseline', 'self', 'use', 'multiple', 'behaviors', 'skills', 'social', 'using', 'effects', 'used', 'study', 'time', 'settings', 'procedures', 'retarded', 'reinforcement', 'data', 'subject', 'performance', 'response', 'students', 'program', 'results', 'group', 'intervention', 'community', 'child', 'increased', 'treatments', 'game', 'procedure', 'target', 'programming', 'experimental', 'temperature', 'showed', 'feedback', 'school', 'acquisition', 'discussed', 'based', 'restraint', 'biofeedback', 'analysis', 'effectiveness', 'coaching', 'breathing', 'control', 'device', 'responses', 'cognitive', 'maintenance', 'interaction', 'severely', 'conditions', 'instructional', 'teaching', 'technology', 'changes', 'trained', 'applied', 'single', 'improvement', 'types', 'suppression', 'disruptive', 'significant', 'setting', 'method', 'handicapped', 'severe', 'agreement', 'reducing', 'evaluated', 'improve', 'responding', 'modeling', 'situations', 'observation', 'casts', 'periods', 'observations', 'taught', 'patients', 'research', 'interval', 'natural', 'following', 'indicated', 'percentage', 'experiment', 'videotape', 'materials', 'investigated', 'telephone', 'improved', 'yr', 'alternative', 'play', 'mentally', 'wk', 'levels', 'phase', 'approach', 'noise', 'tone', 'acceptability', 'sentence', 'examined', 'injurious', 'average', 'appropriate', 'employed', 'present', 'assessment', 'correct', 'length', 'peers', 'effective', 'comparison', 'contingent', 'increase', 'tests', 'strategy', 'did', 'effect', 'tok', 'package', 'increasing', 'activity', 'stimulation', 'chiropractic', 'number', 'occurred', 'low', 'rate', 'motor', 'measure', 'preschool', 'demonstrated', 'language', 'persons', 'provided', 'findings', 'hearing', 'classroom', 'techniques', 'staff', 'assessed', 'interrogative', 'follow', 'direct', 'production', 'measures', 'stimulus', 'dra', 'limited', 'specific', 'included', 'standard', 'revealed', 'frequency', 'harry', 'bus', 'developed', 'aba', 'reduction', 'treated', 'timeout', 'produced', 'cerebral', 'trainers', 'session', 'instruction', 'skill', 'socialization', 'day', 'functional', 'sequentially', 'variable', 'criterion', 'methods', 'task', 'consisted', 'games', 'deviant', 'events', 'evaluate', 'exemplars', 'experiments', 'diaphragmatic', 'combination', 'old', 'maintain', 'work', 'forms', 'visual', 'areas', 'positive', 'interactions', 'case', 'sessions', 'young', 'untrained', 'systematic', 'stable', 'sib', 'human', 'peer', 'football', 'generalized', 'collected', 'female', 'learned', 'observed', 'male', 'novel', 'resulted', 'participants', '1st', 'percent', 'terms', 'water', 'autistic', 'implications', 'modified', 'dependent', 'rated', 'facilitate', 'phases', 'maintained', 'obtained', 'home', 'laundry', 'lip', 'closure', 'interrupted', 'stereotyped', 'mild', 'slap', 'music', 'plus', 'riding', 'adequacy', 'objects', 'achieved', 'rapid', 'treating', 'management', 'individuals', 'syntax', 'verbal', 'given', 'tasks', 'demonstrate', 'care', 'volume', 'aphasia', 'stress', 'prompted', 'decreased', 'selected', 'wh', 'designed', 'different', 'conducted', 'period', 'sampling', 'reversal', 'assess', 'residents', 'tennis', 'virtually', 'units', 'accuracy', 'condition', 'total', 'rates', 'apparently', 'described', 'particular', 'increases', 'involvement', 'calculator', 'relaxation', 'gains', 'digital', 'normal', 'women', 'schedule', 'strategies', 'communicative', 'usage', 'free', 'withdrawal', 'category', 'parent', 'receptacle', 'litter', 'addition', 'judged', 'profoundly', 'suggestion', 'slowing', 'therapy', 'psychiatric', 'inpatients', 'residential', 'available', 'systems', 'opportunities', 'sign', 'longer', 'presentation', 'cueing', 'remained', 'varying', 'suggest', 'inappropriate', 'signs', 'independent', 'valence', 'tended', 'indicate', 'dramatic', 'seven', 'clinical', 'deposited', 'hyperactivity', 'high', 'conventional', 'habilitative', 'evidence', 'problem', 'questions', 'daily', 'disabilities', 'aids', 'studies', 'communicator', 'moderately', 'alternating', 'scale', 'class', 'discriminative', 'tension', 'headaches', 'differential', 'maladaptive', 'phenomena', 'support', 'compared', 'items', 'determining', 'emergency', 'determined', 'influenced', 'teachers', 'general', 'dimensions', 'ability', 'voice', 'validation', 'ratings', 'highly', 'evaluations', 'reliabilities', 'index', 'ii', 'improvements', 'auditory', 'derived', 'negative', 'learning', 'associated', 'mothers', 'trainer', 'components', 'individualized', 'properties', 'provide', 'exp', 'acceptable', 'severity', 'gymnastics', 'relatively', 'licensed', 'sport', 'sample', 'subsequent', 'interrogatives', 'form', 'agrammatic', 'utility', 'development', 'relationship', 'monitoring', 'need', 'long', 'sets', 'communication', 'practice', '10', 'mobility', 'initiated', 'function', 'consistently', 'efficacy', 'additional', 'gait', 'possible', 'application', 'technique', 'duration', 'occurrence', 'recording', 'various', 'assessments', 'computer', 'record', 'complex', 'observers', 'palsy', 'instructed', 'autogenic', 'raynaud', 'disease', 'cold', 'hand', 'disorders', 'initial', 'end', 'studied', 'machine', 'useful', 'mist', 'face', 'component', 'instructions', 'scores', 'aid', 'played', 'collateral', 'paper', 'speech', 'good', 'automatic', 'statistical', 'defined', 'valenced', 'unsystematic', '18', 'observer', 'gender', 'analog', 'presented', 'collection', 'determine', 'investigators', 'manipulation', 'fourth', 'reported', 'unreliable', 'linear', 'placebo', 'prior', 'completed', 'electrodermal', 'majority', 'taken', 'positively', 'negatively', 'college', 'basketball', 'appears', 'continues', 'combined', 'feeding', 'successfully', 'spinal', 'analyses', 'better', 'regardless', 'aphasic', 'throw', 'implemented', '88', 'enhance', 'sports', 'complementary', 'drug', 'electric', 'shock', 'cases', 'replicated', 'incompatible', 'screaming', 'placed', 'implementation', 'loud', 'adult', 'examine', 'difficulties', 'practical', 'efficient', 'versus', 'laundromat', 'acquired', 'deficits', 'simple', 'conversational', 'result', 'like', 'handicaps', 'requires', 'reversals', 'comprehensive', 'future', 'mental', 'retardation', 'relation', 'aversive', 'disruptively', 'interruption', 'took', 'place', 'boy', 'diagnosed', 'context', 'processes', 'related', 'focus', 'concomitant', 'headache', 'minimal', 'calls', 'treat', 'extremely', 'prosthetic', 'assistance', 'methodological', 'palsied', 'adolescent', 'continued', 'represented', 'fully', 'trials', 'destructive', 'rubella', 'aggression', 'aggressive', 'gave', 'improving', 'cues', 'client', 'dro', 'cue', 'population', 'integrated', 'machines', 'generality', 'empirical', 'abab', 'reliably', 'codes', 'sbd', 'represent', 'television', 'instituted', 'holding', 'hands', 'size', 'held', 'parenting', 'identified', 'maltreaters', 'serve', 'nonintervention', 'promote', 'receive', 'counterbalanced', 'light', 'suggests', 'vocational', 'differences', 'change', 'purchasing', 'entering', 'pocket', 'making', 'financial', 'transactions', 'degree', 'twice', 'skin', 'progressive', '21', 'strength', 'boys', 'girls', 'powered', 'reports', '23', 'action', '43', 'providing', 'spina', 'bifida', 'current', 'physical', 'scientists', 'naturalistic', 'intervals', 'spatial', 'exploration', 'weeks', 'proved', 'bisexual', '2nd', 'fashion', 'greeting', 'fading', 'man', 'reinforcing', 'peripheral', 'question', 'probes', 'licensure', 'similar', '52', 'dramatically', 'blocking', 'temperatures', 'mouth', 'basis', 'regression', 'fitted', 'thoracic', 'involving', 'cognitions', 'means', 'interobserver', 'times', 'order', 'simultaneous', 'supported', 'underlying', '3rd', 'males', 'suppressing', 'relative', 'activities', 'real', 'age', 'area', 'certainly', 'video', 'multi', 'consisting', 'seriously', 'manual', 'commercially', 'overcorrection', 'past', 'drum', 'mean', 'teach', 'oral', 'members', 'adaptive', 'emitted', 'required', 'printing', 'kg', 'attending', 'distractible', 'people', 'container', '55', 'gal', 'engaged', 'designs', 'valuable', 'lengths', 'recorded', 'decrease', 'distractors', 'math', 'problems', 'displayed', 'isolation', 'washing', 'dropped', 'reductions', 'teacher', 'prompting', 'maintaining', 'perceived', 'constructions', 'reduce', 'stereotypic', 'occurring', 'eliminated', 'introduced', 'elicited', 'adults', 'job', 'monitor', 'examines', 'consequence', 'recruited', 'cost', 'instance', 'subjective', 'approaches', 'presence', 'yielded', 'chronic', 'produce', 'helm', 'accidental', 'ride', 'sitting', 'appropriately', 'abcdcdcda', 'introduction', 'report', 'easy', 'administer', 'predictability', 'material', 'spin', 'test', 'conclude', 'neutral', 'accurately', 'applications', 'signal', 'processing', 'asp', 'zeta', 'blocker', 'znb', 'markedly', 'listener', 'representatively', 'females', 'overestimated', 'rationale', 'employing', 'investigate', 'preliminary', 'siemens', 'written', 'discussion', 'ward', 'spontaneously', 'targeted', 'reaction', 'including', 'compliments', 'justified', 'environments', '12', 'asking', 'request', 'necessary', 'prompts', 'faceted', 'kappa', 'instead', 'lenient', 'half', 'fourths', 'stringent', 'suggested', 'undermined', 'psychology', 'goes', 'outdoors', 'organized', 'fields', 'algebraic', 'chance', 'corrected', 'outside', 'applicable', 'targets', 'variety', 'employs', 'standardized', 'replicability', 'division', 'pattern', 'reassessment', 'popular', 'reliability', 'criteria', 'groups', 'ss', 'newly', 'pointed', 'linguistic', 'spontaneous', 'dysfunction', 'level', 'adapative', 'integration', 'normalized', 'politeness', 'criticism', 'confrontation', 'answers', 'features', 'reinforcers', 'lack', 'constitute', 'maneuvers', 'physiograph', 'recordings', 'expansion', 'sampled', 'min', 'lines', 'probably', 'facilitating', 'paralleled', 'evident', 'numbers', 'volunteers', 'eastern', 'meditative', 'opposite', 'principles', 'neurologically', 'morphemes', 'complete', 'contexts', 'samples', 'atd', 'administered', 'players', 'finding', '78', '50', 'measured', 'reconstruction', 'process', 'anlyzed', 'importance', 'replication', 'continuity', 'science', 'positon', 'believed', 'effectively', 'identify', 'new', 'behaviorism', 'interbehaviorism', 'reification', 'section', 'reviews', 'models', 'stressing', 'respiratory', 'vasomotor', 'uncontrolled', 'ready', 'parapsychology', 'return', 'argument', 'parapsychological', 'warm', 'outdoor', 'cool', 'indoor', 'generally', 'decreases', 'differ', 'labile', 'displaying', 'specificity', 'marked', 'speed', 'contrast', 'interdisciplinary', 'documentation', 'patient', 'ultimately', 'enable', 'exploit', 'fullest', 'extent', 'reinforcer', 'increasingly', 'noninjury', 'wheelchairs', 'hour', 'videorecorded', 'giver', 'bind', 'inventing', 'strange', 'appear', 'common', 'problematic', 'recidivism', 'locomotor', 'disability', '38', 'months', 'motorized', 'consists', 'symbolic', 'taps', 'nose', 'arm', 'bites', 'therapeutic', 'make', 'eyeglasses', 'substituted', 'wear', 'token', 'enriched', 'unit', 'member', 'nonexistent', 'rewards', 'contingencies', 'episode', 'begun', 'restraining', 'point', 'ceased', 'wearing', 'reference', 'adaptation', 'existing', 'multiply', 'effectivness', 'midly', 'facility', 'standards', 'viewing', 'variability', 'feature', 'posttreatment', 'multihandicapped', 'display', 'acting', 'property', 'substituting', '14', 'topographic', 'parten', 'averaged', 'statistically', 'clear', 'outcome', 'student', 'lifestyle', '13', 'year', 'way', 'overcoming', 'iatrogenic', 'restrainers', 'primary', 'nontrained', 'document', 'efficiency', 'eighteen', 'month', 'shows', 'regular', '15', 'impaired', 'documenting', 'persisted', 'rapidly', 'absent', 'mo', 'working', 'artificial', 'pictures', 'simulated', 'cardboard', 'replica', 'model', 'developmentally', 'disabled', 'moderate', 'selecting', 'examples', 'supervisors', 'series', 'efffective', 'apply', 'involved', 'destruction', 'laundromats', 'final', 'probe', 'enhanced', 'regard', 'issue', 'recommendations', 'tissue', 'backs', 'contained', 'public', 'suppressive', 'personnel', 'able', 'educational', 'remaining', 'judgments', 'history', 'mouthing', 'biting', 'evinced', 'noticeable', 'scar', 'frequently', 'recruit', 'broca', 'estabrooks', '1981', 'served', 'naive', 'judges', 'issues', 'relevant', 'clients', 'sprayed', 'punisher', 'declarative', 'grammatical', 'faced', 'ears', 'provides', 'sounds', 'scream', 'specified', 'quiet', 'substantial', 'multielement', 'brocas', 'addressed', 'affected', 'crest', 'shaped', 'lightweight', 'plastic', 'covers', 'shown', 'attributable', 'gradually', 'refining', 'tailor', 'interventions', 'individually', 'characteristics', 'adverse', 'attempt', 'escape', 'struggle', 'ethicl', 'considerations', 'fewer', 'initiations', '19', 'implementing', 'removal', 'signaled', 'conjunction', 'advantages', 'mediating', 'transfer', 'non', 'exclusionary', 'recent', 'nonexclusionary', 'replicate', 'modifying', 'basic', 'original', 'nonhandicapped', 'mediated', 'normally', 'developing', 'preschoolers', 'facilitative', 'ocurred', 'classmates', 'compare', 'soft', 'higher', 'learner', 'post', 'testing', 'confirmed', 'augmenting', 'involve', 'emphasis', 'modification', 'view', 'affective', 'symptom', 'tool', 'studying', 'guidelines', 'programs', 'psychosomatic', 'coping', 'alleviation', 'frontalis', 'electromyographic', 'absence', 'subsequently', 'contact', 'requirements', 'agency', 'modelled', 'engelmann', 'carnine', '1982', 'portable', 'emg', 'effort', 'role', 'structured', 'unstructured', 'syndrome', 'discriminate', 'price', 'power', 'item', 'paying', 'money', 'knowing', 'checking', 'individual', 'critical', 'pretest', 'posttest', 'sequence', 'cued', 'monetary', 'denomination', 'purchase', 'praised', 'irrespective', 'afer', 'unprompted', 'interctions', 'tested', 'numerical', 'concepts', 'physiological', 'consequences', 'identifying', 'anxiety', 'provoking', 'antecedent', 'consequent', 'friendship', 'variables', 'widespread', 'lasting', 'pedophilia', 'assisted', 'pedophile', 'days', 'erection', 'favoured', 'needed', 'reached', 'objectives', 'hours', '90', 'emit', 'hi', 'angle', 'videotapes', 'clinicians', 'noted', 'mildly', 'cast', 'parents', 'therapists', 'socially', 'repeated', 'stride', 'step', 'ratio', 'base', 'foot', 'progression', 'covert', 'sensitization', 'suppress', 'confirm', 'validate', 'comparative', 'suffering', 'idiopathic', 'inhibitive', 'patterns', 'develop', 'concurrent', 'separate', 'successful', 'nondeviant', 'debriefing', 'antecedents', 'affect', '42', 'information', 'state', 'transition', 'vs', 'plaster', 'sexually', 'stimuli', 'closed', 'circuit', 'told', 'judge', 'static', 'act', 'close', 'association', 'successive', 'reapplications', 'videotaped', 'continuing', 'purpose', 'microcomputer', 'challenge', 'symptomatic', 'start', 'swimming', 'edited', 'replay', 'aged', 'occur', '9th', 'underwent', 'laboratory', 'ambient', 'slowly', '26', '17', 'week', 'raise', 'muscle', 'spaced', 'apart', 'kept', 'records', 'vasospastic', 'attacks', 'latin', 'square', 'differentially', 'presenting', 'sharply', 'distinguished', 'overall', 'followed', 'researchers', 'today', 'devices', 'allow', 'impossible', 'standing', 'clinicial', 'undergraduate', 'assessing', 'lag', 'sequential', 'allows', 'investigation', 'warranted', 'conducting', 'pencil', 'programmed', 'continuous', 'researcher', 'beginning', 'ending', 'seconds', 'totals', 'automated', '51', 'gymnasts', 'performances', 'averages', '57', 'strokes', 'success', 'offer', 'walkovers', 'springs', 'reverse', 'kips', 'forehand', 'backhand', 'immediately', 'execution', 'validated', 'focused', 'remediation', 'errors', '11', '35', 'depending', 'backward', 'small', 'accounted', 'large', 'portions', 'variance', 'operant', 'paradigm', 'scientifically', 'arousal', '009', 'principal', 'detect', 'motion', 'recorder', 'rays', 'distortions', 'spent', 'stimulating', 'abusive', 'failure', 'governmental', 'regulations', 'adequately', 'littering', 'differed', 'active', '160', '000', 'resident', 'just', 'derelict', 'unlicensed', 'environment', 'institutionalized', 'decisions', 'years', 'organizations', 'strikingly', 'documents', 'institutions', 'plywood', 'hat', 'alternated', 'stadium', 'count', 'articles', 'respectively', 'weight', 'autonomic', 'nervous', 'biomechanics', 'analyzed', 'visually', 'nonparametric', 'specially', 'adorned', 'important', 'nondrug', 'unique', 'wristwatch', 'type', 'mechanically', 'simulating', 'schoolwork', 'considered', 'suggestive', 'strong', 'intertest', 'impressive', 'fact', 'conclusive', 'potential', 'phonics', 'reliable', 'academic', 'representation', 'observe', 'electronic', 'equipment', 'analyze', 'lunchroom', 'vivo', 'kindergarten', 'playing', 'wooden', 'blocks', 'entire', 'handled', 'systematically', 'exposed', 'photo', 'slides', 'distracting', 'audio', 'composed', 'noisy', '65', 'educable', 'monitored', 'purposes', 'having', 'attentional', 'attention', 'cope', 'representativeness', 'multifactorial', 'observing', 'inspected', 'code', 'accurate', 'factor', 'interacted', 'abandoned', 'decision', 'empirically', 'determinants', 'error', 'factors', 'thought', 'influence', 'principle', 'aim', 'manipulative', 'blinds', 'hyperactive', 'durations', 'arbitrary', 'convention', 'shortest', 'little', 'suggesting', 'listening', 'situation', 'contextually', 'difficult', 'evaluation', 'bingo', 'textual', 'sight', 'words', 'promising', 'eco', 'perspective', 'aimed', 'humidity', 'comfort', 'clothing', 'worn', 'winter', 'summer', 'library', 'word', 'near', 'playground', 'recognition', 'sudanese', 'elementary', 'loose', 'electricity', 'conservation', 'forearm', 'selfinjurious', 'girl', 'nontarget', 'slight', 'evidenced', 'ineffective', 'accelerating', 'protection', 'emerging', 'youth', 'occupational', 'exposures', 'styrene', 'vending', 'table', 'significantly', 'volleys', 'explanations', 'comments', 'computers', 'normalization', 'values', 'services', 'zero', 'attained', 'perceptual', 'hypnotized', 'videotennis', 'ababab', 'hypnotic', 'ball', 'quantifying', 'benefits', 'user', 'expect', 'purported', 'background', 'widely', 'inferential']</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>['accidental', 'ride', 'sitting', 'appropriately', 'abcdcdcda', 'introduction', 'report', 'easy', 'administer', 'predictability', 'material', 'spin', 'test', 'conclude', 'neutral', 'accurately', 'applications', 'signal', 'processing', 'asp', 'zeta', 'blocker', 'znb', 'markedly', 'listener', 'representatively', 'females', 'overestimated', 'rationale', 'employing', 'investigate', 'preliminary', 'siemens', 'written', 'discussion', 'ward', 'spontaneously', 'targeted', 'reaction', 'including', 'compliments', 'justified', 'environments', '12', 'asking', 'request', 'necessary', 'prompts', 'faceted', 'kappa', 'instead', 'lenient', 'half', 'fourths', 'stringent', 'suggested', 'undermined', 'psychology', 'goes', 'outdoors', 'organized', 'fields', 'algebraic', 'chance', 'corrected', 'outside', 'applicable', 'targets', 'variety', 'employs', 'standardized', 'replicability', 'division', 'pattern', 'reassessment', 'popular', 'reliability', 'criteria', 'groups', 'ss', 'newly', 'pointed', 'linguistic', 'spontaneous', 'dysfunction', 'level', 'adapative', 'integration', 'normalized', 'politeness', 'criticism', 'confrontation', 'answers', 'features', 'reinforcers', 'lack', 'constitute', 'maneuvers', 'physiograph', 'recordings', 'expansion', 'sampled', 'min', 'lines', 'probably', 'facilitating', 'paralleled', 'evident', 'numbers', 'volunteers', 'eastern', 'meditative', 'opposite', 'principles', 'neurologically', 'morphemes', 'complete', 'contexts', 'samples', 'atd', 'administered', 'players', 'finding', '78', '50', 'measured', 'reconstruction', 'process', 'anlyzed', 'importance', 'replication', 'continuity', 'science', 'positon', 'believed', 'effectively', 'identify', 'new', 'behaviorism', 'interbehaviorism', 'reification', 'section', 'reviews', 'models', 'stressing', 'respiratory', 'vasomotor', 'uncontrolled', 'ready', 'parapsychology', 'return', 'argument', 'parapsychological', 'warm', 'outdoor', 'cool', 'indoor', 'generally', 'decreases', 'differ', 'labile', 'displaying', 'specificity', 'marked', 'speed', 'contrast', 'interdisciplinary', 'documentation', 'patient', 'ultimately', 'enable', 'exploit', 'fullest', 'extent', 'reinforcer', 'increasingly', 'noninjury', 'wheelchairs', 'hour', 'videorecorded', 'giver', 'bind', 'inventing', 'strange', 'appear', 'common', 'problematic', 'recidivism', 'locomotor', 'disability', '38', 'months', 'motorized', 'consists', 'symbolic', 'taps', 'nose', 'arm', 'bites', 'therapeutic', 'make', 'eyeglasses', 'substituted', 'wear', 'token', 'enriched', 'unit', 'member', 'nonexistent', 'rewards', 'contingencies', 'episode', 'begun', 'restraining', 'point', 'ceased', 'wearing', 'reference', 'adaptation', 'existing', 'multiply', 'effectivness', 'midly', 'facility', 'standards', 'viewing', 'variability', 'feature', 'posttreatment', 'multihandicapped', 'display', 'acting', 'property', 'substituting', '14', 'topographic', 'parten', 'averaged', 'statistically', 'clear', 'outcome', 'student', 'lifestyle', '13', 'year', 'way', 'overcoming', 'iatrogenic', 'restrainers', 'primary', 'nontrained', 'document', 'efficiency', 'eighteen', 'month', 'shows', 'regular', '15', 'impaired', 'documenting', 'persisted', 'rapidly', 'absent', 'mo', 'working', 'artificial', 'pictures', 'simulated', 'cardboard', 'replica', 'model', 'developmentally', 'disabled', 'moderate', 'selecting', 'examples', 'supervisors', 'series', 'efffective', 'apply', 'involved', 'destruction', 'laundromats', 'final', 'probe', 'enhanced', 'regard', 'issue', 'recommendations', 'tissue', 'backs', 'contained', 'public', 'suppressive', 'personnel', 'able', 'educational', 'remaining', 'judgments', 'history', 'mouthing', 'biting', 'evinced', 'noticeable', 'scar', 'frequently', 'recruit', 'broca', 'estabrooks', '1981', 'served', 'naive', 'judges', 'issues', 'relevant', 'clients', 'sprayed', 'punisher', 'declarative', 'grammatical', 'faced', 'ears', 'provides', 'sounds', 'scream', 'specified', 'quiet', 'substantial', 'multielement', 'brocas', 'addressed', 'affected', 'crest', 'shaped', 'lightweight', 'plastic', 'covers', 'shown', 'attributable', 'gradually', 'refining', 'tailor', 'interventions', 'individually', 'characteristics', 'adverse', 'attempt', 'escape', 'struggle', 'ethicl', 'considerations', 'fewer', 'initiations', '19', 'implementing', 'removal', 'signaled', 'conjunction', 'advantages', 'mediating', 'transfer', 'non', 'exclusionary', 'recent', 'nonexclusionary', 'replicate', 'modifying', 'basic', 'original', 'nonhandicapped', 'mediated', 'normally', 'developing', 'preschoolers', 'facilitative', 'ocurred', 'classmates', 'compare', 'soft', 'higher', 'learner', 'post', 'testing', 'confirmed', 'augmenting', 'involve', 'emphasis', 'modification', 'view', 'affective', 'symptom', 'tool', 'studying', 'guidelines', 'programs', 'psychosomatic', 'coping', 'alleviation', 'frontalis', 'electromyographic', 'absence', 'subsequently', 'contact', 'requirements', 'agency', 'modelled', 'engelmann', 'carnine', '1982', 'portable', 'emg', 'effort', 'role', 'structured', 'unstructured', 'syndrome', 'discriminate', 'price', 'power', 'item', 'paying', 'money', 'knowing', 'checking', 'individual', 'critical', 'pretest', 'posttest', 'sequence', 'cued', 'monetary', 'denomination', 'purchase', 'praised', 'irrespective', 'afer', 'unprompted', 'interctions', 'tested', 'numerical', 'concepts', 'physiological', 'consequences', 'identifying', 'anxiety', 'provoking', 'antecedent', 'consequent', 'friendship', 'variables', 'widespread', 'lasting', 'pedophilia', 'assisted', 'pedophile', 'days', 'erection', 'favoured', 'needed', 'reached', 'objectives', 'hours', '90', 'emit', 'hi', 'angle', 'videotapes', 'clinicians', 'noted', 'mildly', 'cast', 'parents', 'therapists', 'socially', 'repeated', 'stride', 'step', 'ratio', 'base', 'foot', 'progression', 'covert', 'sensitization', 'suppress', 'confirm', 'validate', 'comparative', 'suffering', 'idiopathic', 'inhibitive', 'patterns', 'develop', 'concurrent', 'separate', 'successful', 'nondeviant', 'debriefing', 'antecedents', 'affect', '42', 'information', 'state', 'transition', 'vs', 'plaster', 'sexually', 'stimuli', 'closed', 'circuit', 'told', 'judge', 'static', 'act', 'close', 'association', 'successive', 'reapplications', 'videotaped', 'continuing', 'purpose', 'microcomputer', 'challenge', 'symptomatic', 'start', 'swimming', 'edited', 'replay', 'aged', 'occur', '9th', 'underwent', 'laboratory', 'ambient', 'slowly', '26', '17', 'week', 'raise', 'muscle', 'spaced', 'apart', 'kept', 'records', 'vasospastic', 'attacks', 'latin', 'square', 'differentially', 'presenting', 'sharply', 'distinguished', 'overall', 'followed', 'researchers', 'today', 'devices', 'allow', 'impossible', 'standing', 'clinicial', 'undergraduate', 'assessing', 'lag', 'sequential', 'allows', 'investigation', 'warranted', 'conducting', 'pencil', 'programmed', 'continuous', 'researcher', 'beginning', 'ending', 'seconds', 'totals', 'automated', '51', 'gymnasts', 'performances', 'averages', '57', 'strokes', 'success', 'offer', 'walkovers', 'springs', 'reverse', 'kips', 'forehand', 'backhand', 'immediately', 'execution', 'validated', 'focused', 'remediation', 'errors', '11', '35', 'depending', 'backward', 'small', 'accounted', 'large', 'portions', 'variance', 'operant', 'paradigm', 'scientifically', 'arousal', '009', 'principal', 'detect', 'motion', 'recorder', 'rays', 'distortions', 'spent', 'stimulating', 'abusive', 'failure', 'governmental', 'regulations', 'adequately', 'littering', 'differed', 'active', '160', '000', 'resident', 'just', 'derelict', 'unlicensed', 'environment', 'institutionalized', 'decisions', 'years', 'organizations', 'strikingly', 'documents', 'institutions', 'plywood', 'hat', 'alternated', 'stadium', 'count', 'articles', 'respectively', 'weight', 'autonomic', 'nervous', 'biomechanics', 'analyzed', 'visually', 'nonparametric', 'specially', 'adorned', 'important', 'nondrug', 'unique', 'wristwatch', 'type', 'mechanically', 'simulating', 'schoolwork', 'considered', 'suggestive', 'strong', 'intertest', 'impressive', 'fact', 'conclusive', 'potential', 'phonics', 'reliable', 'academic', 'representation', 'observe', 'electronic', 'equipment', 'analyze', 'lunchroom', 'vivo', 'kindergarten', 'playing', 'wooden', 'blocks', 'entire', 'handled', 'systematically', 'exposed', 'photo', 'slides', 'distracting', 'audio', 'composed', 'noisy', '65', 'educable', 'monitored', 'purposes', 'having', 'attentional', 'attention', 'cope', 'representativeness', 'multifactorial', 'observing', 'inspected', 'code', 'accurate', 'factor', 'interacted', 'abandoned', 'decision', 'empirically', 'determinants', 'error', 'factors', 'thought', 'influence', 'principle', 'aim', 'manipulative', 'blinds', 'hyperactive', 'durations', 'arbitrary', 'convention', 'shortest', 'little', 'suggesting', 'listening', 'situation', 'contextually', 'difficult', 'evaluation', 'bingo', 'textual', 'sight', 'words', 'promising', 'eco', 'perspective', 'aimed', 'humidity', 'comfort', 'clothing', 'worn', 'winter', 'summer', 'library', 'word', 'near', 'playground', 'recognition', 'sudanese', 'elementary', 'loose', 'electricity', 'conservation', 'forearm', 'selfinjurious', 'girl', 'nontarget', 'slight', 'evidenced', 'ineffective', 'accelerating', 'protection', 'emerging', 'youth', 'occupational', 'exposures', 'styrene', 'vending', 'table', 'significantly', 'volleys', 'explanations', 'comments', 'computers', 'normalization', 'values', 'services', 'zero', 'attained', 'perceptual', 'hypnotized', 'videotennis', 'ababab', 'hypnotic', 'ball', 'quantifying', 'benefits', 'user', 'expect', 'purported', 'background', 'widely', 'inferential']</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>801</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['behavior', 'subjects', 'children', 'design', 'training', 'treatment', 'behavioral', 'generalization', 'baseline', 'self', 'use', 'multiple', 'behaviors', 'skills', 'social', 'using', 'effects', 'used', 'study', 'time', 'settings', 'procedures', 'retarded', 'reinforcement', 'data', 'subject', 'performance', 'response', 'students', 'program', 'results', 'group', 'intervention', 'community', 'child', 'increased', 'treatments', 'game', 'procedure', 'target', 'programming', 'experimental', 'temperature', 'showed', 'feedback', 'school', 'acquisition', 'discussed', 'based', 'restraint', 'biofeedback', 'analysis', 'effectiveness', 'coaching', 'breathing', 'control', 'device', 'responses', 'cognitive', 'maintenance', 'interaction', 'severely', 'conditions', 'instructional', 'teaching', 'technology', 'changes', 'trained', 'applied', 'single', 'improvement', 'types', 'suppression', 'disruptive', 'significant', 'setting', 'method', 'handicapped', 'severe', 'agreement', 'reducing', 'evaluated', 'improve', 'responding', 'modeling', 'situations', 'observation', 'casts', 'periods', 'observations', 'taught', 'patients', 'research', 'interval', 'natural', 'following', 'indicated', 'percentage', 'experiment', 'videotape', 'materials', 'investigated', 'telephone', 'improved', 'yr', 'alternative', 'play', 'mentally', 'wk', 'levels', 'phase', 'approach', 'noise', 'tone', 'acceptability', 'sentence', 'examined', 'injurious', 'average', 'appropriate', 'employed', 'present', 'assessment', 'correct', 'length', 'peers', 'effective', 'comparison', 'contingent', 'increase', 'tests', 'strategy', 'did', 'effect', 'tok', 'package', 'increasing', 'activity', 'stimulation', 'chiropractic', 'number', 'occurred', 'low', 'rate', 'motor', 'measure', 'preschool', 'demonstrated', 'language', 'persons', 'provided', 'findings', 'hearing', 'classroom', 'techniques', 'staff', 'assessed', 'interrogative', 'follow', 'direct', 'production', 'measures', 'stimulus', 'dra', 'limited', 'specific', 'included', 'standard', 'revealed', 'frequency', 'harry', 'bus', 'developed', 'aba', 'reduction', 'treated', 'timeout', 'produced', 'cerebral', 'trainers', 'session', 'instruction', 'skill', 'socialization', 'day', 'functional', 'sequentially', 'variable', 'criterion', 'methods', 'task', 'consisted', 'games', 'deviant', 'events', 'evaluate', 'exemplars', 'experiments', 'diaphragmatic', 'combination', 'old', 'maintain', 'work', 'forms', 'visual', 'areas', 'positive', 'interactions', 'case', 'sessions', 'young', 'untrained', 'systematic', 'stable', 'sib', 'human', 'peer', 'football', 'generalized', 'collected', 'female', 'learned', 'observed', 'male', 'novel', 'resulted', 'participants', '1st', 'percent', 'terms', 'water', 'autistic', 'implications', 'modified', 'dependent', 'rated', 'facilitate', 'phases', 'maintained', 'obtained', 'home', 'laundry', 'lip', 'closure', 'interrupted', 'stereotyped', 'mild', 'slap', 'music', 'plus', 'riding', 'adequacy', 'objects', 'achieved', 'rapid', 'treating', 'management', 'individuals', 'syntax', 'verbal', 'given', 'tasks', 'demonstrate', 'care', 'volume', 'aphasia', 'stress', 'prompted', 'decreased', 'selected', 'wh', 'designed', 'different', 'conducted', 'period', 'sampling', 'reversal', 'assess', 'residents', 'tennis', 'virtually', 'units', 'accuracy', 'condition', 'total', 'rates', 'apparently', 'described', 'particular', 'increases', 'involvement', 'calculator', 'relaxation', 'gains', 'digital', 'normal', 'women', 'schedule', 'strategies', 'communicative', 'usage', 'free', 'withdrawal', 'category', 'parent', 'receptacle', 'litter', 'addition', 'judged', 'profoundly', 'suggestion', 'slowing', 'therapy', 'psychiatric', 'inpatients', 'residential', 'available', 'systems', 'opportunities', 'sign', 'longer', 'presentation', 'cueing', 'remained', 'varying', 'suggest', 'inappropriate', 'signs', 'independent', 'valence', 'tended', 'indicate', 'dramatic', 'seven', 'clinical', 'deposited', 'hyperactivity', 'high', 'conventional', 'habilitative', 'evidence', 'problem', 'questions', 'daily', 'disabilities', 'aids', 'studies', 'communicator', 'moderately', 'alternating', 'scale', 'class', 'discriminative', 'tension', 'headaches', 'differential', 'maladaptive', 'phenomena', 'support', 'compared', 'items', 'determining', 'emergency', 'determined', 'influenced', 'teachers', 'general', 'dimensions', 'ability', 'voice', 'validation', 'ratings', 'highly', 'evaluations', 'reliabilities', 'index', 'ii', 'improvements', 'auditory', 'derived', 'negative', 'learning', 'associated', 'mothers', 'trainer', 'components', 'individualized', 'properties', 'provide', 'exp', 'acceptable', 'severity', 'gymnastics', 'relatively', 'licensed', 'sport', 'sample', 'subsequent', 'interrogatives', 'form', 'agrammatic', 'utility', 'development', 'relationship', 'monitoring', 'need', 'long', 'sets', 'communication', 'practice', '10', 'mobility', 'initiated', 'function', 'consistently', 'efficacy', 'additional', 'gait', 'possible', 'application', 'technique', 'duration', 'occurrence', 'recording', 'various', 'assessments', 'computer', 'record', 'complex', 'observers', 'palsy', 'instructed', 'autogenic', 'raynaud', 'disease', 'cold', 'hand', 'disorders', 'initial', 'end', 'studied', 'machine', 'useful', 'mist', 'face', 'component', 'instructions', 'scores', 'aid', 'played', 'collateral', 'paper', 'speech', 'good', 'automatic', 'statistical', 'defined', 'valenced', 'unsystematic', '18', 'observer', 'gender', 'analog', 'presented', 'collection', 'determine', 'investigators', 'manipulation', 'fourth', 'reported', 'unreliable', 'linear', 'placebo', 'prior', 'completed', 'electrodermal', 'majority', 'taken', 'positively', 'negatively', 'college', 'basketball', 'appears', 'continues', 'combined', 'feeding', 'successfully', 'spinal', 'analyses', 'better', 'regardless', 'aphasic', 'throw', 'implemented', '88', 'enhance', 'sports', 'complementary', 'drug', 'electric', 'shock', 'cases', 'replicated', 'incompatible', 'screaming', 'placed', 'implementation', 'loud', 'adult', 'examine', 'difficulties', 'practical', 'efficient', 'versus', 'laundromat', 'acquired', 'deficits', 'simple', 'conversational', 'result', 'like', 'handicaps', 'requires', 'reversals', 'comprehensive', 'future', 'mental', 'retardation', 'relation', 'aversive', 'disruptively', 'interruption', 'took', 'place', 'boy', 'diagnosed', 'context', 'processes', 'related', 'focus', 'concomitant', 'headache', 'minimal', 'calls', 'treat', 'extremely', 'prosthetic', 'assistance', 'methodological', 'palsied', 'adolescent', 'continued', 'represented', 'fully', 'trials', 'destructive', 'rubella', 'aggression', 'aggressive', 'gave', 'improving', 'cues', 'client', 'dro', 'cue', 'population', 'integrated', 'machines', 'generality', 'empirical', 'abab', 'reliably', 'codes', 'sbd', 'represent', 'television', 'instituted', 'holding', 'hands', 'size', 'held', 'parenting', 'identified', 'maltreaters', 'serve', 'nonintervention', 'promote', 'receive', 'counterbalanced', 'light', 'suggests', 'vocational', 'differences', 'change', 'purchasing', 'entering', 'pocket', 'making', 'financial', 'transactions', 'degree', 'twice', 'skin', 'progressive', '21', 'strength', 'boys', 'girls', 'powered', 'reports', '23', 'action', '43', 'providing', 'spina', 'bifida', 'current', 'physical', 'scientists', 'naturalistic', 'intervals', 'spatial', 'exploration', 'weeks', 'proved', 'bisexual', '2nd', 'fashion', 'greeting', 'fading', 'man', 'reinforcing', 'peripheral', 'question', 'probes', 'licensure', 'similar', '52', 'dramatically', 'blocking', 'temperatures', 'mouth', 'basis', 'regression', 'fitted', 'thoracic', 'involving', 'cognitions', 'means', 'interobserver', 'times', 'order', 'simultaneous', 'supported', 'underlying', '3rd', 'males', 'suppressing', 'relative', 'activities', 'real', 'age', 'area', 'certainly', 'video', 'multi', 'consisting', 'seriously', 'manual', 'commercially', 'overcorrection', 'past', 'drum', 'mean', 'teach', 'oral', 'members', 'adaptive', 'emitted', 'required', 'printing', 'kg', 'attending', 'distractible', 'people', 'container', '55', 'gal', 'engaged', 'designs', 'valuable', 'lengths', 'recorded', 'decrease', 'distractors', 'math', 'problems', 'displayed', 'isolation', 'washing', 'dropped', 'reductions', 'teacher', 'prompting', 'maintaining', 'perceived', 'constructions', 'reduce', 'stereotypic', 'occurring', 'eliminated', 'introduced', 'elicited', 'adults', 'job', 'monitor', 'examines', 'consequence', 'recruited', 'cost', 'instance', 'subjective', 'approaches', 'presence', 'yielded', 'chronic', 'produce', 'helm']</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>728</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4542</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1529</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.970568999345978</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.800446887258514</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.500339181392611</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>37.99852422875433</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1980s</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>['behavior', 'study', 'treatment', 'design', 'results', 'self', 'children', 'training', 'social', 'effects', 'analysis', 'use', 'used', 'multiple', 'using', 'subject', 'students', 'data', 'single', 'intervention', 'baseline', 'subjects', 'research', 'time', 'performance', 'reinforcement', 'participants', 'behaviors', 'skills', 'instruction', 'generalization', 'disabilities', 'functional', 'computer', 'control', 'stimulus', 'communication', 'procedures', 'showed', 'assessment', 'increased', 'conditions', 'behavioral', 'based', 'hearing', 'autism', 'patients', 'speech', 'effective', 'effect', 'maintained', 'mental', 'indicated', 'evaluated', 'matching', 'teaching', 'condition', 'program', 'evaluation', 'delay', 'retardation', 'case', 'stimuli', 'child', 'sessions', 'visual', 'procedure', 'interactions', 'taught', 'severe', 'injurious', 'sib', 'discussed', 'video', 'problem', 'student', 'group', 'systems', 'response', 'examined', 'modeling', 'sample', 'developmental', 'play', 'technology', 'follow', 'individuals', 'community', 'phase', 'peer', 'conducted', 'activities', 'levels', 'device', 'significant', 'therapy', 'staff', 'following', 'frequency', 'provided', 'method', 'individual', 'did', 'strategies', 'manipulation', 'different', 'aba', 'object', 'instructional', 'presented', 'test', 'rate', 'prompting', 'school', 'stimulation', 'high', 'related', 'participant', 'produced', 'aid', 'applied', 'support', 'measures', 'hand', 'period', 'feedback', '10', 'extinction', 'task', 'interaction', 'classroom', 'experimental', 'settings', 'increase', 'demonstrated', 'setting', 'present', 'studies', 'treatments', 'automatic', 'injury', 'spelling', 'determine', 'reversal', 'years', 'efficacy', 'videotape', 'methods', 'devices', 'maintenance', 'number', 'changes', 'compared', 'practice', 'attention', 'positive', 'preschool', 'game', 'application', 'improved', 'second', 'observed', 'appropriate', 'programming', 'level', 'interventions', 'development', 'clinical', 'responses', 'information', 'change', 'new', 'problems', 'contingencies', 'moderate', 'included', 'acquisition', 'reduced', 'effectiveness', 'evaluate', 'suggest', 'increasing', 'involved', 'output', 'verbal', 'series', 'comparison', 'validity', 'package', 'programmed', 'model', 'young', 'learning', 'year', 'programs', 'words', 'specific', 'tests', 'provide', 'participation', 'reinforcer', 'management', 'future', 'adults', 'investigation', 'trained', 'improvements', 'old', 'flexion', 'analyses', 'cervical', 'direct', 'pressure', 'videotapes', 'persons', 'day', 'experiment', 'tasks', 'computerized', 'accuracy', 'collected', 'alternating', 'disorders', 'function', 'home', 'groups', 'decreased', 'measured', 'preference', 'access', '20', 'videotaped', 'education', 'daily', 'important', 'increases', 'range', 'developed', 'sie', 'benefit', 'implemented', 'report', 'teams', 'mean', 'rates', 'cerebral', 'assessed', 'parent', 'improvement', 'palsy', 'brief', 'patient', 'differences', 'aids', 'aggression', 'peers', 'phases', 'sensory', 'correspondence', 'care', 'compliance', 'assisted', 'probe', 'cooperative', 'text', 'pictures', 'teach', 'implications', 'recognition', 'findings', 'negative', 'contingent', 'auditory', 'significantly', 'employment', 'responding', 'delayed', 'differential', 'approach', 'instructions', 'lower', 'picture', 'motion', 'session', 'employed', 'matched', 'free', 'fading', 'printed', 'indicate', 'criterion', 'target', 'variables', 'movement', 'alternative', 'oral', 'ability', 'greater', 'profound', 'music', 'habit', 'difference', 'long', 'preferred', 'paper', 'aac', 'hair', 'rehabilitation', 'designs', 'voice', 'received', 'reading', 'novel', 'terms', 'outcomes', 'suggested', 'resulted', 'classes', 'displayed', 'described', 'various', 'purpose', 'mouthing', 'leisure', 'errors', 'activity', 'low', 'reduce', 'general', 'health', 'upper', 'word', 'reinforcers', 'choice', 'reports', 'strategy', 'work', 'adult', 'teacher', 'investigated', 'question', 'generalized', 'reinforced', 'letter', 'weeks', 'fluency', 'months', 'parameters', 'physical', 'people', 'impairments', 'letters', 'schedule', 'parents', 'basketball', 'previous', 'goal', 'trials', 'type', 'dynamic', 'complete', 'cognitive', 'influence', 'toys', 'relation', 'current', 'functions', '15', 'total', 'making', 'initial', 'materials', 'addition', 'required', 'participated', 'supported', 'stereotypic', 'inappropriate', 'combined', 'reducing', 'motor', 'team', 'basic', 'component', 'protective', 'form', 'available', 'size', 'completed', 'consisted', 'term', 'efficient', 'techniques', 'models', 'alcohol', 'samples', 'games', 'cases', 'exercise', 'questions', 'introduced', 'food', 'issues', 'members', 'independent', 'potential', 'involving', 'values', 'skill', 'observation', 'limitations', 'review', 'course', 'relations', 'disorder', 'common', 'objects', 'order', 'designed', 'items', 'situations', 'similar', 'efficiency', 'process', 'ratings', 'learned', 'mpa', 'stuttering', 'eye', 'cost', 'identified', 'reduction', 'mentally', 'obtained', 'patterns', 'noncontingent', 'college', 'software', 'completion', 'voca', 'gait', 'minute', 'integration', 'compare', 'male', 'environmental', 'occupational', 'improve', 'validation', 'correct', 'public', 'comprehensive', 'routines', 'variety', 'bone', 'bilateral', 'viewing', 'examine', 'improving', 'adaptive', 'assistive', 'presentation', 'socially', 'praise', 'min', 'larger', 'contact', 'stereotypy', 'language', 'preschoolers', 'delays', 'edited', 'poking', 'useful', 'given', 'biofeedback', 'assess', 'decrease', 'ear', 'better', '25', 'baha', 'air', 'associated', 'chronic', 'augmentative', 'modified', 'objective', 'continued', 'ci', 'need', 'plus', 'mild', 'format', 'statistical', 'equivalence', 'coaching', 'electrical', 'list', 'identity', 'teachers', 'assessments', 'small', 'occurred', 'components', 'including', 'literature', 'services', 'non', 'adherence', 'appeared', 'analyzed', 'conduction', 'therapist', 'traditional', 'week', 'escape', 'trial', 'cochlear', 'shown', 'recommendations', 'frequently', 'content', 'equipment', 'occur', 'class', 'reactions', 'swallow', 'retarded', 'majority', 'preliminary', 'post', 'head', 'reinforcing', 'accurate', 'operant', 'requests', 'family', 'delivery', 'demonstrate', 'criteria', 'conversation', 'tapes', 'passive', 'selection', 'higher', 'times', 'symptoms', 'analysts', 'randomization', 'keyboard', 'neglect', 'walking', 'stroke', 'technique', 'revealed', 'return', 'line', 'studied', 'transfer', 'recorded', 'result', 'naturalistic', 'human', 'performed', 'pulling', 'dissemination', 'role', 'safety', 'maintaining', 'served', 'journal', 'lists', 'develop', 'parking', 'targeted', 'emotional', 'reductions', 'changing', 'researchers', 'percentage', 'screen', 'history', 'enrichment', 'probes', 'serial', 'previously', 'continuous', 'developing', 'microwave', 'living', 'enhance', 'entry', 'help', 'balance', 'emg', 'set', 'selected', '12', '14', 'experiments', 'statistic', 'restraint', 'implant', 'context', 'areas', 'frequent', 'diagnosed', 'affect', 'elderly', 'surgery', 'substantial', 'academic', 'reported', 'variability', 'discussion', 'methodology', 'sizes', 'gains', 'indicating', 'subsequent', 'constant', 'constructed', 'necessary', 'players', 'combination', 'destruction', 'periods', 'request', 'experienced', 'supervisor', '1993', 'natural', 'article', '1994', 'sets', 'determined', 'client', 'pica', 'controlled', 'orthotic', 'shock', 'measurement', 'recruitment', 'rom', 'good', 'month', 'rapid', 'corresponding', 'early', 'pain', 'open', 'standard', 'contrast', 'population', 'gambling', 'sitting', 'lottery', 'having', 'consequences', 'performances', 'women', 'attempts', 'property', 'observational', 'punishment', 'extremity', 'objectives', 'replication', 'mediated', 'intellectual', 'initiations', 'man', 'solution', 'loss', 'graphic', 'met', 'subsequently', 'conclusions', 'tested', 'replicated', 'behaviour', 'posttest', 'impairment', 'handicapped', 'brain', 'relative', 'correctly', 'computers', 'boy', 'consecutive', 'autocorrelation', 'promote', 'age', 'exposure', 'environment', 'marginal', 'pediatric', 'directions', 'produce', 'identify', 'ext', 'communicative', 'removed', 'prompt', 'discrimination', 'center', 'overall', 'dysphagia', 'pediatrics', 'simplified', 'relationship', 'personalized', 'elementary', 'affected', 'investigate', 'prior', 'examination', 'prompted', 'factors', 'blocking', 'lesions', 'reciprocal', 'implementation', 'serve', 'specifically', 'key', 'ankle', 'opportunities', 'outcome', 'muscle', 'regarding', 'scores', 'functioning', 'measure', 'provides', 'body', 'testing', 'splint', 'systematic', 'skinner', 'performing', 'aggressive', 'situation', 'special', '24', 'engaged', 'expressive', 'mode', 'decision', 'events', 'inspection', 'statistics', 'trainees', 'articles', 'survival', 'producing', 'contralateral', 'led', 'success', 'schedules', 'science', 'successful', 'wagering', 'semg', 'end', 'degree', 'importance', 'tennis', 'poor', 'reviews', 'indicates', 'comparing', 'supervisee', 'intentions', 'concentration', 'spinal', 'characteristics', 'reflex', 'applications', 'overt', 'influenced', 'positively', 'remained', 'parental', 'linguistic', 'structures', 'interface', 'educational', 'ambulation', 'orthoses', 'exemplars', 'writing', 'point', 'caregiver', 'imposed', 'postfeedback', 'variable', 'therapeutic', 'swallowing', 'pilot', 'regulation', 'appointment', 'trends', 'adolescents', 'added', 'treated', 'zero', 'power', 'evidence', 'viewed', 'varied', 'guidelines', 'sign', 'illegal', 'large', 'repeated', 'default', 'modification', 'specialists', 'grade', '30', 'supervision', 'needed', 'providing', 'woman', 'systematically', 'consonant', 'identification', 'implantation', 'basis', 'simulation', 'involvement', 'naming', 'little', 'researcher', 'additional', 'person', 'market', 'orthographic', 'consistent', 'acquired', 'extended', 'types', 'gradually', 'message', 'synthetic', 'contingency', 'myelomeningocele', 'observations', 'descriptive', 'sperm', 'conclusion', 'recently', 'make', 'boys', 'consultation', 'nonverbal', 'medication', 'speechreading', 'wheelchair', 'trend', 'footwear', 'vi', 'absence', 'families', 'removing', 'withdrawal', 'determining', 'speaking', 'aimed', 'associative', 'dissociative', '40', 'written', 'examples', 'major', 'consistently', 'relevant', 'demand', 'demands', 'presentations', 'amplification', 'impact', 'requiring', 'court', 'returns', 'flying', 'intensive', 'anxiety', 'graphs', 'checklist', 'nutritive', 'best', 'sucking', 'infant', 'days', 'needs', 'clients', 'difficulty', 'men', 'multielement', 'sleeves', 'awareness', 'mu', 'tsd', 'toy', 'oven', 'nature', 'habits', 'keeping', 'appointments', 'radical', 'behaviorism', 'distinct', 'suggests', 'fear', 'ncr', 'turn', 'aged', 'touch', 'aberrant', 'pronation', 'recordings', 'main', 'normal', 'muscles', 'fit', 'scanning', 'normative', 'score', 'cooking', 'standing', 'intradiscal', 'resolution', 'implanted', 'nucleus', 'action', 'store', 'asked', 'fraction', 'state', 'ask', 'rewards', 'paired', 'repertoires', '26', 'requesting', 'feeding', 'value', 'successfully', 'technological', 'inclusion', 'remaining', 'meeting', 'production', 'difficult', 'introduction', 'restraints', 'interactive', 'active', 'greatest', 'suggesting', '22', 'preoperative', 'vs', 'exposed', 'way', 'complex', 'disability', 'compound', 'ranging', 'resulting', 'concepts', 'chin', 'means', 'keller', 'intermittent', 'drinks', 'conduct', 'processes', 'theory', 'technologies', 'nro', 'energy', 'argo', 'occurrence', 'barriers', 'deficits', 'skin', 'job', 'grinding', 'adapted', 'concurrent', 'nicotine', 'independence', 'controlling', 'item', 'concluded', 'evident', 'concerning', 'real', 'furthermore', 'hands', 'selecting', 'spanish', 'observers', 'recent', 'ha', 'accounted', 'followed', 'address', 'indirect', 'relevance', 'select', 'cc', 'critical', '1982', 'productivity', 'solving', 'throw', 'microswitch', 'exhibited', 'machine', 'ventricular', 'step', 'collection', 'immediate', 'playing', 'telephone', 'medical', 'life', 'disc', 'measurements', 'homes', 'schools', 'interval', 'increasingly', 'psychology', 'female', 'significance', 'initially', 'arm', 'restriction', 'videodisc', 'leukoplakia', 'hairy', 'normally', 'topical', 'short', 'favorable', 'tool', 'satisfaction', 'acoustic', 'published', 'mediating', 'readily', 'consisting', 'conversational', 'incorporated', 'delivered', 'grocery', 'housing', 'focus', 'competitive', 'hour', 'hypothesized', 'topographies', 'interrupted', 'topography', 'version', 'pnd', 'seven', 'identifying', 'meetings', 'classrooms', 'maximum', 'exercises', 'flash', 'final', 'require', 'construction', 'spent', 'competing', 'graphed', 'points', 'consider', 'prompts', 'initiation', 'average', 'disease', 'ad', 'fitting', 'guide', 'directly', 'regular', 'member', 'blind', 'independently', 'promising', 'symmetry', 'stance', 'decimal', 'ratios', 'representations', 'positions', 'lying', 'antecedent', 'weekly', 'tse', 'jones', 'payne', 'changed', 'promoting', 'sufficient', 'later', 'hypothesis', 'quality', 'hours', 'aphasic', 'benefits', 'questionnaire', 'considered', 'lack', 'stapedius', 'recruit', 'versus', 'facilitators', 'scenes', 'implants', 'movements', 'original', 'numbers', 'clinics', 'sentence', 'analytic', 'collecting', 'minimal', 'directed', 'priced', 'achieved', 'driving', 'contribute', 'hitting', '13', 'analyze', 'background', 'adhd', 'mothers', 'internet', 'presence', 'sight', 'perform', 'pacing', 'noted', 'duration', '3rd', 'involve', 'allowed', 'gottman', 'half', 'examines', 'particular', 'automatically', 'outpatient', 'scheduled', 'remote', 'near', 'ac', 'aided', 'undesirable', 'instructing', 'manipulated', 'screaming', 'poorer', 'db', 'mixed', 'interdisciplinary', 'possible', 'generate', 'phrases', 'slow', 'understanding', 'hemiplegia', 'threshold', 'participating', 'communities', 'microcomputers', 'microcomputer', 'momentum', 'preceding', 'psychotherapy', 'weights', 'wrist', 'experience', 'anchored', 'pure', 'residual', 'concurrently', 'abuse', 'jaba', 'amplitude', 'odor', 'headmaster', 'mouthstick', 'congenital', 'thresholds', 'commonly', 'symbols', 'adjustment', 'capsules', 'manipulating', 'regimens', 'imagery', 'adjustments', 'retrieval', 'match', 'disruptive', 'recall', 'virtual', 'examining', 'decreasing', 'prescribed', '18', 'assist', 'typically', 'selective', 'effort', 'spell', 'decreases', 'clinically', 'purposes', 'belt', 'signal', 'intersection', 'paradigm', 'sequence', 'assigned', 'reached', 'transcutaneous', 'highly', 'regard', 'nerve', 'engagement', 'discriminated', 'separate', 'simultaneously', 'collateral', 'practical', 'coping', 'shot', 'density', 'linkage', 'channel', 'called', 'wore', 'communicate', 'prevented', 'ages', 'chat', 'wide', 'athlete', 'extension', 'impulsivity', '2nd', 'evaluating', 'desirable', 'routine', 'arbitrary', 'effectively', 'ensure', 'difficulties', 'a2', 'spastic', 'errorless', 'established', 'scientists', 'account', 'orthosis', 'empirical', 'rationale', 'twice', 'continuum', 'mouse', 'prices', 'aluminum', 'engage', 'likely', 'microsoft', 'ergometer', 'a1', 'foul', 'adversity', '90', 'girl', 'che', 'pervasive', 'dysphonia', 'fold', 'meyers', '1989', 'a3', 'atresia', 'conductive', 'wear', 'framework', 'tactile', 'digital', 'authors', 'precane', 'cane', 'mobility', 'creating', 'expertise', 'kept', 'untrained', 'author', 'past', 'represent', 'contributions', 'ethical', 'engaging', 'markedly', 'comprehension', 'analyzing', 'wpm', 'impaired', 'limit', 'deafened', 'postlinguistically', 'tone', 'played', 'rigid', 'limited', 'bahas', 'kris', 'lag', 'imaging', 'taking', 'challenges', 'pyramid', 'employees', 'expert', 'breast', 'showing', 'noise', 'efforts', 's1', 'interactional', 's2', 'maladaptive', 'supplements', 'describes', 'rules', 'clear', 'journals', 'place', 'traumatic', 'oxygen', 'plantar', 'insert', 'downward', 'responded', 'encodings', 'simple', 'facilitative', 'classmates', 'physically', 'vibrotactile', 'noncompliance', 'monitored', 'manipulations', 'probability', 'water', 'discuss', 'area', 'quantitative', 'highest', 'foot', 'guidance', 'career', 'reserved', 'surface', 'strong', 'mouth', 'comprised', 'nijmegen', 'prospective', 'females', 'intermediate', 'anticipation', 'vertical', 'profoundly', 'respectively', 'electromyography', 'spaces', 'volatile', 'perception', 'recommended', 'advantages', 'segments', 'spine', 'fix', 'cord', 'layouts', 'qwerty', 'layout', 'promise', 'ss', 'procedural', 'table', 'occurs', '95', 'comparisons', 'relatively', 'does', 'poorly', 'smaller', 'excel', 'keystroke', 'sexual', 'achieving', 'minutes', 'board', 'alpha', 'underwear', 'syndrome', 'scored', 'vsm', 'mechanical', 'represents', 'experimenter', 'mid', 'judges', 'negotiating', 'criticism', 'accepting', 'referenced', 'clinician', 'aphasia', '50', 'shift', 'view', '05', 'persisted', 'external', 'pizza', 'recruited', 'challenging', 'relationships', 'draws', '45', 'vocas', 'ball', 'apparent', 'room', 'inclusive', 'testicular', 'detection', 'idiosyncratic', 'organizational', 'steps', 'abnormality', 'formula', 'chained', 'yield', 'overcome', 'contributed', 'widely', 'structured', 'holland', 'correlates', 'confirmed', 'simulated', 'resin', 'podophyllum', 'goals', 'computing', 'hiv', 'earlier', 'summary', 'stops', 'males', 'defined', 'financial', 'conclude', 'stock', 'modest', 'regardless', 'create', 'percent', 'volleyball', 'accountable', 'randomized', 'nachemson', 'parts', 'handicaps', 'assessing', 'advanced', 'alzheimer', 'able', 'stutter', 'substantially', 'walk', 'practices', 'societal', 'continuing', 'dimensions', 'parallel', 'powerful', 'quiet', 'reminder', 'verbalizations', 'serves', 'perceived', 'medium', 'enhancement', 'innovative', 'fixed', 'battering', 'finger', 'consequent', 'contribution', 'lip', 'avoidance', 'flexed', 'weight', 'reality', 'answer', 'card', 'vr', 'detect', 'presents', 'alternated', 'ovens', 'abab', 'fred', 'arrow', 'schooling', 'operating', 'learn', 'entire', 'individualized', 'valid', 'face', 'dependence', 'virtually', 'recognized', 'rarely', 'offered', 'names', 'wrote', 'identical', 'nearly', 'supplemental', 'american', '1961', 'hr', 'methodologies', 'monitoring', 'designing', 'withdrawn', 'partner', 'psychological', 'false', 'sources', 'demonstrating', 'atd', 'restricted', 'competition', 'pre', '73', 'gap', 'chose', 'supplement', 'service', 'collaboration', 'synthesized', 'substitutability', 'user', 'cable', 'efficacious', 'structure', 'partners', 'faster', 'travel', 'discusses', 'working', 'edematous', 'vocational', 'proposed', 'flaccid', 'paraplegic', 'administration', 'aspects', 'consumption', 'formats', 'casting', 'continue', 'multicomponent', 'durable', 'occurring', 'equal', 'absent', 'yielded', 'dropped', 'establish', 'medicine', 'investigators', 'stopping', 'undergraduate', 'targeting', 'carried', 'utility', 'allow', 'problematic', 'gravity', 'retraining', 'despite', 'percentages', 'drink', 'modes', 'manual', 'attempted', 'vowel', 'vocal', 'spoken', 'display', 'initiated', 'depicting', 'participate', 'forms', 'collaborative', 'cai', 'occasions', 'evidenced', 'oneself', 'math', 'university', 'viable', 'allison', 'exemplary', 'gorman', 'qualitative', 'variations', 'extensive', 'mands', 'laboratory', 'commands', 'fundamental', 'achievement', 'capsule', 'curriculum', 'fo', 'illness', 'correction', 'determination', 'provision', 'replications', 'supply', 'anesthetic', 'semen', 'motile', 'crutches', 'walker', 'dexterity', 'migraine', '37', 'propelled', 'visuomotor', 'fleshler', 'hoffman', 'equation', 'listening', '23', 'replace', 'op', 'cacg', 'teeth', 'scratching', 'announced', 'dispenser', 'disabled', 'perspective', 'diabetes', 'deficit', 'perceive', 'anesthetics', 'ordering', 'counter', 'isoflurane', 'intraoperative', 'multiply', 'tens', 'halothane', 'esrt', 'esrts', 'netherlands', 'enhancing', 'peak', 'breakdown', 'hyperactivity', 'modality', 'scientist', 'practitioner', 'warranted', 'remains', 'pressures', 'preventing', 'fluent', 'ranges', 'schizophrenic', 'applicable', 'nineteen', 'native', 'array', 'arrangement', 'predict', 'bagged', 'lunch', 'balanced', 'naturally', 'additionally', 'administered', 'certain', 'severity', 'shoes', 'depicted', 'sst', 'roles', 'tools', 'sites', 'athetoid', 'local', 'aphasiology', 'cigarettes', 'smoked', 'arima', 'rehearsed', 'disordered', 'caused', 'actors', 'keystrokes', 'semc', 'typing', 'summarized', 'windows', 'macos', 'started', 'publication', 'detailed', 'advances', 'digit', 'postoperative', 'handheld', 'sam', 'dictated', 'paraspinals', 'sternocleidomastoid', 'degrees', 'recruits', 'configuration', 'dyads', 'briskly', 'deviation', 'sequentially', '79', 'unfavorable', 'differentiation', 'copyright', 'john', 'wiley', 'diapering', 'severely', 'caregiving', 'pathological', 'sons', '1990', 'surveyed', 'erroneous', 'candidacy', 'incidence', 'postimplant', 'labeling', 'functioned', 'hazards', 'accident', 'prevention', 'european', 'graph', 'suitable', '97', 'features', 'mastery', 'turnovers', 'adversities', 'subjective', 'relearning', 'watched', 'posttreatment', 'restructuring', 'remediation', 'intention', 'nondisabled', 'sociopolitical', 'ideologies', 'evolution', 'culture', 'hierarchies', 'helpfulness', 'dyad', 'sentences', 'discontinued', 'connected', 'personal', 'agreement', 'stable', 'preterm', '85', 'respective', 'nonsignificant', 'confounds', 'thirty', 'plant', '1986', 'marked', 'rated', 'depression', 'bidirectional', 'causal', 'rare', 'untreated', 'nonvocalizing', 'laryngeal', 'instead', 'fits', 'aerodynamic', '51', 'therblig', 'photocopier', 'folding', 'mini', '39', 'hl', 'milk', '57', 'ii', 'appears', 'premature', 'maternal', 'arising', 'baselines', 'existence', 'fct', 'pursue', 'price', 'grown', 'documents', 'realities', 'providers', 'ignoring', 'implement', 'lesser', 'reviewing', 'sedation', 'inhibition', 'prescription', 'integrated', 'unfortunately', 'pediatricians', 'experts', 'resonance', 'diagnosis', '44', '64', 'closely', 'deteriorate', '60', 'necessity', '1998', 'symmetrical', 'fitted', 'pta', 'khz', 'mother', 'audiometric', 'citation', 'citations', 'stimulating', 'overview', 'comparative', 'circulation', 'scientific', 'mailed', 'nontraining', 'environments', '19', 'magnetic', 'generalize', 'conceptual', 'combinations', 'cancellations', 'educable', 'advance', 'classification', 'read', 'preceded', 'treat', 'iwata', 'dorsey', 'pattern', 'rudimentary', 'express', 'acceptable', 'adolescent', 'march', 'adequate', 'pulled', 'augmenting', 'accomplished', 'legacy', 'nonspeaking', 'clinic', 'conversations', 'biting', 'nail', 'rhetoric', 'philosophy', 'discrepancy', 'supporting', 'functionally', 'particularly', 'stored', 'coaches', 'preservice', 'disciplines', 'consumer', 'gathered', 'edema', '53', '63', 'richman', 'shifts', 'drill', 'thought', 'augment', 'perfect', 'prove', 'autocorrelated', 'youths', 'search', 'matrix', 'organized', 'held', 'randomly', 'standardized', 'extent', 'lead', 'reliance', 'parameter', '11', '000', 'repeat', 'practitioners', 'blank', 'accompanied', 'investigator', 'random', 'assignment', 'proportion', 'drank', 'specification', 'wish', 'example', 'dissatisfaction', 'hemiparetic', 'cent', 'frame', 'incorrect', 'involves', 'sides', 'explicate', 'distribution', 'moved', 'participatory', 'slifer', 'bauman', 'purchasing', 'ratd', 'modify', 'chairperson', 'strengths', 'theoretical', 'counterbalanced', 'tangible', 'consequence', 'partially', 'regression', 'generally', 'breath', 'alert', 'existing', 'irrational', 'law', 'shows', 'determinants', 'bac', 'oropharyngeal', 'focused', 'physiology', 'investing', 'topics', 'themes', 'perseverated', 'incorporating', 'girls', 'improves', 'obsessions', 'visually', 'guided', 'shapes', 'courses', 'digits', 'investigations', 'immediately', 'acceptance', 'systemic', 'capsi', 'proctors', 'investment', 'dramatic', 'build', 'intervertebral', 'according', 'ceased', 'unchanged', 'planning', 'factor', 'volunteer', 'sports', 'vivo', 'fluently', 'seen', 'adl', 'revisited', 'estimating', 'permit', 'restrictive', 'straight', 'reference', 'elsevier', 'mechanisms', 'broad', 'loading', 'knowledge', 'judged', 'source', 'attempt', 'private', 'recreation', 'goggles', 'cancer', 'disturbance', 'unable', '70', 'kg', 'states', 'million', 'left', 'splinting', 'forced', 'prefer', 'wearing', 'right', 'unit', 'fine', 'fell', 'progress', 'accountability', 'lifting', 'approximately', 'maintain', 'ail', 'ratio', 'pictorial', 'fractions', 'emergence', 'represented', 'scale', 'lotteries', 'aversive', 'arizona', 'modifications', 'counterpart', 'decimals', 'properties', 'usually', 'oregon', 'frames', 'blanks', 'answers', 'programmatic', 'repertoire', 'preparing', 'sustained', 'meals', 'aspect', 'gross', 'principles', 'motivation', 'resting', 'winning', 'rehearsal', 'gym', 'predominant', 'stimulatory', 'documentation', 'building', 'receiving', 'stick', '46', 'exception', 'forward', 'position', 'fact', 'domestic', 'violence', 'residents', 'shr', '17', 'externally', 'palatal', 'prosthesis', 'contexts', 'operated', 'lasted', 'appliances', 'prepared', 'slightly', 'cabas', 'encouraging', 'vision', 'prerecorded', 'rest', 'vocabulary', 'story', 'receive', 'covert', 'remove', 'autocorrelations', 'clgs', 'intended', '1991', 'exist', 'physiotherapy', 'autoreg', 'amt', 'debilitating', 'status', 'tolerance', 'predicted', 'ineffective', 'evaluates', 'currently', 'optimal', 'crosbie', 'taken', 'event', 'failure', 'calendar', 'site', 'primary', 'flight', 'narratives', 'dose', 'dependent', 'declined', 'generality', 'assistant', 'corrected', 'editing', 'window', 'enlarged', 'al', 'ducharme', 'nervous', 'bored', 'caregivers', '1996', 'pointing', 'error', 'b2', 'matches', 'interpretation', 'personnel', 'undifferentiated', 'suppression', 'sampling', 'contextual', 'participative', 'deliverers', 'locations', 'sec', 'intervals', 'assistance', 'adverse', 'deglutition', 'audio', 'pulse', 'ma', 'foods', 'beverages', 'appendix', 'inherent', 'computation', 'sidman', 'receptive', 'experiences', 'unprompted', 'experimenters', 'formation', 'acquire', 'expansion', 'appropriately', 'inverse', 'instructors', 'referred', '1992', 'skilled', 'cards', 'material', 'destroyed', 'ones', 'bivalved', 'shortened', 'continuously', 'formed', 'chain', 'fewer', 'snack', 'regularly', 'enhanced', 'interpreting', 'unknown', 'dramatically', 'derived', 'supplemented', 'compete', '100', 'individually', 'season', 'treating', 'applying', 'exchange', 'servers', 'commentary', 'promotion', 'options', 'world', 'tbi', 'force', 'dimensional', 'camera', 'breaking', 'tapping', 'plastic', 'facilitated', 'briefly', 'reviewed', 'association', 'probably', 'unmatched', 'pick', 'blocked', 'rowing', 'addresses', 'workout', 'varsity', 'adaptations', 'primarily', 'behaviours', 'amounts', 'implementing', 'encountering', 'far', 'utilized', 'varying', 'preschools', 'reciprocating', 't12', 'internal', 'physiological', 'prevent', 'length', 't4', 'tm', 'gastrocnemius', 'feedforward', 'issue', 'matter', 'complicated', 'sequential', 'questioned', '27', 'eliminating', 'clusters', 'respond', 'rights', 'reach', 'trainer', 'illustrate', 'conducting', 'construct', 'ed', 'elicited', 'compliant', 'risks', 'removal', 'concept', 'presenting', 'encountered', 'documented', 'substitutable', 'project', 'description', 'methodological', 'considerations', 'field', 'measuring', 'index', 'photographic', 'fault', 'respite', 'impulsive', 'fourth', 'yoked', 'briefs', 'loose', 'superior', 'regimen', 'analogue', 'overfitting', 'statistically', 'tight', 'produces', 'expense', 'captured', 'sensing', 'corporate', 'ar', 'evaluations', '1981', 'itsa', 'williams', 'anomalous', 'uncovered', 'requirement', 'worst', 'rely', 'calls', 'undocumented', 'belief', 'infuence', 'agent', 'supports', 'processor', 'contributes', 'candies', 'progressively', 'tablets', 'coupled', 'gas', 'authoring', '155', 'dense', 'trainability', 'replayed', 'deaf', 'undergoing', 'overfitted', 'ltoreq', 'inflated', 'spermatogenesis', 'healthy', 'thirties', 'formulae', 'postsurgery', 'meter', 'multihandicapped', 'intake', 'demonstration', 'boxer', 'technologist', 'abstinence', 'flawed', 'contingently', 'interruption', 'insufficient', 'draw', 'expenditure', 't9', 'lost', 'proposes', 'prognosis', 'cure', 'managed', 'critiques', 'traded', 'inversely', 'unsuccessful', 'preferences', 'interpreted', 'visible', 'cited', 'ucla', 'teacch', 'leap', 'denver', 'obtain', 'topic', 'ballistic', 'swing', 'supination', 'fool', 'angles', 'postintervention', 'descriptively', '20s', '29', 'exelusively', 'paedophilia', 'reassigned', 'sociometric', 'kinematic', 'collect', 'cluster', 'containing', 'ccs', 'urgent', 'oriented', 'modelling', 'elements', 'alaskan', 'earning', 'designated', 'reward', 'consulted', 'pair', 'kind', 'circumvented', 'costly', 'grabbing', 'remarks', 'interrupting', 'mist', 'aware', 'overselectivity', 'demineralization', 'rigidity', '33', 'stay', 'talk', 'distribute', 'instituted', 'cohorts', 'eventually', 'buddy', 'argos', 'limits', 'mounted', 'deviations', 'loot', 'judgments', 'en', 'attending', 'stride', 'biomechanical', 'inter', 'freely', 'swinging', 'legs', 'reciprocally', 'linked', 'musgrave', 'footprint', 'tightness', 'predispose', 'stretching', 'joint', 'positioning', 'compensatory', 'novice', 'rowers', 'sat', 'station', 'pressed', 'liberator', 'rural', 'adap', 'row', 'institutionalisation', 'paedophilic', 'supervised', 'apartments', 'choosing', 'arlother', 'route', 'thousands', 'permitted', 'giving', 'visits', 'laundry', 'avoid', 'instruct', 'requested', 'encouraged', 'completing', 'chores', 'siblings', 'braining', 'resources', 'internee', 'confederation', '21', 'web', 'reside', 'took', 'covering', 'globe', 'plaud', '1996b', 'ecology', 'childhood', 'iq', 'destructive', 'conventional', 'standards', 'division', 'empirically', 'undestroyed', 'driver', 'license', 'plate', 'posted', 'nontargeted', 'drivers', 'embedding', 'allocated', 'thar', 'bath', 'operants', 'outlined', 'basics', 'connecting', 'replaced', 'reaching', 'assistants', 'indirectly', 'accommodate', 'ongoing', 'reinforces', 'resiliency', 'wanted', 'simultaneous', 'fashion', 'ecological', 'verify', 'ameliorating', 'empowering', 'terminal', 'unnecessary', 'illustrates', 'appropriateness', 'likewise', 'messages', 'yes', 'statements', 'named', 'dictation', 'availability', 'b3', 'encompassed', '35', 'ababab', 'contrasts', 'b1', 'allocation', 'piece', 'accessible', 'includes', 'taped', 'capitalized', 'semantic', '69', 'alphabet', 'depict', 'behaving', 'lessons', 'include', 'reactive', 'gaps', 'overcoming', 'concludes', 'clarify', 'differing', 'ascertain', 'manipulate', 'stayed', 'terminating', 'maintains', 'referent', 'greeting', 'steadily', 'breaks', 'scoring', 'eikeseth', 'smith', 'ways', 'facilitate', 'thirst', 'illustrating', 'accelerated', 'extend', 'horne', 'lowe', 'gestures', 'drawings', 'professional', 'comments', 'focusing', 'precise', 'attributes', 'reductive', 'unfamiliar', 'hunger', 'facilitation', 'starting', '200', 'barium', 'paste', 'opportunity', 'sampled', 'managing', 'selections', 'fast', 'er', 'tedious', 'cursor', 'minor', 'morning', 'tolerated', 'handicap', 'fight', 'ology', 'shelf', 'returned', 'comfortable', 'handwritten', 'timing', 'potentially', 'nonintrusive', 'cooperation', 'attributable', 'enemy', 'bias', 'temporal', 'biased', 'popynick', 'et', 'durability', 'oppositional', 'prepare', 'imitate', 'competent', 'videos', 'bi', 'nonreferred', 'neutral', 'covertly', 'recording', 'input', 'uppercase', 'quadriplegic', 'repetitive', 'limbs', 'graded', 'airplane', '42', 'planned', 'heoring', 'depends', 'listener', 'existed', 'ml', 'videofluoroscopy', 'illustrative', 'adequately', 'masked', 'believed', 'whit', 'inefficacy', 'alternatives', 'collectively', 'electronic', 'employs', 'overlays', 'feed', 'advantage', 'gloves', 'attenuate', 'allowing', 'recommending', 'initiating', 'ultimate', 'intent', 'forearm', 'pretreatment', 'ideas', 'mapping', 'nonelectronic', 'soundtrack', 'prediction', 'speechless', 'huitema', 'mckean', 'inflate', 'deflate', 'texts', 'consists', 'itsacorr', 'nondominant', 'fluid', 'nutrition', 'biomechanics', 'largely', 'ignored', 'areg', 'spss', 'sas', 'presupposes', 'complaints', 'unrecognized', 'outside', 'administer', 'deterioration', 'dependencies', 'flow', 'facilities', 'facility', 'mildly', 'familiar', 'representative', 'coercion', 'oppression', 'erect', 'unobtrusive', '36', 'satisfied', 'kelly', 'shorter', 'couple', 'barrier', 'lexigrams', 'owned', 'accurately', 'pace', 'exploratory', 'persistent', 'videofluoroscopic', 'gentle', 'multiphase', 'insubstantial', 'batter', 'observing', 'yonkers', 'york', 'correcting', 'sustaining', 'assisting', 'hot', 'sabre', 'burns', 'worn', 'remotely', 'radio', 'cha</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3963</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>['captured', 'sensing', 'corporate', 'ar', 'evaluations', '1981', 'itsa', 'williams', 'anomalous', 'uncovered', 'requirement', 'worst', 'rely', 'calls', 'undocumented', 'belief', 'infuence', 'agent', 'supports', 'processor', 'contributes', 'candies', 'progressively', 'tablets', 'coupled', 'gas', 'authoring', '155', 'dense', 'trainability', 'replayed', 'deaf', 'undergoing', 'overfitted', 'ltoreq', 'inflated', 'spermatogenesis', 'healthy', 'thirties', 'formulae', 'postsurgery', 'meter', 'multihandicapped', 'intake', 'demonstration', 'boxer', 'technologist', 'abstinence', 'flawed', 'contingently', 'interruption', 'insufficient', 'draw', 'expenditure', 't9', 'lost', 'proposes', 'prognosis', 'cure', 'managed', 'critiques', 'traded', 'inversely', 'unsuccessful', 'preferences', 'interpreted', 'visible', 'cited', 'ucla', 'teacch', 'leap', 'denver', 'obtain', 'topic', 'ballistic', 'swing', 'supination', 'fool', 'angles', 'postintervention', 'descriptively', '20s', '29', 'exelusively', 'paedophilia', 'reassigned', 'sociometric', 'kinematic', 'collect', 'cluster', 'containing', 'ccs', 'urgent', 'oriented', 'modelling', 'elements', 'alaskan', 'earning', 'designated', 'reward', 'consulted', 'pair', 'kind', 'circumvented', 'costly', 'grabbing', 'remarks', 'interrupting', 'mist', 'aware', 'overselectivity', 'demineralization', 'rigidity', '33', 'stay', 'talk', 'distribute', 'instituted', 'cohorts', 'eventually', 'buddy', 'argos', 'limits', 'mounted', 'deviations', 'loot', 'judgments', 'en', 'attending', 'stride', 'biomechanical', 'inter', 'freely', 'swinging', 'legs', 'reciprocally', 'linked', 'musgrave', 'footprint', 'tightness', 'predispose', 'stretching', 'joint', 'positioning', 'compensatory', 'novice', 'rowers', 'sat', 'station', 'pressed', 'liberator', 'rural', 'adap', 'row', 'institutionalisation', 'paedophilic', 'supervised', 'apartments', 'choosing', 'arlother', 'route', 'thousands', 'permitted', 'giving', 'visits', 'laundry', 'avoid', 'instruct', 'requested', 'encouraged', 'completing', 'chores', 'siblings', 'braining', 'resources', 'internee', 'confederation', '21', 'web', 'reside', 'took', 'covering', 'globe', 'plaud', '1996b', 'ecology', 'childhood', 'iq', 'destructive', 'conventional', 'standards', 'division', 'empirically', 'undestroyed', 'driver', 'license', 'plate', 'posted', 'nontargeted', 'drivers', 'embedding', 'allocated', 'thar', 'bath', 'operants', 'outlined', 'basics', 'connecting', 'replaced', 'reaching', 'assistants', 'indirectly', 'accommodate', 'ongoing', 'reinforces', 'resiliency', 'wanted', 'simultaneous', 'fashion', 'ecological', 'verify', 'ameliorating', 'empowering', 'terminal', 'unnecessary', 'illustrates', 'appropriateness', 'likewise', 'messages', 'yes', 'statements', 'named', 'dictation', 'availability', 'b3', 'encompassed', '35', 'ababab', 'contrasts', 'b1', 'allocation', 'piece', 'accessible', 'includes', 'taped', 'capitalized', 'semantic', '69', 'alphabet', 'depict', 'behaving', 'lessons', 'include', 'reactive', 'gaps', 'overcoming', 'concludes', 'clarify', 'differing', 'ascertain', 'manipulate', 'stayed', 'terminating', 'maintains', 'referent', 'greeting', 'steadily', 'breaks', 'scoring', 'eikeseth', 'smith', 'ways', 'facilitate', 'thirst', 'illustrating', 'accelerated', 'extend', 'horne', 'lowe', 'gestures', 'drawings', 'professional', 'comments', 'focusing', 'precise', 'attributes', 'reductive', 'unfamiliar', 'hunger', 'facilitation', 'starting', '200', 'barium', 'paste', 'opportunity', 'sampled', 'managing', 'selections', 'fast', 'er', 'tedious', 'cursor', 'minor', 'morning', 'tolerated', 'handicap', 'fight', 'ology', 'shelf', 'returned', 'comfortable', 'handwritten', 'timing', 'potentially', 'nonintrusive', 'cooperation', 'attributable', 'enemy', 'bias', 'temporal', 'biased', 'popynick', 'et', 'durability', 'oppositional', 'prepare', 'imitate', 'competent', 'videos', 'bi', 'nonreferred', 'neutral', 'covertly', 'recording', 'input', 'uppercase', 'quadriplegic', 'repetitive', 'limbs', 'graded', 'airplane', '42', 'planned', 'heoring', 'depends', 'listener', 'existed', 'ml', 'videofluoroscopy', 'illustrative', 'adequately', 'masked', 'believed', 'whit', 'inefficacy', 'alternatives', 'collectively', 'electronic', 'employs', 'overlays', 'feed', 'advantage', 'gloves', 'attenuate', 'allowing', 'recommending', 'initiating', 'ultimate', 'intent', 'forearm', 'pretreatment', 'ideas', 'mapping', 'nonelectronic', 'soundtrack', 'prediction', 'speechless', 'huitema', 'mckean', 'inflate', 'deflate', 'texts', 'consists', 'itsacorr', 'nondominant', 'fluid', 'nutrition', 'biomechanics', 'largely', 'ignored', 'areg', 'spss', 'sas', 'presupposes', 'complaints', 'unrecognized', 'outside', 'administer', 'deterioration', 'dependencies', 'flow', 'facilities', 'facility', 'mildly', 'familiar', 'representative', 'coercion', 'oppression', 'erect', 'unobtrusive', '36', 'satisfied', 'kelly', 'shorter', 'couple', 'barrier', 'lexigrams', 'owned', 'accurately', 'pace', 'exploratory', 'persistent', 'videofluoroscopic', 'gentle', 'multiphase', 'insubstantial', 'batter', 'observing', 'yonkers', 'york', 'correcting', 'sustaining', 'assisting', 'hot', 'sabre', 'burns', 'worn', 'remotely', 'radio', 'char', 'came', 'round', 'knees', 'aloud', 'tutoring', 'clg', 'fostering', 'introductory', 'composition', 'notwithstanding', 'explained', 'transducers', 'cautiously', 'relaxed', 'unsupported', '83', 'nonchalant', 'constantly', 'bonus', 'marks', 'summarize', 'comic', 'close', 'night', 'correlation', 'master', 'located', 'isolating', 'worked', 'strips', 'overwhelmingly', 'lecture', 'midterm', 'ill', 'meal', 'preparation', 'diet', 'incorporate', 'cybernetic', 'influences', 'supervisors', 'sw', 'ay', 'contacting', 'supplementary', 'integrity', 'checks', 'tied', 'relate', 'ninth', 'losing', 'persist', 'substituted', 'purported', 'nonuse', 'directing', 'disappeared', 'commissions', 'seek', 'asking', 'stair', 'climbing', 'load', 'hydration', 'sleeping', 'tissue', 'damage', 'mired', 'rimes', 'appear', 'semiweekly', 'sales', 'jackpots', 'quantities', 'contrary', 'substitute', 'sb', 'casks', '02', '06', 'causing', 'earn', 'nonsocial', '523', 'megabucks', '540', 'underwent', 'odds', 'ro', 'imbalance', 'pezziball', 'ergonomic', 'sneezing', 'laughing', 'jogging', 'minimum', 'jackpot', 'quantity', 'voluntary', 'spontaneously', 'occupations', 'complied', 'waking', 'restrict', 'presplinting', 'semiformal', 'lesson', '67', 'grades', 'awarding', 'postsplinting', 'peabody', 'scales', 'prone', 'laterally', 'chair', 'armchair', 'register', 'admissions', 'parenting', 'obsession', 'substantive', 'pamphlet', 'l5', 'infected', 'tongue', 'lesion', 'worsening', 'burning', 'films', 'completeness', 'examinations', '48', 'visit', 'longer', 'tses', 'youth', 'interactivity', 'physicians', 'discriminate', 'reliably', 'document', 'morbidity', 'mortality', 'professionally', 'weighing', 'telemetry', 'emotionally', 'behaviorally', 'additive', 'feasibility', 'activated', 'interacted', 'sokal', 'rohlf', '1995', 'crawford', 'posting', 'establishment', 'understood', 'pioneering', 'howell', 'tin', 'press', 'unlike', 'treats', 'sway', '1957', 'extending', 'complement', 'holding', 'technically', 'ns', 'salience', 'dangerously', 'intense', 'splints', 'sterile', 'surgical', 'transducer', 'diameter', 'mm', 'pulposus', 'nondegenerated', 'l4', 'bad', 'altered', 'taste', 'intensity', 'psi', 'rnd', 'academy', 'reply', 'safe', 'option', 'analog', 'escalation', 'persistence', 'invested', 'markets', 'sensation', 'meets', 'faced', 'fdor', 'mathematics', 'shaped', 'emerged', 'translating', 'efficiently', '1960s', 'corroborate', 'dispute', 'click', '101', 'baba', 'intrasubject', 'constructing', 'circumstances', 'overestimates', 'automates', 'calculations', 'obsessive', 'introducing', 'vocalizations', 'reasons', 'cadiz', 'district', 'theme', 'maps', 'tag', 'giant', 'outline', 'map', 'withdrawing', 'failing', 'capitalize', 'interests', 'valued', 'color', 'follows', 'gagne', 'synthesis', 'maneuvers', 'congress', 'incidental', 'cyberspace', 'allotted', 'slots', 'persisting', 'overlapping', 'proposals', 'resident', 'demonstrates', 'conversely', 'answered', 'incorrectly', 'universiteit', 'complementary', 'meta', 'partly', 'quantified', '31', '621', '631', 'listed', 'road', 'tester', 'synthesizing', 'blood', 'susceptible', 'thorough', 'strongly', 'integrative', 'multidisciplinary', 'quantifying', 'precipitously', 'economically', 'predictable', 'patrons', 'club', 'digitalized', 'van', 'damme', 'onghena', 'department', 'katholieke', 'usual', 'consumed', 'cause', 'logic', '72', 'gathering', 'ln', 'anticipate', 'concrete', 'elaborate', 'intrinsically', 'organization', 'ground', 'yr', 'stood', 'dual', 'forceplates', 'enclosed', 'motivate', 'leuven', 'belgium', 'transferred', 'stores', 'survives', 'withdraw', 'possibilities', 'derive', '152', '66', '16', 'accompanying', 'resort', 'pragmatics', 'essay', 'lessened', 'uniformly', '145', 'hallways', 'blended', 'specialized', 'promotes', 'rested', 'epidemiologic', 'extremely', 'fades', 'secondary', 'mailing', 'cashing', 'check', 'crossing', 'street', 'administrations', 'exclude', '58', 'largest', '38', 'cyclical', 'inconsistent', 'uninterpretable', 'negatively', 'evalated', 'volumeter', 'circumference', 'offering', 'protocols', 'references', 'databases', 'reemergence', 'beginning', 'faded', 'reinforcfment', 'assertive', 'responsiveness', 'makes', 'banging', 'meet', 'extensions', 'probed', 'guiding', 'accumulation', 'rigorous', 'epidemiological', 'epidemiology', 'reimplemented', 'novelty', 'prestored', 'reusable', 'resumed', 'eliminated', 'exposures', '150', 'scope', 'cerebrovascular', 'sided', 'promoted', 'considerable', 'paid', 'vast', 'consumers', 'lets', 'spaced', 'volunteering', 'raising', 'ranged', 'inconclusive', 'surround', 'wk', 'simulate', 'write', 'firmly', 'pressing', 'bones', 'kicking', 'tradition', 'educative', 'portion', 'broaden', 'mediate', 'refrained', 'maximizing', 'minimizing', 'autoregressive', 'equations', 'responsible', 'highlight', 'principle', 'topographically', 'dissimilar', 'classifying', 'growth', 'noticed', 'stand', 'supervising', 'deliver', 'helped', 'helping', 'periodically', 'grading', 'discontinuation', 'addressing', 'mentioned', 'specialization', 'brings', 'heightened', 'expected', 'vehicle', 'professionals', 'imperative', 'acceptability', 'disorganization', 'misunderstandings', 'observe', 'twofold', 'sought', 'differentially', 'solvers', 'doing', 'computerised', 'programme', 'vaughan', 'michael', 'institutions', 'foster', 'enjoyable', 'implication', 'cut', 'rubber', 'glove', 'trichotillomania', 'eliminates', 'fingernail', 'aim', 'utterances', 'quickly', 'remain', 'characterized', 'bulk', 'categories', 'overlap', 'contained', 'writings', 'underlying', 'promises', 'preconstructed', 'capable', 'succession', 'pragmatic', 'mathematic', 'welfare', 'reverted', 'critique', 'reveals', 'society', 'argued', 'log', 'mediation', 'vowels', 'consonants', 'explored', 'arranged', 'macrosocial', 'preoccupation', 'institutional', 'percutaneous', '34', 'diminished', 'infections', 'merged', 'intact', 'economical', 'establishing', 'beneficial', 'eyes', 'inferential', 'variance', 'opposition', '28', 'exacerbates', 'otitis', 'interfere', 'enter', 'technicians', 'strengthening', '1st', 'occasion', 'th', 'anniversary', 'thoroughly', 'assumed', 'complexity', 'shortcomings', 'mechanism', 'obscured', 'clearly', 'simpler', 'suggestions', 'revision', 'easier', 'protected', 'obstacles', 'pass', 'reminding', 'analyse', 'linear', 'scheduling', 'want', 'neuroimaging', 'reminders', 'replicate', 'meaningful', 'experimentally', 'uncooperative', 'scans', 'conditioning', 'childcare', 'workers', 'reprimands', 'lend', 'north', 'romping', '43', 'approximated', 'surpassed', 'contraindicated', 'bearing', 'diseases', 'collaboratively', 'uailateral', 'drug', 'approved', 'sensorineural', 'multicentre', 'approval', 'postlingual', 'centres', 'decades', 'undergone', 'infectious', 'unaided', 'mo', 'aural', 'directional', 'healing', 'therbligs', 'images', 'finished', 'unlikely', 'recruiting', 'presumably', 'translated', 'monitor', 'quarter', 'century', 'apace', 'proofreading', 'processed', 'sheets', 'adaptation', 'occupation', 'defining', 'behalf', 'prototype', 'widespread', 'devoted', 'concerted', 'reflect', 'breadth', 'america', 'industry', 'product', 'offer', 'adopted', 'arrangements', 'diminish', 'argues', 'deriving', 'skiba', 'casey', '1985', 'laboratories', 'departments', 'resource', 'occasionally', 'slope', 'advocated', 'computational', 'algorithm', 'entails', 'hardware', 'calculating', 'metaanalysis', 'readers', 'typical', 'macintosh', 'iici', 'equipped', '86', '387', '400', 'page', 'scanner', 'optical', 'character', 'convert', 'scanned', 'tentative', 'validated', 'procrastination', 'attitudes', 'transition', 'sporadic', 'lived', 'combining', 'transitions', 'duplicating', 'preoperatively', 'postoperatively', 'soundfield', 'originating', 'treacher', 'collins', 'combat', 'funding', 'bilaterally', 'sound', 'localization', 'intraindividual', 'stop', 'causes', '108', '99', 'ra', 'iia', 'speakers', 'olfactory', 'iii', '49', 'iv', 'bisyllablic', 'integrating', 'lifelong', 'feelings', 'openly', 'undiagnosed', 'leads', 'lifetime', 'consciousness', 'cords', 'counting', 'estimate', 'telecommunication', 'distance', 'sciences', 'dowrick', 'pw', 'endoscopic', 'recurring', 'phonation', 'filling', 'soda', 'electromyographic', 'folds', 'true', 'committing', 'ended', 'multimodality', 'disabilitities', 'equally', 'consideration', 'perceptual', 'unaware', 'pathologist', 'remission', 'graders', '1988', '1997', 'smooth', 'effortless', 'stutters', 'thirdly', 'depending', 'stronger', 'piagetian', 'surrounding', 'pertaining', 'longitudinal', 'diagnostic', 'psychodynamic', 'fluctuations', 'preserving', 'meaning', 'actions', 'threefold', 'firstly', 'secondly', 'mutual', 'sufficiently', 'explicit', 'uncovering', 'americans', 'begins', 'articulates', 'depressive', 'precision', 'descriptions', 'interpersonal', 'teamwork', 'manufacturing', 'doubt', 'unrealized', 'millions', 'tetraplegia', 'informed', 'decisions', 'choices', 'commercially', 'prentke', 'romich', 'cid', '92', 'preexisting', '76', 'qa', 'gavage', 'sucked', 'nipple', 'suckometer', 'qualified', 'cbcbcb', 'bcbc', 'tao', 'costing', '500', 'compute', 'interobserver', 'knife', 'leather', 'narration', 'exclusively', 'canadian', 'caliber', '32', 'visualization', 'differentiated', 'alertness', '4th', 'stability', 'shirt', 'emergency', 'spreading', 'soft', 'rooted', 'semester', 'rating', 'explore', 'restructure', 'younger', 'recreational', 'dearly', 'disfluency', 'develops', 'permanent', 'impediment', 'woodford', 'predictive', 'great', 'contrasted', 'collegiate', 'athletic', 'tournament', 'missed', 'shots', 'emphasizing', 'ab', 'nonengagement', 'psycological', 'hemisphere', 'hemineglect', 'pretest', 'household', 'videorecorded', 'pencil', 'national', 'shooting', 'albert', 'filmed', 'film', 'stopped', 'dialogue', 'interpret', 'assumptions', 'relaxation', 'poker', 'cognition', 'emergent', 'pool', 'engendered', 'equivalent', 'arts', 'neurological', 'opinions', '1968', '1977', 'gambler', 'perceptions', 'gamblers', 'willing', 'jive', 'attained', 'inventory', 'revised', 'paralysis', 'obtaining', 'english', 'c5', 'conform', 'technical', 'proficiency', 'conditional', 'crossmodal', 'cornerstone', 'packages', 'successively', 'clips', 'nonengaged', 'pairs', '1970s', 'ensuing', 'perspectives', 'contains', 'conducive', 'considerably', 'concern', 'especially', 'instructed', 'monte', 'carlo', 'achieve', 'atlantoaxial', 'fouls', 'possession', 'outscored', 'opponents', 'calling', 'outs', 'opponent', 'exhibiting', 'vertebrae', '1999', 'resistance', 'stating', 'say', 'reporting', 'space', 'referring', 'hypotheses', 'inception', 'emphasis', 'paraprofessional', 'infants', 'mainstreamed', 'diaper', 'mains', 'null', 'reliability', 'conjunction', 'keyboards', 'liaison', 'proportional', 'drive', 'controller', 'dos', 'semiautomated', 'survey', 'developers', 'laptop', 'nt', 'configurations', 'falsely', 'went', 'compares', 'mpeak', 'bar', 'code', 'scanners', 'ibm', 'compatible', '98', 'carryover', 'accrued', 'consecutively', 'retrospectively', 'records', 'countries', 'note', 'strength', 'therapists', 'interact', 'facilitates', 'volunteered', 'utilization', 'abductors', 'refusing', 'predictions', 'direction', 'mathematically', 'turns', 'responsive', 'facilitator', '62', 'smoking', 'dependency', 'principal', 'postures', 'guarding', 'salivary', 'cotinine', 'carbon', 'monoxide', 'corrections', 'distinctive', 'looking', 'began', 'favorably', 'resolve', 'conflicts', 'clearest', 'finding', 'capacity', 'finally', 'addressed', 'ulcer', 'painful', 'spasm', 'antalgic', 'judgment', 'competence', 'employing', 'prominent', 'stacking', 'deck', 'extrapyramidal', 'unstable', 'invitations', 'strangers', 'confederates', 'concealed', 'acted', 'authority', 'actor', 'lowest', 'lure', 'generalizability', 'respect', 'seeks', 'uncertainty', 'signs', 'cue', 'textual', 'seductive', 'continues', 'begin', 'sparse', 'explores', 'bringing', 'maximize', 'vocalization', 'older', 'audiograms', 'frequencies', 'speak', 'coding', 'fourteen', 'childrens', 'triads', 'com', 'pared', 'resemble', 'seemingly', 'guarantee', 'france', 'germany', 'spain', 'generization', 'discriminative', 'speed', 'occluded', 'racquet', 'depth', 'width', 'ears', 'german', 'asymmetry', 'restaurant', 'occured', 'uses', 'behave', 'hyper', 'employ', 'intraoperatively', 'concentrations', 'greatly', 'motivated', 'switch', 'conservation', 'multichannel', 'french', 'hospital', 'tertiary', 'populations', 'microcurrent', 'electromedical', 'classified', 'stimulator', 'inactive', 'titrated', 'fidgeting', 'distractibility', 'magnitude', 'stresses', 'identifies', 'variant', 'instances', 'counseling', 'unanalyzed', 'unless', 'essential', 'impractical', 'abacada', 'ascii', 'disk', 'prohibitively', 'expensive', 'disliked', 'fines', 'complaining', 'inexpensive', 'sustainable', 'counselors', 'possibility', 'surveillance', 'dispensed', 'deter', 'obstacle', 'abacaca', 'exhibit', 'preintervention', 'hyperactive', 'deficithyperactivity', 'intervened', 'inattention', 'corresponded', 'actual', 'reversed', 'displays', 'band', 'biobehavioral', 'thermal', 'validates', 'exportable', 'pill', '00', 'beats', 'politely', 'worded', 'notes', 'dispensers', 'failed', 'horizon', 'calculated', 'ambulated', 'randomizes', 'saves', 'instrument', 'arithmetic', 'progression', 'correlated', '1962', 'iterative', 'file', 'clinicians', 'educators', 'interested', 'meningomyelocele', 'calculate', 'easy', 'generates', 'capabilities', 'transformed', 'sinewaves', 'f0', 'vibrator', 'corpus', 'talkers', 'requirements', 'gesture', 'timer', 'issuing', 'screening', 'covariance', 'depend', 'intensively', 'analysed', 'pulses', 'suited', 'tactual', 'flaws', 'explanations', 'provider', 'television', 'signaled', 'enduring', 'developmentally', 'nonacceptance', 'impedes', 'aims', 'scaling', 'shifting', 'glottal', 'unequal', 'attributed', 'favour', 'cues', 'microphone', 'electroglottograph', 'syllable', 'acknowledged', 'pinpointing', 'art', 'facilitating', 'moderating', 'base', 'partial', 'record', 'differentation', 'encourage', 'eliminate', 'complaint', '87', 'headache', 'followups', 'warm', 'nonpharmacological', 'simply', 'tapped', 'bikini', 'alter', 'issued', 'concise', 'exploration', 'robust']</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1617</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>['behavior', 'study', 'treatment', 'design', 'results', 'self', 'children', 'training', 'social', 'effects', 'analysis', 'use', 'used', 'multiple', 'using', 'subject', 'students', 'data', 'single', 'intervention', 'baseline', 'subjects', 'research', 'time', 'performance', 'reinforcement', 'participants', 'behaviors', 'skills', 'instruction', 'generalization', 'disabilities', 'functional', 'computer', 'control', 'stimulus', 'communication', 'procedures', 'showed', 'assessment', 'increased', 'conditions', 'behavioral', 'based', 'hearing', 'autism', 'patients', 'speech', 'effective', 'effect', 'maintained', 'mental', 'indicated', 'evaluated', 'matching', 'teaching', 'condition', 'program', 'evaluation', 'delay', 'retardation', 'case', 'stimuli', 'child', 'sessions', 'visual', 'procedure', 'interactions', 'taught', 'severe', 'injurious', 'sib', 'discussed', 'video', 'problem', 'student', 'group', 'systems', 'response', 'examined', 'modeling', 'sample', 'developmental', 'play', 'technology', 'follow', 'individuals', 'community', 'phase', 'peer', 'conducted', 'activities', 'levels', 'device', 'significant', 'therapy', 'staff', 'following', 'frequency', 'provided', 'method', 'individual', 'did', 'strategies', 'manipulation', 'different', 'aba', 'object', 'instructional', 'presented', 'test', 'rate', 'prompting', 'school', 'stimulation', 'high', 'related', 'participant', 'produced', 'aid', 'applied', 'support', 'measures', 'hand', 'period', 'feedback', '10', 'extinction', 'task', 'interaction', 'classroom', 'experimental', 'settings', 'increase', 'demonstrated', 'setting', 'present', 'studies', 'treatments', 'automatic', 'injury', 'spelling', 'determine', 'reversal', 'years', 'efficacy', 'videotape', 'methods', 'devices', 'maintenance', 'number', 'changes', 'compared', 'practice', 'attention', 'positive', 'preschool', 'game', 'application', 'improved', 'second', 'observed', 'appropriate', 'programming', 'level', 'interventions', 'development', 'clinical', 'responses', 'information', 'change', 'new', 'problems', 'contingencies', 'moderate', 'included', 'acquisition', 'reduced', 'effectiveness', 'evaluate', 'suggest', 'increasing', 'involved', 'output', 'verbal', 'series', 'comparison', 'validity', 'package', 'programmed', 'model', 'young', 'learning', 'year', 'programs', 'words', 'specific', 'tests', 'provide', 'participation', 'reinforcer', 'management', 'future', 'adults', 'investigation', 'trained', 'improvements', 'old', 'flexion', 'analyses', 'cervical', 'direct', 'pressure', 'videotapes', 'persons', 'day', 'experiment', 'tasks', 'computerized', 'accuracy', 'collected', 'alternating', 'disorders', 'function', 'home', 'groups', 'decreased', 'measured', 'preference', 'access', '20', 'videotaped', 'education', 'daily', 'important', 'increases', 'range', 'developed', 'sie', 'benefit', 'implemented', 'report', 'teams', 'mean', 'rates', 'cerebral', 'assessed', 'parent', 'improvement', 'palsy', 'brief', 'patient', 'differences', 'aids', 'aggression', 'peers', 'phases', 'sensory', 'correspondence', 'care', 'compliance', 'assisted', 'probe', 'cooperative', 'text', 'pictures', 'teach', 'implications', 'recognition', 'findings', 'negative', 'contingent', 'auditory', 'significantly', 'employment', 'responding', 'delayed', 'differential', 'approach', 'instructions', 'lower', 'picture', 'motion', 'session', 'employed', 'matched', 'free', 'fading', 'printed', 'indicate', 'criterion', 'target', 'variables', 'movement', 'alternative', 'oral', 'ability', 'greater', 'profound', 'music', 'habit', 'difference', 'long', 'preferred', 'paper', 'aac', 'hair', 'rehabilitation', 'designs', 'voice', 'received', 'reading', 'novel', 'terms', 'outcomes', 'suggested', 'resulted', 'classes', 'displayed', 'described', 'various', 'purpose', 'mouthing', 'leisure', 'errors', 'activity', 'low', 'reduce', 'general', 'health', 'upper', 'word', 'reinforcers', 'choice', 'reports', 'strategy', 'work', 'adult', 'teacher', 'investigated', 'question', 'generalized', 'reinforced', 'letter', 'weeks', 'fluency', 'months', 'parameters', 'physical', 'people', 'impairments', 'letters', 'schedule', 'parents', 'basketball', 'previous', 'goal', 'trials', 'type', 'dynamic', 'complete', 'cognitive', 'influence', 'toys', 'relation', 'current', 'functions', '15', 'total', 'making', 'initial', 'materials', 'addition', 'required', 'participated', 'supported', 'stereotypic', 'inappropriate', 'combined', 'reducing', 'motor', 'team', 'basic', 'component', 'protective', 'form', 'available', 'size', 'completed', 'consisted', 'term', 'efficient', 'techniques', 'models', 'alcohol', 'samples', 'games', 'cases', 'exercise', 'questions', 'introduced', 'food', 'issues', 'members', 'independent', 'potential', 'involving', 'values', 'skill', 'observation', 'limitations', 'review', 'course', 'relations', 'disorder', 'common', 'objects', 'order', 'designed', 'items', 'situations', 'similar', 'efficiency', 'process', 'ratings', 'learned', 'mpa', 'stuttering', 'eye', 'cost', 'identified', 'reduction', 'mentally', 'obtained', 'patterns', 'noncontingent', 'college', 'software', 'completion', 'voca', 'gait', 'minute', 'integration', 'compare', 'male', 'environmental', 'occupational', 'improve', 'validation', 'correct', 'public', 'comprehensive', 'routines', 'variety', 'bone', 'bilateral', 'viewing', 'examine', 'improving', 'adaptive', 'assistive', 'presentation', 'socially', 'praise', 'min', 'larger', 'contact', 'stereotypy', 'language', 'preschoolers', 'delays', 'edited', 'poking', 'useful', 'given', 'biofeedback', 'assess', 'decrease', 'ear', 'better', '25', 'baha', 'air', 'associated', 'chronic', 'augmentative', 'modified', 'objective', 'continued', 'ci', 'need', 'plus', 'mild', 'format', 'statistical', 'equivalence', 'coaching', 'electrical', 'list', 'identity', 'teachers', 'assessments', 'small', 'occurred', 'components', 'including', 'literature', 'services', 'non', 'adherence', 'appeared', 'analyzed', 'conduction', 'therapist', 'traditional', 'week', 'escape', 'trial', 'cochlear', 'shown', 'recommendations', 'frequently', 'content', 'equipment', 'occur', 'class', 'reactions', 'swallow', 'retarded', 'majority', 'preliminary', 'post', 'head', 'reinforcing', 'accurate', 'operant', 'requests', 'family', 'delivery', 'demonstrate', 'criteria', 'conversation', 'tapes', 'passive', 'selection', 'higher', 'times', 'symptoms', 'analysts', 'randomization', 'keyboard', 'neglect', 'walking', 'stroke', 'technique', 'revealed', 'return', 'line', 'studied', 'transfer', 'recorded', 'result', 'naturalistic', 'human', 'performed', 'pulling', 'dissemination', 'role', 'safety', 'maintaining', 'served', 'journal', 'lists', 'develop', 'parking', 'targeted', 'emotional', 'reductions', 'changing', 'researchers', 'percentage', 'screen', 'history', 'enrichment', 'probes', 'serial', 'previously', 'continuous', 'developing', 'microwave', 'living', 'enhance', 'entry', 'help', 'balance', 'emg', 'set', 'selected', '12', '14', 'experiments', 'statistic', 'restraint', 'implant', 'context', 'areas', 'frequent', 'diagnosed', 'affect', 'elderly', 'surgery', 'substantial', 'academic', 'reported', 'variability', 'discussion', 'methodology', 'sizes', 'gains', 'indicating', 'subsequent', 'constant', 'constructed', 'necessary', 'players', 'combination', 'destruction', 'periods', 'request', 'experienced', 'supervisor', '1993', 'natural', 'article', '1994', 'sets', 'determined', 'client', 'pica', 'controlled', 'orthotic', 'shock', 'measurement', 'recruitment', 'rom', 'good', 'month', 'rapid', 'corresponding', 'early', 'pain', 'open', 'standard', 'contrast', 'population', 'gambling', 'sitting', 'lottery', 'having', 'consequences', 'performances', 'women', 'attempts', 'property', 'observational', 'punishment', 'extremity', 'objectives', 'replication', 'mediated', 'intellectual', 'initiations', 'man', 'solution', 'loss', 'graphic', 'met', 'subsequently', 'conclusions', 'tested', 'replicated', 'behaviour', 'posttest', 'impairment', 'handicapped', 'brain', 'relative', 'correctly', 'computers', 'boy', 'consecutive', 'autocorrelation', 'promote', 'age', 'exposure', 'environment', 'marginal', 'pediatric', 'directions', 'produce', 'identify', 'ext', 'communicative', 'removed', 'prompt', 'discrimination', 'center', 'overall', 'dysphagia', 'pediatrics', 'simplified', 'relationship', 'personalized', 'elementary', 'affected', 'investigate', 'prior', 'examination', 'prompted', 'factors', 'blocking', 'lesions', 'reciprocal', 'implementation', 'serve', 'specifically', 'key', 'ankle', 'opportunities', 'outcome', 'muscle', 'regarding', 'scores', 'functioning', 'measure', 'provides', 'body', 'testing', 'splint', 'systematic', 'skinner', 'performing', 'aggressive', 'situation', 'special', '24', 'engaged', 'expressive', 'mode', 'decision', 'events', 'inspection', 'statistics', 'trainees', 'articles', 'survival', 'producing', 'contralateral', 'led', 'success', 'schedules', 'science', 'successful', 'wagering', 'semg', 'end', 'degree', 'importance', 'tennis', 'poor', 'reviews', 'indicates', 'comparing', 'supervisee', 'intentions', 'concentration', 'spinal', 'characteristics', 'reflex', 'applications', 'overt', 'influenced', 'positively', 'remained', 'parental', 'linguistic', 'structures', 'interface', 'educational', 'ambulation', 'orthoses', 'exemplars', 'writing', 'point', 'caregiver', 'imposed', 'postfeedback', 'variable', 'therapeutic', 'swallowing', 'pilot', 'regulation', 'appointment', 'trends', 'adolescents', 'added', 'treated', 'zero', 'power', 'evidence', 'viewed', 'varied', 'guidelines', 'sign', 'illegal', 'large', 'repeated', 'default', 'modification', 'specialists', 'grade', '30', 'supervision', 'needed', 'providing', 'woman', 'systematically', 'consonant', 'identification', 'implantation', 'basis', 'simulation', 'involvement', 'naming', 'little', 'researcher', 'additional', 'person', 'market', 'orthographic', 'consistent', 'acquired', 'extended', 'types', 'gradually', 'message', 'synthetic', 'contingency', 'myelomeningocele', 'observations', 'descriptive', 'sperm', 'conclusion', 'recently', 'make', 'boys', 'consultation', 'nonverbal', 'medication', 'speechreading', 'wheelchair', 'trend', 'footwear', 'vi', 'absence', 'families', 'removing', 'withdrawal', 'determining', 'speaking', 'aimed', 'associative', 'dissociative', '40', 'written', 'examples', 'major', 'consistently', 'relevant', 'demand', 'demands', 'presentations', 'amplification', 'impact', 'requiring', 'court', 'returns', 'flying', 'intensive', 'anxiety', 'graphs', 'checklist', 'nutritive', 'best', 'sucking', 'infant', 'days', 'needs', 'clients', 'difficulty', 'men', 'multielement', 'sleeves', 'awareness', 'mu', 'tsd', 'toy', 'oven', 'nature', 'habits', 'keeping', 'appointments', 'radical', 'behaviorism', 'distinct', 'suggests', 'fear', 'ncr', 'turn', 'aged', 'touch', 'aberrant', 'pronation', 'recordings', 'main', 'normal', 'muscles', 'fit', 'scanning', 'normative', 'score', 'cooking', 'standing', 'intradiscal', 'resolution', 'implanted', 'nucleus', 'action', 'store', 'asked', 'fraction', 'state', 'ask', 'rewards', 'paired', 'repertoires', '26', 'requesting', 'feeding', 'value', 'successfully', 'technological', 'inclusion', 'remaining', 'meeting', 'production', 'difficult', 'introduction', 'restraints', 'interactive', 'active', 'greatest', 'suggesting', '22', 'preoperative', 'vs', 'exposed', 'way', 'complex', 'disability', 'compound', 'ranging', 'resulting', 'concepts', 'chin', 'means', 'keller', 'intermittent', 'drinks', 'conduct', 'processes', 'theory', 'technologies', 'nro', 'energy', 'argo', 'occurrence', 'barriers', 'deficits', 'skin', 'job', 'grinding', 'adapted', 'concurrent', 'nicotine', 'independence', 'controlling', 'item', 'concluded', 'evident', 'concerning', 'real', 'furthermore', 'hands', 'selecting', 'spanish', 'observers', 'recent', 'ha', 'accounted', 'followed', 'address', 'indirect', 'relevance', 'select', 'cc', 'critical', '1982', 'productivity', 'solving', 'throw', 'microswitch', 'exhibited', 'machine', 'ventricular', 'step', 'collection', 'immediate', 'playing', 'telephone', 'medical', 'life', 'disc', 'measurements', 'homes', 'schools', 'interval', 'increasingly', 'psychology', 'female', 'significance', 'initially', 'arm', 'restriction', 'videodisc', 'leukoplakia', 'hairy', 'normally', 'topical', 'short', 'favorable', 'tool', 'satisfaction', 'acoustic', 'published', 'mediating', 'readily', 'consisting', 'conversational', 'incorporated', 'delivered', 'grocery', 'housing', 'focus', 'competitive', 'hour', 'hypothesized', 'topographies', 'interrupted', 'topography', 'version', 'pnd', 'seven', 'identifying', 'meetings', 'classrooms', 'maximum', 'exercises', 'flash', 'final', 'require', 'construction', 'spent', 'competing', 'graphed', 'points', 'consider', 'prompts', 'initiation', 'average', 'disease', 'ad', 'fitting', 'guide', 'directly', 'regular', 'member', 'blind', 'independently', 'promising', 'symmetry', 'stance', 'decimal', 'ratios', 'representations', 'positions', 'lying', 'antecedent', 'weekly', 'tse', 'jones', 'payne', 'changed', 'promoting', 'sufficient', 'later', 'hypothesis', 'quality', 'hours', 'aphasic', 'benefits', 'questionnaire', 'considered', 'lack', 'stapedius', 'recruit', 'versus', 'facilitators', 'scenes', 'implants', 'movements', 'original', 'numbers', 'clinics', 'sentence', 'analytic', 'collecting', 'minimal', 'directed', 'priced', 'achieved', 'driving', 'contribute', 'hitting', '13', 'analyze', 'background', 'adhd', 'mothers', 'internet', 'presence', 'sight', 'perform', 'pacing', 'noted', 'duration', '3rd', 'involve', 'allowed', 'gottman', 'half', 'examines', 'particular', 'automatically', 'outpatient', 'scheduled', 'remote', 'near', 'ac', 'aided', 'undesirable', 'instructing', 'manipulated', 'screaming', 'poorer', 'db', 'mixed', 'interdisciplinary', 'possible', 'generate', 'phrases', 'slow', 'understanding', 'hemiplegia', 'threshold', 'participating', 'communities', 'microcomputers', 'microcomputer', 'momentum', 'preceding', 'psychotherapy', 'weights', 'wrist', 'experience', 'anchored', 'pure', 'residual', 'concurrently', 'abuse', 'jaba', 'amplitude', 'odor', 'headmaster', 'mouthstick', 'congenital', 'thresholds', 'commonly', 'symbols', 'adjustment', 'capsules', 'manipulating', 'regimens', 'imagery', 'adjustments', 'retrieval', 'match', 'disruptive', 'recall', 'virtual', 'examining', 'decreasing', 'prescribed', '18', 'assist', 'typically', 'selective', 'effort', 'spell', 'decreases', 'clinically', 'purposes', 'belt', 'signal', 'intersection', 'paradigm', 'sequence', 'assigned', 'reached', 'transcutaneous', 'highly', 'regard', 'nerve', 'engagement', 'discriminated', 'separate', 'simultaneously', 'collateral', 'practical', 'coping', 'shot', 'density', 'linkage', 'channel', 'called', 'wore', 'communicate', 'prevented', 'ages', 'chat', 'wide', 'athlete', 'extension', 'impulsivity', '2nd', 'evaluating', 'desirable', 'routine', 'arbitrary', 'effectively', 'ensure', 'difficulties', 'a2', 'spastic', 'errorless', 'established', 'scientists', 'account', 'orthosis', 'empirical', 'rationale', 'twice', 'continuum', 'mouse', 'prices', 'aluminum', 'engage', 'likely', 'microsoft', 'ergometer', 'a1', 'foul', 'adversity', '90', 'girl', 'che', 'pervasive', 'dysphonia', 'fold', 'meyers', '1989', 'a3', 'atresia', 'conductive', 'wear', 'framework', 'tactile', 'digital', 'authors', 'precane', 'cane', 'mobility', 'creating', 'expertise', 'kept', 'untrained', 'author', 'past', 'represent', 'contributions', 'ethical', 'engaging', 'markedly', 'comprehension', 'analyzing', 'wpm', 'impaired', 'limit', 'deafened', 'postlinguistically', 'tone', 'played', 'rigid', 'limited', 'bahas', 'kris', 'lag', 'imaging', 'taking', 'challenges', 'pyramid', 'employees', 'expert', 'breast', 'showing', 'noise', 'efforts', 's1', 'interactional', 's2', 'maladaptive', 'supplements', 'describes', 'rules', 'clear', 'journals', 'place', 'traumatic', 'oxygen', 'plantar', 'insert', 'downward', 'responded', 'encodings', 'simple', 'facilitative', 'classmates', 'physically', 'vibrotactile', 'noncompliance', 'monitored', 'manipulations', 'probability', 'water', 'discuss', 'area', 'quantitative', 'highest', 'foot', 'guidance', 'career', 'reserved', 'surface', 'strong', 'mouth', 'comprised', 'nijmegen', 'prospective', 'females', 'intermediate', 'anticipation', 'vertical', 'profoundly', 'respectively', 'electromyography', 'spaces', 'volatile', 'perception', 'recommended', 'advantages', 'segments', 'spine', 'fix', 'cord', 'layouts', 'qwerty', 'layout', 'promise', 'ss', 'procedural', 'table', 'occurs', '95', 'comparisons', 'relatively', 'does', 'poorly', 'smaller', 'excel', 'keystroke', 'sexual', 'achieving', 'minutes', 'board', 'alpha', 'underwear', 'syndrome', 'scored', 'vsm', 'mechanical', 'represents', 'experimenter', 'mid', 'judges', 'negotiating', 'criticism', 'accepting', 'referenced', 'clinician', 'aphasia', '50', 'shift', 'view', '05', 'persisted', 'external', 'pizza', 'recruited', 'challenging', 'relationships', 'draws', '45', 'vocas', 'ball', 'apparent', 'room', 'inclusive', 'testicular', 'detection', 'idiosyncratic', 'organizational', 'steps', 'abnormality', 'formula', 'chained', 'yield', 'overcome', 'contributed', 'widely', 'structured', 'holland', 'correlates', 'confirmed', 'simulated', 'resin', 'podophyllum', 'goals', 'computing', 'hiv', 'earlier', 'summary', 'stops', 'males', 'defined', 'financial', 'conclude', 'stock', 'modest', 'regardless', 'create', 'percent', 'volleyball', 'accountable', 'randomized', 'nachemson', 'parts', 'handicaps', 'assessing', 'advanced', 'alzheimer', 'able', 'stutter', 'substantially', 'walk', 'practices', 'societal', 'continuing', 'dimensions', 'parallel', 'powerful', 'quiet', 'reminder', 'verbalizations', 'serves', 'perceived', 'medium', 'enhancement', 'innovative', 'fixed', 'battering', 'finger', 'consequent', 'contribution', 'lip', 'avoidance', 'flexed', 'weight', 'reality', 'answer', 'card', 'vr', 'detect', 'presents', 'alternated', 'ovens', 'abab', 'fred', 'arrow', 'schooling', 'operating', 'learn', 'entire', 'individualized', 'valid', 'face', 'dependence', 'virtually', 'recognized', 'rarely', 'offered', 'names', 'wrote', 'identical', 'nearly', 'supplemental', 'american', '1961', 'hr', 'methodologies', 'monitoring', 'designing', 'withdrawn', 'partner', 'psychological', 'false', 'sources', 'demonstrating', 'atd', 'restricted', 'competition', 'pre', '73', 'gap', 'chose', 'supplement', 'service', 'collaboration', 'synthesized', 'substitutability', 'user', 'cable', 'efficacious', 'structure', 'partners', 'faster', 'travel', 'discusses', 'working', 'edematous', 'vocational', 'proposed', 'flaccid', 'paraplegic', 'administration', 'aspects', 'consumption', 'formats', 'casting', 'continue', 'multicomponent', 'durable', 'occurring', 'equal', 'absent', 'yielded', 'dropped', 'establish', 'medicine', 'investigators', 'stopping', 'undergraduate', 'targeting', 'carried', 'utility', 'allow', 'problematic', 'gravity', 'retraining', 'despite', 'percentages', 'drink', 'modes', 'manual', 'attempted', 'vowel', 'vocal', 'spoken', 'display', 'initiated', 'depicting', 'participate', 'forms', 'collaborative', 'cai', 'occasions', 'evidenced', 'oneself', 'math', 'university', 'viable', 'allison', 'exemplary', 'gorman', 'qualitative', 'variations', 'extensive', 'mands', 'laboratory', 'commands', 'fundamental', 'achievement', 'capsule', 'curriculum', 'fo', 'illness', 'correction', 'determination', 'provision', 'replications', 'supply', 'anesthetic', 'semen', 'motile', 'crutches', 'walker', 'dexterity', 'migraine', '37', 'propelled', 'visuomotor', 'fleshler', 'hoffman', 'equation', 'listening', '23', 'replace', 'op', 'cacg', 'teeth', 'scratching', 'announced', 'dispenser', 'disabled', 'perspective', 'diabetes', 'deficit', 'perceive', 'anesthetics', 'ordering', 'counter', 'isoflurane', 'intraoperative', 'multiply', 'tens', 'halothane', 'esrt', 'esrts', 'netherlands', 'enhancing', 'peak', 'breakdown', 'hyperactivity', 'modality', 'scientist', 'practitioner', 'warranted', 'remains', 'pressures', 'preventing', 'fluent', 'ranges', 'schizophrenic', 'applicable', 'nineteen', 'native', 'array', 'arrangement', 'predict', 'bagged', 'lunch', 'balanced', 'naturally', 'additionally', 'administered', 'certain', 'severity', 'shoes', 'depicted', 'sst', 'roles', 'tools', 'sites', 'athetoid', 'local', 'aphasiology', 'cigarettes', 'smoked', 'arima', 'rehearsed', 'disordered', 'caused', 'actors', 'keystrokes', 'semc', 'typing', 'summarized', 'windows', 'macos', 'started', 'publication', 'detailed', 'advances', 'digit', 'postoperative', 'handheld', 'sam', 'dictated', 'paraspinals', 'sternocleidomastoid', 'degrees', 'recruits', 'configuration', 'dyads', 'briskly', 'deviation', 'sequentially', '79', 'unfavorable', 'differentiation', 'copyright', 'john', 'wiley', 'diapering', 'severely', 'caregiving', 'pathological', 'sons', '1990', 'surveyed', 'erroneous', 'candidacy', 'incidence', 'postimplant', 'labeling', 'functioned', 'hazards', 'accident', 'prevention', 'european', 'graph', 'suitable', '97', 'features', 'mastery', 'turnovers', 'adversities', 'subjective', 'relearning', 'watched', 'posttreatment', 'restructuring', 'remediation', 'intention', 'nondisabled', 'sociopolitical', 'ideologies', 'evolution', 'culture', 'hierarchies', 'helpfulness', 'dyad', 'sentences', 'discontinued', 'connected', 'personal', 'agreement', 'stable', 'preterm', '85', 'respective', 'nonsignificant', 'confounds', 'thirty', 'plant', '1986', 'marked', 'rated', 'depression', 'bidirectional', 'causal', 'rare', 'untreated', 'nonvocalizing', 'laryngeal', 'instead', 'fits', 'aerodynamic', '51', 'therblig', 'photocopier', 'folding', 'mini', '39', 'hl', 'milk', '57', 'ii', 'appears', 'premature', 'maternal', 'arising', 'baselines', 'existence', 'fct', 'pursue', 'price', 'grown', 'documents', 'realities', 'providers', 'ignoring', 'implement', 'lesser', 'reviewing', 'sedation', 'inhibition', 'prescription', 'integrated', 'unfortunately', 'pediatricians', 'experts', 'resonance', 'diagnosis', '44', '64', 'closely', 'deteriorate', '60', 'necessity', '1998', 'symmetrical', 'fitted', 'pta', 'khz', 'mother', 'audiometric', 'citation', 'citations', 'stimulating', 'overview', 'comparative', 'circulation', 'scientific', 'mailed', 'nontraining', 'environments', '19', 'magnetic', 'generalize', 'conceptual', 'combinations', 'cancellations', 'educable', 'advance', 'classification', 'read', 'preceded', 'treat', 'iwata', 'dorsey', 'pattern', 'rudimentary', 'express', 'acceptable', 'adolescent', 'march', 'adequate', 'pulled', 'augmenting', 'accomplished', 'legacy', 'nonspeaking', 'clinic', 'conversations', 'biting', 'nail', 'rhetoric', 'philosophy', 'discrepancy', 'supporting', 'functionally', 'particularly', 'stored', 'coaches', 'preservice', 'disciplines', 'consumer', 'gathered', 'edema', '53', '63', 'richman', 'shifts', 'drill', 'thought', 'augment', 'perfect', 'prove', 'autocorrelated', 'youths', 'search', 'matrix', 'organized', 'held', 'randomly', 'standardized', 'extent', 'lead', 'reliance', 'parameter', '11', '000', 'repeat', 'practitioners', 'blank', 'accompanied', 'investigator', 'random', 'assignment', 'proportion', 'drank', 'specification', 'wish', 'example', 'dissatisfaction', 'hemiparetic', 'cent', 'frame', 'incorrect', 'involves', 'sides', 'explicate', 'distribution', 'moved', 'participatory', 'slifer', 'bauman', 'purchasing', 'ratd', 'modify', 'chairperson', 'strengths', 'theoretical', 'counterbalanced', 'tangible', 'consequence', 'partially', 'regression', 'generally', 'breath', 'alert', 'existing', 'irrational', 'law', 'shows', 'determinants', 'bac', 'oropharyngeal', 'focused', 'physiology', 'investing', 'topics', 'themes', 'perseverated', 'incorporating', 'girls', 'improves', 'obsessions', 'visually', 'guided', 'shapes', 'courses', 'digits', 'investigations', 'immediately', 'acceptance', 'systemic', 'capsi', 'proctors', 'investment', 'dramatic', 'build', 'intervertebral', 'according', 'ceased', 'unchanged', 'planning', 'factor', 'volunteer', 'sports', 'vivo', 'fluently', 'seen', 'adl', 'revisited', 'estimating', 'permit', 'restrictive', 'straight', 'reference', 'elsevier', 'mechanisms', 'broad', 'loading', 'knowledge', 'judged', 'source', 'attempt', 'private', 'recreation', 'goggles', 'cancer', 'disturbance', 'unable', '70', 'kg', 'states', 'million', 'left', 'splinting', 'forced', 'prefer', 'wearing', 'right', 'unit', 'fine', 'fell', 'progress', 'accountability', 'lifting', 'approximately', 'maintain', 'ail', 'ratio', 'pictorial', 'fractions', 'emergence', 'represented', 'scale', 'lotteries', 'aversive', 'arizona', 'modifications', 'counterpart', 'decimals', 'properties', 'usually', 'oregon', 'frames', 'blanks', 'answers', 'programmatic', 'repertoire', 'preparing', 'sustained', 'meals', 'aspect', 'gross', 'principles', 'motivation', 'resting', 'winning', 'rehearsal', 'gym', 'predominant', 'stimulatory', 'documentation', 'building', 'receiving', 'stick', '46', 'exception', 'forward', 'position', 'fact', 'domestic', 'violence', 'residents', 'shr', '17', 'externally', 'palatal', 'prosthesis', 'contexts', 'operated', 'lasted', 'appliances', 'prepared', 'slightly', 'cabas', 'encouraging', 'vision', 'prerecorded', 'rest', 'vocabulary', 'story', 'receive', 'covert', 'remove', 'autocorrelations', 'clgs', 'intended', '1991', 'exist', 'physiotherapy', 'autoreg', 'amt', 'debilitating', 'status', 'tolerance', 'predicted', 'ineffective', 'evaluates', 'currently', 'optimal', 'crosbie', 'taken', 'event', 'failure', 'calendar', 'site', 'primary', 'flight', 'narratives', 'dose', 'dependent', 'declined', 'generality', 'assistant', 'corrected', 'editing', 'window', 'enlarged', 'al', 'ducharme', 'nervous', 'bored', 'caregivers', '1996', 'pointing', 'error', 'b2', 'matches', 'interpretation', 'personnel', 'undifferentiated', 'suppression', 'sampling', 'contextual', 'participative', 'deliverers', 'locations', 'sec', 'intervals', 'assistance', 'adverse', 'deglutition', 'audio', 'pulse', 'ma', 'foods', 'beverages', 'appendix', 'inherent', 'computation', 'sidman', 'receptive', 'experiences', 'unprompted', 'experimenters', 'formation', 'acquire', 'expansion', 'appropriately', 'inverse', 'instructors', 'referred', '1992', 'skilled', 'cards', 'material', 'destroyed', 'ones', 'bivalved', 'shortened', 'continuously', 'formed', 'chain', 'fewer', 'snack', 'regularly', 'enhanced', 'interpreting', 'unknown', 'dramatically', 'derived', 'supplemented', 'compete', '100', 'individually', 'season', 'treating', 'applying', 'exchange', 'servers', 'commentary', 'promotion', 'options', 'world', 'tbi', 'force', 'dimensional', 'camera', 'breaking', 'tapping', 'plastic', 'facilitated', 'briefly', 'reviewed', 'association', 'probably', 'unmatched', 'pick', 'blocked', 'rowing', 'addresses', 'workout', 'varsity', 'adaptations', 'primarily', 'behaviours', 'amounts', 'implementing', 'encountering', 'far', 'utilized', 'varying', 'preschools', 'reciprocating', 't12', 'internal', 'physiological', 'prevent', 'length', 't4', 'tm', 'gastrocnemius', 'feedforward', 'issue', 'matter', 'complicated', 'sequential', 'questioned', '27', 'eliminating', 'clusters', 'respond', 'rights', 'reach', 'trainer', 'illustrate', 'conducting', 'construct', 'ed', 'elicited', 'compliant', 'risks', 'removal', 'concept', 'presenting', 'encountered', 'documented', 'substitutable', 'project', 'description', 'methodological', 'considerations', 'field', 'measuring', 'index', 'photographic', 'fault', 'respite', 'impulsive', 'fourth', 'yoked', 'briefs', 'loose', 'superior', 'regimen', 'analogue', 'overfitting', 'statistically', 'tight', 'produces', 'expense']</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2346</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>21306</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3963</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>207</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.376230128690386</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12.03813602890815</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7.599483873444695</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>79.0457710603057</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1990s</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>['children', 'study', 'design', 'behavior', 'treatment', 'results', 'video', 'participants', 'training', 'effects', 'used', 'intervention', 'autism', 'using', 'students', 'multiple', 'use', 'baseline', 'based', 'self', 'analysis', 'skills', 'research', 'single', 'reinforcement', 'speech', 'social', 'modeling', 'computer', 'communication', 'functional', 'data', 'subject', 'disabilities', 'teaching', 'instruction', 'performance', 'effective', 'program', 'response', 'effectiveness', 'feedback', 'therapy', 'assessment', 'time', 'learning', 'showed', 'behaviors', 'generalization', 'behavioral', 'increased', 'play', 'subjects', 'language', 'child', 'conditions', 'maintained', 'discussed', 'methods', 'procedures', 'following', 'visual', 'condition', 'case', 'phase', 'participant', 'control', 'support', 'group', 'studies', 'responses', 'evaluate', 'staff', 'words', 'task', 'stimulus', 'stimuli', 'technology', 'word', 'aac', 'test', 'levels', 'evaluated', 'indicated', 'purpose', 'individuals', 'practice', 'method', 'attention', 'verbal', 'interventions', 'developmental', 'tasks', 'effect', 'experimental', 'increase', 'problem', 'examined', 'procedure', 'school', 'adults', 'stereotypy', 'measures', 'setting', 'high', 'clinical', 'strategies', 'treatments', 'rate', 'evidence', 'patients', '10', 'student', 'strategy', 'device', 'classroom', 'present', 'automatic', 'outcomes', 'compared', 'significant', 'vocal', 'implications', 'management', 'findings', 'settings', 'reading', 'teach', 'acquisition', 'items', 'parents', 'follow', 'production', 'demonstrated', 'disorders', 'pain', 'generalized', 'sessions', 'aphasia', 'improve', 'teacher', 'home', 'frequency', 'maintenance', 'received', 'peer', 'development', 'aba', 'presented', 'number', 'conducted', 'preferred', 'efficacy', 'positive', 'young', 'problems', 'matching', 'suggest', 'provided', 'assessed', 'analyses', 'target', 'percentage', 'hearing', 'approach', 'review', 'food', 'participated', 'probe', 'stuttering', 'noncontingent', 'activity', 'preference', 'phases', 'produced', 'different', 'symbol', 'activities', 'future', 'specific', 'mental', 'schedules', 'novel', 'years', 'improved', 'prompting', 'accuracy', 'low', 'daily', 'moderate', 'paper', 'software', 'correct', 'implemented', 'intellectual', 'rehabilitation', 'stimulation', 'provide', 'associated', 'determine', 'model', 'injury', 'increasing', 'interaction', 'designed', 'safety', 'did', 'new', 'reinforcer', 'related', 'disorder', 'improvements', 'week', 'taught', 'instructional', 'current', 'recognition', 'hand', 'examine', 'level', 'higher', 'access', 'addition', 'individual', 'skill', 'severe', 'applied', 'picture', 'primary', 'alternative', 'included', 'schedule', 'physical', 'measured', 'delay', 'process', 'improvement', 'information', 'reduce', 'relative', 'objective', 'assess', 'basic', 'pecs', 'responding', 'terms', 'consisted', 'systems', 'communicative', 'community', 'direct', 'auditory', 'reversal', 'game', 'care', 'grocery', 'evaluation', 'greater', 'reported', 'adhd', 'alternating', 'suggested', 'outcome', 'effort', 'abstinence', 'stroke', 'conclusions', 'persons', 'natural', 'trial', 'function', 'year', 'compare', 'sets', 'devices', 'relations', 'application', 'impact', 'delivery', 'variables', 'cognitive', 'independent', 'quality', 'ability', 'exchange', 'second', 'age', 'improving', 'written', 'processing', 'trained', 'probes', 'smoking', 'work', 'games', 'important', 'investigated', 'appropriate', 'controlled', 'motor', 'weeks', 'retardation', 'preschool', 'duration', 'reduced', 'package', 'brief', 'including', 'decreased', 'observed', 'changes', 'interactions', 'teachers', 'environment', 'investigate', 'sample', 'months', 'monitoring', 'term', 'comprehension', 'exhibited', 'investigation', 'article', 'observation', 'additional', 'indicate', 'session', 'gambling', 'long', 'choice', 'criteria', 'significantly', 'exercise', 'education', 'experiment', 'selected', 'background', 'gains', 'identified', 'focused', 'completed', 'programming', 'matched', 'old', 'adult', 'employed', 'contingent', 'stories', 'chronic', 'discrimination', 'testing', 'asd', 'developed', 'lower', 'variable', 'available', 'models', 'adolescents', 'conclusion', 'combination', 'replicated', 'deficit', 'life', 'parent', 'sensory', 'non', 'techniques', 'point', 'goal', 'challenging', 'assisted', 'computerized', 'automatically', 'occurred', 'min', 'seven', 'internet', 'step', 'post', 'extinction', 'aided', 'pica', 'object', 'free', 'early', 'learned', 'delivered', 'various', 'comparison', 'assessments', 'knowledge', 'hyperactivity', 'interactive', 'peers', 'revealed', 'characteristics', 'vivo', 'field', 'health', 'tool', 'conversational', 'sib', 'injurious', 'increases', 'discussion', 'promote', 'successful', 'psychology', 'followed', 'similar', 'change', 'set', 'completion', 'validity', 'personal', 'literature', 'main', 'correctly', 'programs', 'approaches', 'role', 'previous', 'inappropriate', 'diagnosed', 'graphic', 'preschoolers', 'brain', 'vr', 'meta', 'anxiety', 'able', 'disease', 'head', 'dependent', 'day', 'reduction', 'mean', 'occupational', 'targeted', 'foods', 'designs', 'pre', 'educational', 'traditional', 'withdrawal', 'consequences', 'exposure', 'disruptive', 'math', 'required', 'differential', 'collected', 'systematic', 'directions', 'fixed', 'syndrome', 'contingencies', 'aged', 'recording', 'reinforced', 'family', 'immediate', 'decrease', 'dimensions', 'types', 'demonstrate', 'protocol', 'spoken', 'equivalence', 'potential', 'output', 'events', 'form', 'variability', 'cues', 'reserved', 'symbols', 'resulted', 'periods', 'subsequent', 'videotaped', 'mouthing', 'impairments', 'acquired', 'context', 'aids', 'rights', 'spectrum', 'given', 'delayed', 'seating', 'shown', 'questions', 'type', 'typically', 'need', 'researchers', 'modified', 'public', 'measure', 'varied', 'implementation', 'experience', 'slot', 'compliance', 'scores', 'repeated', 'vsm', 'limited', 'reducing', 'mild', 'highly', 'leisure', 'recorded', 'programmed', 'overall', 'complete', 'means', 'range', 'common', 'versus', 'scale', 'series', 'clinic', 'order', 'fct', 'influence', 'media', 'developing', 'elsevier', 'engagement', 'cases', 'samples', 'laboratory', 'steps', 'patient', 'behaviour', 'oral', 'ratio', 'eating', 'components', 'gait', 'benefits', 'blocking', 'ratings', 'sound', 'hr', 'medication', 'obtained', 'individualized', 'tested', 'therapists', 'academic', 'untrained', 'identify', 'component', 'involving', 'prompts', 'fast', 'preliminary', 'times', 'involved', 'rates', 'little', 'period', 'letter', 'mediated', 'multi', 'wheelchair', 'complex', 'fluency', 'service', 'presentation', 'perspective', 'reinforcers', 'perceived', 'met', 'literacy', 'agreement', 'discrete', 'analyzed', 'criterion', 'relatively', 'methodology', 'contingency', 'promoting', 'suggests', 'item', 'tests', 'ncr', 'punishment', 'useful', 'request', 'movement', 'aims', 'observational', 'general', 'introduced', 'videotape', 'groups', 'instructions', 'virtual', 'operant', 'conversation', 'enhancing', 'therapeutic', 'initiations', 'members', 'blending', 'regarding', 'achieved', 'routines', 'reductions', 'enhance', 'solution', 'special', 'surface', 'typical', 'machine', 'postural', 'practices', 'transfer', 'providing', 'variety', 'plus', 'produce', '30', 'people', 'described', 'impairment', 'standard', 'establishing', 'therapist', 'relevant', 'disability', 'short', 'continuous', 'repair', 'sounds', 'effectively', 'report', 'ineffective', 'sbw', 'randomized', 'intensive', 'movements', 'identification', 'learn', 'signs', 'negative', 'collection', 'prompt', 'initial', 'integration', 'facts', 'contextual', 'toy', 'players', 'assistance', 'phoneme', 'conduct', 'modelling', 'active', 'btds', 'girls', 'relationship', 'initiated', 'phonological', 'initiation', 'concurrent', 'toys', 'cooking', '15', 'categories', 'substantial', 'intervals', 'voucher', 'conventional', 'player', 'mobility', 'focus', 'formula', 'evaluating', 'boys', 'equipment', 'random', 'making', 'varying', 'left', 'progressive', 'taking', 'small', 'planning', 'asperger', 'consistent', 'especially', 'profound', 'requesting', 'fading', 'possible', 'combined', 'combining', 'cycle', 'delays', 'length', 'result', 'conversations', 'format', 'cost', 'requests', 'real', 'month', 'store', 'needed', 'observations', 'absence', 'microsoft', 'cigarette', 'example', 'implant', 'functions', 'decreases', 'middle', 'having', 'board', 'awareness', 'participation', 'aspects', 'appeared', 'total', 'difficulty', 'aid', 'conducting', 'augmentative', 'female', 'vouchers', '11', 'factors', 'classes', 'coding', 'experienced', 'statistical', 'empirical', 'rules', 'descriptive', 'large', 'extended', 'sign', 'understanding', 'course', 'inspiratory', 'videotapes', 'helping', 'goals', 'analytic', 'return', 'constant', 'end', 'maintaining', 'benefit', 'pressure', 'impaired', 'provides', 'knee', 'successfully', '16', 'dyads', 'help', 'elementary', 'cai', 'recovery', 'parameters', 'created', 'adaptive', 'secondary', 'proportion', 'patterns', 'law', 'residents', '2007', 'speaking', 'letters', 'loss', 'sucking', 'science', 'structured', 'exposed', 'published', 'voice', 'presence', 'complexity', 'simulated', 'animated', 'simple', 'line', 'drivers', 'tutoring', 'choices', 'recall', 'guided', 'issues', 'despite', 'perform', 'strength', 'electrodes', '40', 'competing', 'medical', 'biofeedback', 'job', 'pairing', 'differences', 'clips', 'living', 'memory', 'manipulation', 'recommendations', 'placebo', 'organizational', 'make', 'authors', 'recordings', 'escape', 'establish', 'served', 'caregiver', 'engaged', 'technique', 'text', 'trials', 'story', 'feasibility', 'arm', 'aim', 'led', 'accurate', 'validation', 'forms', '20', 'deposit', 'theory', 'nicotine', 'needs', 'situations', 'aphasic', 'multiplication', 'excel', 'extension', 'supported', 'size', 'generally', 'immediately', 'efforts', 'discuss', 'statistically', 'nonpreferred', 'mathematics', 'systematically', 'affected', '12', 'robot', 'according', 'precision', 'remained', 'minute', 'seat', 'praise', 'abab', 'existing', 'interval', 'assessing', 'indirect', 'person', 'experiments', 'stutter', 'questionnaire', '2005', 'ft', 'cerebral', 'noise', 'error', 'survey', 'conditional', 'generated', 'specifically', 'switch', 'seatbelt', 'half', 'reward', 'corresponding', 'facial', 'articles', 'posting', 'reports', 'dysarthria', 'book', 'static', 'adapted', 'recent', 'defined', 'phone', 'male', 'finally', 'photographs', 'difficulties', 'allowed', 'mechanical', 'vocabulary', 'solving', 'programme', 'partners', 'better', 'deficits', 'occurrence', 'writing', 'units', 'rapid', 'took', 'empirically', 'status', 'examining', 'grade', 'world', 'selection', 'exercises', 'relationships', 'monitor', 'regular', 'human', 'risk', 'sequences', 'graph', 'examples', 'blind', 'patch', '95', 'reviewed', 'clinically', 'actions', 'commonly', 'behaviours', 'cochlear', 'paired', 'fear', 'stable', 'pictorial', 'aides', 'stability', 'administered', 'ad', 'electronic', 'pictures', 'wiley', 'controls', 'performed', 'vs', 'relation', 'football', 'utility', 'processes', 'scoring', 'success', 'noncompliance', 'days', 'computers', 'embedded', 'frequently', 'producing', 'shows', 'threshold', 'rating', 'college', 'objects', 'efficient', 'dot', 'train', 'larger', 'examination', 'way', 'practical', 'probability', 'multielement', 'reached', 'digital', 'aberrant', 'areas', 'identifying', 'near', 'difference', 'antecedent', 'face', 'stereotypic', 'breath', 'cbvi', 'pilot', 'facilitate', 'tact', 'proposed', 'users', 'continued', 'preferences', 'calling', 'prior', 'dynamic', 'postures', 'shared', 'partial', 'removal', 'explore', 'include', 'lectures', 'operations', 'principles', 'roles', 'respond', 'ages', 'right', 'materials', 'traumatic', 'transdermal', 'concerns', 'material', 'palsy', 'men', 'acceptance', 'drug', 'input', 'university', 'electromyography', 'values', 'penetrating', 'history', 'private', 'progress', 'suggesting', 'primarily', 'electrode', 'run', 'protective', 'independently', '80', 'severity', 'fewer', 'st', 'women', 'boy', 'implement', 'nature', 'heart', 'personalized', 'minutes', 'inclusive', 'normal', 'inspection', 'abilities', 'leg', 'tools', 'upper', '2004', 'perception', '2000', 'scripted', 'reciprocal', 'extent', 'scenarios', 'restraint', 'clear', 'reality', 'directly', 'intraoperative', 'playing', 'environmental', 'initially', 'efficiency', 'sentences', 'dvd', 'longer', 'obtain', 'performances', 'rehearsal', 'muscle', 'event', 'abductor', 'powered', 'clients', 'demands', 'weekly', 'printed', 'spontaneous', 'basketball', 'judges', 'team', 'discipline', 'apraxia', 'degree', 'objectives', 'decoding', 'client', 'hypothesis', 'balance', 'reaching', 'maintain', 'limitations', 'purchasing', 'multimedia', 'rated', 'sons', 'vocalizations', 'john', 'copyright', 'cat', 'shots', 'aggression', 'unilateral', 'simulation', 'combinations', 'web', 'adolescent', 'giving', 'driving', 'mr', 'domestic', 'importance', 'finger', 'fns', 'motion', 'read', 'pass', 'working', 'ssp', 'observer', 'power', 'treating', 'seen', 'twice', 'final', 'coaching', 'deliver', '25', 'prediction', 'grammar', 'centered', 'print', 'naive', 'laryngeal', 'cue', 'theoretical', 'appears', 'sizes', 'imitation', 'portable', 'translucency', 'machines', 'narrative', 'foot', 'sports', 'hospital', 'respectively', 'interobserver', 'addressed', 'require', '100', 'points', 'pairs', 'flying', 'american', 'intensity', 'sight', '13', 'autistic', 'discomfort', 'color', 'pretend', 'displayed', 'interviews', 'ergonomic', 'percentages', 'nerve', 'dbs', 'subsequently', 'environments', 'spinal', 'talk', 'domains', 'trend', 'score', 'acoustic', 'mastery', 'persistent', 'restaurants', 'scored', 'supports', 'iconicity', 'alzheimer', 'immediacy', 'anger', 'orthoses', 'aisle', 'impulsivity', 'acetaminophen', 'utilized', '24', 'develop', 'satisfaction', 'propose', 'discriminations', 'receiving', 'previously', 'functioning', 'describes', 'services', 'independence', 'measurement', 'analysts', 'lg', 'rird', 'extremity', 'weight', 'requirements', 'technical', 'potentially', 'residential', 'braille', 'visually', 'sport', 'showing', 'performing', 'eye', 'necessary', 'telephone', '1998', 'exemplars', 'class', 'hair', 'activation', 'naturalistic', 'pabi', 'double', 'treadmill', 'affective', 'decreasing', 'agent', 'automated', 'majority', 'reporting', 'recently', 'attempt', 'older', 'elements', 'names', 'ear', 'listener', 'equation', 'quantitative', 'office', 'interpretation', 'tactile', 'assigned', 'opportunities', 'consisting', 'selecting', 'spelling', 'facilitated', 'speecheasy', 'longitudinal', 'sdl', 'posttreatment', 'orienting', 'array', 'tm', 'watching', 'demonstrating', 'sustained', 'skinner', 'operants', 'comparisons', 'efficiently', 'frequent', 'lack', 'assistive', 'sufficient', 'view', 'curriculum', 'unit', 'contact', 'significance', 'attempted', 'extend', 'verbalizations', 'cop', 'particular', 'addressing', 'refusal', 'infants', 'fact', 'inclusion', 'content', 'replication', 'select', 'identical', 'raised', 'posture', 'hour', 'drill', 'athletes', 'orthographic', 'enrolled', 'aggressive', 'location', 'blissymbols', 'neglect', 'alignment', 'beginning', 'affect', 'concurrently', 'engage', 'live', 'contexts', 'beneficial', 'describing', 'write', '14', 'chat', 'differed', 'block', 'suggestions', 'plan', 'differentially', 'hip', 'advocacy', 'participating', 'spray', 'traction', 'riding', 'token', 'match', 'pda', 'methodological', 'grip', 'tremor', 'socially', 'mands', 'resulting', 'involvement', 'rett', 'widely', 'implementing', 'momentum', '2002', 'errors', 'tic', 'checklist', 'formulas', 'entailment', 'unfamiliar', 'standardized', 'substantially', 'finding', 'consecutive', 'affecting', 'mathematical', 'quickly', 'reliable', 'participate', 'engaging', 'population', 'fm', 'randomly', 'suppressed', 'soccer', 'hierarchical', 'linear', 'generation', 'viewed', 'introduction', 'derived', 'usage', 'cueing', 'vcs', 'wide', 'minimal', 'redirection', 'lateral', 'focuses', 'developmentally', 'unprompted', 'medium', 'reinforcing', 'past', 'difficult', 'occurring', 'generating', '19', 'features', 'entire', 'graphs', 'creating', 'procedural', 'earn', 'question', 'repetition', 'longstanding', 'parkinson', 'requested', 'indicates', 'im', 'contribute', 'technologies', 'consistently', 'schools', 'comparing', 'conditioning', 'best', 'professionals', 'smart', 'continue', 'position', 'afos', 'employing', 'hdt', 'applications', 'enhancement', 'claustrophobic', 'slightly', 'stores', 'tense', 'represents', 'baselines', 'mobile', 'pocket', 'pc', 'concepts', 'added', '22', 'resource', 'trends', 'growing', 'topic', 'interview', 'twirling', 'habit', 'attained', 'verb', 'established', 'accompanied', 'stress', 'pencil', 'brainstem', 'includes', 'understand', 'considered', 'populations', 'communicate', 'disruptions', 'pel', 'safe', 'bst', 'properties', 'interviewing', 'open', 'opioid', 'pitch', 'selectivity', 'critical', 'area', 'involves', '1985', 'allows', 'feeding', 'airway', 'treated', 'partner', 'win', 'acute', 'grammatical', 'online', 'isolation', 'efficacious', 'positions', 'cord', 'fourth', 'families', 'a1', 'a2', 'woman', 'joint', 'exploring', 'placed', 'pd', 'phobia', 'expressive', 'practised', 'physiotherapy', 'manipulated', '18', 'girl', 'skin', 'appear', 'clinician', 'vehicles', 'spouse', 'measurements', 'psychological', 'remaining', 'failed', 'dti', 'discriminative', 'learners', 'integrity', 'explored', 'morning', 'happiness', 'computerised', 'customer', 'reliability', 'sought', 'allocation', 'providers', 'satiation', 'asthma', 'cover', 'preservation', 'module', 'challenges', 'withdrawn', 'pwds', 'facilitating', 'modalities', '90', 'create', 'blended', 'explicit', 'removed', 'detection', 'practitioners', 'volitional', 'functionally', 'cfs', 'gamblers', 'explanations', 'specified', 'multicomponent', 'monitored', 'influenced', 'gained', 'constructed', 'combinatorial', 'speed', 'relational', 'hypothesized', 'displacement', 'attend', 'dementia', 'currently', 'explain', 'writers', 'journal', 'fashion', 'scripts', 'manual', 'user', 'carried', 'handwriting', 'unable', 'poor', 'telemedicine', 'iowa', 'scanning', 'uvn', 'ihp', 'payback', 'educators', 'allow', 'pattern', 'receive', 'music', 'rewards', 'nfc', 'meaningful', 'photograph', 'statements', 'collecting', 'fr', 'inventory', '21', 'pm', 'ill', 'hands', 'combine', 'dtt', 'classrooms', 'bilateral', 'limb', 'conjunction', 'stimulant', 'sportsmanlike', 'interruption', 'rumination', 'reinforce', 'concomitant', 'simulations', 'base', 'spent', 'sentence', '61', 'achieve', 'plane', 'outpatient', 'segments', 'demonstrates', 'naming', 'progressively', 'ranged', 'mainstream', 'body', 'factored', 'exploration', 'enabled', 'algorithms', 'deafness', 'listeners', 'sensitivity', 'passing', 'contrast', 'stop', 'ffw', 'lls', 'charcot', 'marie', 'tooth', 'essay', 'toilet', 'intrusive', 'microprocessor', 'prosthetic', 'completing', 'carbon', 'monoxide', 'exploratory', 'tbi', 'parental', 'called', 'furthermore', 'mechanisms', 'studied', 'watched', 'flashcards', 'carr', 'perfect', 'haworth', 'confederate', 'typing', 'modification', 'attentive', 'enhanced', 'dyspraxia', 'room', 'managing', 'network', 'repetitive', 'presentations', 'stuttered', 'syllables', 'supervision', 'cbi', 'additionally', 'place', 'mastered', 'spell', 'balls', 'prelinguistic', 'achievement', 'easily', 'al', 'optimal', 'et', 'prize', 'emotional', 'bug', 'homes', 'scientific', 'conceptual', 'basis', 'actual', 'sie', 'recombinative', 'rps', 'expression', '55', 'lhs', 'address', 'monosyllabic', 'advantages', 'man', 'elicited', 'emerged', 'clinics', 'complied', 'assistant', 'picking', 'augmented', 'utterances', 'fold', 'suspension', 'pathological', 'does', 'occur', 'noted', 'gradual', 'attitudes', 'wearing', 'electrophysiologic', 'apply', 'consideration', 'determined', 'amplification', 'somewhat', 'acceptability', 'vmc', 'utilizing', 'easy', 'promising', 'predicted', 'lasted', 'investigating', 'external', 'meal', 'spoon', 'driven', 'look', 'foam', 'neuromotor', 'indicators', 'commitment', 'computing', 'sublexical', 'avoid', 'regulated', 'policy', 'equally', 'rotations', 'searches', 'pews', 'poking', 'remain', 'readily', 'edible', 'ms', 'pervasive', 'evaluations', 'sm', 'mixed', 'allocated', 'analyze', 'presents', 'falls', 'contained', 'camera', 'feasible', 'preventing', 'caregivers', 'achieving', 'measuring', 'sleep', 'cordic', 'guide', 'decision', 'played', 'questionnaires', 'wore', 'cued', 'thinned', 'break', 'start', 'script', 'recipes', 'breathing', 'counterbalanced', 'clinicians', 'modifying', 'surgical', 'depicted', 'musculoskeletal', 'economy', 'sertraline', 'intake', 'paradigm', 'reprimands', 'warranted', 'perceptions', 'vehicle', 'gearshift', 'residual', 'hemisphere', 'responsive', 'supporting', 'manage', 'began', '60', 'subthalamic', 'nucleus', 'path', 'label', '05', 'zero', '2006', 'situation', 'concept', 'cbt', 'version', 'engineering', 'applying', 'elearning', 'recommender', 'extinguishing', 'kickball', 'ungrammatical', 'errorless', 'ranging', 'videomonitoring', '2003', 'directed', 'add', 'arbitrary', 'aversiveness', '50', 'document', 'availability', 'statement', 'maternal', 'partially', 'taken', '85', 'hard', 'tracing', 'comfort', 'weighted', 'morphology', 'formal', 'cerebrovascular', 'tutor', 'descriptors', 'graduate', 'graphing', 'youth', 'abc', 'dpi', 'generalizing', 'copy', 'dysphonia', 'irritation', 'acquire', 'incorporated', 'dwelling', 'replacement', 'standards', 'avoidance', 'force', 'profile', 'responsible', 'wrist', 'fail', 'documented', 'relate', 'supervisors', 'generalize', 'manding', 'highchair', 'loneliness', 'mood', 'universal', 'assignments', 'noncancer', '65', 'reliably', 'echolalia', 'prereading', 'autobiographical', 'kindergarten', 'valid', 'prevention', 'addiction', 'maximize', 'faster', 'resistance', 'infrared', 'conditioned', 'burkholder', 'comparable', 'voca', 'marked', 'reason', 'mouth', 'dental', 'consumption', 'baer', 'particularly', 'note', 'yielded', 'requiring', 'technological', 'rushing', 'compliment', 'season', 'overview', 'exertion', 'attainment', 'submaximal', 'tokens', 'extends', 'key', 'gymnastics', 'bite', 'degrees', 'cause', 'faded', 'exact', 'gender', 'robust', 'athletic', 'intersections', 'business', 'estimation', 'establishment', 'nms', 'generalised', 'excess', 'influential', 'dimension', 'stim', 'deprivation', 'equations', 'nonconcurrent', 'states', 'unmatched', 'reviews', 'concern', 'healthy', 'advances', 'neighborhood', 'contractures', 'sclerosis', 'uses', 'ties', 'thumb', 'organizations', 'value', 'engine', 'lead', 'signal', 'known', 'expectations', 'opportunity', 'accepted', 'sent', 'variance', 'collegiate', 'competition', 'smokers', 'tics', 'represent', 'national', 'yoga', 'workstation', 'started', 'facility', 'motivating', 'presenting', 'pentop', 'treat', 'phonomotor', 'illustrate', '1994', 'legs', 'later', 'white', 'dro', 'viewing', 'contract', 'exhibit', 'iv', 'validated', 'outside', 'counts', 'tourette', 'pretest', 'dose', 'hint', 'reasons', 'interact', 'capi', 'matrix', 'nontarget', 'greeting', 'aching', 'electronically', 'sources', 'abolishing', 'vomit', 'operation', 'instructed', 'explanation', 'representing', 'magnitude', 'manifested', 'workers', 'mutual', 'locate', '120', 'idiosyncratic', 'pulling', 'percent', 'desktop', 'analogue', 'verbally', 'researcher', 'emerging', 'experts', 'stokes', 'ignored', 'mucosa', 'like', 'cross', 'keller', 'legally', 'considerable', 'emg', 'articulation', 'investigator', 'eyes', 'feature', 'map', 'transformations', 'dramatically', 'analgesic', 'desire', 'great', 'specifications', 'edited', 'postflight', 'counter', 'tms', 'flight', 'assist', 'greatest', 'focusing', 'ld', 'caused', 'arithmetic', 'childhood', 'challenge', 'repertoires', 'architecture', 'reactivity', 'insufficient', 'discriminate', 'threatening', 'starbright', 'choose', 'projects', 'stones', 'stem', 'expected', 'provision', 'conclude', 'physicians', 'numbers', 'originally', 'desensitization', 'breakdowns', 'informed', 'exhaustive', 'metaphor', 'project', 'good', 'oriented', 'incredible', 'gt', 'cocaine', '45', 'anchors', 'winning', 'action', 'activations', 'usually', 'framework', 'calculated', 'passages', 'pediatric', 'minimum', 'mip', 'juvenile', 'views', 'mail', 'fine', 'newly', 'buprenorphine', 'issue', 'ancillary', 'cervical', 'innovative', 'decade', 'plays', 'baldi', 'photos', 'league', 'frost', 'homework', 'pneumosensorial', 'papers', '1997', 'shift', 'employees', 'consequent', 'accident', 'thinking', 'prototype', 'productivity', 'fiction', 'scrimmages', 'continuity', 'personnel', 'illustrating', 'compression', 'indicating', 'retrospective', 'rapidly', 'exclusively', 'ssd', 'novice', 'distributed', 'simply', 'cp', 'tai', 'ppm', 'contextually', 'formats', 'likelihood', 'parts', 'asked', 'paralysis', 'trainer', 'dyspnea', 'resident', 'maximal', 'mmn', 'negativity', 'vectors', 'comply', 'undergraduate', 'execution', 'lap', 'argues', 'clearly', 'explicitly', 'allowing', '001', 'rom', 'histories', 'truetales', '79', '98', 'passive', 'deviant', 'multicenter', 'frontal', 'center', 'equal', 'belt', 'anomia', 'respective', 'divergence', 'prospective', 'recommended', 'mismatch', 'improves', 'distribution', 'communicated', 'arthritis', 'amounts', 'consonant', 'approximately', 'simultaneous', '52', 'incidental', 'relief', 'edition', 'refers', 'geller', 'dc', 'adjunct', 'turn', 'description', 'coordinate', 'topographies', 'damian', 'stn', 'promise', 'classwide', 'incomplete', 'steady', 'cognition', 'discontinued', 'adverse', 'deep', 'appropriately', 'transferred', 'nursing', 'amputees', 'answer', 'hill', 'wolf', 'rvi', 'returned', 'referents', 'chip', 'easier', 'dct', 'cr', 'consequence', 'op', 'discourse', 'nail', 'correlated', 'narratives', 'attempts', 'correspond', 'discovered', 'member', 'named', 'rcts', 'examines', 'median', 'nonoverlapping', 'tutorials', 'impede', 'meet', 'aimed', 'punisher', 'ratios', 'recruited', 'replications', 'sensitive', 'progressed', 'sequence', 'generate', 'supplement', 'underlie', 'confidence', 'average', 'fetal', 'supplemental', 'encouraged', 'speakers', 'semantic', 'automaticity', 'alcohol', 'heavy', 'substitute', 'deal', 'feeling', 'beck', 'electrical', 'surgery', 'resources', 'conflicts', 'consider', 'injuries', '27', 'observe', 'bias', 'guidelines', 'latency', 'modality', 'predict', 'preparation', 'termination', 'induction', 'laser', 'recapture', 'eliminated', 'closed', 'motivation', 'concentration', 'beam', 'journals', 'press', 'ambulation', 'compensatory', 'p5', 'p1', 'handbook', '2008', 'realistic', 'gaming', 'routine', 'depth', 'topography', 'table', 'band', 'aerobic', 'elderly', 'intended', 'occurrences', 'lbp', 'pbws', 'pedals', 'broad', 'databases', 'spine', 'flavor', 'psychosocial', 'familiar', 'sec', 'unloading', 'endurance', 'postintervention', 'wheelchairs', 'compliments', 'walking', 'represented', 'screen', 'medicine', 'prose', 'exemplar', 'instructor', 'striving', 'coded', 'formed', 'containing', 'equivalent', 'struggle', 'evident', 'appreciation', 'come', 'bundle', 'cooperation', 'obm', 'aed', 'contoured', 'advanced', 'index', 'alternated', 'certain', 'recreational', 'miss', 'neurofibromatosis', 'motoric', 'ways', 'neutral', 'phrases', 'abnormal', 'density', 'wrote', 'freezes', 'nonverbal', 'walker', 'favorite', 'clarification', 'kinesia', 'meals', 'selective', 'paradoxa', 'popular', '43', 'separate', 'exclusion', 'professional', 'judged', 'photo', '1977', 'externalizing', 'displaying', 'sitting', 'exposing', '1995', 'bimanual', 'qualitative', 'transformation', 'willingness', 'meets', 'intralesson', 'representation', '36', 'probabilistic', 'comments', 'differing', 'experimenters', 'lottery', 'options', '39', 'limitation', 'numerous', 'link', 'opening', 'coordination', 'forword', 'thirty', 'sling', '1993', 'absent', 'themes', 'emitting', 'synthetic', 'regrand', 'earned', 'db', 'distinguish', 'source', 'schoolwide', 'destructive', 'extreme', 'gain', 'vol', 'topics', 'plans', 'durations', 'emergent', 'nonpathological', 'depression', 'records', 'mode', 'answers', 'limits', 'considerably', 'validate', 'analysed', 'moved', 'ball', 'timed', 'flexion', 'rtt', 'ct', 'categorization', 'attitude', 'changed', 'onset', 'linguistic', 'argued', 'product', 'entailed', '1999', 'ease', 'mothers', 'enrichment', 'walk', 'targets', 'designing', 'psychotherapeutic', 'unknown', 'concluded', 'evidenced', 'regard', 'incorrect', 'palin', 'adding', 'contribution', 'acceptable', 'induced', 'wear', 'eap', 'cessation', 'opiate', 'vic', 'sup', 'combines', 'reviewers', 'automation', 'encourages', 'postexercise', 'count', 'english', 'confirm', 'algebraic', 'trigonometric', 'rectangular', 'vowel', 'split', 'accompanying', 'bondy', 'translabyrinthine', 'repositioning', 'rigid', 'powerpoint', 'boxed', 'briefly', 'tradition', 'seconds', 'diverse', 'generality', 'exception', 'syllable', 'instructive', '70', 'vestibular', 'schwannoma', 'biobehavioral', 'rural', 'just', 'greetings', 'facilitates', 'correction', 'chose', 'aversive', 'pivotal', 'expanding', 'restricted', 'neurological', 'closures', 'cumulative', 'informative', 'signals', 'file', 'retention', 'underwent', 'pathologists', 'lesson', 'association', 'reassessment', 'introduces', 'guiding', '2001', 'mother', 'lesions', 'accessibility', 'makes', 'closing', 'persistence', 'house', 'central', 'purported', 'prompted', 'retained', 'ivf', 'timer', '94', 'redesign', 'effertiveness', 'leach', 'scales', 'pdms', 'deviation', 'kinematics', 'padding', 'grades', 'gaps', 'signaling', 'adjustment', 'horizontal', 'rma', '150', 'dissemination', 'broaden', 'inputs', 'domain', 'wizard', 'maximum', 'muscles', 'execute', 'think', 'classified', 'spastic', 'hours', 'kinematic', '01', 'masked', 'cursor', 'operate', 'dual', 'oxygen', 'posttraining', 'depicting', 'adequate', 'mutants', 'strings', 'lifelong', 'conservative', 'internalizing', 'intention', 'cuff', 'glottal', '87', 'leader', 'stopped', 'unchanged', 'textual', 'individually', 'fundamentals', 'pages', 'ail', 'cdc', 'incorporating', 'suppression', 'mg', 'tablets', 'meeting', 'variation', 'severely', 'anchor', 'boat', 'virtually', 'frames', 'reexposed', 'proved', 'quite', 'customize', 'continuum', 'termed', 'lists', 'hygiene', 'irrelevant', 'uppercase', 'lowercase', 'pains', 'physician', 'bulimics', 'closer', '63', 'analgesia', 'hierarchy', 'specificity', 'site', '76', '51', 'encouraging', '1992', 'serial', 'comes', 'norm', 'ignore', 'diversity', 'actually', 'pronated', 'shoe', 'bridge', 'evolving', 'universally', 'applicable', 'frame', 'justify', 'sat', 'indication', 'inconclusive', 'modes', 'runtime', 'placing', 'integrate', 'exist', 'construct', 'mucosal', 'carrier', 'interdependent', 'medications', 'emphasizes', 'calendar', 'asds', 'disseminate', 'legibility', 'informing', 'associations', 'reverberation', 'analgesics', 'employee', 'decades', 'amplitude', 'mechanism', 'inhalers', 'interpreted', 'arrive', 'interpret', 'demand', 'recess', 'holland', 'alternate', 'rime', 'corticosteroid', 'bronchodilator', 'readers', 'practicality', 'regimens', 'fit', 'tacts', '1987', 'psychologists', 'investigators', 'structures', 'decrement', 'sharing', 'pronation', 'episodes', 'causality', 'breakdown', 'comparative', 'odds', 'failures', 'consumed', 'lifestyle', 'convicted', 'assault', 'account', 'slope', 'adaptations', 'corticospinal', 'connectivity', 'code', 'mutation', 'slow', 'vomiting', 'bulimic', 'illnesses', 'feelings', 'offended', '2009', 'responders', 'commentary', 'pursue', 'contextualized', 'computation', 'hlac', 'regression', 'commands', 'pinch', 'dexterity', 'becs', 'exchanges', 'neural', 'biology', 'limit', 'interacting', 'keyboard', 'emotionally', 'disturbed', 'transportability', 'paucity', 'competence', 'adoption', 'nih', 'happens', 'lerman', 'controversial', 'managed', 'seriously', 'commercial', 'pay', 'sense', 'phenomenon', 'neck', 'sustaining', 'tray', 'learns', 'local', 'udl', 'anticipatory', 'detect', 'watch', 'dictated', 'thought', 'internal', 'vm', 'superior', 'elicit', 'imagery', 'barriers', 'acquiring', 'phonology', 'phonetic', 'lexical', 'encoding', 'interpersonal', 'uk', 'sixteen', 'reflected', 'incorporate', 'videos', 'altering', 'mini', 'urinary', 'toileting', 'resistant', 'flashcard', 'applicability', 'communications', 'cooperating', 'experiencing', 'sfa', 'disciplines', 'likely', 'emit', 'simultaneously', 'diagnoses', 'multidisciplinary', 'psychiatry', 'jaba', 'arrived', 'radio', 'exit', 'colli', 'evaluative', 'guidance', 'investigations', '38', 'image', 'consists', 'ab', 'cancellation', 'lighthouse', 'posttest', 'inattention', 'phonemic', 'costs', 'attended', 'emergence', 'mealtimes</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>['meniere', 'duction', 'nonfluent', 'remarkable', 'sever', 'eras', 'dissimilar', 'dangerous', 'climbing', 'jumping', 'saliva', 'arbitrarily', 'stems', 'conceptualizations', 'unnecessarily', 'hope', 'spark', 'yes', 'touch', 'anchored', 'somatization', 'diet', 'nutrition', 'links', 'urine', '116', 'prizes', 'urines', 'collaborated', 'consume', 'handle', 'illness', 'principal', 'reactions', 'tu', 'visits', 'cerebellar', 'tumor', 'fall', 'motivated', 'bob', 'measurable', 'carl', 'tv', 'page', 'editing', 'manuscripts', 'birth', 'database', 'interventionists', 'coupling', 'excised', 'teaming', 'digit', 'fly', 'leapfrog', 'multichannel', 'summary', 'multitreatment', 'receiver', 'substitutability', 'lattal', 'perone', 'want', 'cm', 'diameter', 'invisible', 'beep', 'impulsive', 'greeted', 'fully', 'supervisor', 'strengths', 'struggling', 'draft', 'qualitatively', 'fsis', 'overlap', 'agencies', 'videoconference', 'pad', 'hyperactive', 'inattentive', 'mornings', 'matheamatical', 'tended', 'shifted', 'selections', 'reversed', 'financial', 'refining', 'anal', 'carls', 'quantify', 'possibilities', 'cut', 'sloping', 'plural', 'lid', 'contributing', 'ordering', 'prosocial', 'videogame', 'stressors', 'cardiovascular', 'distributions', 'synthesis', 'comorbid', 'accurately', 'aviation', 'pcatd', 'specialty', 'yale', 'lengths', 'sampling', 'quantified', 'pcs', 'aggregate', 'undermatching', 'imperfect', 'yardage', 'correlations', 'processor', 'applies', 'embedding', 'proficient', 'replicates', 'shortly', 'matrices', 'milieu', 'concomitantly', 'trainers', 'transported', 'configuration', 'improvised', 'portion', 'hoc', 'maturational', 'predictions', 'undesirable', 'forefront', 'customary', 'enjoyed', 'neurology', 'hesitation', 'largely', 'generalizability', 'consensus', 'improvise', 'deviances', 'gestures', 'feed', 'expands', 'groceries', 'filmed', 'reach', 'mbd', 'carrying', 'holding', 'lagged', 'postonset', 'predominant', 'perceptually', 'apprehension', 'consonants', 'phonemes', 'intelligibility', 'scl', 'bdi', 'convenient', 'realised', 'randomised', 'losses', 'preuse', 'simulating', 'accidental', 'supplies', 'festinating', 'calculations', 'articulated', 'symptom', 'eighteen', 'spectacles', 'mimicking', 'akinesia', 'iii', 'hoehn', 'yahr', 'interests', 'modulate', 'normalized', 'panic', 'phobias', 'egm', 'gambler', 'gscl', 'gray', 'retesting', 'implements', 'neuropsychologists', 'serves', 'accomplished', 'structurally', 'approval', 'compute', 'files', 'susceptible', 'inflated', 'overly', 'worked', 'neuropsychological', 'garthwaite', 'submitted', 'returns', 'diets', 'supplements', 'pillow', 'noncontingently', 'reciprocity', 'argument', 'warrants', 'listed', 'colleagues', 'chapters', 'society', 'america', 'worldwide', '552', 'arch', 'phys', 'med', 'rehabil', '86', '1381', 'crossover', 'neurorehabilitation', 'manifestation', 'facilitation', 'differentiation', 'wanting', 'cattaneo', 'ferrarin', 'frasson', 'casiraghi', '140', 'smoke', 'earlier', 'winborn', 'andelman', 'mtsukawa', 'omitting', 'strategically', 'contrived', 'fails', 'rich', 'figurines', 'adds', 'modify', 'sympathy', 'disapproval', 'reminders', 'fell', 'rbmt', 'tower', 'deterioration', 'debilitating', '72', 'walked', 'http', 'www', 'maximizing', 'prove', 'lire', 'incentives', 'females', 'ireland', 'doi', '1300', 'j018v31n02_06', 'copies', 'fee', '800', 'docdelivery', 'website', 'inflate', 'nurses', 'repairs', 'paraphrases', 'interjects', 'impacted', 'coherent', 'prevent', 'drilled', 'hypotheses', 'discrepancies', 'periodicals', 'adopt', 'loved', 'nonfacililative', 'news', 'hills', 'stumbling', 'artificial', 'limbs', 'slis', 'goniometry', 'representatives', 'deaf', 'academy', '1972', 'discusses', 'bcbc', 'forming', 'multitasking', 'negotiating', 'stairs', 'voluntarily', 'projected', 'positional', 'stabilize', 'oscillation', 'planes', 'conversely', 'congress', 'prebaseline', 'installed', 'regardless', '1935', 'madison', 'discovery', 'nonviolent', 'parenting', 'nurse', 'formation', 'unclear', 'concentrated', 'canadian', 'unbelted', 'buckle', 'gear', 'essays', 'tutorial', 'transition', 'otto', 'bock', 'divided', 'amputee', 'transfers', 'lie', 'motorists', 'regularly', 'pem', 'metrics', 'locating', 'putting', 'interpretive', 'founding', 'died', 'huntington', 'march', 'lawrence', 'kansas', 'preserving', 'spondees', 'sterotypy', 'paradoxically', 'orchestrated', 'massive', 'refined', 'adjust', 'delinquent', 'reinvented', 'exploited', 'acab', '37', 'products', 'complementary', 'readings', 'mailed', 'patches', 'artificially', 'engineered', 'alternatively', 'persistently', 'halted', 'payment', 'european', 'funded', '125', '000', 'hz', '69', 'recipients', 'quiet', 'melodies', '96', 'perseverative', 'impeded', 'workplace', 'keyboarding', 'characters', 'skip', 'proceed', 'averaged', 'acknowledged', 'aide', 'overtime', 'designation', 'discontinue', 'plateau', 'involve', 'diagnostics', 'viral', 'infection', 'iron', 'salad', 'sedat', 'washing', 'soup', 'meetings', 'bullying', 'insubordination', 'tardiness', 'fighting', 'prepared', 'expulsion', 'worse', 'extremely', 'productions', 'naturalness', 'spared', 'violence', 'abehavior', 'faced', 'infrequent', 'shootings', 'majoring', 'anova', 'truly', 'revealing', 'elders', 'compromised', 'fluent', 'probed', 'volunteers', 'preoperative', 'accelerometer', 'matter', 'behavioural', 'rater', 'possibility', 'hickey', 'reliance', 'introductory', 'pertain', 'reflections', 'shifts', 'mutually', 'combinatorially', 'variations', 'aysun', 'encountering', 'tenets', 'stove', 'microwave', 'purchases', 'cashiers', 'restaurant', 'responsibilities', 'aires', 'sinem', 'clean', 'nozzle', 'handkerchief', 'shirt', 'shoeshine', 'internalize', 'cartoons', 'sufficiently', 'moving', 'tacting', 'boards', 'stated', 'know', 'imposition', 'usefullness', 'carry', 'paintings', 'kind', 'psychologist', 'rees', '2061', 'magnesium', 'unbiased', 'generaring', 'sonic', 'labeling', 'tangible', 'withheld', 'super', 'helmet', 'shield', 'chains', 'dealer', 'nineteen', 'interviewed', 'experiences', 'b6', 'commonality', 'ordinal', 'deficity', 'minimally', 'highlighted', 'underscore', 'careful', 'occurs', 'mid', 'western', 'exceptional', 'tone', 'deficiencies', 'antecedents', 'enforcement', 'centres', 'running', 'windows', 'moble', 'operating', 'studio', 'morphological', 'inflections', 'clauses', 'illusion', 'physiology', 'philosophy', 'melding', 'expanded', 'laboratories', 'persuasive', 'kindergartner', 'durrant', 'redpath', 'harper', 'rhodes', 'investigates', 'busy', 'broca', 'turns', 'vague', 'inexpensive', 'daytime', 'urinations', 'stages', 'distinguished', 'selectively', 'subgroup', 'tends', 'noncommunicative', 'redirected', 'issuing', 'irrational', 'advance', 'optimize', 'historic', 'coda', 'lexicality', 'pseudowords', 'unspecific', 'sonority', 'reproduction', 'practising', 'implies', 'intelligence', 'dyslexia', 'concerned', 'indices', 'headsprout', 'ps', 'conduction', 'contrasts', 'expansive', 'requires', 'disparate', 'evelyn', 'fox', 'outlines', 'biologists', 'animate', 'ebis', 'favored', 'favoring', 'institutional', 'adaptability', 'alpha', 'beta', 'vibrant', 'pg', '737', 'explaining', 'biological', 'metaphors', 'seeking', 'transporting', 'consultation', 'gaiam', 'relaxation', 'orientating', '77', 'arise', 'implementations', 'lifts', 'feet', 'longterm', 'fp', 'scenario', 'airport', 'maladaptive', 'tantruming', 'follows', 'cookbooks', 'latencies', 'oneself', 'conduit', 'ascertain', 'remove', 'speak', 'ameliorate', 'relapse', 'peg', 'nuts', 'bolts', 'conclusive', 'transcranial', 'magnetic', '5760', '560', 'parallels', 'disabled', 'unique', 'ioa', 'ensure', 'blindness', 'knob', 'hole', 'northwest', 'womens', 'adversities', 'fouls', 'subset', 'dry', 'powder', 'inhaler', 'belief', 'catastrophic', 'thoughts', 'meaures', 'flew', 'preprimer', 'vocabularies', 'pacific', 'echoics', 'assertion', 'hall', 'sundberg', 'lamarre', 'sigafoos', 'reichle', 'doss', 'cookbook', 'aatd', 'fragmented', 'definitions', 'nonexistent', 'filling', '1957', 'intraverbals', 'chi', 'interspersed', 'unpaired', 'salience', 'interpretations', 'passed', 'publication', 'structure', 'inhalation', 'leads', 'deposition', 'particles', 'believe', 'minimized', '281', '00001', 'switched', 'folds', 'hyperemia', 'plaque', 'vibration', 'wave', 'propagation', 'videostroboscopy', 'nonsmokers', 'excision', 'proton', 'pump', 'inhibitor', 'gastroesophageal', 'reflux', 'videostroboscopic', 'disturbance', 'inacademic', 'antisocial', 'superiority', 'rely', 'leading', 'snack', 'initiate', 'scant', 'dopaminergic', 'region', 'comparability', 'proper', 'separately', 'vibratory', 'mates', 'cati', 'personalizes', 'permits', 'flexibility', 'dealing', 'biographies', 'yields', 'standardization', 'reconstructive', 'flexibly', 'interconnections', 'memories', 'german', 'modularization', 'forward', 'introduce', 'mixing', 'periodic', 'reversals', 'deters', 'accepting', 'demographic', '99', '56', 'exemplify', 'fault', 'intractable', 'faults', 'triggered', 'tuples', 'nonremoval', 'refused', 'schlosser', 'blischak', 'belfiore', 'bartley', 'barnett', 'speeck', 'distinct', 'profiles', 'supplementing', 'communicating', 'opinions', 'chair', 'bench', 'carpet', 'square', 'seated', 'listened', 'lined', 'ceiling', 'decisions', 'reverberant', 'noisy', 'listening', 'acoustics', 'strengthened', 'modifications', 'interventionist', 'nonspeaking', 'intentions', 'interfere', 'modulated', 'olds', '015', 'pruritus', 'headache', 'somnolence', 'tolerated', 'deals', 'dates', 'limiting', '59', 'ci', '09', '022', '011', '67', 'discontinuation', '028', 'correspondences', 'systeamtic', 'teas', 'deficient', 'reimplemented', 'daring', 'ribs', 'operationally', 'vital', 'eighty', 'entered', '267', '129', '138', 'protocols', 'friendly', 'titrated', 'tolerate', '500', 'rescue', 'predefined', 'keeping', 'affixed', 'discontinuing', 'ising', 'specialized', 'authoring', 'recommend', 'construction', 'employment', 'recommendation', 'agents', 'athlete', 'regional', 'shooting', 'satisfied', 'believed', 'capture', 'testers', 'update', 'underlined', 'syndromes', 'undergone', 'revisions', 'newer', 'constructing', 'doubled', 'quadrupled', 'ace', 'fluently', 'passage', 'answering', 'nondifferential', 'default', 'infarction', '0001', 'attending', 'arts', 'outs', 'ambiguous', 'culturally', 'linguistically', 'hawaii', 'referred', 'stratton', 'playtime', 'whiteboard', 'ctd', 'disabilties', 'arrangment', 'creates', 'negligible', 'deficiency', 'perceptive', 'reserve', 'potent', 'dependence', 'preceded', 'contributions', 'webster', 'velocity', 'outward', 'inward', 'peabody', 'detectable', 'inability', 'intact', 'explained', 'regenerate', 'detailed', 'lesion', 'click', 'struggles', 'ob', 'dominant', 'peak', 'sex', 'centre', 'artery', 'territory', 'supplemented', 'grasping', 'transport', 'disseminated', 'causing', 'activate', 'momentary', 'closure', 'converted', 'telehealth', 'circumstances', 'gpm', 'multimodal', 'baron', 'cohen', 'leslie', 'frith', 'concurred', 'wider', 'desirable', 'fairly', 'asymptotic', 'degrade', 'ended', 'nearly', 'grounded', 'references', 'positively', 'isotonic', 'dimensional', '102', '118', 'precise', 'adjective', 'inversion', 'auxiliary', 'rests', 'comfortable', 'teenagers', 'streaming', 'disseminating', 'sawing', 'rivermead', 'section', 'tawc', 'wks', 'automotive', 'pneumatic', 'bladders', 'tilt', 'recline', 'elevating', 'ready', 'stamp', 'draw', 'replicable', 'integral', 'wellness', 'adjustable', 'relieve', 'surveys', 'subjective', 'station', 'determining', 'tremors', '81', 'fabric', 'weights', 'personalization', 'realworld', 'complexities', 'calls', 'explores', 'semester', 'consult', 'offices', 'forearm', 'automate', 'stand', 'pitched', 'proposal', 'goes', 'graphical', 'recommenders', 'wh', 'possessive', 'pronouns', 'infinitives', 'modal', 'verbs', 'cuffs', 'weighting', 'air', 'maneuver', '47', 'ventilation', 'uptake', 'pause', 'declining', 'neurophysiological', 'diminish', 'thyroidectomy', 'strengthen', 'intent', 'enabling', 'pressures', '75', 'bring', 'gottman', '1981', 'slide', '71', 'answered', 'inspectors', 'interrater', 'strengthens', 'grams', 'eaten', 'spilled', 'spills', 'diminished', 'twofold', 'allison', 'gorman', 'physically', 'rare', 'string', 'reverse', 'anterior', '400', 'spatiotemporal', 'cortical', 'properly', 'adaptation', 'ph', 'ceased', 'recite', 'fires', 'stud', 'heard', 'educated', 'mismanage', 'simulator', 'satisfactory', 'aloud', 'debriefing', 'discussing', 'depends', 'silent', 'film', 'located', 'realtively', 'outline', 'manufacturing', 'managers', 'master', 'loosely', 'indiscriminable', 'refine', 'actively', 'mind', 'illustrative', 'troubleshooting', 'tips', 'unsupervised', 'programmes', 'anomic', 'subgroups', 'heterogeneous', 'specify', 'anonymity', 'attentiveness', 'sparse', 'estimated', 'moderating', 'analytical', 'busk', 'serlin', 'sas', 'estimating', 'grammaticality', 'cortex', 'neurobiological', 'tentative', 'trace', 'estimate', 'detector', 'widespread', 'lies', 'philosophical', 'radical', 'behaviorism', 'clarifying', 'distinctions', 'pinching', 'screaming', 'composite', 'nonrandomized', 'concerning', 'disrupted', 'spelled', 'preferable', 'annotated', 'distinguishing', 'intervening', 'starting', 'articulate', 'culminating', 'rubrics', 'charts', 'ergonomically', 'adjustments', 'summarized', 'dyad', 'legible', 'losing', 'photography', 'callouts', 'unproved', 'opinion', 'centers', 'breadth', 'connections', 'toot', 'collaborative', 'marketing', 'podiatric', 'complaint', 'methodical', 'compete', 'lamented', 'disconnection', 'christophersen', 'mortweet', '200', 'gap', 'staged', 'optimising', 'pairwise', 'adequately', 'coursework', 'extending', 'continually', 'lot', 'crying', 'alto', 'natives', 'leaching', 'reference', 'kill', 'factor', 'overhead', 'squares', 'coefficients', 'violent', 'tendencies', 'offenses', 'verified', 'recidivism', 'arousal', 'purging', 'spaced', 'taboo', 'industrial', 'adequacy', 'flaws', 'multivariate', 'ordinary', 'determinant', 'slowed', 'eat', 'lit', 'urge', 'slowly', 'binge', 'bulimia', 'triplane', 'wedges', 'aiming', 'obviates', 'impetus', 'calculation', 'die', 'complements', 'chronically', 'institutes', 'distraction', 'enjoyment', 'seventy', 'hiv', 'infected', 'willing', 'relies', 'unscripted', 'cooperative', 'influencing', 'pregambling', 'zlomke', 'dixon', 'dice', 'vocational', 'ecological', 'suggestion', 'hold', 'promises', 'certainly', 'panacea', 'specification', 'uniform', 'act', 'committed', 'unacceptable', 'acts', 'escalating', 'property', 'destruction', 'packages', 'jeopardize', 'ecocultural', 'laminated', 'replica', 'linking', 'handicaps', 'aisles', 'resolve', 'consequently', 'necessitates', 'individualize', 'collaboration', 'contextulized', 'intermittently', 'goodness', 'delineated', 'vomdran', 'vorndran', 'thesis', 'akin', 'ignoring', 'universe', 'caveats', 'marginally', 'worried', 'returning', 'helped', 'inloneliness', 'depressed', 'energetic', 'dropped', 'cutting', 'edge', 'assisting', 'aspire', 'semistructured', 'sit', 'liner', 'insert', 'postgraduate', 'institution', 'kinesiology', 'quizzes', 'culture', 'operationalizing', 'qol', 'resolution', 'saliency', 'firstly', 'weakly', 'supervised', 'institutions', 'importantly', 'innovations', 'carefully', 'misapplied', 'remedied', 'paying', 'encourage', 'consumers', 'advocated', 'autocorrelation', 'determines', 'route', 'postdischarge', 'discharge', 'promotes', 'meagre', 'usefulness', 'utilising', 'mosstalk', 'volumes', '28', '168', 'accidents', 'inpatient', 'caucasian', 'mesulam', 'drawing', 'nontreatment', 'release', 'state', 'osteoarthritis', 'reliever', 'inducing', 'planned', 'taped', 'infant', 'arms', 'everyday', 'washington', 'deitz', 'jc', 'schwartz', 'observable', 'ness', 'autonomy', 'guessability', 'referent', 'lines', 'hindered', 'ucla', '26', 'cogent', 'dosing', 'prescriptive', 'interrogative', 'compatibility', 'clarity', 'differentiate', 'promoted', 'disclosure', 'connection', 'moments', 'durand', 'replacing', 'consist', 'fisher', 'wacker', 'phonologically', 'practicum', 'dyadic', 'likert', 'postlesson', 'predominantly', 'psychotherapy', 'connecting', 'inspired', 'registration', 'ssris', 'feamale', 'kept', 'possession', 'restart', 'corner', 'haptic', 'microprocesses', 'dialogue', 'transcripts', 'emotion', 'abstraction', 'kiel', 'classic', 'manipulations', 'highest', 'extensive', 'gentle', 'dysfunction', 'acb', 'department', 'lasting', 'examinations', 'discriminant', 'classification', 'exceeded', '78', 'bond', 'siegel', 'yamall', 'iep', 'conference', 'sixth', 'sequentially', 'adversely', 'contra', 'lesional', 'copying', 'extensively', 'held', 'gambled', 'bets', '1989', 'consultants', 'purposes', 'ran', 'periodically', 'ss', 'simplified', 'wearable', 'videorecorded', 'winnings', 'bet', 'humans', 'kick', 'coaches', 'archived', 'incorrectness', 'agree', 'existence', 'seldom', 'bos', 'voltage', 'ipsilateral', 'commissure', 'undergoing', 'electromyographic', 'artifact', 'cauterization', 'totally', 'coached', 'standardised', 'frattali', 'fromm', 'understood', 'ones', 'necessitating', 'otoneurosurgical', 'warrant', 'hemi', 'chosen', 'couple', 'unanswered', '41', 'share', 'intervened', 'hemispace', 'blinded', 'examiner', 'star', 'bisection', 'baking', 'inferential', 'assured', 'resequenced', 'suppress', 'disadvantages', 'postvideo', 'rode', 'tired', 'elapsed', 'cycling', 'pertinent', 'guiders', 'retrieving', 'getting', 'orientation', 'subtypes', 'macros', 'pair', 'b1', 'b2', 'cusum', 'corresponded', 'gradually', 'therapyst', 'formulated', 'instances', 'masking', 'negatively', 'requirement', 'equipped', 'switches', 'enable', 'telling', '07', 'mitigated', 'herald', 'pharmacological', 'linebackers', 'intercollegiate', 'athletics', 'occasions', 'bas', 'protracted', 'utilised', 'solicited', 'raters', 'abandoned', 'pertaining', 'comprehensibility', 'extracted', '2sdbm', 'holds', 'flavored', 'dieters', 'administer', 'complaints', 'speaker', 'targeting', 'tine', 'adherence', 'suffering', 'aggravated', 'axial', 'roland', 'morris', 'vas', 'rise', 'mainly', 'echo', 'lose', 'true', 'storybook', 'song', 'crime', 'linebacker', 'positioned', 'scrimmage', 'plot', 'positioning', 'tackled', 'vibrating', 'pager', 'lending', 'bear', 'intertrial', 'varmble', 'marcros', 'cyrano', 'communicator', 'messagemate', 'bad', 'picked', 'fingers', 'tissue', 'damage', 'bold', 'predictive', 'iconic', 'payout', 'topographically', 'pupil', 'hospitalized', 'aggregated', 'manipulating', 'rvq', 'rve', 'pqrs', 'display', 'bebavior', 'suitable', 'chapter', 'prerequisites', 'motorized', 'quantities', 'dissertation', 'compilations', 'theses', 'dissertations', 'ancestry', 'extraction', 'stakeholders', 'bicycling', 'quadriplegia', 'gym', 'outdoor', 'competently', 'synthesizing', 'multifaceted', '1975', 'bibliographic', 'posed', 'neuroscience', 'expertise', 'helps', 'doubling', 'compensation', 'integer', 'rotation', 'proof', 'bedtimes', 'hollon', 'lonigan', 'elbert', 'johnson', 'possibly', 'endorsing', 'parametric', 'nails', 'biting', 'habits', 'precursor', 'mittens', 'insurance', 'companies', 'qye', 'ive', 'reflecting', 'readministration', 'portions', 'cuing', 'triads', 'bites', 'mum', 'cmos', 'throughput', '263', 'codec', 'favorable', 'confirming', 'brace', 'multiply', 'mac', 'replaced', 'processors', 'compact', 'realize', 'multipliers', 'mhz', 'flow', 'emphasis', 'minimizing', 'computational', 'dedicated', 'consuming', 'coder', 'chips', 'cosine', 'interpolated', 'extracts', 'multiplier', 'achieves', 'hardware', 'saving', 'far', 'tithe', 'adolescence', 'incorporates', 'terminology', 'fictional', 'segment', 'replay', 'analyzing', 'released', 'entitled', 'kids', 'phones', 'contributor', 'fitness', 'obesity', 'cell', 'grown', 'exponentially', 'complement', 'date', 'extant', 'locomotor', '1986', 'learnt', 'identity', 'analyzes', 'raid', 'recount', 'offer', 'ultimate', 'therapies', 'popularity', 'economics', 'crashes', 'light', 'diode', 'featured', 'eves', 'angle', 'braking', 'mazes', 'assertive', 'floor', 'similarity', 'surprising', 'chan', 'similarly', 'casks', 'optimizing', 'afo', 'prescription', 'neuropathy', 'orthotic', 'corporation', 'utterance', 'morphemes', 'ankle', 'expenditure', 'hemiplegia', 'prescribed', 'balke', 'calorimetry', 'borg', 'intensities', 'methylphenidate', 'conners', 'remediation', 'ivis', 'miles', 'told', 'direction', 'counted', 'cohort', 'ventral', 'excessive', 'kaiser', 'major', 'minor', 'road', 'transportation', '33', 'charge', 'interference', 'maps', 'abis', 'city', 'york', '64', 'suddenly', 'swerving', 'crash', 'hemispheric', '360', 'speeds', 'consent', 'tertiary', 'benefited', 'considers', 'influences', 'socioeconomic', 'expansions', 'supplied', 'noncompliant', 'log', 'cits', 'mass', 'milten', 'berger', 'dialogues', 'friends', 'youngest', 'liked', 'origins', 'deafened', 'nuclei', 'microelectrodes', 'microstimulation', 'strict', 'weakness', 'paretic', 'pronounced', 'relied', 'driver', 'capabilities', 'neef', 'shade', 'miller', 'rapp', 'cult', 'obfuscation', 'mythical', 'failure', 'box', 'governed', 'surplus', 'challenged', 'visited', 'hopes', 'closely', 'align', 'highway', 'unspoken', 'biases', 'excellent', 'defining', 'details', 'misuse', 'claim', 'ludwig', 'pizza', 'risley', '1968', 'repositioned', 'worn', 'modeled', 'implying', 'unsuccessful', 'stuffed', 'afternoon', 'evening', 'sug', 'mop', 'mug', '3rd', 'waned', 'rotating', 'luiselli', 'cameron', 'mediation', 'perpetual', 'composed', 'tie', 'qi', 'ica', 'mat', 'sop', 'bbs', 'sis', 'signi', 'bilaterally', 'abductors', 'sgd', 'mealtime', 'sgds', 'viability', 'cards', 'versatility', 'sighted', 'market', 'audiologic', 'bearing', 'berg', 'capitalizing', 'ngr', 'dense', 'habilitation', 'decelerative', 'consumer', 'stimulators', 'shapers', '00', 'recoup', '178', 'credibility', 'durable', 'observing', 'qualities', 'midday', 'publishing', 'prevalent', 'ago', 'substance', 'abuse', 'submitting', 'prolonged', 'snickers', 'identifies', 'crucial', 'broadly', 'books', 'elaborate', 'welcomes', 'exceptionalities', 'legitimized', 'behaviorally', 'disparity', 'calculating', 'statistic', '1978', 'peterson', 'reiss', 'shea', 'electrically', 'intramuscular', 'ambulated', 'cane', 'wk', 'residences', 'companion', 'jones', 'certification', 'continent', 'videotaping', 'contributed', 'au', 'manipulatives', 'preacademic', 'ababcbc', 'controversy', 'uncertainties', 'fundamentally', 'contemporary', 'nonconducive', 'districts', 'hostile', 'priorities', 'symposium', 'orientations', 'conceptualized', 'noting', 'incorporation', 'gathered', 'recurred', 'agrammatic', 'irt', 'interresponse', 'macintosh', 'nonparametric', 'koehler', 'levin', 'illustration', 'belong', 'ice', 'competencies', 'emitted', 'approximate', 'quiz', 'increment', 'deliveries', 'adjusting', 'proportional', 'adjusted', 'shot', 'perfectly', 'preceding', 'substrate', 'percentile', 'sen', 'otoneurologic', 'deriving', 'convergence', 'otoneurosurgery', 'compares', 'drawbacks', 'otitis', 'terminated', 'assignment', 'credit', 'departure', 'differentiated', 'chained', 'organisation', 'profession', 'otologic', 'visipitch', 'integrating', 'demonstration', 'economically', 'oppressed', 'favorably', 'fairness', '5th', 'soft', 'historical', 'fundamental', 'aspect', 'evolution', 'converging', 'diverging', 'fruitful', 'bugs', 'depend', 'ghitza', 'won', 'jumbo', 'flexible', 'sleeves', 'elbow', 'permitted', 'jobs', 'chalkboard', 'decorating', 'organizing', 'tapes', 'convenience', 'checkout', 'expiratory', 'stream', 'traces', 'prognostic', 'false', 'electric', 'artifacts', 'gives', 'root', 'attribute', 'disturbances', 'inductance', 'plethsymography', 'respitrace', 'rib', 'cage']</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1988</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>['children', 'study', 'design', 'behavior', 'treatment', 'results', 'video', 'participants', 'training', 'effects', 'used', 'intervention', 'autism', 'using', 'students', 'multiple', 'use', 'baseline', 'based', 'self', 'analysis', 'skills', 'research', 'single', 'reinforcement', 'speech', 'social', 'modeling', 'computer', 'communication', 'functional', 'data', 'subject', 'disabilities', 'teaching', 'instruction', 'performance', 'effective', 'program', 'response', 'effectiveness', 'feedback', 'therapy', 'assessment', 'time', 'learning', 'showed', 'behaviors', 'generalization', 'behavioral', 'increased', 'play', 'subjects', 'language', 'child', 'conditions', 'maintained', 'discussed', 'methods', 'procedures', 'following', 'visual', 'condition', 'case', 'phase', 'participant', 'control', 'support', 'group', 'studies', 'responses', 'evaluate', 'staff', 'words', 'task', 'stimulus', 'stimuli', 'technology', 'word', 'aac', 'test', 'levels', 'evaluated', 'indicated', 'purpose', 'individuals', 'practice', 'method', 'attention', 'verbal', 'interventions', 'developmental', 'tasks', 'effect', 'experimental', 'increase', 'problem', 'examined', 'procedure', 'school', 'adults', 'stereotypy', 'measures', 'setting', 'high', 'clinical', 'strategies', 'treatments', 'rate', 'evidence', 'patients', '10', 'student', 'strategy', 'device', 'classroom', 'present', 'automatic', 'outcomes', 'compared', 'significant', 'vocal', 'implications', 'management', 'findings', 'settings', 'reading', 'teach', 'acquisition', 'items', 'parents', 'follow', 'production', 'demonstrated', 'disorders', 'pain', 'generalized', 'sessions', 'aphasia', 'improve', 'teacher', 'home', 'frequency', 'maintenance', 'received', 'peer', 'development', 'aba', 'presented', 'number', 'conducted', 'preferred', 'efficacy', 'positive', 'young', 'problems', 'matching', 'suggest', 'provided', 'assessed', 'analyses', 'target', 'percentage', 'hearing', 'approach', 'review', 'food', 'participated', 'probe', 'stuttering', 'noncontingent', 'activity', 'preference', 'phases', 'produced', 'different', 'symbol', 'activities', 'future', 'specific', 'mental', 'schedules', 'novel', 'years', 'improved', 'prompting', 'accuracy', 'low', 'daily', 'moderate', 'paper', 'software', 'correct', 'implemented', 'intellectual', 'rehabilitation', 'stimulation', 'provide', 'associated', 'determine', 'model', 'injury', 'increasing', 'interaction', 'designed', 'safety', 'did', 'new', 'reinforcer', 'related', 'disorder', 'improvements', 'week', 'taught', 'instructional', 'current', 'recognition', 'hand', 'examine', 'level', 'higher', 'access', 'addition', 'individual', 'skill', 'severe', 'applied', 'picture', 'primary', 'alternative', 'included', 'schedule', 'physical', 'measured', 'delay', 'process', 'improvement', 'information', 'reduce', 'relative', 'objective', 'assess', 'basic', 'pecs', 'responding', 'terms', 'consisted', 'systems', 'communicative', 'community', 'direct', 'auditory', 'reversal', 'game', 'care', 'grocery', 'evaluation', 'greater', 'reported', 'adhd', 'alternating', 'suggested', 'outcome', 'effort', 'abstinence', 'stroke', 'conclusions', 'persons', 'natural', 'trial', 'function', 'year', 'compare', 'sets', 'devices', 'relations', 'application', 'impact', 'delivery', 'variables', 'cognitive', 'independent', 'quality', 'ability', 'exchange', 'second', 'age', 'improving', 'written', 'processing', 'trained', 'probes', 'smoking', 'work', 'games', 'important', 'investigated', 'appropriate', 'controlled', 'motor', 'weeks', 'retardation', 'preschool', 'duration', 'reduced', 'package', 'brief', 'including', 'decreased', 'observed', 'changes', 'interactions', 'teachers', 'environment', 'investigate', 'sample', 'months', 'monitoring', 'term', 'comprehension', 'exhibited', 'investigation', 'article', 'observation', 'additional', 'indicate', 'session', 'gambling', 'long', 'choice', 'criteria', 'significantly', 'exercise', 'education', 'experiment', 'selected', 'background', 'gains', 'identified', 'focused', 'completed', 'programming', 'matched', 'old', 'adult', 'employed', 'contingent', 'stories', 'chronic', 'discrimination', 'testing', 'asd', 'developed', 'lower', 'variable', 'available', 'models', 'adolescents', 'conclusion', 'combination', 'replicated', 'deficit', 'life', 'parent', 'sensory', 'non', 'techniques', 'point', 'goal', 'challenging', 'assisted', 'computerized', 'automatically', 'occurred', 'min', 'seven', 'internet', 'step', 'post', 'extinction', 'aided', 'pica', 'object', 'free', 'early', 'learned', 'delivered', 'various', 'comparison', 'assessments', 'knowledge', 'hyperactivity', 'interactive', 'peers', 'revealed', 'characteristics', 'vivo', 'field', 'health', 'tool', 'conversational', 'sib', 'injurious', 'increases', 'discussion', 'promote', 'successful', 'psychology', 'followed', 'similar', 'change', 'set', 'completion', 'validity', 'personal', 'literature', 'main', 'correctly', 'programs', 'approaches', 'role', 'previous', 'inappropriate', 'diagnosed', 'graphic', 'preschoolers', 'brain', 'vr', 'meta', 'anxiety', 'able', 'disease', 'head', 'dependent', 'day', 'reduction', 'mean', 'occupational', 'targeted', 'foods', 'designs', 'pre', 'educational', 'traditional', 'withdrawal', 'consequences', 'exposure', 'disruptive', 'math', 'required', 'differential', 'collected', 'systematic', 'directions', 'fixed', 'syndrome', 'contingencies', 'aged', 'recording', 'reinforced', 'family', 'immediate', 'decrease', 'dimensions', 'types', 'demonstrate', 'protocol', 'spoken', 'equivalence', 'potential', 'output', 'events', 'form', 'variability', 'cues', 'reserved', 'symbols', 'resulted', 'periods', 'subsequent', 'videotaped', 'mouthing', 'impairments', 'acquired', 'context', 'aids', 'rights', 'spectrum', 'given', 'delayed', 'seating', 'shown', 'questions', 'type', 'typically', 'need', 'researchers', 'modified', 'public', 'measure', 'varied', 'implementation', 'experience', 'slot', 'compliance', 'scores', 'repeated', 'vsm', 'limited', 'reducing', 'mild', 'highly', 'leisure', 'recorded', 'programmed', 'overall', 'complete', 'means', 'range', 'common', 'versus', 'scale', 'series', 'clinic', 'order', 'fct', 'influence', 'media', 'developing', 'elsevier', 'engagement', 'cases', 'samples', 'laboratory', 'steps', 'patient', 'behaviour', 'oral', 'ratio', 'eating', 'components', 'gait', 'benefits', 'blocking', 'ratings', 'sound', 'hr', 'medication', 'obtained', 'individualized', 'tested', 'therapists', 'academic', 'untrained', 'identify', 'component', 'involving', 'prompts', 'fast', 'preliminary', 'times', 'involved', 'rates', 'little', 'period', 'letter', 'mediated', 'multi', 'wheelchair', 'complex', 'fluency', 'service', 'presentation', 'perspective', 'reinforcers', 'perceived', 'met', 'literacy', 'agreement', 'discrete', 'analyzed', 'criterion', 'relatively', 'methodology', 'contingency', 'promoting', 'suggests', 'item', 'tests', 'ncr', 'punishment', 'useful', 'request', 'movement', 'aims', 'observational', 'general', 'introduced', 'videotape', 'groups', 'instructions', 'virtual', 'operant', 'conversation', 'enhancing', 'therapeutic', 'initiations', 'members', 'blending', 'regarding', 'achieved', 'routines', 'reductions', 'enhance', 'solution', 'special', 'surface', 'typical', 'machine', 'postural', 'practices', 'transfer', 'providing', 'variety', 'plus', 'produce', '30', 'people', 'described', 'impairment', 'standard', 'establishing', 'therapist', 'relevant', 'disability', 'short', 'continuous', 'repair', 'sounds', 'effectively', 'report', 'ineffective', 'sbw', 'randomized', 'intensive', 'movements', 'identification', 'learn', 'signs', 'negative', 'collection', 'prompt', 'initial', 'integration', 'facts', 'contextual', 'toy', 'players', 'assistance', 'phoneme', 'conduct', 'modelling', 'active', 'btds', 'girls', 'relationship', 'initiated', 'phonological', 'initiation', 'concurrent', 'toys', 'cooking', '15', 'categories', 'substantial', 'intervals', 'voucher', 'conventional', 'player', 'mobility', 'focus', 'formula', 'evaluating', 'boys', 'equipment', 'random', 'making', 'varying', 'left', 'progressive', 'taking', 'small', 'planning', 'asperger', 'consistent', 'especially', 'profound', 'requesting', 'fading', 'possible', 'combined', 'combining', 'cycle', 'delays', 'length', 'result', 'conversations', 'format', 'cost', 'requests', 'real', 'month', 'store', 'needed', 'observations', 'absence', 'microsoft', 'cigarette', 'example', 'implant', 'functions', 'decreases', 'middle', 'having', 'board', 'awareness', 'participation', 'aspects', 'appeared', 'total', 'difficulty', 'aid', 'conducting', 'augmentative', 'female', 'vouchers', '11', 'factors', 'classes', 'coding', 'experienced', 'statistical', 'empirical', 'rules', 'descriptive', 'large', 'extended', 'sign', 'understanding', 'course', 'inspiratory', 'videotapes', 'helping', 'goals', 'analytic', 'return', 'constant', 'end', 'maintaining', 'benefit', 'pressure', 'impaired', 'provides', 'knee', 'successfully', '16', 'dyads', 'help', 'elementary', 'cai', 'recovery', 'parameters', 'created', 'adaptive', 'secondary', 'proportion', 'patterns', 'law', 'residents', '2007', 'speaking', 'letters', 'loss', 'sucking', 'science', 'structured', 'exposed', 'published', 'voice', 'presence', 'complexity', 'simulated', 'animated', 'simple', 'line', 'drivers', 'tutoring', 'choices', 'recall', 'guided', 'issues', 'despite', 'perform', 'strength', 'electrodes', '40', 'competing', 'medical', 'biofeedback', 'job', 'pairing', 'differences', 'clips', 'living', 'memory', 'manipulation', 'recommendations', 'placebo', 'organizational', 'make', 'authors', 'recordings', 'escape', 'establish', 'served', 'caregiver', 'engaged', 'technique', 'text', 'trials', 'story', 'feasibility', 'arm', 'aim', 'led', 'accurate', 'validation', 'forms', '20', 'deposit', 'theory', 'nicotine', 'needs', 'situations', 'aphasic', 'multiplication', 'excel', 'extension', 'supported', 'size', 'generally', 'immediately', 'efforts', 'discuss', 'statistically', 'nonpreferred', 'mathematics', 'systematically', 'affected', '12', 'robot', 'according', 'precision', 'remained', 'minute', 'seat', 'praise', 'abab', 'existing', 'interval', 'assessing', 'indirect', 'person', 'experiments', 'stutter', 'questionnaire', '2005', 'ft', 'cerebral', 'noise', 'error', 'survey', 'conditional', 'generated', 'specifically', 'switch', 'seatbelt', 'half', 'reward', 'corresponding', 'facial', 'articles', 'posting', 'reports', 'dysarthria', 'book', 'static', 'adapted', 'recent', 'defined', 'phone', 'male', 'finally', 'photographs', 'difficulties', 'allowed', 'mechanical', 'vocabulary', 'solving', 'programme', 'partners', 'better', 'deficits', 'occurrence', 'writing', 'units', 'rapid', 'took', 'empirically', 'status', 'examining', 'grade', 'world', 'selection', 'exercises', 'relationships', 'monitor', 'regular', 'human', 'risk', 'sequences', 'graph', 'examples', 'blind', 'patch', '95', 'reviewed', 'clinically', 'actions', 'commonly', 'behaviours', 'cochlear', 'paired', 'fear', 'stable', 'pictorial', 'aides', 'stability', 'administered', 'ad', 'electronic', 'pictures', 'wiley', 'controls', 'performed', 'vs', 'relation', 'football', 'utility', 'processes', 'scoring', 'success', 'noncompliance', 'days', 'computers', 'embedded', 'frequently', 'producing', 'shows', 'threshold', 'rating', 'college', 'objects', 'efficient', 'dot', 'train', 'larger', 'examination', 'way', 'practical', 'probability', 'multielement', 'reached', 'digital', 'aberrant', 'areas', 'identifying', 'near', 'difference', 'antecedent', 'face', 'stereotypic', 'breath', 'cbvi', 'pilot', 'facilitate', 'tact', 'proposed', 'users', 'continued', 'preferences', 'calling', 'prior', 'dynamic', 'postures', 'shared', 'partial', 'removal', 'explore', 'include', 'lectures', 'operations', 'principles', 'roles', 'respond', 'ages', 'right', 'materials', 'traumatic', 'transdermal', 'concerns', 'material', 'palsy', 'men', 'acceptance', 'drug', 'input', 'university', 'electromyography', 'values', 'penetrating', 'history', 'private', 'progress', 'suggesting', 'primarily', 'electrode', 'run', 'protective', 'independently', '80', 'severity', 'fewer', 'st', 'women', 'boy', 'implement', 'nature', 'heart', 'personalized', 'minutes', 'inclusive', 'normal', 'inspection', 'abilities', 'leg', 'tools', 'upper', '2004', 'perception', '2000', 'scripted', 'reciprocal', 'extent', 'scenarios', 'restraint', 'clear', 'reality', 'directly', 'intraoperative', 'playing', 'environmental', 'initially', 'efficiency', 'sentences', 'dvd', 'longer', 'obtain', 'performances', 'rehearsal', 'muscle', 'event', 'abductor', 'powered', 'clients', 'demands', 'weekly', 'printed', 'spontaneous', 'basketball', 'judges', 'team', 'discipline', 'apraxia', 'degree', 'objectives', 'decoding', 'client', 'hypothesis', 'balance', 'reaching', 'maintain', 'limitations', 'purchasing', 'multimedia', 'rated', 'sons', 'vocalizations', 'john', 'copyright', 'cat', 'shots', 'aggression', 'unilateral', 'simulation', 'combinations', 'web', 'adolescent', 'giving', 'driving', 'mr', 'domestic', 'importance', 'finger', 'fns', 'motion', 'read', 'pass', 'working', 'ssp', 'observer', 'power', 'treating', 'seen', 'twice', 'final', 'coaching', 'deliver', '25', 'prediction', 'grammar', 'centered', 'print', 'naive', 'laryngeal', 'cue', 'theoretical', 'appears', 'sizes', 'imitation', 'portable', 'translucency', 'machines', 'narrative', 'foot', 'sports', 'hospital', 'respectively', 'interobserver', 'addressed', 'require', '100', 'points', 'pairs', 'flying', 'american', 'intensity', 'sight', '13', 'autistic', 'discomfort', 'color', 'pretend', 'displayed', 'interviews', 'ergonomic', 'percentages', 'nerve', 'dbs', 'subsequently', 'environments', 'spinal', 'talk', 'domains', 'trend', 'score', 'acoustic', 'mastery', 'persistent', 'restaurants', 'scored', 'supports', 'iconicity', 'alzheimer', 'immediacy', 'anger', 'orthoses', 'aisle', 'impulsivity', 'acetaminophen', 'utilized', '24', 'develop', 'satisfaction', 'propose', 'discriminations', 'receiving', 'previously', 'functioning', 'describes', 'services', 'independence', 'measurement', 'analysts', 'lg', 'rird', 'extremity', 'weight', 'requirements', 'technical', 'potentially', 'residential', 'braille', 'visually', 'sport', 'showing', 'performing', 'eye', 'necessary', 'telephone', '1998', 'exemplars', 'class', 'hair', 'activation', 'naturalistic', 'pabi', 'double', 'treadmill', 'affective', 'decreasing', 'agent', 'automated', 'majority', 'reporting', 'recently', 'attempt', 'older', 'elements', 'names', 'ear', 'listener', 'equation', 'quantitative', 'office', 'interpretation', 'tactile', 'assigned', 'opportunities', 'consisting', 'selecting', 'spelling', 'facilitated', 'speecheasy', 'longitudinal', 'sdl', 'posttreatment', 'orienting', 'array', 'tm', 'watching', 'demonstrating', 'sustained', 'skinner', 'operants', 'comparisons', 'efficiently', 'frequent', 'lack', 'assistive', 'sufficient', 'view', 'curriculum', 'unit', 'contact', 'significance', 'attempted', 'extend', 'verbalizations', 'cop', 'particular', 'addressing', 'refusal', 'infants', 'fact', 'inclusion', 'content', 'replication', 'select', 'identical', 'raised', 'posture', 'hour', 'drill', 'athletes', 'orthographic', 'enrolled', 'aggressive', 'location', 'blissymbols', 'neglect', 'alignment', 'beginning', 'affect', 'concurrently', 'engage', 'live', 'contexts', 'beneficial', 'describing', 'write', '14', 'chat', 'differed', 'block', 'suggestions', 'plan', 'differentially', 'hip', 'advocacy', 'participating', 'spray', 'traction', 'riding', 'token', 'match', 'pda', 'methodological', 'grip', 'tremor', 'socially', 'mands', 'resulting', 'involvement', 'rett', 'widely', 'implementing', 'momentum', '2002', 'errors', 'tic', 'checklist', 'formulas', 'entailment', 'unfamiliar', 'standardized', 'substantially', 'finding', 'consecutive', 'affecting', 'mathematical', 'quickly', 'reliable', 'participate', 'engaging', 'population', 'fm', 'randomly', 'suppressed', 'soccer', 'hierarchical', 'linear', 'generation', 'viewed', 'introduction', 'derived', 'usage', 'cueing', 'vcs', 'wide', 'minimal', 'redirection', 'lateral', 'focuses', 'developmentally', 'unprompted', 'medium', 'reinforcing', 'past', 'difficult', 'occurring', 'generating', '19', 'features', 'entire', 'graphs', 'creating', 'procedural', 'earn', 'question', 'repetition', 'longstanding', 'parkinson', 'requested', 'indicates', 'im', 'contribute', 'technologies', 'consistently', 'schools', 'comparing', 'conditioning', 'best', 'professionals', 'smart', 'continue', 'position', 'afos', 'employing', 'hdt', 'applications', 'enhancement', 'claustrophobic', 'slightly', 'stores', 'tense', 'represents', 'baselines', 'mobile', 'pocket', 'pc', 'concepts', 'added', '22', 'resource', 'trends', 'growing', 'topic', 'interview', 'twirling', 'habit', 'attained', 'verb', 'established', 'accompanied', 'stress', 'pencil', 'brainstem', 'includes', 'understand', 'considered', 'populations', 'communicate', 'disruptions', 'pel', 'safe', 'bst', 'properties', 'interviewing', 'open', 'opioid', 'pitch', 'selectivity', 'critical', 'area', 'involves', '1985', 'allows', 'feeding', 'airway', 'treated', 'partner', 'win', 'acute', 'grammatical', 'online', 'isolation', 'efficacious', 'positions', 'cord', 'fourth', 'families', 'a1', 'a2', 'woman', 'joint', 'exploring', 'placed', 'pd', 'phobia', 'expressive', 'practised', 'physiotherapy', 'manipulated', '18', 'girl', 'skin', 'appear', 'clinician', 'vehicles', 'spouse', 'measurements', 'psychological', 'remaining', 'failed', 'dti', 'discriminative', 'learners', 'integrity', 'explored', 'morning', 'happiness', 'computerised', 'customer', 'reliability', 'sought', 'allocation', 'providers', 'satiation', 'asthma', 'cover', 'preservation', 'module', 'challenges', 'withdrawn', 'pwds', 'facilitating', 'modalities', '90', 'create', 'blended', 'explicit', 'removed', 'detection', 'practitioners', 'volitional', 'functionally', 'cfs', 'gamblers', 'explanations', 'specified', 'multicomponent', 'monitored', 'influenced', 'gained', 'constructed', 'combinatorial', 'speed', 'relational', 'hypothesized', 'displacement', 'attend', 'dementia', 'currently', 'explain', 'writers', 'journal', 'fashion', 'scripts', 'manual', 'user', 'carried', 'handwriting', 'unable', 'poor', 'telemedicine', 'iowa', 'scanning', 'uvn', 'ihp', 'payback', 'educators', 'allow', 'pattern', 'receive', 'music', 'rewards', 'nfc', 'meaningful', 'photograph', 'statements', 'collecting', 'fr', 'inventory', '21', 'pm', 'ill', 'hands', 'combine', 'dtt', 'classrooms', 'bilateral', 'limb', 'conjunction', 'stimulant', 'sportsmanlike', 'interruption', 'rumination', 'reinforce', 'concomitant', 'simulations', 'base', 'spent', 'sentence', '61', 'achieve', 'plane', 'outpatient', 'segments', 'demonstrates', 'naming', 'progressively', 'ranged', 'mainstream', 'body', 'factored', 'exploration', 'enabled', 'algorithms', 'deafness', 'listeners', 'sensitivity', 'passing', 'contrast', 'stop', 'ffw', 'lls', 'charcot', 'marie', 'tooth', 'essay', 'toilet', 'intrusive', 'microprocessor', 'prosthetic', 'completing', 'carbon', 'monoxide', 'exploratory', 'tbi', 'parental', 'called', 'furthermore', 'mechanisms', 'studied', 'watched', 'flashcards', 'carr', 'perfect', 'haworth', 'confederate', 'typing', 'modification', 'attentive', 'enhanced', 'dyspraxia', 'room', 'managing', 'network', 'repetitive', 'presentations', 'stuttered', 'syllables', 'supervision', 'cbi', 'additionally', 'place', 'mastered', 'spell', 'balls', 'prelinguistic', 'achievement', 'easily', 'al', 'optimal', 'et', 'prize', 'emotional', 'bug', 'homes', 'scientific', 'conceptual', 'basis', 'actual', 'sie', 'recombinative', 'rps', 'expression', '55', 'lhs', 'address', 'monosyllabic', 'advantages', 'man', 'elicited', 'emerged', 'clinics', 'complied', 'assistant', 'picking', 'augmented', 'utterances', 'fold', 'suspension', 'pathological', 'does', 'occur', 'noted', 'gradual', 'attitudes', 'wearing', 'electrophysiologic', 'apply', 'consideration', 'determined', 'amplification', 'somewhat', 'acceptability', 'vmc', 'utilizing', 'easy', 'promising', 'predicted', 'lasted', 'investigating', 'external', 'meal', 'spoon', 'driven', 'look', 'foam', 'neuromotor', 'indicators', 'commitment', 'computing', 'sublexical', 'avoid', 'regulated', 'policy', 'equally', 'rotations', 'searches', 'pews', 'poking', 'remain', 'readily', 'edible', 'ms', 'pervasive', 'evaluations', 'sm', 'mixed', 'allocated', 'analyze', 'presents', 'falls', 'contained', 'camera', 'feasible', 'preventing', 'caregivers', 'achieving', 'measuring', 'sleep', 'cordic', 'guide', 'decision', 'played', 'questionnaires', 'wore', 'cued', 'thinned', 'break', 'start', 'script', 'recipes', 'breathing', 'counterbalanced', 'clinicians', 'modifying', 'surgical', 'depicted', 'musculoskeletal', 'economy', 'sertraline', 'intake', 'paradigm', 'reprimands', 'warranted', 'perceptions', 'vehicle', 'gearshift', 'residual', 'hemisphere', 'responsive', 'supporting', 'manage', 'began', '60', 'subthalamic', 'nucleus', 'path', 'label', '05', 'zero', '2006', 'situation', 'concept', 'cbt', 'version', 'engineering', 'applying', 'elearning', 'recommender', 'extinguishing', 'kickball', 'ungrammatical', 'errorless', 'ranging', 'videomonitoring', '2003', 'directed', 'add', 'arbitrary', 'aversiveness', '50', 'document', 'availability', 'statement', 'maternal', 'partially', 'taken', '85', 'hard', 'tracing', 'comfort', 'weighted', 'morphology', 'formal', 'cerebrovascular', 'tutor', 'descriptors', 'graduate', 'graphing', 'youth', 'abc', 'dpi', 'generalizing', 'copy', 'dysphonia', 'irritation', 'acquire', 'incorporated', 'dwelling', 'replacement', 'standards', 'avoidance', 'force', 'profile', 'responsible', 'wrist', 'fail', 'documented', 'relate', 'supervisors', 'generalize', 'manding', 'highchair', 'loneliness', 'mood', 'universal', 'assignments', 'noncancer', '65', 'reliably', 'echolalia', 'prereading', 'autobiographical', 'kindergarten', 'valid', 'prevention', 'addiction', 'maximize', 'faster', 'resistance', 'infrared', 'conditioned', 'burkholder', 'comparable', 'voca', 'marked', 'reason', 'mouth', 'dental', 'consumption', 'baer', 'particularly', 'note', 'yielded', 'requiring', 'technological', 'rushing', 'compliment', 'season', 'overview', 'exertion', 'attainment', 'submaximal', 'tokens', 'extends', 'key', 'gymnastics', 'bite', 'degrees', 'cause', 'faded', 'exact', 'gender', 'robust', 'athletic', 'intersections', 'business', 'estimation', 'establishment', 'nms', 'generalised', 'excess', 'influential', 'dimension', 'stim', 'deprivation', 'equations', 'nonconcurrent', 'states', 'unmatched', 'reviews', 'concern', 'healthy', 'advances', 'neighborhood', 'contractures', 'sclerosis', 'uses', 'ties', 'thumb', 'organizations', 'value', 'engine', 'lead', 'signal', 'known', 'expectations', 'opportunity', 'accepted', 'sent', 'variance', 'collegiate', 'competition', 'smokers', 'tics', 'represent', 'national', 'yoga', 'workstation', 'started', 'facility', 'motivating', 'presenting', 'pentop', 'treat', 'phonomotor', 'illustrate', '1994', 'legs', 'later', 'white', 'dro', 'viewing', 'contract', 'exhibit', 'iv', 'validated', 'outside', 'counts', 'tourette', 'pretest', 'dose', 'hint', 'reasons', 'interact', 'capi', 'matrix', 'nontarget', 'greeting', 'aching', 'electronically', 'sources', 'abolishing', 'vomit', 'operation', 'instructed', 'explanation', 'representing', 'magnitude', 'manifested', 'workers', 'mutual', 'locate', '120', 'idiosyncratic', 'pulling', 'percent', 'desktop', 'analogue', 'verbally', 'researcher', 'emerging', 'experts', 'stokes', 'ignored', 'mucosa', 'like', 'cross', 'keller', 'legally', 'considerable', 'emg', 'articulation', 'investigator', 'eyes', 'feature', 'map', 'transformations', 'dramatically', 'analgesic', 'desire', 'great', 'specifications', 'edited', 'postflight', 'counter', 'tms', 'flight', 'assist', 'greatest', 'focusing', 'ld', 'caused', 'arithmetic', 'childhood', 'challenge', 'repertoires', 'architecture', 'reactivity', 'insufficient', 'discriminate', 'threatening', 'starbright', 'choose', 'projects', 'stones', 'stem', 'expected', 'provision', 'conclude', 'physicians', 'numbers', 'originally', 'desensitization', 'breakdowns', 'informed', 'exhaustive', 'metaphor', 'project', 'good', 'oriented', 'incredible', 'gt', 'cocaine', '45', 'anchors', 'winning', 'action', 'activations', 'usually', 'framework', 'calculated', 'passages', 'pediatric', 'minimum', 'mip', 'juvenile', 'views', 'mail', 'fine', 'newly', 'buprenorphine', 'issue', 'ancillary', 'cervical', 'innovative', 'decade', 'plays', 'baldi', 'photos', 'league', 'frost', 'homework', 'pneumosensorial', 'papers', '1997', 'shift', 'employees', 'consequent', 'accident', 'thinking', 'prototype', 'productivity', 'fiction', 'scrimmages', 'continuity', 'personnel', 'illustrating', 'compression', 'indicating', 'retrospective', 'rapidly', 'exclusively', 'ssd', 'novice', 'distributed', 'simply', 'cp', 'tai', 'ppm', 'contextually', 'formats', 'likelihood', 'parts', 'asked', 'paralysis', 'trainer', 'dyspnea', 'resident', 'maximal', 'mmn', 'negativity', 'vectors', 'comply', 'undergraduate', 'execution', 'lap', 'argues', 'clearly', 'explicitly', 'allowing', '001', 'rom', 'histories', 'truetales', '79', '98', 'passive', 'deviant', 'multicenter', 'frontal', 'center', 'equal', 'belt', 'anomia', 'respective', 'divergence', 'prospective', 'recommended', 'mismatch', 'improves', 'distribution', 'communicated', 'arthritis', 'amounts', 'consonant', 'approximately', 'simultaneous', '52', 'incidental', 'relief', 'edition', 'refers', 'geller', 'dc', 'adjunct', 'turn', 'description', 'coordinate', 'topographies', 'damian', 'stn', 'promise', 'classwide', 'incomplete', 'steady', 'cognition', 'discontinued', 'adverse', 'deep', 'appropriately', 'transferred', 'nursing', 'amputees', 'answer', 'hill', 'wolf', 'rvi', 'returned', 'referents', 'chip', 'easier', 'dct', 'cr', 'consequence', 'op', 'discourse', 'nail', 'correlated', 'narratives', 'attempts', 'correspond', 'discovered', 'member', 'named', 'rcts', 'examines', 'median', 'nonoverlapping', 'tutorials', 'impede', 'meet', 'aimed', 'punisher', 'ratios', 'recruited', 'replications', 'sensitive', 'progressed', 'sequence', 'generate', 'supplement', 'underlie', 'confidence', 'average', 'fetal', 'supplemental', 'encouraged', 'speakers', 'semantic', 'automaticity', 'alcohol', 'heavy', 'substitute', 'deal', 'feeling', 'beck', 'electrical', 'surgery', 'resources', 'conflicts', 'consider', 'injuries', '27', 'observe', 'bias', 'guidelines', 'latency', 'modality', 'predict', 'preparation', 'termination', 'induction', 'laser', 'recapture', 'eliminated', 'closed', 'motivation', 'concentration', 'beam', 'journals', 'press', 'ambulation', 'compensatory', 'p5', 'p1', 'handbook', '2008', 'realistic', 'gaming', 'routine', 'depth', 'topography', 'table', 'band', 'aerobic', 'elderly', 'intended', 'occurrences', 'lbp', 'pbws', 'pedals', 'broad', 'databases', 'spine', 'flavor', 'psychosocial', 'familiar', 'sec', 'unloading', 'endurance', 'postintervention', 'wheelchairs', 'compliments', 'walking', 'represented', 'screen', 'medicine', 'prose', 'exemplar', 'instructor', 'striving', 'coded', 'formed', 'containing', 'equivalent', 'struggle', 'evident', 'appreciation', 'come', 'bundle', 'cooperation', 'obm', 'aed', 'contoured', 'advanced', 'index', 'alternated', 'certain', 'recreational', 'miss', 'neurofibromatosis', 'motoric', 'ways', 'neutral', 'phrases', 'abnormal', 'density', 'wrote', 'freezes', 'nonverbal', 'walker', 'favorite', 'clarification', 'kinesia', 'meals', 'selective', 'paradoxa', 'popular', '43', 'separate', 'exclusion', 'professional', 'judged', 'photo', '1977', 'externalizing', 'displaying', 'sitting', 'exposing', '1995', 'bimanual', 'qualitative', 'transformation', 'willingness', 'meets', 'intralesson', 'representation', '36', 'probabilistic', 'comments', 'differing', 'experimenters', 'lottery', 'options', '39', 'limitation', 'numerous', 'link', 'opening', 'coordination', 'forword', 'thirty', 'sling', '1993', 'absent', 'themes', 'emitting', 'synthetic', 'regrand', 'earned', 'db', 'distinguish', 'source', 'schoolwide', 'destructive', 'extreme', 'gain', 'vol', 'topics', 'plans', 'durations', 'emergent', 'nonpathological', 'depression', 'records', 'mode', 'answers', 'limits', 'considerably', 'validate', 'analysed', 'moved', 'ball', 'timed', 'flexion', 'rtt', 'ct', 'categorization', 'attitude', 'changed', 'onset', 'linguistic', 'argued', 'product', 'entailed', '1999', 'ease', 'mothers', 'enrichment', 'walk', 'targets', 'designing', 'psychotherapeutic', 'unknown', 'concluded', 'evidenced', 'regard', 'incorrect', 'palin', 'adding', 'contribution', 'acceptable', 'induced', 'wear', 'eap', 'cessation', 'opiate', 'vic', 'sup', 'combines', 'reviewers', 'automation', 'encourages', 'postexercise', 'count', 'english', 'confirm', 'algebraic', 'trigonometric', 'rectangular', 'vowel', 'split', 'accompanying', 'bondy', 'translabyrinthine', 'repositioning', 'rigid', 'powerpoint', 'boxed', 'briefly', 'tradition', 'seconds', 'diverse', 'generality', 'exception', 'syllable', 'instructive', '70', 'vestibular', 'schwannoma', 'biobehavioral', 'rural', 'just', 'greetings', 'facilitates', 'correction', 'chose', 'aversive', 'pivotal', 'expanding', 'restricted', 'neurological', 'closures', 'cumulative', 'informative', 'signals', 'file', 'retention', 'underwent', 'pathologists', 'lesson', 'association', 'reassessment', 'introduces', 'guiding', '2001', 'mother', 'lesions', 'accessibility', 'makes', 'closing', 'persistence', 'house', 'central', 'purported', 'prompted', 'retained', 'ivf', 'timer', '94', 'redesign', 'effertiveness', 'leach', 'scales', 'pdms', 'deviation', 'kinematics', 'padding', 'grades', 'gaps', 'signaling', 'adjustment', 'horizontal', 'rma', '150', 'dissemination', 'broaden', 'inputs', 'domain', 'wizard', 'maximum', 'muscles', 'execute', 'think', 'classified', 'spastic', 'hours', 'kinematic', '01', 'masked', 'cursor', 'operate', 'dual', 'oxygen', 'posttraining', 'depicting', 'adequate', 'mutants', 'strings', 'lifelong', 'conservative', 'internalizing', 'intention', 'cuff', 'glottal', '87', 'leader', 'stopped', 'unchanged', 'textual', 'individually', 'fundamentals', 'pages', 'ail', 'cdc', 'incorporating', 'suppression', 'mg', 'tablets', 'meeting', 'variation', 'severely', 'anchor', 'boat', 'virtually', 'frames', 'reexposed', 'proved', 'quite', 'customize', 'continuum', 'termed', 'lists', 'hygiene', 'irrelevant', 'uppercase', 'lowercase', 'pains', 'physician', 'bulimics', 'closer', '63', 'analgesia', 'hierarchy', 'specificity', 'site', '76', '51', 'encouraging', '1992', 'serial', 'comes', 'norm', 'ignore', 'diversity', 'actually', 'pronated', 'shoe', 'bridge', 'evolving', 'universally', 'applicable', 'frame', 'justify', 'sat', 'indication', 'inconclusive', 'modes', 'runtime', 'placing', 'integrate', 'exist', 'construct', 'mucosal', 'carrier', 'interdependent', 'medications', 'emphasizes', 'calendar', 'asds', 'disseminate', 'legibility', 'informing', 'associations', 'reverberation', 'analgesics', 'employee', 'decades', 'amplitude', 'mechanism', 'inhalers', 'interpreted', 'arrive', 'interpret', 'demand', 'recess', 'holland', 'alternate', 'rime', 'corticosteroid', 'bronchodilator', 'readers', 'practicality', 'regimens', 'fit', 'tacts', '1987', 'psychologists', 'investigators', 'structures', 'decrement', 'sharing', 'pronation', 'episodes', 'causality', 'breakdown', 'comparative', 'odds', 'failures', 'consumed', 'lifestyle', 'convicted', 'assault', 'account', 'slope', 'adaptations', 'corticospinal', 'connectivity', 'code', 'mutation', 'slow', 'vomiting', 'bulimic', 'illnesses', 'feelings', 'offended', '2009', 'responders', 'commentary', 'pursue', 'contextualized', 'computation', 'hlac', 'regression', 'commands', 'pinch', 'dexterity', 'becs', 'exchanges', 'neural', 'biology', 'limit', 'interacting', 'keyboard', 'emotionally', 'disturbed', 'transportability', 'paucity', 'competence', 'adoption', 'nih', 'happens', 'lerman', 'controversial', 'managed', 'seriously', 'commercial', 'pay', 'sense', 'phenomenon', 'neck', 'sustaining', 'tray', 'learns', 'local', 'udl', 'anticipatory', 'detect', 'watch', 'dictated', 'thought', 'internal', 'vm', 'superior', 'elicit', 'imagery', 'barriers', 'acquiring', 'phonology', 'phonetic', 'lexical', 'encoding', 'interpersonal', 'uk', 'sixteen', 'reflected', 'incorporate', 'videos', 'altering', 'mini', 'urinary', 'toileting', 'resistant', 'flashcard', 'applicability', 'communications', 'cooperating', 'experiencing', 'sfa', 'disciplines', 'likely', 'emit', 'simultaneously', 'diagnoses', 'multidisciplinary', 'psychiatry', 'jaba', 'arrived', 'radio', 'exit', 'colli', 'evaluative', 'guidance', 'investigations', '38', 'image', 'consists', 'ab', 'cancellation', 'lighthouse', 'posttest', 'inattention', 'phonemic', 'costs', 'attended', 'emergence', 'mealtimes</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3304</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>41419</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5292</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>433</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.826719576719577</v>
-      </c>
-      <c r="O5" t="n">
-        <v>21.6327751624043</v>
-      </c>
-      <c r="P5" t="n">
-        <v>9.220325998376923</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>115.1084782814069</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>['intervention', 'study', 'design', 'children', 'participants', 'results', 'students', 'video', 'based', 'behavior', 'training', 'research', 'single', 'using', 'asd', 'treatment', 'skills', 'autism', 'used', 'effects', 'use', 'social', 'multiple', 'analysis', 'case', 'baseline', 'data', 'studies', 'self', 'disabilities', 'communication', 'technology', 'modeling', 'interventions', 'effective', 'instruction', 'learning', 'teaching', 'subject', 'effectiveness', 'individuals', 'performance', 'behavioral', 'effect', 'speech', 'functional', 'aba', 'intellectual', 'reinforcement', 'school', 'computer', 'aac', 'time', 'support', 'behaviors', 'evidence', 'response', 'program', 'methods', 'outcomes', 'group', 'showed', 'feedback', 'high', 'increased', 'evaluated', 'sessions', 'child', 'visual', 'discussed', 'disorders', 'participant', 'compared', 'findings', 'prompting', 'assessment', 'practice', 'disability', 'activity', 'demonstrated', 'phase', 'implications', 'education', 'experimental', 'task', 'increase', 'purpose', 'teach', 'reading', 'teachers', 'therapy', 'method', 'positive', 'measures', 'included', 'procedures', 'following', 'review', 'significant', 'student', 'evaluate', 'future', 'improve', 'game', 'strategies', 'developmental', 'play', 'conducted', 'indicated', 'generalization', 'quality', 'problem', 'different', 'evaluation', 'classroom', 'development', 'maintained', 'stimulus', 'improved', 'preference', 'spectrum', 'approach', 'instructional', 'adults', 'acquisition', 'implementation', 'levels', 'people', 'cognitive', 'probe', 'physical', 'maintenance', 'provide', 'young', 'parents', 'present', 'efficacy', 'engagement', 'motor', 'suggest', 'peer', 'management', 'settings', 'conditions', 'examined', 'control', 'current', 'systematic', 'language', 'academic', 'procedure', 'applied', 'condition', 'responses', 'clinical', 'level', 'word', 'number', 'target', 'words', 'subjects', 'device', 'stereotypy', 'test', 'provided', 'related', 'stimuli', 'picture', 'activities', 'treatments', 'low', 'meta', 'alternating', 'implemented', 'setting', 'moderate', 'teacher', 'application', 'conclusions', 'model', 'skill', 'verbal', 'comparison', 'designs', 'specific', 'non', 'health', 'change', 'ipad', 'validity', 'phases', 'parent', 'assessed', 'years', 'severe', 'daily', 'follow', 'weeks', 'potential', 'patients', 'impact', 'examine', 'virtual', 'increasing', 'staff', 'literature', 'post', 'size', 'software', 'attention', 'tasks', 'interaction', 'improvement', 'devices', 'memory', 'reported', 'injury', 'function', 'changes', 'did', 'preferred', 'monitoring', 'individual', 'package', 'including', 'accuracy', 'overall', 'responding', 'age', 'independent', 'objective', 'new', 'trial', 'ability', 'access', 'developed', 'paper', 'elsevier', 'observed', 'associated', 'mean', 'prompts', 'scores', 'taught', 'early', 'improving', 'special', 'sample', 'adolescents', 'care', 'acquired', 'determine', 'rehabilitation', 'week', 'elementary', 'trials', 'investigated', '10', 'participated', 'improvements', 'brain', 'year', 'analyses', 'significantly', 'information', 'delivered', 'novel', 'outcome', 'rights', 'problems', 'small', 'session', 'addition', 'reserved', 'peers', 'vocabulary', 'need', 'rate', 'generalized', 'combined', 'designed', 'challenging', 'assess', 'context', 'appropriate', 'reduce', 'items', 'strategy', 'indicate', 'pre', 'community', 'completed', 'vocal', 'models', 'automatic', 'writing', 'criteria', '12', 'generating', 'conclusion', 'limited', 'direct', 'mobile', 'home', 'authors', 'programs', 'researchers', 'equivalence', 'assistive', 'measured', 'interactions', 'presented', 'received', 'able', 'class', 'patient', 'classrooms', 'assessments', 'alternative', 'living', 'rates', 'investigate', 'preschool', 'syndrome', 'complex', 'measure', 'secondary', 'promote', 'components', 'identified', 'help', 'aged', 'previous', 'systems', 'disruptive', 'good', 'anxiety', 'behaviour', 'terms', 'schedules', 'background', 'differential', 'work', 'additional', 'implement', 'increases', 'traditional', '2016', 'initial', 'article', 'knowledge', 'adapted', 'correct', 'contingency', 'needs', 'targeted', 'online', 'decreased', 'text', 'mathematics', 'needed', 'groups', 'old', 'diagnosed', 'process', 'reality', 'criterion', 'robot', 'variables', 'important', 'assisted', 'disorder', 'primary', 'hearing', 'pain', 'sizes', 'published', 'limitations', 'collected', 'environment', 'emotional', 'learned', 'compare', 'higher', 'developing', 'reporting', 'long', 'preliminary', 'games', 'trained', 'life', 'tablet', 'stimulation', 'large', 'step', 'scale', 'aphasia', 'service', 'reduced', 'term', 'provides', 'gbg', 'met', 'types', 'reducing', 'performed', 'randomized', 'series', 'period', 'techniques', 'frequency', 'statistical', 'type', 'practices', 'vsm', 'mobility', 'digital', 'average', 'available', 'decrease', 'differences', 'gains', 'experiment', 'range', 'general', 'telehealth', 'months', 'regarding', 'walking', 'interactive', 'required', 'revealed', 'percentage', 'aim', 'common', 'greater', 'educational', 'identify', 'tool', 'fidelity', 'cost', 'aided', 'sgd', 'schedule', 'pecs', 'coaching', 'technologies', 'chronic', 'persons', 'comparing', 'shown', 'role', 'functioning', 'report', 'standards', 'cerebral', 'participation', 'employed', 'efficient', 'according', 'integrity', 'recognition', 'vm', 'modified', 'tests', 'efficiency', 'matching', 'inclusion', 'component', 'exchange', 'college', 'body', 'relations', 'modelling', 'second', 'withdrawal', 'mediated', 'mental', 'investigation', 'lack', 'palsy', 'approaches', 'directions', 'total', 'methodology', 'communicative', 'given', 'highly', 'order', 'al', 'practical', 'impairments', 'providing', 'month', 'quantitative', 'applications', 'produced', 'evaluating', 'embedded', 'adult', 'involved', 'exercise', 'grade', 'difficulties', 'transition', 'demonstrate', 'symptoms', 'resulted', 'controlled', 'typically', 'choice', 'error', 'noncontingent', 'videos', 'discrete', 'et', 'delay', 'mild', 'successful', 'measurement', 'duration', 'materials', 'mixed', 'result', 'family', 'reliability', 'contingent', 'job', 'pilot', 'focused', 'behaviours', 'focus', 'tools', 'develop', 'enhance', 'risk', 'opportunities', 'independently', 'difference', 'services', 'augmented', 'relation', 'journal', 'relative', 'literacy', 'completion', 'working', 'aid', 'recorded', 'identification', 'standard', 'hand', 'experience', 'understanding', 'lower', 'production', 'basic', 'make', 'characteristics', 'concurrent', 'versus', 'safety', 'consistent', 'main', 'stories', 'various', 'braille', 'supporting', 'feasibility', '20', 'aims', 'considered', 'better', 'selected', 'internet', 'questions', 'rird', 'smart', 'professional', 'end', 'imitation', 'fluency', 'address', 'reversal', 'protocol', 'dependent', 'specifically', 'mastery', 'content', 'supported', 'app', 'impairment', 'personal', 'area', 'goals', 'real', 'trend', 'socially', 'benefits', '11', 'consisted', 'automatically', 'comprehension', 'facial', 'framework', 'balance', 'manipulatives', 'reduction', 'prior', 'selection', 'form', 'stroke', '100', 'analyzed', 'variety', 'feasible', 'little', 'goal', 'adherence', 'learn', 'exposure', 'employment', 'articles', 'delivery', 'supports', 'person', 'variable', 'steps', 'ages', 'relevant', '2014', 'human', 'sight', 'combination', 'furthermore', 'auditory', 'point', 'day', 'scribe', 'cochlear', 'decreasing', 'brief', 'critical', 'requesting', 'analytic', 'aimed', 'patterns', 'utilized', 'ncr', 'individualized', 'disease', 'id', 'conduct', 'directed', 'natural', 'immediate', 'reviewed', 'electronic', 'include', 'making', 'weekly', 'areas', 'facilitate', 'reports', 'discuss', 'abilities', 'subsequent', 'manual', 'loss', 'theory', 'influence', 'families', 'reinforcer', 'taking', 'environmental', 'way', 'initiations', 'despite', 'fit', 'multi', 'points', '15', 'praise', 'likely', 'autistic', 'intensive', 'educators', 'suggested', 'probes', 'factors', 'methodological', 'conversation', 'instructions', 'introduction', 'cues', 'reinforced', 'programming', 'introduced', 'recommendations', 'challenges', 'deficits', '18', 'qualitative', 'tau', 'active', 'population', 'continuous', 'suggests', 'engaged', 'situations', 'promising', 'schools', 'written', 'maintain', 'carried', '30', 'therapeutic', 'graphs', 'train', 'objectives', 'score', 'similar', 'issues', 'sets', 'structured', 'principles', 'behavioural', 'middle', 'observational', 'min', 'means', 'joint', 'search', 'collection', 'negative', 'replicated', 'repeated', 'movement', 'complete', 'classes', 'users', 'times', 'repetitive', 'contingencies', 'acceptable', 'screen', 'promoting', 'set', 'perform', 'variability', 'relationship', 'technique', 'user', 'replication', 'course', 'benefit', 'preschoolers', 'short', 'necessary', 'successfully', 'childhood', 'environments', 'motivation', 'recent', 'features', 'effectively', 'discussion', 'science', 'followed', 'simultaneous', 'examining', 'presentation', 'therapists', 'observation', 'web', 'concept', 'contexts', 'finally', 'tested', 'independence', 'paraprofessionals', 'power', '17', 'occurred', 'testing', 'guidelines', 'possible', 'medical', 'descriptive', 'value', 'minimal', '16', 'gait', 'format', 'useful', 'ci', 'wide', '2010', 'empirical', 'changing', '2015', 'redirection', 'reinforcers', 'obtained', 'messages', 'consequences', 'aggression', '2011', 'depression', 'processing', '14', 'concepts', 'eye', 'speed', 'noise', 'ratings', 'running', 'public', 'assist', 'commonly', 'cases', '2013', 'base', 'tm', 'larger', 'psychological', 'acceptability', 'practitioners', 'tech', 'boys', 'seven', 'spoken', 'engage', 'contact', 'correction', 'involving', 'graphic', 'errors', 'mood', 'members', '24', 'hybrid', 'curriculum', 'shared', 'weight', 'interruption', 'perception', 'prototype', 'face', 'rated', 'dynamic', 'vocational', 'music', 'receptive', 'simulation', 'regression', 'best', 'existing', 'motion', 'progress', 'programme', 'blocking', 'university', 'resources', 'events', 'respectively', 'recording', 'interviews', 'pictures', 'scientific', 'stress', 'expressions', 'perceived', 'untrained', 'solving', 'screening', 'awareness', 'implant', 'food', 'field', 'retrieval', 'frequently', 'discrimination', 'action', 'varied', 'experiments', 'sound', 'particular', 'satisfaction', 'extinction', 'clear', 'interview', 'caregivers', 'prompt', 'generalize', 'automated', 'suggestions', 'previously', 'sib', 'values', 'led', '50', 'psychology', 'limb', 'emotions', 'diagnosis', 'detection', 'comprehensive', 'derived', 'consisting', 'item', 'symbols', 'intensity', 'tbi', 'sleep', 'lead', 'explore', 'guidance', 'tier', '2012', 'core', 'key', 'smartphone', 'objects', 'cbt', 'statistically', 'telephone', 'obesity', 'generally', 'indices', 'known', 'tracking', 'particularly', 'request', 'options', 'identifying', 'assessing', 'free', 'therapist', 'implementing', 'taken', 'phonological', 'synthesis', 'inclusive', 'combining', 'older', 'advanced', 'guideline', 'extended', 'strong', 'produce', 'spelling', 'enhanced', 'exhibited', 'concrete', 'bst', 'consumption', 'enhancing', 'targets', 'plus', 'partners', 'presence', 'bias', 'tootling', 'immediately', 'fading', 'sensory', 'interval', 'transitions', '13', 'fewer', 'success', 'open', 'utility', 'meet', 'accurately', 'procedural', 'ms', 'accurate', 'additionally', 'constant', 'story', 'extend', 'requests', 'toy', 'traumatic', 'aspects', 'days', 'standardized', 'uses', 'proposed', 'antecedent', 'emotion', 'publication', '3d', 'remote', 'turn', 'emerging', 'naming', 'delayed', 'occupational', 'partner', 'option', 'comparisons', 'widely', 'randomization', '19', 'continued', 'caregiver', 'deaf', 'biofeedback', 'right', 'significance', 'adaptive', 'substantial', 'comparative', 'sampling', 'restraint', 'affect', '95', 'expressive', 'machine', 'majority', 'computerized', 'directly', 'project', 'beneficial', 'upper', 'touch', 'established', 'importance', 'animal', 'voice', 'object', 'describes', 'vr', 'relatively', 'longer', 'validation', 'processes', 'display', 'attending', 'receiving', 'checklist', 'abab', 'learners', 'mand', 'material', 'distance', 'explored', 'interface', 'offer', 'classwide', 'affected', 'eeg', 'external', 'electrical', 'samples', 'hypothesis', 'administered', 'temporal', 'microswitch', 'incorporating', 'potentially', 'line', 'raw', 'nonverbal', 'remained', 'mouse', 'chaining', 'decreases', 'preferences', 'enrolled', 'demonstrating', 'emergence', 'women', 'experienced', 'randomised', 'psychotherapy', 'organizational', 'injurious', 'state', 'affective', 'understand', 'oral', 'reviews', 'view', 'arm', 'ar', 'simple', 'showing', 'linear', 'delays', 'adequate', 'slightly', 'sequence', 'delivering', 'systematically', 'team', 'conversational', 'consecutive', 'everyday', 'integrated', 'fct', 'wearable', 'seen', 'gross', 'operant', 'mts', 'robust', 'pattern', 'survey', 'smoking', 'reach', 'computing', 'toys', 'meat', 'residual', 'examples', 'alzheimer', 'professionals', 'forward', 'assigned', 'ipod', 'version', 'vocalizations', 'variations', 'confidence', 'questionnaire', 'pairs', 'randomly', 'usability', 'leisure', 'create', 'elements', 'especially', 'forms', 'respond', 'medium', 'presents', 'index', 'medication', 'sced', 'dyads', 'took', 'signal', 'normal', 'barefoot', 'match', 'observations', 'suggesting', '25', 'audio', 'half', 'extent', 'neck', 'addressing', 'profound', 'failure', 'called', '90', 'rapid', 'variation', 'paired', 'translational', 'recommended', 'output', 'achieved', 'happiness', 'transfer', 'ear', 'infant', 'network', 'providers', 'phone', 'fine', 'subjective', 'sentence', 'displayed', 'coding', 'adolescent', 'described', 'addressed', 'aggressive', 'mother', 'simulated', 'focuses', 'suitable', 'reviewers', 'clinic', 'planning', 'math', 'portable', 'reductions', 'computers', 'demand', '40', 'performing', 'perspective', 'periods', '80', 'clips', 'yielded', 'adhd', 'detailed', '22', '21', 'capacity', 'stage', 'acquire', 'iphone', 'multimodal', 'diverse', 'targeting', 'wii', 'actions', 'script', 'consistently', 'live', 'playing', 'involves', 'aids', 'monitor', 'meeting', 'unique', 'sensor', '26', 'difficulty', 'absence', 'noted', 'schizophrenia', 'positively', 'movements', 'engaging', 'functions', 'creating', 'major', 'consonant', 'ratio', 'adopted', 'capability', 'decision', 'motivating', 'indicates', 'exposed', 'wheelchair', 'mothers', 'world', 'sentences', 'thinking', 'sufficient', 'ict', 'expression', 'handheld', 'generated', 'degree', 'meaningful', 'drivers', 'extension', 'trends', 'impaired', 'rats', 'reinforcing', 'requires', 'perspectives', 'arrangement', 'mechanisms', 'mathematical', 'viewed', 'cognition', 'statistics', 'eating', 'parameters', 'english', 'interdependent', 'sustained', 'integration', 'works', 'lessons', 'message', 'presenting', 'male', 'acoustic', 'pa', 'history', 'minute', 'nucleus', 'editors', 'compliance', 'reached', 'place', 'utilizing', 'healthy', 'internal', 'rules', 'accessible', 'displays', 'typical', 'experiences', 'foot', 'powered', 'youth', 'calculated', 'clinicians', 'studied', 'statement', 'avoidance', 'diagnostic', 'punishment', 'dtt', 'capabilities', 'consultation', 'vibration', 'original', 'propose', 'narrative', 'vivo', 'clinically', 'correctly', 'includes', 'states', 'conventional', 'global', 'dementia', 'restricted', 'courses', 'investigations', 'tutors', 'tutor', 'requirements', 'quiet', 'phobia', 'exploration', 'token', 'adverse', 'sports', 'contribute', 'graphing', 'abstract', '35', 'valid', 'innovative', 'microswitches', 'separate', 'spatial', 'treat', 'backward', 'operation', 'guide', 'properties', 'parental', 'united', 'female', 'created', 'lexical', 'mode', 'difficult', 'agreement', 'sgds', 'prevention', 'productivity', 'contextual', 'read', 'naturalistic', 'final', 'pediatric', 'sd', 'allowed', 'client', 'intervals', 'girl', 'compound', 'played', 'recordings', 'inappropriate', 'distress', 'pda', 'sciences', 'appears', 'guided', 'left', 'clearinghouse', 'populations', 'check', 'growing', 'modes', 'typing', 'investigating', 'documented', 'accommodation', 'achievement', 'comparable', 'muscle', 'relationships', 'having', 'performances', 'explicit', 'collaboration', 'varying', 'prospective', 'tangible', 'vision', 'mastered', 'trainer', 'does', 'tablets', 'pointing', 'allows', 'card', 'categories', 'initially', 'resulting', 'advantages', 'kinematic', 'completing', 'currently', 'appeared', 'peak', 'book', 'equally', 'static', 'actual', 'inspection', 'experts', 'respect', 'surveys', 'rationale', 'length', 'multimedia', 'advocacy', 'personalized', 'decisions', 'applying', 'added', 'description', 'possibility', 'scripts', 'retention', 'warranted', 'posttest', 'leadership', 'bilateral', 'letter', 'grocery', 'augmentative', 'depressive', 'placebo', 'preparation', 'journals', 'cp', 'helping', 'competing', 'religious', 'reaching', 'ongoing', 'demands', 'later', 'custom', 'price', 'opinions', 'require', 'energy', 'longitudinal', 'beginning', 'served', '60', 'involvement', 'undergraduate', 'cai', 'designing', 'asymmetry', 'sign', 'severity', 'basis', 'regulation', 'medicine', 'evaluations', 'verb', 'statements', 'measurements', 'technological', 'assistance', 'ways', 'replications', 'researcher', 'kindergarten', 'determined', 'essential', 'newly', 'comments', 'viewing', 'ii', 'force', 'examination', 'indicating', 'estimation', 'observer', 'modalities', 'modality', 'listening', '2008', 'woman', 'ipads', 'compulsive', 'onset', 'relational', 'applicable', 'module', 'dra', 'numbers', 'defined', 'mindfulness', 'percent', 'instructor', 'measuring', 'concerns', 'visually', 'excel', '36', 'member', 'abuse', '29', 'incorporated', 'seat', 'offers', 'sought', 'deficit', 'treating', 'fourth', 'enable', 'pnd', 'topic', 'fa', 'usual', 'videoconferencing', 'extensive', 'considering', 'simultaneously', 'considerations', 'tact', 'conditional', 'modification', 'manage', 'faster', 'multicomponent', 'characters', 'uk', 'signs', 'participating', 'analyze', 'past', 'generalisation', 'nature', 'elearning', 'lists', 'neurofeedback', 'sitting', 'advances', 'laboratory', 'rating', 'enabling', 'teams', 'start', 'expected', 'academically', 'transparency', 'recovery', 'proven', 'explanation', 'assistant', 'recruited', 'exist', 'clinician', 'orientation', 'coping', 'extremity', 'vs', 'record', 'symbol', 'building', 'treated', 'analysts', 'nonoverlap', 'provision', 'maintaining', '2007', 'cross', 'escape', 'classification', '2009', 'contrast', 'heart', 'minutes', 'estimates', 'reminder', 'improves', 'stuttering', 'operations', 'growth', 'perceptions', 'dti', 'ball', 'inform', 'routine', 'usually', 'scenarios', 'postsecondary', 'preparing', 'scene', 'solve', 'analyzing', 'methodologies', 'rule', 'adaptation', 'implanted', 'characterized', 'neuropathic', 'graphical', 'indicators', 'resilience', 'latency', 'desired', 'poor', 'conducting', 'programmed', '2018', 'travel', 'reminders', 'tactile', 'asked', 'extracted', 'repertoire', 'gesture', 'quickly', 'pitch', 'facilitated', 'frame', 'coordination', 'prevalence', 'like', 'standing', 'contribution', 'wiley', 'facilitating', 'prepare', 'manuscripts', 'serve', 'mini', 'postintervention', 'cord', 'progressive', 'fes', 'unilateral', 'calls', 'gain', '28', 'consider', 'hospital', 'verbs', 'random', 'probability', 'revised', 'fast', 'multielement', 'grades', 'remains', 'regard', 'resource', 'competence', 'matched', 'popular', 'hydromorphone', 'grasp', 'papers', 'blinded', 'american', 'workshop', 'direction', 'domains', 'classdojo', '33', 'comprised', 'males', 'office', 'narration', 'overlap', 'personnel', 'select', 'consumers', 'optimal', 'conceptual', 'highlight', 'strength', 'responsiveness', 'alcohol', 'microsoft', 'expert', 'weighted', 'subtraction', 'vegetable', 'nonconcurrent', 'ride', 'attempted', '34', 'mind', 'rumination', 'account', 'shows', 'theoretical', 'seeking', 'demonstration', 'vp', 'camera', 'ab', 'extraction', 'girls', 'recommend', 'phrases', 'sensecam', 'boy', 'primarily', 'considerably', 'predicted', 'analytics', 'linguistic', 'chained', 'trainers', 'fentanyl', 'databases', 'enabled', 'bi', 'solutions', 'offered', 'intention', 'promise', 'examines', 'searched', 'describing', 'abi', 'cw', 'purposes', 'socio', 'minimally', 'neglect', 'baselines', 'tutorial', 'knee', 'algebra', 'exemplar', 'concerning', 'lines', 'emerged', 'establish', 'concluded', 'metabolic', 'clarity', 'effort', 'parts', 'appraisal', 'establishing', 'interdisciplinary', 'overview', 'imitate', 'light', 'interact', 'detect', 'man', 'healthcare', 'interventionists', 'rct', 'maximum', 'walk', '23', 'photos', 'srsd', 'unknown', 'apps', 'ebi', 'correspondence', 'pretend', 'roles', 'pretest', 'shopping', 'bug', 'collaborative', 'leg', 'struggle', 'recognize', 'symptom', 'facts', 'playfulness', 'neural', 'signals', 'example', 'critically', 'repertoires', 'dro', 'estimated', 'flexion', 'ocd', 'disruption', 'chains', 'pen', 'rural', 'aquatic', 'hyperactivity', 'solution', 'continue', 'easy', 'acts', 'stereotypic', 'increasingly', 'allowing', 'head', 'attempts', 'interpretation', 'replacement', 'cannabis', 'barriers', 'achieve', 'opportunity', 'deliver', 'platform', 'carry', 'return', 'mands', 'apply', 'sequential', 'largely', 'cm', 'idd', 'marked', 'hip', 'availability', 'stutter', 'frequencies', 'employees', 'products', 'obtain', 'density', 'flexibility', 'occurrence', 'instead', 'hard', 'questionnaires', 'board', 'comorbid', 'routines', 'exercises', 'fitness', 'placed', 'distributed', 'medline', 'list', 'acute', 'brac', 'corresponding', 'driven', 'greeting', 'reference', 'dimensions', 'allow', 'sequences', 'moderately', 'zero', 'studying', 'highlighted', 'exploratory', '05', 'ankle', 'completeness', 'status', 'messaging', 'air', 'tate', 'copyright', 'cbi', 'pivotal', 'scales', 'surface', 'ranging', 'discounting', 'sounds', 'representing', 'extends', 'robotic', 'correlation', 'indirect', 'optic', 'spontaneous', 'money', '42', 'signing', 'didactic', 'arranging', 'coded', 'workplace', 'efficacious', 'machines', 'athletic', 'fruit', 'tts', 'central', 'spastic', 'responded', 'store', 'exhibit', 'specificity', 'consort', 'clients', 'skin', 'responders', 'double', 'alliance', 'dental', 'commercial', 'began', 'located', 'maternal', 'topographical', 'lean', 'healthier', 'f0', 'reliable', 'racetrack', 'exemplars', '70', 'gathered', 'occur', 'counterbalanced', 'referred', 'choose', 'learner', 'fundamental', 'scd', 'overweight', 'apple', 'innovation', 'initiated', 'safe', 'certain', 'seek', 'city', 'fixed', 'event', 'ld', 'ccn', 'temperature', 'incentives', 'modest', 'watch', 'causes', 'neurodevelopmental', 'obsessive', 'estimate', 'interrupted', 'act', '38', 'analogue', 'names', '47', 'confirmed', 'pd', 'intelligibility', 'adoption', 'society', 'percentages', 'focusing', 'frequent', 'preventive', 'gestures', 'momentary', 'observing', 'incidental', 'tutoring', 'median', 'drug', 'socialization', 'artificial', 'elaboration', '39', 'twice', 'close', '2005', 'withdrawn', 'construction', 'contributes', 'tootles', 'altering', 'cvm', 'gave', 'illustrate', 'determining', 'viable', 'mswo', 'printed', 'fitting', 'contained', 'syllables', 'posttreatment', 'moving', 'label', 'fact', 'wwc', '78', 'distribution', 'enrichment', 'media', 'favorably', 'yield', 'motivational', 'remain', 'posture', 'dbt', 'vests', 'aesthetic', 'novice', 'prosocial', 'summary', 'accumulated', '111', 'perceptual', 'coaches', 'outside', 'greatest', 'stop', 'spinal', 'packages', 'operational', 'statistic', 'held', 'spaces', 'hierarchy', 'multistep', 'ssd', 'dog', 'instructed', 'attempt', 'centers', 'ai', 'contributions', 'flexible', 'shod', 'oriented', 'slot', 'factor', 'resolution', 'receive', 'actors', 'observers', 'cue', 'labels', 'producing', 'easily', 'adjectives', 'prompted', 'blind', 'choices', 'helped', 'rigorous', 'ird', 'mouthing', 'space', '66', 'anger', 'experimentation', 'technical', 'insufficient', 'modifications', 'exists', 'urban', '96', 'driving', 'conscious', 'successive', 'sat', 'gaming', 'hour', 'clergy', 'question', 'transitioning', 'respiratory', 'recently', 'complements', 'curve', 'stages', 'consumer', 'acceptance', 'illness', 'tone', 'opal', 'incorrect', 'iromec', 'challenge', 'sensors', 'confederate', 'divided', 'financial', 'nurses', 'graduated', 'iws', 'quantity', 'circle', 'semi', 'subsequently', 'considerable', 'sons', 'paradigm', 'element', 'shoes', 'bayesian', 'consequence', 'position', 'issue', 'evident', 'applicability', 'john', 'graduate', 'superior', 'bullying', 'modules', 'washing', 'intended', 'recall', 'thermal', 'proficiency', 'encouraging', 'participate', 'pe', 'cam', 'exclusion', 'pwds', 'arrangements', 'linked', 'economy', 'foster', 'treadmill', 'appear', 'author', 'watches', 'cnc', 'toilet', 'football', 'videogame', 'route', 'earlier', 'heeled', 'instructors', 'inconclusive', 'parkinson', 'cued', 'speaking', 'educator', 'regular', 'meetings', 'iii', 'physiological', 'emergent', 'gradually', 'rr', 'placement', 'attentional', 'belt', 'implants', 'location', 'tele', 'ibs', 'controlling', 'strengthening', 'trainees', 'master', 'pts', 'cards', 'depth', 'cbgo', 'reveal', 'avoid', 'smaller', 'fifth', '58', 'galantamine', 'mechanism', 'resistance', 'calculations', 'gaze', 'absent', 'kinect', 'kinematics', 'structure', 'overlapping', '27', 'song', 'antecedents', 'durations', 'nap', 'impulsivity', 'apparent', 'stable', 'topography', 'commands', 'para', 'remaining', 'entire', 'addiction', 'exceeded', 'print', 'cuing', 'essay', 'idea', 'nearly', 'productions', 'pressure', 'car', 'toddlers', 'formats', 'equations', 'analytical', 'keyboard', 'generality', 'alphabet', 'psychosocial', 'interventionist', 'resurgence', 'portion', 'distressing', 'retained', 'highlights', 'exploring', 'tailored', 'details', '001', 'vret', 'wheel', 'drag', 'alpha', 'homes', 'hr', 'income', 'humans', 'complexity', 'monetary', 'continues', 'recipes', 'reverse', 'chose', 'prism', 'sharing', 'pwd', 'approximately', 'articulatory', 'predict', 'started', 'videotaped', 'introduce', 'built', 'ipada', 'sceds', 'scripted', 'economic', 'magnitude', 'expressed', 'commitment', 'influenced', 'eibi', 'conclude', 'infants', 'intra', 'parametric', 'nonparametric', 'tilt', 'workshops', 'affects', 'suited', 'drop', 'leading', 'shape', 'phonics', 'hiv', 'equal', 'lost', 'hero', 'trigger', 'dimensional', 'collect', 'vsp', 'costs', 'gap', 'vest', 'link', 'pictorial', 'sophisticated', 'proloquo2go', 'great', 'efforts', 'customized', 'alternatives', 'verbalizations', 'nssi', 'untaught', 'tdi', 'box', '93', 'prevent', 'aggregate', 'attended', '54', 'attainment', '94', 'limitation', 'supplementary', 'decades', 'rigor', 'protocols', 'dose', 'monitored', 'equivalent', 'abstinence', 'topics', 'concurrently', 'lecture', 'animals', 'ended', 'insights', 'bonus', 'absolute', 'isolated', 'lasted', 'classified', 'finding', 'earned', 'quiz', 'fluent', 'intelligent', 'nonoverlapping', 'personally', 'biomechanical', 'tended', 'activation', 'interfaces', 'passage', 'consistency', 'versions', 'add', 'competencies', 'makes', 'mva', 'ad', 'multilevel', 'policy', 'emotive', 'rra', 'unit', 'paraprofessional', 'wearables', 'ltm', 'consensus', 'integrating', 'speeds', 'construct', 'clip', 'strengths', 'persuasive', 'category', 'efl', 'engineering', 'ap', 'substantially', 'stability', 'vaporizer', 'thinning', 'provider', 'smartphones', '46', 'demonstrates', 'inter', 'achieving', 'proved', 'identity', 'land', 'dysfunction', 'pastoral', 'individually', 'ranged', 'domain', 'source', 'analysed', 'men', 'telepractice', 'requiring', 'players', 'clinics', 'product', 'prosthesis', 'undergoing', 'dd', 'hemiplegic', 'asds', 'blindness', 'azbio', 'implantation', 'sas', 'sense', 'november', 'beta', 'tac', 'scored', 'untreated', 'neutral', 'utterances', 'consultants', 'numeracy', 'communicate', 'talk', 'safecare', 'explain', 'ecoaching', 'adjunct', 'adding', 'expanding', 'networks', 'precision', 'kws', 'named', 'relaxation', 'randomisation', 'weak', 'multiplication', 'inferential', 'volume', 'purchasing', 'culture', 'fragile', 'confirm', 'ebd', 'topographies', 'locations', '45', 'connect', 'rett', 'younger', 'residents', 'eclectic', 'progression', 'emergency', 'passive', 'distraction', 'carers', 'attendance', 'dnd', 'date', 'mit', 'relating', 'paraeducators', '87', 'cooking', 'tax', 'mouth', 'usage', 'organizations', 'precursors', 'suffering', 'evoke', 'conjunction', 'postural', 'precursor', 'occurring', 'selective', 'scent', 'produces', 'proximity', 'pay', 'publications', 'hyperactive', 'rehabilitative', 'controller', 'allocation', 'culturally', 'manipulative', 'usa', 'kinds', 'pervasive', 'mechanics', 'regulated', 'ip', 'extending', 'lowest', 'minority', 'benefited', 'citations', 'breaks', 'fail', 'problematic', 'regardless', 'connected', 'reduces', 'vital', 'enhancement', 'executive', 'readiness', 'near', 'transdiagnostic', 'accomplished', 'emphasized', 'goact', 'cb', 'lifestyle', 'nintendo', 'update', 'stem', 'additive', 'highest', 'occupation', 'sorting', 'rehearsal', 'supplement', 'validated', 'deviation', 'dance', 'trunk', 'operated', 'records', 'beliefs', 'adaptations', 'reciprocal', 'evaluates', 'containing', '52', '64', 'sr', 'estimations', 'expansion', 'reflected', 'citation', 'experimenters', 'caused', 'blood', 'modern', 'articulation', 'satiation', 'friends', 'empirically', 'institute', 'ease', 'counting', 'generative', 'retraining', 'accepted', 'predator', 'functioned', 'ext', 'segments', 'block', 'dogs', 'hours', 'late', 'assistants', 'bring', 'remotely', 'alternated', 'coma', 'augment', 'discusses', 'regrouping', 'economics', 'tabletop', 'makey', 'customer', 'ot', 'removal', 'ace', 'intonation', 'compensatory', 'lmem', 'reward', 'hlm', 'promoted', 'shorter', 'females', 'grammatically', 'just', '31', 'feature', 'emitted', 'technicians', 'distal', 'competition', 'ec', 'ocr', 'episodes', 'restructuring', 'micro', 'accessibility', 'understood', 'relevance', 'photographs', 'hou', '2017', 'atc', 'mst', 'eventually', 'calibration', '84', 'lobe', 'assignments', 'ignore', 'break', 'ensure', 'prevalent', 'pedagogy', 'decoding', 'parenting', 'autobiographical', 'contributed', 'destructive', 'illustrated', 'appropriately', 'conversations', 'build', 'differ', 'doing', 'diabetes', 'manipulated', 'vbf', 'fm', 'intelligence', '75', 'standardised', 'plays', 'prenatal', 'dohsa', 'lag', 'vocalization', 'pc', 'assisting', 'code', 'represented', 'comprising', 'rcts', 'numerous', 'angle', 'hemispatial', 'drawn', 'rapidly', 'commenting', 'bowel', 'reasons', 'psychologists', '01', 'turnover', 'commercially', 'scoring', 'forwarding', 'instances', 'wear', 'neurological', 'correlated', 'experiencing', 'crucial', 'units', 'turns', 'incidence', 'load', 'sci', 'intermediate', 'changed', 'therapies', 'embase', 'psycinfo', 'unable', 'encourage', 's8', 'electric', 'prosody', 'glove', 'ddndap', 'rest', 'discriminative', 'geometry', 'screened', 'ppa', 'cochat', 'association', 'collecting', 'adequately', 'reaction', 'advertising', 'starting', 'vnest', 'books', 'distinct', 'sw', 'disruptions', 'incorporate', 'reliance', '2d', '57', 'operate', 'follows', 'shaping', 'mock', 'animated', 'swing', 'mi', 'covert', 'advocates', 'continuing', 'transdermal', 'initiate', 'academics', 'raters', '1st', 'centered', 'hands', 'idiosyncratic', 'controls', 'looking', 'concentration', 'slots', 'sent', 'charge', 'integral', 'homework', 'situation', 'cas', 'combine', 'referral', 'strike', 'quantified', 'acclimatization', 'publicly', 'purchase', 'amplitude', 'rhotic', 'ssq', 'resection', 'center', 'smile', 'risks', 'descriptions', 'bus', 'telecare', 'mindful', 'siblings', 'graphed', 'immersion', 'schema', 'influences', 'icbt', 'bmi', 'mail', 'cause', 'raising', 'worked', '65', 'hygiene', 'modeled', 'said', 'table', 'graph', 'appliance', 'welfare', 'introducing', 'administration', 'asymmetric', 'sensorineural', '55', 'preschooler', 'neuroanatomy', 'tackling', 'greet', 'tacts', 'physiotherapy', 'moderator', 'usefulness', 'affecting', 'hypothesized', 'plan', 'asperger', 'maps', 'intact', 'selecting', 'fitbit', 'amputees', 'countries', 'operating', 'practitioner', '32', 'emesis', 'scds', '76', 'breeding', 'tumor', 'pouched', 'pedagogical', 'responsible', '41', 'wrote', 'sequentially', 'hemiplegia', 'patting', 'dat', 'actively', 'iep', 'reliably', 'representation', 'stance', 'pdd', 'definition', 'sites', 'searching', 'replicate', 'consists', 'definitions', 'sub', 'rich', 'ubiquitous', 'biological', 'intrusive', '83', 'informed', 'cleaning', '48', 'far', 'jaba', 'removed', '82', 'prerequisite', 'watching', 'button', 'vending', 'arch', 'atm', 'centred', 'enabler', 'black', 'universal', 'injections', 'television', 'struggling', 'accommodations', 'sad', 'car</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9566</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>['appealing', 'vi', 'electromyogram', 'scans', 'elkins', 'alternation', 'caseload', 'february', 'niatx', 'welcoming', 'plantarflexion', 'subacute', 'scanner', 'inferring', 'midcervical', 'es', 'evaluator', 'tulder', 'affiliated', 'comment', 'plantar', 'contents', 'charter', 'entirely', 'host', 'reluctant', 'delaware', 'robertson', 'formulae', 'lateral', 'yen5', 'margins', 'suits', 'moderation', 'nollet', 'wilke', 'ltdelsevier', 'nowtm', 'seaman', 'thousand', 'lexile', 'usm', 'wolfe', 'deviations', 'angry', 'voluntary', 'overuse', 'quotients', 'ladder', 'resided', 'sewing', 'heavy', 'toileting', 'edit', 'maher', 'yearlong', 'inside', 'crises', 'filming', 'super', 'staged', 'lobo', 'trademarked', 'redressing', 'ebsco', 'imposes', 'habituating', 'utilise', 'sherrington', 'expectation', 'fellows', 'surviving', 'equaled', 'suicide', 'moseley', 'reservations', 'returns', 'fma', 'battery', 'outlets', 'anticipating', 'lovaas', 't10', 'publicity', 'avb', 'pooling', 'moments', 'contended', 'varus', 'speakall', 'colleague', 'obedience', 'afterdeployment', 'mri', 'promotefunctional', 'enduring', 'cable', 'practised', 'overlaid', 'iso', 'empowering', 'seconday', 'satisfactorily', '214', 'ideally', 'pub', 'plasticity', 'quadratus', 'solitaire', 'najdowski', 'barnoy', 'trail', 'putt', 'effectuality', 'clenching', 'tutees', 'ankara', 'retardations', 'drasgow', 'paralyzed', 'violated', 'iteration', 'golf', 'voiding', 'orthotic', 'spatially', 'phi', 'cautions', 'ordered', 'syndromes', 'traits', 'nodal', '7226', 'volunteer', '010', 'hamstrings', 'adductor', 'ward', 'maximus', '021', 'nonstructured', 'discriminable', 'tonic', 'sounding', 'arbd', 'generalisability', 'delivers', 'grow', 'lumborum', 'extensor', 'arising', 'tarbox', 'groundwork', 'hypothesised', 'sagittal', '048', 'rivaled', 'electroencephalographic', 'ramp', 'erector', 'spinae', 'playback', 'happier', 'diagnosable', 'umbrella', 'essence', 'grippitr', 'closing', 'flourish', 'symptomatic', 'ancestral', 'psychophysics', '149', 'mal', '9y', 'ordinal', 'bypassed', 'identifies', 'paid', 'calculable', 'theoretically', 'combo', 'abilhand', 'reconstruct', 'deserves', 'shortlist', 'endowment', 'sprinting', 'km', 'approbate', '178', 'multinomial', 'execute', 'arrive', 'stimulate', 'diurnal', 'plotted', 'deflated', 'thereof', '3min', 'sequenced', 'phentermine', 'kelvin', 'jerk', 'reconstructed', 'satisfying', 'optimally', 'hispanic', 'clock', 'differs', 'literatures', 'faithful', 'abstained', 'tics', 'scrutinized', 'ghz', 'subthreshold', 'cpu', 'acceleration', 'proceduresa', 'backgroundtreatment', 'wm', 'newer', 'mandarin', 'anticipated', 'adjective', 'qr', 'familial', 'cohesion', 'prezi', 'justification', 'protected', 'ready', 'caring', 'developmentally', 'obligatory', 'pertain', 'buttocks', 'fostering', 'lifespan', 'cbstmay', '20122014', 'inverted', 'discernible', 'evolved', 'realities', 'keyword', 'assists', 'esteem', 'apples', 'exceedingly', 'daytime', 'handball', 'pragmatism', 'annotated', 'practioner', 'practioners', 'covariances', 'charting', 'interfaced', 'unobtrusively', 'silent', 'silently', 'portability', 'father', 'respected', 'verified', 'infusion', 'diffuse', 'ancillary', 'wirelessly', 'irrespective', 'vocas', 'mirenda', 'fingers', '216', 'drawbacks', 'galaxy', 'istwas', 'cites', 'predefined', 'exceeds', 'immersed', 'haemorrhage', 'paediatrics', 'realize', 'gordon', 'facilitators', 'psychometrically', 'larsen', 'inhibition', '166', 'earning', 'propensity', 'adair', '891', 'aacpdm', 'paresis', 'overconsumption', 'overeating', 'calibrate', 'consume', 'bstmay', 'putaminal', 'exert', 'outreach', '052', 'abababa', 'mississippi', 'mathematician', 'attenuation', 'magnetic', 'fairly', 'substitute', 'resonance', 'mention', 'conceptualizing', 'accelerating', 'bstwhen', 'lighters', 'abandon', 'tacted', 'postmaintenance', '013', 'grained', 'biosensors', 'kept', 'illustrating', 'granular', 'lateralization', 'suicidal', 'oxygenation', 'ideation', 'emitter', 'homemade', 'noticed', 'simplistic', '057', 'receiver', 'uninstructed', 'dignity', 'freedom', 'unreliable', 'shrinks', 'nimmo', 'quo', 'automobiles', 'instrumentation', 'physiology', 'moral', 'buffet', 'obscuring', 'multitask', 'converted', 'compact', 'playthings', 'precluding', 'restrictions', 'forming', 'exacerbate', 'li', 'holding', 'poison', 'drains', 'drawing', 'consensual', 'marketing', 'accidental', 'townsend', 'itching', 'equivalently', 'uncontrolled', 'critiques', '251', 'kertesz', 'utah', 'heroic', 'psychotropic', 'agree', 'hooks', 'fictional', 'intuit', 'generates', 'cube', 'ignores', 'renal', 'implicationsfindings', 'repeats', 'noteworthy', 'convert', 'prices', 'towels', 'assortment', 'stammering', 'wh', 'repetitively', 'shop', 'danov', 'resultsone', 'arousing', 'convoluted', 'want', 'barry', 'pragmatist', 'sohlberg', 'reviewing', 'ninth', 'predominant', 'goh', '269', 'nurturance', 'responsivity', 'mateer', 'multiprobe', 'ridgeway', 'remediated', 'succinct', 'diller', 'teletherapy', 'kelly', 'ctm', 'transactional', '112', 'synchrony', 'newark', 'notice', 'farmer', 'symons', 'weighing', 'whimpering', 'deochand', 'hot', 'intermittent', 'poling', 'cos', 'unity', 'standalone', 'homepages', 'decrements', 'carpenter', 'lumber', 'poulson', 'earnings', 'howard', 'arise', 'bayley', 'lindsey', 'neologisms', 'rehfeldt', 'sparkman', 'stanislaw', 'fienup', '2component', 'gp', 'clusters', 'concretely', 'paca', 'brodsky', 'gelino', 'definitive', 'confirmation', 'predilection', 'confusion', 'spoke', 'autoregressive', 'singles', 'cannella', 'malone', 'wash', 'affection', 'hunger', 'temptation', 'doctors', 'overdue', 'suspected', 'pertussis', 'boosters', 'attributable', 'flee', 'hatch', 'cresci', 'yarandi', 'morrell', 'emailing', 'teenager', 'negotiate', 'continuously', 'palatable', 'diphtheria', 'kcal', 'prepositional', 'sham', 'demographic', 'pretesting', 'regimen', 'abcadea', 'adeabca', 'roadside', 'curb', 'crosswalk', 'retardation', 'scaffolded', 'eat', 'transcribing', 'youtube', 'convey', 'conform', 'conventions', 'saharan', 'africa', 'parasites', 'exergames', 'victory', 'mozambique', '378', '265', 'sole', 'phonemic', 'responds', 'multidimensional', 'scaling', 'anomalous', 'hyperlink', 'vcrs', 'bulk', 'emerge', 'fairness', 'ingestion', 'fecal', 'sigurdsson', 'austin', 'surgical', 'highpreference', 'collectors', 'unaware', 'constituted', 'denied', 'aircraft', 'pilots', 'postflight', 'simulators', 'braindamaged', 'kinaesthetic', 'illusion', 'industry', 'violators', 'ergonomics', 'peds', '400', 'detectors', 'accrediting', 'merit', 'biology', 'improper', 'akin', 'unbuckled', 'buckle', 'impressed', 'carpet', 'snatch', 'usable', 'millions', 'clearance', 'deploy', 'demining', 'nonspoken', 'hepatitis', 'wished', 'doubtful', 'unstable', 'ideal', 'unexploded', 'ordnance', 'conforming', 'participatory', 'fair', 'brainstem', 'shielding', 'phasing', '180', 'rereferencing', 'cabrs', 'medians', 'recognizable', 'nonfunction', 'ubiquity', 'interpretative', 'horizontal', 'trimmed', 'restocking', 'bars', 'disproportionately', 'underpowered', 'plague', 'quasiexperimental', 'truth', 'hits', '0008', '0005', 'psychopathology', 'execution', 'carefully', 'thai', 'numeral', 'thoroughlyexamining', 'exemplary', 'tapes', 'vliet', 'pm', 'wimperis', 'creak', 'vandereijk', 'worldcat', 'metaregister', 'commencing', 'evidential', 'borne', '0009', '4b', '1980', '1806', '1937', '1966', 'sociological', '1952', '1970', 'controllability', 'bypass', 'poorest', 'benefitted', 'lessen', 'curative', 'psychopharmacological', '1948', 'saving', 'guaranteed', 'noncontingently', 'procrastinated', 'evenly', 'depiction', 'ther', '266', 'psychomotor', 'embark', 'distill', 'devising', 'redundant', 'underscoring', 'downward', 'faculty', 'regressed', 'pediatr', 'renders', 'iphones', 'safecarea', 'logistics', 'hazards', 'retaining', 'drink', 'emptied', 'operationalised', 'sales', 'approached', 'genetic', 'gonorrhea', 'chlamydia', '2323', 'ehealth', 'tie', 'healthiness', 'poke', 'generalizations', 'mc', 'subcategories', 'morbid', 'outperformed', 'collaborators', 'presumably', 'csas', 'nondirected', 'kitchen', 'pillow', 'intraverbals', 'coin', 'thumb', 'dividing', 'youngest', 'restaurant', 'urologic', 'overtreatment', 'tactical', 'lilacs', 'attrition', 'sees', 'ost', 'salkovskis', 'hellstrom', '1991', 'gear', 'hundreds', 'seldomly', 'acted', 'succession', '4yrs', 'touching', 'infractions', 'insensitive', 'terminate', 'brought', 'dialectical', 'stimulated', '867', 'sdt', 'passing', 'takers', 'deadlines', 'scallop', 'onsets', 'rimes', 'nonharmful', 'proprioceptive', 'illuminate', 'sensation', 'firefighter', 'mascot', 'presenter', 'pcs', 'facail', 'justified', 'goodness', 'unjustified', 'extrapolations', 'proficiently', 'varsity', 'athletics', 'certainly', 'linemen', 'submitting', 'guardians', 'shiny', 'forecasting', 'damping', 'pickups', 'trucks', 'fastening', 'contextually', 'null', 'formally', 'proficient', 'refused', 'marijuana', 'unwanted', 'aversiveness', 'bolstering', '17days', 'neediest', 'supervising', 'liked', 'bitmap', 'incoming', 'extracurricular', 'andused', 'literate', 'excelled', 'thinned', 'inputs', 'kids', 'pekanbaru', 'capital', 'riau', 'province', 'notoriously', 'profiling', 'arrang', 'signaling', 'deduce', 'sketches', 'maintainable', 'maladaptive', 'orientated', 'geographically', 'disparate', 'bolster', 'rotating', 'strain', 'capitalise', 'potent', 'nos', 'characteristically', 'eikeseth', 'eldevik', 'smoked', 'neuropsychologist', 'neuropsychologists', 'inservices', 'adjustable', 'culminated', 'a1b1a2b2', 'overpower', 'theme', 'intoning', 'rhythmic', 'gentleman', 'welch', 'tably', 'spouse', 'ababa', 'aristotle', 'humankind', 'kind', 'improvise', 'prevailed', 'charles', 'bridges', 'academia', 'rigors', 'interior', 'mere', 'introverted', 'teamwork', 'ott', 'faceted', 'vantage', 'mutual', 'proffers', 'recommendation', 'eschew', 'ahistoric', 'prematurely', 'delaying', 'mitigate', 'happening', 'tips', 'irksome', 'mg', 'exposes', 'charted', 'gateway', 'residence', 'residences', 'purposely', 'enriching', 'multiethnic', 'infraction', 'weakness', 'worsened', 'interconnections', 'cybocs', 'cgi', 'sum', 'handwritten', 'listed', 'inevitable', 'operationalize', 'professionalism', 'habit', 'darwin', 'ocean', 'ryunosuke', 'satoro', 'handwrite', 'persistently', 'intersubject', 'notion', 'psychoeducation', 'sn', 'nd', 'narrator', 'historic', 'sheets', 'atr', 'psychotherapies', 'conners', 'unblinded', 'expose', 'roleplayed', 'voted', 'conversely', 'dropout', 'agency', 'powerpointa', 'pretraining', 'reviewer', 'consulted', 'adjudicate', 'registry', 'prerequisites', 'omissions', 'path', 'turning', 'bending', 'sits', 'brim', 'intersection', 'cox', 'discontinue', 'failing', 'retrievable', 'transferable', 'subscribe', 'passes', 'preserve', 'stored', 'cabinet', 'intensities', 'electrophysiologic', 'cauterization', 'spain', 'masking', 'invasivity', 'schwannoma', 'uncomfortable', 'otologic', 'otoneurosurgical', 'classical', 'lifetime', 'episode', 'electromyographic', 'translabyrinthine', 'pupils', 'fighting', 'andalusia', 'totally', 'doze', 'infarct', 'jebson', 'corticospinal', 'excitability', 'washout', 'ssdanalysis', 'singwin', 'vicon', 'motus', 'interrater', 'diaries', 'nighttime', 'inhaler', '10y', 'utterance', 'leveraging', 'pioneering', 'disrespectful', 'att', 'dis', '233', '248', 'hi', 'hello', 'actigraph', 'outperforms', '3y', 'bang', 'buck', 'braingame', 'brian', 'wampold', 'worsham', 'svoboda', 'richards', 'brand', 'esy', 'summer', 'interpreters', 'particularities', 'microphone', 'painful', 'instance', 'diary', 'biophysical', 'imp', 'derby', '2013b', 'residing', 'infarction', 'dictation', 'perfect', 'directing', 'chute', 'nevins', 'fed', 'withheld', 'thing', '024', 'govern', 'resistive', 'asymmetrical', 'singular', 'tolerate', 'jmir', '2227', 'regress', 'simulates', 'ymca', 'reactivity', 'setback', 'bands', 'misunderstood', 'heuristics', 'res', 'e22', '2196', 'weber', 'beard', 'bomyea', 'schmidt', 'richey', 'buckner', 'timpano', 'gym', 'reflects', 'mile', 'formula', 'ranks', 'individualization', 'otv', 'hawaii', 'otvs', 'malleability', 'amir', '1983', 'elemental', 'automaticity', 'lengthy', 'achievable', 'tristram', 'bases', 'inedible', 'inconsistency', 'aligning', 'discrepancies', 'hrycaiko', 'bedroom', 'waking', 'norms', 'disrupting', '802', 'refinements', 'telescoping', 'trolley', 'sectional', 'rti', 'decodable', 'illustrations', 'richness', 'preparations', 'intractable', 'workload', 'navigating', 'disparities', 'morbidity', 'preventable', 'finished', 'hitting', 'manoeuvre', 'wall', 'cane', 'categorize', 'obstacle', 'collisions', 'vignette', 'scripting', 'embedding', 'wo', 'categorised', 'lifeskills', 'naturally', 'modifiable', 'gluteus', 'alsop', 'shahan', 'reacquisition', 'discriminability', 'lever', 'conventionally', 'follower', '108', 'attentiveness', 'etiquette', 'figures', 'retellings', 'assembling', 'defects', 'discontinuity', 'overlarge', 'transmission', 'vibrations', 'assemble', 'wobble', 'recommends', 'relieve', 'inclines', 'surfaces', 'extensors', 'torso', 'assembly', 'deign', 'keyed', 'cellular', 'ultimate', 'complicate', 'synthesise', 'relearning', 'refining', 'charlop', 'kurtz', 'casey', 'hanley', 'thompson', 'lindberg', 'slim', 'subtracting', 'county', 'protective', 'alabama', 'equalized', 'fluid', 'revisions', 'scorer', 'comparatively', 'timelier', 'classroomwide', 'employer', 'verbalizing', 'verbalized', 'hung', 'grants', 'faith', 'finance', 'combinedp', 'dish', 'trauautism', 'annotation', 'lingual', 'sporadically', 'underestimate', 'toll', 'church', '1114', 'tiger', 'incarnation', 'williams', 'seizures', 'surgeries', 'filtered', 'epilepsy', 'spurious', 'spellings', 'handed', 'orthographic', 'durability', 'agraphia', 'fbas', 'scheithauer', 'stewardship', 'jargon', 'diagrams', 'adelinis', 'loads', 'copies', 'ml', 't7', 'outperforming', 'rigidity', 'rows', 'antiretroviral', 'detectable', 'hyperbolic', 'dot', 'retaught', 'noodles', 'noting', 'sticker', 'industries', 'diplegic', 'botulium', 'concomittant', 'polish', 'prelude', 'uzunboylu', 'lose', 'psychosis', 'tells', 'olds', 'nonexistent', 'dtf', 'page', 'promptings', 'counterparts', 'profited', 'deeply', 'epistemology', 'objectification', 'intersubjectivity', 'singularity', 'gast', 'slideshow', 'expertise', 'worksheets', 'morpheme', 'prebaseline', 'institutionalized', 'behaviourally', 'microanalysis', 'depend', '3gs', 'hammond', 'whatley', 'ayres', 'orthoses', 'schemes', 'paraplegia', 'unused', '40s', 'manualised', 'metaphors', 'suds', '77', '07', '08', 'linnan', 'steckler', 'triangulated', 'convergence', '114ms', 'supplies', 'invoking', 'etymotic', 'rivermead', '60ms', '296', '1212', 'mrc', 'unanticipated', 'pipeline', 'rehabil', '20122012', '167', 'accessory', 'jar', 'artery', 'spls', 'serially', 'amplified', 'tuning', 'anomalies', 'prof', 'huseyin', 'exchangeable', 'reallocation', 'isocial', 'takes', 'muves', 'neuromotor', 'workspace', 'preparatory', 'optimise', 'nonadherent', 'inhalers', 'mdilogii', 'bimonthly', 'dissimilar', 'ordination', 'contemplated', 'recognised', 'antipsychotic', 'doubted', 'looped', 'coda', 'performer', 'translation', '268', 'lieu', 'agility', 'bruininks', 'oserestky', 'researching', 'organise', 'noncongenital', 'preimplant', 'preschoolaged', 'arriving', 'ears', 'inserting', 'alstot', 'standpoint', 'designer', 'agnostic', 'argument', 'scholars', 'sufficiency', 'quit', '8341', 'disaggregated', 'futility', 'financially', 'specification', 'ecs', 'bluetooth', 'adapts', 'badger', 'fox', 'customizable', 'automates', 'architecture', 'defines', 'synchronization', 'powering', 'mains', 'exceed', 'habitat', 'protecting', 'characterize', '3862', 'habitats', 'nests', 'chicks', 'fledged', 'annual', 'lee', 'declines', 'mammals', 'compounding', 'chick', 'balances', '8286', '86198', '434', 'gmbh', 'electrodermal', 'neihart', 'impart', 'admissible', 'squared', 'plural', 'spuriously', 'noninvasive', 'tissue', 'mates', 'engines', 'pubmed', 'operationalized', 'inverse', 'pnds', '687', '195', 'lewis', 'distractions', 'cuts', 'abrasions', 'minor', 'burns', 'xcode', 'philadelphia', 'adobe', 'attendant', 'successes', '145', 'flavor', 'textbook', 'entries', 'illuminated', 'analogy', 'situated', 'nomothetic', 'pools', 'favoured', 'expended', 'comprehended', 'seminar', 'associate', 'ababab', 'voluntarily', 'intrasubject', 'discrepancy', 'pathways', 'topical', 'isolating', 'dutt', 'originally', '97', 'andragogical', 'unfettered', 'criterions', 'corroborative', 'revisited', 'desensitization', 'multitiered', 'sort', 'containers', 'ensured', 'nonresponding', 'corroboration', 'executed', 'ratesmeasured', 'presrxocr', 'waned', 'midway', 'pharmacy', 'noncompleters', 'cumbersome', 'demystifies', 'plausible', 'phylogeny', 'ontogeny', 'prescription', 'serviceable', 'artists', 'unforeseen', 'relegated', 'unknowable', 'spirit', 'francis', 'bootstrapping', 'leverage', 'brews', 'confluence', 'requisite', 'combinatorial', 'punished', 'forcibleness', 'remarks', 'resolved', 'afore', 'notions', 'purportedly', '1969', 'pustejovsky', 'jenson', 'sauber', 'literary', '572', 'evil', 'comic', 'currency', 'adjudicated', 'illegal', 'nonsexual', 'outbursts', 'noncompliance', 'choiceworks', 'relieved', 'superheroes', 'shadish', 'bay', 'blos', 'lts', 'heterogeneity', 'latent', 'bicycles', 'prioritize', 'insufficiently', 'san', 'big', 'garnered', 'feasibly', 'undermine', 'optical', 'multiplestimulus', 'underreported', 'trialing', 'abduction', 'dealt', 'jointly', 'practically', 'emulating', 'vicariously', 'howes', 'staggering', 'workbook', 'los', 'permitting', 'autopopulates', 'scholarly', 'tweaking', 'optimism', 'indispensable', 'heads', 'adjuncts', 'gregory', 'uran', 'fantetti', 'lectures', 'suppression', 'odors', 'francisco', 'landscape', 'collage', 'salt', 'commonalities', 'saini', 'ourmedicationmanagement', 'preventative', 'lyrical', 'olfactometer', 'scents', 'cinnamon', 'hitter', 'league', 'season', 'persisted', 'overactivation', 'northwick', 'flexor', 'flexors', 'incorrectly', 'sbi', 'administrations', 'questioner', 'harness', 'neuroplastic', 'evidencing', '1957', 'flap', 'diagnostically', 'repairs', '1year', 'cpq', 'sma', 'unexpectedly', 'rupture', 'questioning', 'expansions', 'figure', 'prominently', 'album', 'hamper', 'truly', 'spot', '395', '436', 'unsafe', 'victims', 'sustain', 'adventure', 'lysosomal', 'begins', 'cures', 'manifestations', 'concentrating', 'vaughn', 'tyler', 'predominately', 'mucopolysaccharidosis', 'prs', 'christian', 'satsangi', 'abundant', 'mytalk', 'coincided', 'chard', 'contraction', 'ccft', 'mss', 'farm', 'doctor', 'rationales', 'audiobooks', 'covering', 'narratively', 'crd42017081532', '733', 'echoics', 'impedes', 'partnerships', 'cab', 'aug', 'longest', 'informs', 'inferences', 'wealth', 'flaws', 'questionsis', 'nongovernmental', 'tbilisi', 'spherical', 'fabric', 'keio', 'criticized', 'identities', 'multiplied', 'proponents', 'interrogation', 'lpts', 'ile', 'ascertained', 'widespread', 'ceased', 'tribology', 'inflammatory', 'acetabulum', 'acetabular', 'formulas', 'straight', 'reproducibility', 'denominators', 'creators', 'makers', 'immediacy', 'operatively', 'fulfilled', 'destined', 'statisticians', 'backgroundpeople', 'methodsingle', 'resultsresults', 'conclusionsresults', 'attribution', 'repositioning', 'prominent', 'pricing', 'elaborate', '22weeks', '8years', '6years', 'proposal', 'stroop', '540', 'exemplified', 'swiping', 'ranking', 'export', 'entailed', 'remits', 'sq', 'performs', 'nested', 'minibest', 'pharmacotherapy', 'activating', 'physiotherapist', 'priest', 'hamilton', 'rang', 'rabbis', 'authorities', 'spiritual', 'admitted', 'belgrade', 'walked', 'stick', 'suffered', 'lumbopelvic', 'physiatrist', 'assume', 'checksis', 'nonsimulated', 'thighs', 'manifested', 'cease', 'stopped', 'likewise', 'revisiting', 'mct', 'font', 'nontablet', 'customization', 'sway', 'fonts', 'rooted', 'tri', 'aerobic', '30minutes', 'unsupervised', 'prro', 'seriously', 'permutation', 'citing', 'summarizes', 'domestically', 'teacching', 'abroad', 'colors', 'expenditure', 'ofeye', 'nonmalignant', 'ultra', 'fourteen', 'limbs', 'formulate', 'mechanistically', 'heel', 'deficient', 'weaker', 'colliding', 'symbolization', 'neglected', 'acetaminophen', 'hysingla', '1207', 'hydraulic', 'referential', 'imagistic', 'verbatim', 'disrupts', 'think', 'stative', 'pointers', 'binomially', 'transfemoral', 'misuse', 'receives', 'priests', 'chaplains', 'imams', 'reservation', 'demographics', 'muscular', 'lumbago', 'stabilization', 'narrated', 'ru', 'bu', 'ka', 'enforced', 'backgrounds', 'emotionals', '08881', 'religion', 'meanings', 'indonesian', 'bo', 'barthel', '598653', '219626', '062591', '207407', '99005', 'amputee', 'ki', 'xy', '12months', 'discussionthe', 'registrationclinicaltrials', 'nct03351712', 'deposited', 'reimbursed', 'submission', 'uptake', 'ault', 'backgroundobesity', 'epidemic', 'designa', 'superiority', 'supersized', 'contract', 'fiction', 'foundations', 'reintroduced', 'undifferentiated', 'arrange', 'actonhealth', 'synonyms', 'endowed', 'labs', 'dyslexia', 'lms', 'educated', 'ebp', 'resembled', 'inning', 'outs', 'multialternative', 'sporting', 'round', 'tiered', 'blue', 'sky', 'convenience', 'organizing', 'itt', 'plots', 'rd', 'computationally', 'transparent', 'supposed', 'coordinates', '596', '168', 'preand', 'tit', 'impressions', '726', 'ordinarily', 'overlooked', 'rohatgi', 'telemental', 'coercion', 'iatrogenic', 'cardboard', 'waist', 'chest', 'chip', 'themes', 'hints', 'meditation', 'earliest', 'inpromptu', 'collate', 'informatics', 'exercised', 'personalised', 'modelled', 'district', 'diagnose', 'trouble', 'executing', 'undergo', 'discovered', 'uncertainties', 'socioeconomic', 'affluent', 'west', 'bengal', 'scrds', 'hfa', 'clicks', 'analogous', 'mimic', 'outloud', 'writer', 'draft', 'builder', '9th', 'pursued', 'griffen', 'macduff', 'krantz', 'mcclannahan', 'capitalizes', 'wolery', 'paragraphs', 'mentioned', 'dictionary', 'translate', 'scarcity', 'designers', 'foremost', 'metaphor', 'emulated', 'enrich', 'intervened', 'moods', 'emoticons', 'neitzel', 'volitionally', '488', 'bed', 'dropcam', 'variants', 'flower', 'mckenna', 'bunuan', 'exchanging', 'contrived', 'ais', 'pulse', 'generator', 'consented', 'distracters', 'redirect', 'rapp', 'singled', 'partnered', 'relevancy', 'neurodegenerative', 'attested', '1829', '858', 'urgently', 'heat', 'thermography', 'vollmer', 'policymakers', 'praised', 'imply', 'actually', 'desires', 'secondly', 'wicked', 'busy', 'complying', 'bureaucratic', 'appointed', 'america', 'sine', '413', 'really', 'matrixes', 'checking', 'firstly', 'keeps', 'reproduced', 'sniff', 'conceived', 'shapes', 'forecast', 'muething', 'vega', 'reprimands', 'volitional', 'qua', 'achieves', 'rad', 'outpatients', 'reflectivity', 'fabricating', 'film', 'thicknesses', 'reflector', 'optoelectronics', '3weeks', 'swallowing', 'wiping', 'pow', 'perspiration', 'measurably', '160', 'kingdom', 'undetectable', 'aluminum', 'nitride', 'silicon', 'uncooled', 'invention', 'patent', 'overarm', 'throw', 'reproduction', 'videotaping', 'thermoregulatory', 'childen', 'pekalongan', '3a', 'disturb', 'jeopardy', 'unpleasant', 'infectious', 'proximal', 'electroencephalograms', 'spatio', 'neurons', 'eegs', 'thermo', 'lunch', 'reversion', 'affirmation', 'unprecedented', 'properly', 'github', 'foreshadowed', 'sasb', 'criticism', '9months', 'nlp', 'engine', 'align', 'misalignment', 'selye', 'gym2learn', 'igniting', 'vaporizers', 'forecasts', 'nonproblem', 'icas', 'raised', 'ica', 'vaporization', 'illicit', 'heats', 'labelling', 'televisions', 'managers', 'economically', 'spontaneously', 'tawc', 'piecewise', 'stabilizes', 'postimplantation', 'ignoring', 'awarding', 'centres', 'timely', 'underutilised', 'sydney', 'australia', 'universe', 'disturbed', 'midsagittal', 'articulography', 'ema', 'articulator', 'sonant', 'erred', 'intersegment', 'distortions', 'confounded', 'perceptually', 'karger', 'ag', 'fvc', 'administrators', 'handicapped', 'comprehensiveness', 'hitherto', 'nonpathological', 'unavailable', 'comprehensible', 'inhibiting', 'horan', 'nih', 'vsd', 'irritation', 'expiratory', 'fev1', 'basel', 'intermediaries', 'parties', 'intuitively', 'reconceptualise', 'dilemma', 'customisation', 'customisable', 'redesigning', 'expedites', 'personalize', 'richman', 'appl', 'behav', 'audiometric', 'accept', 'tug', 'approval', 'tightly', 'permitted', 'individualistic', 'intermediary', 'innovate', 'commercialize', 'elaborates', 'skeletons', 'skeleton', 'categorizes', 'realigned', 'anal', '125', 'consistencies', 'unskilled', 'relatives', 'annoyed', 'playful', 'empower', 'printing', 'gutman', 'backbone', 'golden', 'imagined', '250', 'incumbent', 'indigenous', 'phased', 'discontinuation', '2006', '902', '131', '152', 'nonfunctional', 'computations', 'busk', 'serlin', 'constrained', 'scrutinises', 'lecturing', '113', 'grid', 'schematically', '1468', 'dosage', 'empathize', 'fortunately', 'attracts', 'reciprocate', 'conceptualize', 'carter', 'discriminating', 'washington', 'postactivation', 'realization', 'timbre', 'cis', 'postlingually', 'deafened', 'reminded', 'db', 'utilities', 'pros', 'contralateral', 'bimodally', 'nijmegen', 'subdomains', 'cultivate', 'melody', 'circumstance', 'winner', 'simon', 'evolutionary', 'claiming', 'homo', 'rehearse', 'unstudied', 'taiicomputer', 'instructionas', 'taiiaugmentative', 'realitywere', 'initiative', 'taxonomically', 'dearth', 'biomarkers', 'translates', 'asib', 'molecular', 'molar', 'flow', 'touchpoints', 'carts', 'debt', 'conservation', 'emphasizes', 'retailing', 'basket', 'solid', 'terrain', 'originated', 'amidst', 'sic', 'crisis', 'conjecture', '747', '762', 'vernucio', 'debert', '439', 'poisson', 'ses', 'unfolds', 'approximate', 'lyddy', 'barnes', 'holmes', 'tovar', 'chavez', 'encouragement', 'api', 'xapi', 'trough', 'mistake', '745', '114', 'relnet', '449', 'diversified', 'explaining', 'endeavors', 'symbiotic', 'karin', 'revolves', 'accelerate', 'alexandra', 'rutherford', 'sociologist', 'tackle', 'awarded', 'fantastic', 'tickets', 'lottery', 'winning', 'preferring', 'simpler', 'stringency', 'pop', 'warner', 'sociology', 'unpacking', 'concentrates', 'considers', 'mb', 'abrupt', 'raffle', 'got', 'miniaturization', 'hope', 'sprung', 'multidisciplinary', 'suboptimal', 'parsimonious', 'overarching', 'unified', 'fulfill', 'classroo', 'carton', 'transporting', 'selectionist', 'fueled', 'distributional', 'comorbidity', 'liver', 'intestines', 'collaborated', 'regulating', 'desks', 'grapheme', 'morphemic', 'rudimentary', 'lungs', 'stomach', 'preprogrammed', 'governments', 'normerally', 'squeeze', 'sale', 'bulky', 'reflection', 'axis', 'res2018', '153', 'summarythe', 'layouts', 'spacestraditional', 'arguing', 'shorten', '019', '012', 'cover', 'compositions', 'orthopedic', 'deeper', 'significances', 'interactivity', 'tries', 'invisible', 'fears', 'pamphlet', 'specialties', 'machinery', 'pod', 'volkmar', 'springer', 'burdens', 'assessme', 'nts', 'feedforward', 'austism', 'dev', 'disord', 'offender', 'rooker', 'zarcone', 'amenable', 'agent', 'turkish', 'scruggs', 'identifier', 'pretended', 'stretch', 'perforlittle', 'practimance', 'ce', 'coordinate', 'economicus', 'eagerness', 'carries', 'substituting', 'mentalistic', 'impede', 'inadequately', 'alleged', 'circumference', 'nondeviant', 'pairedstimulus', 'transitivity', 'ba', 'ca', 'midst', 'postulates', 'portugal', 'precurrents', 'origins', 'cicchetti', 'nonhumans', 'touched', 'raises', 'tais', 'morrison', '523', 'proves', 'deodorant', 'nobel', 'laureate', 'award', '1311', '1319', 'doehring', 'sounder', 'asset', 'playtime', 'observable', 'confrontation', 'incarcerated', 'boot', 'ma', 'summarising', 'neurobehavioural', 'dystonia', 'dyskinetic', 'followup', 'anadolu', 'suggestive', 'schooler', 'expectant', 'tootle', 'gvsm', 'commensurate', 'mineral', 'firm', 'clay', 'interventional', '187', 'groupings', 'anonymously', 'slips', 'participations', 'useable', 'intraindividual', 'scalable', 'bike', 'overscaffolding', 'redesigns', 'empowers', 'decorating', 'holidays', 'abcdcd', 'spillover', 'perpetuating', 'deferred', 'illnesses', 'ebm', 'handbookthe', 'mixture', 'misleading', 'vries', 'morey', 'frontotemporal', 'vismara', 'manualized', 'probably', 'priorities', 'adapting', 'distinguished', 'allergies', 'streams', 'gift', 'wrapping', 'ranova', 'fluently', 'casino', 'winnings', 'maggin', 'spec', 'educ', '3331', '4102', 'friedman', 'seminal', 'intersperses', 'distressed', 'planar', 'inserts', 'saturation', '60th', 'accomplishments', 'southern', 'california', 'technician', 'professor', 'na', 've', 'coincide', 'respiration', 'conducts', 'cycles', 'delineating', 'warrant', 'browse', 'embolic', 'cerebro', 'vascular', 'accident', 'narratives', 'latencies', 'unstandardised', 'methodologically', '0741932511435176', 'integrations', 'consequent', 'sided', 'completely', 'interviewer', 'interviewstream', 'converge', 'projecting', 'probabilities', 'expore', 'pool', 'ranovas', 'kindergarteners', '1177', 'comparability', 'citizenship', 'wequiv', 'supervisor', 'props', 'wmft', 'pmal', 'shooting', 'baskets', 'basketball', 'shots', 'sides', '14th', 'updating', 'kickball', 'crso', 'grading', 'morphine', 'tapering', 'withdrawals', 'audiologist', 'unassisted', 'fda', '163', 'approximates', 'somnolence', 'dizziness', 'postherpetic', 'splitting', 'tetany', 'abnormal', 'ruled', 'conflicts', 'civil', 'legal', 'joints', 'preponderant', 'malta', 'navigational', 'weakening', 'dysesthesia', 'courts', 'exam', 'kg', 'height', 'handsprings', 'synchronised', 'covariates', 'gifted', 'multisite', 'debilitating', 'arguably', 'manifests', 'mandate', 'disagree', '847', 'exams', 'underpins', 'snyder', 'dayton', 'concordance', 'beats', 'electrocardiography', 'photoplethysmography', 'projector', 'sleeping', 'vrije', 'universiteit', '740', 'heartbeats', 'bland', 'neuralgia', 'wallace', 'zhou', 'goff', 'splint', 'discharged', 'presumed', 'electrocardiogram', 'chores', 'sonoflex', 'deficiency', 'mounted', 't1', 't2', 'kidney', 'altman', 'analgesics', 'patch', 'mu', 'intolerable', 'blank', 'unsolicited', 'splints', 'investigational', 'ninety', 'eighty', 'corroborating', 'amplification', 'interpose', 'yoking', 'complicated', 'cluster', 'enterprise', 'utaut', 'judgement', 'tolerant', 'apa', 'entitled', '467', 'factorability', 'confirmatory', 'garners', 'maximizing', 'pairings', 'seventh', '71children', '0125', 'reinforces', 'underscores', 'caregiving', 'ambulating', 'inactive', 'encoder', 'processor', 'stipulations', 'paperwork', 'federal', 'funding', 'stemming', 'adequacy', 'invariant', '1975', 'cornerstone', 'voicing', 'systemic', 'suburban', 'omit', 'asserts', 'assuming', 'borrowed', '823', 'quantifier', 'acknowledged', 'discriminations', 'overselective', 'yielding', 'tertile', 'kappa', 'accounting', 'ipad2', 'disappearance', 'substance', 'locating', 'trapped', 'sized', 'inanimate', 'benchmarking', 'reaffirm', 'interspersed', 'tenable', '1200', '900', 'loudness', 'modulated', 'channels', 'acutely', 'northern', 'oromotor', 'prioritized', 'dysphagia', 'implicationsthe', 'merits', 'taichung', 'niche', 'hri', 'tune', 'syllabus', 'covers', 'shall', 'changesfrom', 'b2', 'desensitisation', 'camperdown', 'givers', 'banks', 'unsatisfactory', 'gratitude', 'adversity', '208', 'recovered', 'loreta', 'insula', 'cingulate', 'spirituality', 'traps', '6640000', 'neuronal', 'neurofeeedback', 'complaint', 'cultivating', 'denoising', 'eminence', 'tomographic', 'stanford', 'neighbourhood', '10x10', 'blob', 'contradict', 'emulator', 'understandable', '1989', 'downes', 'hci', 'remainder', 'ambient', 'borders', 'continual', 'markets', 'hampering', 'routinely', 'periodic', 'juggle', 'c2', 'incongruence', 'companies', 'mediating', 'ib', 'eaa', 'resist', '3x3', 'matrices', 'recombined', 'invoked', 'pigeons', 'recover', 'tenets', 'clarifying', 'nonvocal', 'forgetting', 'emphasises', 'videotote', 'appreciated', 'bid', 'thank', 'ipoda', 'admired', 'hesitated', 'alerts', 'unwilling', 'bluffing', 'expenditures', 'parceled', 'exp', 'ameta', 'taste', 'sensed', 'intellitools', 'concur', 'lesser', 'distinguishing', 'damages', 'compromises', 'bedrock', 'circumvent', 'seekers', 'navigated', 'conner', 'smartwatches', 'moto360', 'dwelling', 'neurosensory', 'ps', 'fisher', '491', '498', 'deleon', '519', '533', 'approachability', 'phonotactic', 'neighborhood', '249', '255', '1985', 'prelingual', 'seizure', 'incompatible', 'motivate', 'inviting', 'tenuous', 'dunn', 'kruskalwallis', 'elementaryaged', 'convergent', 'l1', 'formant', 'f3', 'nhs', 'royal', 'deceptive', 'resultstwo', 'england', '199', 'wales', 'scotland', 'attaining', 'slt', 'backgroundcommunication', 'comprises', 'exacerbating', 'proceduresan', 'publicized', 'boiling', 'permanence', 'rcslt', 'secrets', 'surprises', 'bourret', 'und</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3219</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>['intervention', 'study', 'design', 'children', 'participants', 'results', 'students', 'video', 'based', 'behavior', 'training', 'research', 'single', 'using', 'asd', 'treatment', 'skills', 'autism', 'used', 'effects', 'use', 'social', 'multiple', 'analysis', 'case', 'baseline', 'data', 'studies', 'self', 'disabilities', 'communication', 'technology', 'modeling', 'interventions', 'effective', 'instruction', 'learning', 'teaching', 'subject', 'effectiveness', 'individuals', 'performance', 'behavioral', 'effect', 'speech', 'functional', 'aba', 'intellectual', 'reinforcement', 'school', 'computer', 'aac', 'time', 'support', 'behaviors', 'evidence', 'response', 'program', 'methods', 'outcomes', 'group', 'showed', 'feedback', 'high', 'increased', 'evaluated', 'sessions', 'child', 'visual', 'discussed', 'disorders', 'participant', 'compared', 'findings', 'prompting', 'assessment', 'practice', 'disability', 'activity', 'demonstrated', 'phase', 'implications', 'education', 'experimental', 'task', 'increase', 'purpose', 'teach', 'reading', 'teachers', 'therapy', 'method', 'positive', 'measures', 'included', 'procedures', 'following', 'review', 'significant', 'student', 'evaluate', 'future', 'improve', 'game', 'strategies', 'developmental', 'play', 'conducted', 'indicated', 'generalization', 'quality', 'problem', 'different', 'evaluation', 'classroom', 'development', 'maintained', 'stimulus', 'improved', 'preference', 'spectrum', 'approach', 'instructional', 'adults', 'acquisition', 'implementation', 'levels', 'people', 'cognitive', 'probe', 'physical', 'maintenance', 'provide', 'young', 'parents', 'present', 'efficacy', 'engagement', 'motor', 'suggest', 'peer', 'management', 'settings', 'conditions', 'examined', 'control', 'current', 'systematic', 'language', 'academic', 'procedure', 'applied', 'condition', 'responses', 'clinical', 'level', 'word', 'number', 'target', 'words', 'subjects', 'device', 'stereotypy', 'test', 'provided', 'related', 'stimuli', 'picture', 'activities', 'treatments', 'low', 'meta', 'alternating', 'implemented', 'setting', 'moderate', 'teacher', 'application', 'conclusions', 'model', 'skill', 'verbal', 'comparison', 'designs', 'specific', 'non', 'health', 'change', 'ipad', 'validity', 'phases', 'parent', 'assessed', 'years', 'severe', 'daily', 'follow', 'weeks', 'potential', 'patients', 'impact', 'examine', 'virtual', 'increasing', 'staff', 'literature', 'post', 'size', 'software', 'attention', 'tasks', 'interaction', 'improvement', 'devices', 'memory', 'reported', 'injury', 'function', 'changes', 'did', 'preferred', 'monitoring', 'individual', 'package', 'including', 'accuracy', 'overall', 'responding', 'age', 'independent', 'objective', 'new', 'trial', 'ability', 'access', 'developed', 'paper', 'elsevier', 'observed', 'associated', 'mean', 'prompts', 'scores', 'taught', 'early', 'improving', 'special', 'sample', 'adolescents', 'care', 'acquired', 'determine', 'rehabilitation', 'week', 'elementary', 'trials', 'investigated', '10', 'participated', 'improvements', 'brain', 'year', 'analyses', 'significantly', 'information', 'delivered', 'novel', 'outcome', 'rights', 'problems', 'small', 'session', 'addition', 'reserved', 'peers', 'vocabulary', 'need', 'rate', 'generalized', 'combined', 'designed', 'challenging', 'assess', 'context', 'appropriate', 'reduce', 'items', 'strategy', 'indicate', 'pre', 'community', 'completed', 'vocal', 'models', 'automatic', 'writing', 'criteria', '12', 'generating', 'conclusion', 'limited', 'direct', 'mobile', 'home', 'authors', 'programs', 'researchers', 'equivalence', 'assistive', 'measured', 'interactions', 'presented', 'received', 'able', 'class', 'patient', 'classrooms', 'assessments', 'alternative', 'living', 'rates', 'investigate', 'preschool', 'syndrome', 'complex', 'measure', 'secondary', 'promote', 'components', 'identified', 'help', 'aged', 'previous', 'systems', 'disruptive', 'good', 'anxiety', 'behaviour', 'terms', 'schedules', 'background', 'differential', 'work', 'additional', 'implement', 'increases', 'traditional', '2016', 'initial', 'article', 'knowledge', 'adapted', 'correct', 'contingency', 'needs', 'targeted', 'online', 'decreased', 'text', 'mathematics', 'needed', 'groups', 'old', 'diagnosed', 'process', 'reality', 'criterion', 'robot', 'variables', 'important', 'assisted', 'disorder', 'primary', 'hearing', 'pain', 'sizes', 'published', 'limitations', 'collected', 'environment', 'emotional', 'learned', 'compare', 'higher', 'developing', 'reporting', 'long', 'preliminary', 'games', 'trained', 'life', 'tablet', 'stimulation', 'large', 'step', 'scale', 'aphasia', 'service', 'reduced', 'term', 'provides', 'gbg', 'met', 'types', 'reducing', 'performed', 'randomized', 'series', 'period', 'techniques', 'frequency', 'statistical', 'type', 'practices', 'vsm', 'mobility', 'digital', 'average', 'available', 'decrease', 'differences', 'gains', 'experiment', 'range', 'general', 'telehealth', 'months', 'regarding', 'walking', 'interactive', 'required', 'revealed', 'percentage', 'aim', 'common', 'greater', 'educational', 'identify', 'tool', 'fidelity', 'cost', 'aided', 'sgd', 'schedule', 'pecs', 'coaching', 'technologies', 'chronic', 'persons', 'comparing', 'shown', 'role', 'functioning', 'report', 'standards', 'cerebral', 'participation', 'employed', 'efficient', 'according', 'integrity', 'recognition', 'vm', 'modified', 'tests', 'efficiency', 'matching', 'inclusion', 'component', 'exchange', 'college', 'body', 'relations', 'modelling', 'second', 'withdrawal', 'mediated', 'mental', 'investigation', 'lack', 'palsy', 'approaches', 'directions', 'total', 'methodology', 'communicative', 'given', 'highly', 'order', 'al', 'practical', 'impairments', 'providing', 'month', 'quantitative', 'applications', 'produced', 'evaluating', 'embedded', 'adult', 'involved', 'exercise', 'grade', 'difficulties', 'transition', 'demonstrate', 'symptoms', 'resulted', 'controlled', 'typically', 'choice', 'error', 'noncontingent', 'videos', 'discrete', 'et', 'delay', 'mild', 'successful', 'measurement', 'duration', 'materials', 'mixed', 'result', 'family', 'reliability', 'contingent', 'job', 'pilot', 'focused', 'behaviours', 'focus', 'tools', 'develop', 'enhance', 'risk', 'opportunities', 'independently', 'difference', 'services', 'augmented', 'relation', 'journal', 'relative', 'literacy', 'completion', 'working', 'aid', 'recorded', 'identification', 'standard', 'hand', 'experience', 'understanding', 'lower', 'production', 'basic', 'make', 'characteristics', 'concurrent', 'versus', 'safety', 'consistent', 'main', 'stories', 'various', 'braille', 'supporting', 'feasibility', '20', 'aims', 'considered', 'better', 'selected', 'internet', 'questions', 'rird', 'smart', 'professional', 'end', 'imitation', 'fluency', 'address', 'reversal', 'protocol', 'dependent', 'specifically', 'mastery', 'content', 'supported', 'app', 'impairment', 'personal', 'area', 'goals', 'real', 'trend', 'socially', 'benefits', '11', 'consisted', 'automatically', 'comprehension', 'facial', 'framework', 'balance', 'manipulatives', 'reduction', 'prior', 'selection', 'form', 'stroke', '100', 'analyzed', 'variety', 'feasible', 'little', 'goal', 'adherence', 'learn', 'exposure', 'employment', 'articles', 'delivery', 'supports', 'person', 'variable', 'steps', 'ages', 'relevant', '2014', 'human', 'sight', 'combination', 'furthermore', 'auditory', 'point', 'day', 'scribe', 'cochlear', 'decreasing', 'brief', 'critical', 'requesting', 'analytic', 'aimed', 'patterns', 'utilized', 'ncr', 'individualized', 'disease', 'id', 'conduct', 'directed', 'natural', 'immediate', 'reviewed', 'electronic', 'include', 'making', 'weekly', 'areas', 'facilitate', 'reports', 'discuss', 'abilities', 'subsequent', 'manual', 'loss', 'theory', 'influence', 'families', 'reinforcer', 'taking', 'environmental', 'way', 'initiations', 'despite', 'fit', 'multi', 'points', '15', 'praise', 'likely', 'autistic', 'intensive', 'educators', 'suggested', 'probes', 'factors', 'methodological', 'conversation', 'instructions', 'introduction', 'cues', 'reinforced', 'programming', 'introduced', 'recommendations', 'challenges', 'deficits', '18', 'qualitative', 'tau', 'active', 'population', 'continuous', 'suggests', 'engaged', 'situations', 'promising', 'schools', 'written', 'maintain', 'carried', '30', 'therapeutic', 'graphs', 'train', 'objectives', 'score', 'similar', 'issues', 'sets', 'structured', 'principles', 'behavioural', 'middle', 'observational', 'min', 'means', 'joint', 'search', 'collection', 'negative', 'replicated', 'repeated', 'movement', 'complete', 'classes', 'users', 'times', 'repetitive', 'contingencies', 'acceptable', 'screen', 'promoting', 'set', 'perform', 'variability', 'relationship', 'technique', 'user', 'replication', 'course', 'benefit', 'preschoolers', 'short', 'necessary', 'successfully', 'childhood', 'environments', 'motivation', 'recent', 'features', 'effectively', 'discussion', 'science', 'followed', 'simultaneous', 'examining', 'presentation', 'therapists', 'observation', 'web', 'concept', 'contexts', 'finally', 'tested', 'independence', 'paraprofessionals', 'power', '17', 'occurred', 'testing', 'guidelines', 'possible', 'medical', 'descriptive', 'value', 'minimal', '16', 'gait', 'format', 'useful', 'ci', 'wide', '2010', 'empirical', 'changing', '2015', 'redirection', 'reinforcers', 'obtained', 'messages', 'consequences', 'aggression', '2011', 'depression', 'processing', '14', 'concepts', 'eye', 'speed', 'noise', 'ratings', 'running', 'public', 'assist', 'commonly', 'cases', '2013', 'base', 'tm', 'larger', 'psychological', 'acceptability', 'practitioners', 'tech', 'boys', 'seven', 'spoken', 'engage', 'contact', 'correction', 'involving', 'graphic', 'errors', 'mood', 'members', '24', 'hybrid', 'curriculum', 'shared', 'weight', 'interruption', 'perception', 'prototype', 'face', 'rated', 'dynamic', 'vocational', 'music', 'receptive', 'simulation', 'regression', 'best', 'existing', 'motion', 'progress', 'programme', 'blocking', 'university', 'resources', 'events', 'respectively', 'recording', 'interviews', 'pictures', 'scientific', 'stress', 'expressions', 'perceived', 'untrained', 'solving', 'screening', 'awareness', 'implant', 'food', 'field', 'retrieval', 'frequently', 'discrimination', 'action', 'varied', 'experiments', 'sound', 'particular', 'satisfaction', 'extinction', 'clear', 'interview', 'caregivers', 'prompt', 'generalize', 'automated', 'suggestions', 'previously', 'sib', 'values', 'led', '50', 'psychology', 'limb', 'emotions', 'diagnosis', 'detection', 'comprehensive', 'derived', 'consisting', 'item', 'symbols', 'intensity', 'tbi', 'sleep', 'lead', 'explore', 'guidance', 'tier', '2012', 'core', 'key', 'smartphone', 'objects', 'cbt', 'statistically', 'telephone', 'obesity', 'generally', 'indices', 'known', 'tracking', 'particularly', 'request', 'options', 'identifying', 'assessing', 'free', 'therapist', 'implementing', 'taken', 'phonological', 'synthesis', 'inclusive', 'combining', 'older', 'advanced', 'guideline', 'extended', 'strong', 'produce', 'spelling', 'enhanced', 'exhibited', 'concrete', 'bst', 'consumption', 'enhancing', 'targets', 'plus', 'partners', 'presence', 'bias', 'tootling', 'immediately', 'fading', 'sensory', 'interval', 'transitions', '13', 'fewer', 'success', 'open', 'utility', 'meet', 'accurately', 'procedural', 'ms', 'accurate', 'additionally', 'constant', 'story', 'extend', 'requests', 'toy', 'traumatic', 'aspects', 'days', 'standardized', 'uses', 'proposed', 'antecedent', 'emotion', 'publication', '3d', 'remote', 'turn', 'emerging', 'naming', 'delayed', 'occupational', 'partner', 'option', 'comparisons', 'widely', 'randomization', '19', 'continued', 'caregiver', 'deaf', 'biofeedback', 'right', 'significance', 'adaptive', 'substantial', 'comparative', 'sampling', 'restraint', 'affect', '95', 'expressive', 'machine', 'majority', 'computerized', 'directly', 'project', 'beneficial', 'upper', 'touch', 'established', 'importance', 'animal', 'voice', 'object', 'describes', 'vr', 'relatively', 'longer', 'validation', 'processes', 'display', 'attending', 'receiving', 'checklist', 'abab', 'learners', 'mand', 'material', 'distance', 'explored', 'interface', 'offer', 'classwide', 'affected', 'eeg', 'external', 'electrical', 'samples', 'hypothesis', 'administered', 'temporal', 'microswitch', 'incorporating', 'potentially', 'line', 'raw', 'nonverbal', 'remained', 'mouse', 'chaining', 'decreases', 'preferences', 'enrolled', 'demonstrating', 'emergence', 'women', 'experienced', 'randomised', 'psychotherapy', 'organizational', 'injurious', 'state', 'affective', 'understand', 'oral', 'reviews', 'view', 'arm', 'ar', 'simple', 'showing', 'linear', 'delays', 'adequate', 'slightly', 'sequence', 'delivering', 'systematically', 'team', 'conversational', 'consecutive', 'everyday', 'integrated', 'fct', 'wearable', 'seen', 'gross', 'operant', 'mts', 'robust', 'pattern', 'survey', 'smoking', 'reach', 'computing', 'toys', 'meat', 'residual', 'examples', 'alzheimer', 'professionals', 'forward', 'assigned', 'ipod', 'version', 'vocalizations', 'variations', 'confidence', 'questionnaire', 'pairs', 'randomly', 'usability', 'leisure', 'create', 'elements', 'especially', 'forms', 'respond', 'medium', 'presents', 'index', 'medication', 'sced', 'dyads', 'took', 'signal', 'normal', 'barefoot', 'match', 'observations', 'suggesting', '25', 'audio', 'half', 'extent', 'neck', 'addressing', 'profound', 'failure', 'called', '90', 'rapid', 'variation', 'paired', 'translational', 'recommended', 'output', 'achieved', 'happiness', 'transfer', 'ear', 'infant', 'network', 'providers', 'phone', 'fine', 'subjective', 'sentence', 'displayed', 'coding', 'adolescent', 'described', 'addressed', 'aggressive', 'mother', 'simulated', 'focuses', 'suitable', 'reviewers', 'clinic', 'planning', 'math', 'portable', 'reductions', 'computers', 'demand', '40', 'performing', 'perspective', 'periods', '80', 'clips', 'yielded', 'adhd', 'detailed', '22', '21', 'capacity', 'stage', 'acquire', 'iphone', 'multimodal', 'diverse', 'targeting', 'wii', 'actions', 'script', 'consistently', 'live', 'playing', 'involves', 'aids', 'monitor', 'meeting', 'unique', 'sensor', '26', 'difficulty', 'absence', 'noted', 'schizophrenia', 'positively', 'movements', 'engaging', 'functions', 'creating', 'major', 'consonant', 'ratio', 'adopted', 'capability', 'decision', 'motivating', 'indicates', 'exposed', 'wheelchair', 'mothers', 'world', 'sentences', 'thinking', 'sufficient', 'ict', 'expression', 'handheld', 'generated', 'degree', 'meaningful', 'drivers', 'extension', 'trends', 'impaired', 'rats', 'reinforcing', 'requires', 'perspectives', 'arrangement', 'mechanisms', 'mathematical', 'viewed', 'cognition', 'statistics', 'eating', 'parameters', 'english', 'interdependent', 'sustained', 'integration', 'works', 'lessons', 'message', 'presenting', 'male', 'acoustic', 'pa', 'history', 'minute', 'nucleus', 'editors', 'compliance', 'reached', 'place', 'utilizing', 'healthy', 'internal', 'rules', 'accessible', 'displays', 'typical', 'experiences', 'foot', 'powered', 'youth', 'calculated', 'clinicians', 'studied', 'statement', 'avoidance', 'diagnostic', 'punishment', 'dtt', 'capabilities', 'consultation', 'vibration', 'original', 'propose', 'narrative', 'vivo', 'clinically', 'correctly', 'includes', 'states', 'conventional', 'global', 'dementia', 'restricted', 'courses', 'investigations', 'tutors', 'tutor', 'requirements', 'quiet', 'phobia', 'exploration', 'token', 'adverse', 'sports', 'contribute', 'graphing', 'abstract', '35', 'valid', 'innovative', 'microswitches', 'separate', 'spatial', 'treat', 'backward', 'operation', 'guide', 'properties', 'parental', 'united', 'female', 'created', 'lexical', 'mode', 'difficult', 'agreement', 'sgds', 'prevention', 'productivity', 'contextual', 'read', 'naturalistic', 'final', 'pediatric', 'sd', 'allowed', 'client', 'intervals', 'girl', 'compound', 'played', 'recordings', 'inappropriate', 'distress', 'pda', 'sciences', 'appears', 'guided', 'left', 'clearinghouse', 'populations', 'check', 'growing', 'modes', 'typing', 'investigating', 'documented', 'accommodation', 'achievement', 'comparable', 'muscle', 'relationships', 'having', 'performances', 'explicit', 'collaboration', 'varying', 'prospective', 'tangible', 'vision', 'mastered', 'trainer', 'does', 'tablets', 'pointing', 'allows', 'card', 'categories', 'initially', 'resulting', 'advantages', 'kinematic', 'completing', 'currently', 'appeared', 'peak', 'book', 'equally', 'static', 'actual', 'inspection', 'experts', 'respect', 'surveys', 'rationale', 'length', 'multimedia', 'advocacy', 'personalized', 'decisions', 'applying', 'added', 'description', 'possibility', 'scripts', 'retention', 'warranted', 'posttest', 'leadership', 'bilateral', 'letter', 'grocery', 'augmentative', 'depressive', 'placebo', 'preparation', 'journals', 'cp', 'helping', 'competing', 'religious', 'reaching', 'ongoing', 'demands', 'later', 'custom', 'price', 'opinions', 'require', 'energy', 'longitudinal', 'beginning', 'served', '60', 'involvement', 'undergraduate', 'cai', 'designing', 'asymmetry', 'sign', 'severity', 'basis', 'regulation', 'medicine', 'evaluations', 'verb', 'statements', 'measurements', 'technological', 'assistance', 'ways', 'replications', 'researcher', 'kindergarten', 'determined', 'essential', 'newly', 'comments', 'viewing', 'ii', 'force', 'examination', 'indicating', 'estimation', 'observer', 'modalities', 'modality', 'listening', '2008', 'woman', 'ipads', 'compulsive', 'onset', 'relational', 'applicable', 'module', 'dra', 'numbers', 'defined', 'mindfulness', 'percent', 'instructor', 'measuring', 'concerns', 'visually', 'excel', '36', 'member', 'abuse', '29', 'incorporated', 'seat', 'offers', 'sought', 'deficit', 'treating', 'fourth', 'enable', 'pnd', 'topic', 'fa', 'usual', 'videoconferencing', 'extensive', 'considering', 'simultaneously', 'considerations', 'tact', 'conditional', 'modification', 'manage', 'faster', 'multicomponent', 'characters', 'uk', 'signs', 'participating', 'analyze', 'past', 'generalisation', 'nature', 'elearning', 'lists', 'neurofeedback', 'sitting', 'advances', 'laboratory', 'rating', 'enabling', 'teams', 'start', 'expected', 'academically', 'transparency', 'recovery', 'proven', 'explanation', 'assistant', 'recruited', 'exist', 'clinician', 'orientation', 'coping', 'extremity', 'vs', 'record', 'symbol', 'building', 'treated', 'analysts', 'nonoverlap', 'provision', 'maintaining', '2007', 'cross', 'escape', 'classification', '2009', 'contrast', 'heart', 'minutes', 'estimates', 'reminder', 'improves', 'stuttering', 'operations', 'growth', 'perceptions', 'dti', 'ball', 'inform', 'routine', 'usually', 'scenarios', 'postsecondary', 'preparing', 'scene', 'solve', 'analyzing', 'methodologies', 'rule', 'adaptation', 'implanted', 'characterized', 'neuropathic', 'graphical', 'indicators', 'resilience', 'latency', 'desired', 'poor', 'conducting', 'programmed', '2018', 'travel', 'reminders', 'tactile', 'asked', 'extracted', 'repertoire', 'gesture', 'quickly', 'pitch', 'facilitated', 'frame', 'coordination', 'prevalence', 'like', 'standing', 'contribution', 'wiley', 'facilitating', 'prepare', 'manuscripts', 'serve', 'mini', 'postintervention', 'cord', 'progressive', 'fes', 'unilateral', 'calls', 'gain', '28', 'consider', 'hospital', 'verbs', 'random', 'probability', 'revised', 'fast', 'multielement', 'grades', 'remains', 'regard', 'resource', 'competence', 'matched', 'popular', 'hydromorphone', 'grasp', 'papers', 'blinded', 'american', 'workshop', 'direction', 'domains', 'classdojo', '33', 'comprised', 'males', 'office', 'narration', 'overlap', 'personnel', 'select', 'consumers', 'optimal', 'conceptual', 'highlight', 'strength', 'responsiveness', 'alcohol', 'microsoft', 'expert', 'weighted', 'subtraction', 'vegetable', 'nonconcurrent', 'ride', 'attempted', '34', 'mind', 'rumination', 'account', 'shows', 'theoretical', 'seeking', 'demonstration', 'vp', 'camera', 'ab', 'extraction', 'girls', 'recommend', 'phrases', 'sensecam', 'boy', 'primarily', 'considerably', 'predicted', 'analytics', 'linguistic', 'chained', 'trainers', 'fentanyl', 'databases', 'enabled', 'bi', 'solutions', 'offered', 'intention', 'promise', 'examines', 'searched', 'describing', 'abi', 'cw', 'purposes', 'socio', 'minimally', 'neglect', 'baselines', 'tutorial', 'knee', 'algebra', 'exemplar', 'concerning', 'lines', 'emerged', 'establish', 'concluded', 'metabolic', 'clarity', 'effort', 'parts', 'appraisal', 'establishing', 'interdisciplinary', 'overview', 'imitate', 'light', 'interact', 'detect', 'man', 'healthcare', 'interventionists', 'rct', 'maximum', 'walk', '23', 'photos', 'srsd', 'unknown', 'apps', 'ebi', 'correspondence', 'pretend', 'roles', 'pretest', 'shopping', 'bug', 'collaborative', 'leg', 'struggle', 'recognize', 'symptom', 'facts', 'playfulness', 'neural', 'signals', 'example', 'critically', 'repertoires', 'dro', 'estimated', 'flexion', 'ocd', 'disruption', 'chains', 'pen', 'rural', 'aquatic', 'hyperactivity', 'solution', 'continue', 'easy', 'acts', 'stereotypic', 'increasingly', 'allowing', 'head', 'attempts', 'interpretation', 'replacement', 'cannabis', 'barriers', 'achieve', 'opportunity', 'deliver', 'platform', 'carry', 'return', 'mands', 'apply', 'sequential', 'largely', 'cm', 'idd', 'marked', 'hip', 'availability', 'stutter', 'frequencies', 'employees', 'products', 'obtain', 'density', 'flexibility', 'occurrence', 'instead', 'hard', 'questionnaires', 'board', 'comorbid', 'routines', 'exercises', 'fitness', 'placed', 'distributed', 'medline', 'list', 'acute', 'brac', 'corresponding', 'driven', 'greeting', 'reference', 'dimensions', 'allow', 'sequences', 'moderately', 'zero', 'studying', 'highlighted', 'exploratory', '05', 'ankle', 'completeness', 'status', 'messaging', 'air', 'tate', 'copyright', 'cbi', 'pivotal', 'scales', 'surface', 'ranging', 'discounting', 'sounds', 'representing', 'extends', 'robotic', 'correlation', 'indirect', 'optic', 'spontaneous', 'money', '42', 'signing', 'didactic', 'arranging', 'coded', 'workplace', 'efficacious', 'machines', 'athletic', 'fruit', 'tts', 'central', 'spastic', 'responded', 'store', 'exhibit', 'specificity', 'consort', 'clients', 'skin', 'responders', 'double', 'alliance', 'dental', 'commercial', 'began', 'located', 'maternal', 'topographical', 'lean', 'healthier', 'f0', 'reliable', 'racetrack', 'exemplars', '70', 'gathered', 'occur', 'counterbalanced', 'referred', 'choose', 'learner', 'fundamental', 'scd', 'overweight', 'apple', 'innovation', 'initiated', 'safe', 'certain', 'seek', 'city', 'fixed', 'event', 'ld', 'ccn', 'temperature', 'incentives', 'modest', 'watch', 'causes', 'neurodevelopmental', 'obsessive', 'estimate', 'interrupted', 'act', '38', 'analogue', 'names', '47', 'confirmed', 'pd', 'intelligibility', 'adoption', 'society', 'percentages', 'focusing', 'frequent', 'preventive', 'gestures', 'momentary', 'observing', 'incidental', 'tutoring', 'median', 'drug', 'socialization', 'artificial', 'elaboration', '39', 'twice', 'close', '2005', 'withdrawn', 'construction', 'contributes', 'tootles', 'altering', 'cvm', 'gave', 'illustrate', 'determining', 'viable', 'mswo', 'printed', 'fitting', 'contained', 'syllables', 'posttreatment', 'moving', 'label', 'fact', 'wwc', '78', 'distribution', 'enrichment', 'media', 'favorably', 'yield', 'motivational', 'remain', 'posture', 'dbt', 'vests', 'aesthetic', 'novice', 'prosocial', 'summary', 'accumulated', '111', 'perceptual', 'coaches', 'outside', 'greatest', 'stop', 'spinal', 'packages', 'operational', 'statistic', 'held', 'spaces', 'hierarchy', 'multistep', 'ssd', 'dog', 'instructed', 'attempt', 'centers', 'ai', 'contributions', 'flexible', 'shod', 'oriented', 'slot', 'factor', 'resolution', 'receive', 'actors', 'observers', 'cue', 'labels', 'producing', 'easily', 'adjectives', 'prompted', 'blind', 'choices', 'helped', 'rigorous', 'ird', 'mouthing', 'space', '66', 'anger', 'experimentation', 'technical', 'insufficient', 'modifications', 'exists', 'urban', '96', 'driving', 'conscious', 'successive', 'sat', 'gaming', 'hour', 'clergy', 'question', 'transitioning', 'respiratory', 'recently', 'complements', 'curve', 'stages', 'consumer', 'acceptance', 'illness', 'tone', 'opal', 'incorrect', 'iromec', 'challenge', 'sensors', 'confederate', 'divided', 'financial', 'nurses', 'graduated', 'iws', 'quantity', 'circle', 'semi', 'subsequently', 'considerable', 'sons', 'paradigm', 'element', 'shoes', 'bayesian', 'consequence', 'position', 'issue', 'evident', 'applicability', 'john', 'graduate', 'superior', 'bullying', 'modules', 'washing', 'intended', 'recall', 'thermal', 'proficiency', 'encouraging', 'participate', 'pe', 'cam', 'exclusion', 'pwds', 'arrangements', 'linked', 'economy', 'foster', 'treadmill', 'appear', 'author', 'watches', 'cnc', 'toilet', 'football', 'videogame', 'route', 'earlier', 'heeled', 'instructors', 'inconclusive', 'parkinson', 'cued', 'speaking', 'educator', 'regular', 'meetings', 'iii', 'physiological', 'emergent', 'gradually', 'rr', 'placement', 'attentional', 'belt', 'implants', 'location', 'tele', 'ibs', 'controlling', 'strengthening', 'trainees', 'master', 'pts', 'cards', 'depth', 'cbgo', 'reveal', 'avoid', 'smaller', 'fifth', '58', 'galantamine', 'mechanism', 'resistance', 'calculations', 'gaze', 'absent', 'kinect', 'kinematics', 'structure', 'overlapping', '27', 'song', 'antecedents', 'durations', 'nap', 'impulsivity', 'apparent', 'stable', 'topography', 'commands', 'para', 'remaining', 'entire', 'addiction', 'exceeded', 'print', 'cuing', 'essay', 'idea', 'nearly', 'productions', 'pressure', 'car', 'toddlers', 'formats', 'equations', 'analytical', 'keyboard', 'generality', 'alphabet', 'psychosocial', 'interventionist', 'resurgence', 'portion', 'distressing', 'retained', 'highlights', 'exploring', 'tailored', 'details', '001', 'vret', 'wheel', 'drag', 'alpha', 'homes', 'hr', 'income', 'humans', 'complexity', 'monetary', 'continues', 'recipes', 'reverse', 'chose', 'prism', 'sharing', 'pwd', 'approximately', 'articulatory', 'predict', 'started', 'videotaped', 'introduce', 'built', 'ipada', 'sceds', 'scripted', 'economic', 'magnitude', 'expressed', 'commitment', 'influenced', 'eibi', 'conclude', 'infants', 'intra', 'parametric', 'nonparametric', 'tilt', 'workshops', 'affects', 'suited', 'drop', 'leading', 'shape', 'phonics', 'hiv', 'equal', 'lost', 'hero', 'trigger', 'dimensional', 'collect', 'vsp', 'costs', 'gap', 'vest', 'link', 'pictorial', 'sophisticated', 'proloquo2go', 'great', 'efforts', 'customized', 'alternatives', 'verbalizations', 'nssi', 'untaught', 'tdi', 'box', '93', 'prevent', 'aggregate', 'attended', '54', 'attainment', '94', 'limitation', 'supplementary', 'decades', 'rigor', 'protocols', 'dose', 'monitored', 'equivalent', 'abstinence', 'topics', 'concurrently', 'lecture', 'animals', 'ended', 'insights', 'bonus', 'absolute', 'isolated', 'lasted', 'classified', 'finding', 'earned', 'quiz', 'fluent', 'intelligent', 'nonoverlapping', 'personally', 'biomechanical', 'tended', 'activation', 'interfaces', 'passage', 'consistency', 'versions', 'add', 'competencies', 'makes', 'mva', 'ad', 'multilevel', 'policy', 'emotive', 'rra', 'unit', 'paraprofessional', 'wearables', 'ltm', 'consensus', 'integrating', 'speeds', 'construct', 'clip', 'strengths', 'persuasive', 'category', 'efl', 'engineering', 'ap', 'substantially', 'stability', 'vaporizer', 'thinning', 'provider', 'smartphones', '46', 'demonstrates', 'inter', 'achieving', 'proved', 'identity', 'land', 'dysfunction', 'pastoral', 'individually', 'ranged', 'domain', 'source', 'analysed', 'men', 'telepractice', 'requiring', 'players', 'clinics', 'product', 'prosthesis', 'undergoing', 'dd', 'hemiplegic', 'asds', 'blindness', 'azbio', 'implantation', 'sas', 'sense', 'november', 'beta', 'tac', 'scored', 'untreated', 'neutral', 'utterances', 'consultants', 'numeracy', 'communicate', 'talk', 'safecare', 'explain', 'ecoaching', 'adjunct', 'adding', 'expanding', 'networks', 'precision', 'kws', 'named', 'relaxation', 'randomisation', 'weak', 'multiplication', 'inferential', 'volume', 'purchasing', 'culture', 'fragile', 'confirm', 'ebd', 'topographies', 'locations', '45', 'connect', 'rett', 'younger', 'residents', 'eclectic', 'progression', 'emergency', 'passive', 'distraction', 'carers', 'attendance', 'dnd', 'date', 'mit', 'relating', 'paraeducators', '87', 'cooking', 'tax', 'mouth', 'usage', 'organizations', 'precursors', 'suffering', 'evoke', 'conjunction', 'postural', 'precursor', 'occurring', 'selective', 'scent', 'produces', 'proximity', 'pay', 'publications', 'hyperactive', 'rehabilitative', 'controller', 'allocation', 'culturally', 'manipulative', 'usa', 'kinds', 'pervasive', 'mechanics', 'regulated', 'ip', 'extending', 'lowest', 'minority', 'benefited', 'citations', 'breaks', 'fail', 'problematic', 'regardless', 'connected', 'reduces', 'vital', 'enhancement', 'executive', 'readiness', 'near', 'transdiagnostic', 'accomplished', 'emphasized', 'goact', 'cb', 'lifestyle', 'nintendo', 'update', 'stem', 'additive', 'highest', 'occupation', 'sorting', 'rehearsal', 'supplement', 'validated', 'deviation', 'dance', 'trunk', 'operated', 'records', 'beliefs', 'adaptations', 'reciprocal', 'evaluates', 'containing', '52', '64', 'sr', 'estimations', 'expansion', 'reflected', 'citation', 'experimenters', 'caused', 'blood', 'modern', 'articulation', 'satiation', 'friends', 'empirically', 'institute', 'ease', 'counting', 'generative', 'retraining', 'accepted', 'predator', 'functioned', 'ext', 'segments', 'block', 'dogs', 'hours', 'late', 'assistants', 'bring', 'remotely', 'alternated', 'coma', 'augment', 'discusses', 'regrouping', 'economics', 'tabletop', 'makey', 'customer', 'ot', 'removal', 'ace', 'intonation', 'compensatory', 'lmem', 'reward', 'hlm', 'promoted', 'shorter', 'females', 'grammatically', 'just', '31', 'feature', 'emitted', 'technicians', 'distal', 'competition', 'ec', 'ocr', 'episodes', 'restructuring', 'micro', 'accessibility', 'understood', 'relevance', 'photographs', 'hou', '2017', 'atc', 'mst', 'eventually', 'calibration', '84', 'lobe', 'assignments', 'ignore', 'break', 'ensure', 'prevalent', 'pedagogy', 'decoding', 'parenting', 'autobiographical', 'contributed', 'destructive', 'illustrated', 'appropriately', 'conversations', 'build', 'differ', 'doing', 'diabetes', 'manipulated', 'vbf', 'fm', 'intelligence', '75', 'standardised', 'plays', 'prenatal', 'dohsa', 'lag', 'vocalization', 'pc', 'assisting', 'code', 'represented', 'comprising', 'rcts', 'numerous', 'angle', 'hemispatial', 'drawn', 'rapidly', 'commenting', 'bowel', 'reasons', 'psychologists', '01', 'turnover', 'commercially', 'scoring', 'forwarding', 'instances', 'wear', 'neurological', 'correlated', 'experiencing', 'crucial', 'units', 'turns', 'incidence', 'load', 'sci', 'intermediate', 'changed', 'therapies', 'embase', 'psycinfo', 'unable', 'encourage', 's8', 'electric', 'prosody', 'glove', 'ddndap', 'rest', 'discriminative', 'geometry', 'screened', 'ppa', 'cochat', 'association', 'collecting', 'adequately', 'reaction', 'advertising', 'starting', 'vnest', 'books', 'distinct', 'sw', 'disruptions', 'incorporate', 'reliance', '2d', '57', 'operate', 'follows', 'shaping', 'mock', 'animated', 'swing', 'mi', 'covert', 'advocates', 'continuing', 'transdermal', 'initiate', 'academics', 'raters', '1st', 'centered', 'hands', 'idiosyncratic', 'controls', 'looking', 'concentration', 'slots', 'sent', 'charge', 'integral', 'homework', 'situation', 'cas', 'combine', 'referral', 'strike', 'quantified', 'acclimatization', 'publicly', 'purchase', 'amplitude', 'rhotic', 'ssq', 'resection', 'center', 'smile', 'risks', 'descriptions', 'bus', 'telecare', 'mindful', 'siblings', 'graphed', 'immersion', 'schema', 'influences', 'icbt', 'bmi', 'mail', 'cause', 'raising', 'worked', '65', 'hygiene', 'modeled', 'said', 'table', 'graph', 'appliance', 'welfare', 'introducing', 'administration', 'asymmetric', 'sensorineural', '55', 'preschooler', 'neuroanatomy', 'tackling', 'greet', 'tacts', 'physiotherapy', 'moderator', 'usefulness', 'affecting', 'hypothesized', 'plan', 'asperger', 'maps', 'intact', 'selecting', 'fitbit', 'amputees', 'countries', 'operating', 'practitioner', '32', 'emesis', 'scds', '76', 'breeding', 'tumor', 'pouched', 'pedagogical', 'responsible', '41', 'wrote', 'sequentially', 'hemiplegia', 'patting', 'dat', 'actively', 'iep', 'reliably', 'representation', 'stance', 'pdd', 'definition', 'sites', 'searching', 'replicate', 'consists', 'definitions', 'sub', 'rich', 'ubiquitous', 'biological', 'intrusive', '83', 'informed', 'cleaning', '48', 'far', 'jaba', 'removed', '82', 'prerequisite', 'watching', 'button', 'vending', 'arch', 'atm', 'centred', 'enabler', 'black', 'universal', 'injections', 'television', 'struggling', 'accommodations', 'sad', 'car</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>6347</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>150661</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9566</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
         <v>9</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1511</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15.74963412084466</v>
-      </c>
-      <c r="O6" t="n">
-        <v>61.83731533275075</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12.51424867829706</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>207.4533340897165</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>['intervention', 'study', 'design', 'participants', 'children', 'training', 'students', 'asd', 'skills', 'based', 'research', 'behavior', 'single', 'using', 'results', 'case', 'treatment', 'social', 'aba', 'use', 'analysis', 'used', 'video', 'effects', 'data', 'baseline', 'learning', 'multiple', 'autism', 'studies', 'interventions', 'behavioral', 'self', 'communication', 'technology', 'teaching', 'disabilities', 'instruction', 'effective', 'therapy', 'individuals', 'support', 'effect', 'intellectual', 'outcomes', 'performance', 'experimental', 'telehealth', 'effectiveness', 'reading', 'functional', 'education', 'behaviors', 'evidence', 'visual', 'time', 'findings', 'parent', 'high', 'parents', 'methods', 'child', 'language', 'practice', 'review', 'aac', 'program', 'modeling', 'sessions', 'school', 'significant', 'assessment', 'group', 'health', 'showed', 'activity', 'purpose', 'feedback', 'online', 'speech', 'positive', 'developmental', 'future', 'subject', 'improve', 'method', 'teachers', 'approach', 'model', 'virtual', 'included', 'disability', 'physical', 'increase', 'conducted', 'strategies', 'autistic', 'increased', 'quality', 'evaluate', 'current', 'teach', 'implementation', 'efficacy', 'participant', 'adults', 'care', 'people', 'phase', 'systematic', 'development', 'cognitive', 'demonstrated', 'evaluated', 'engagement', 'related', 'clinical', 'student', 'daily', 'implications', 'coaching', 'activities', 'provide', 'reinforcement', 'task', 'services', 'implemented', 'management', 'post', 'discussed', 'patients', 'level', 'needs', 'reported', 'game', 'impact', 'control', 'following', '19', 'application', 'compared', 'measures', 'prompting', 'response', 'caregivers', 'levels', 'indicated', 'including', 'years', 'generalization', 'literature', 'follow', 'potential', 'improved', 'validity', 'different', 'number', 'trial', 'accuracy', 'specific', 'pain', 'early', 'skill', 'problem', 'conditions', 'app', 'acquisition', 'change', 'procedures', 'present', 'target', 'probe', 'teacher', 'individual', 'applied', 'special', 'covid', 'weeks', 'practices', 'examined', 'non', 'evaluation', 'young', 'computer', 'assessed', 'suggest', 'settings', 'disorders', 'provided', 'limited', 'reality', '10', 'age', 'maintained', 'anxiety', 'process', 'maintenance', 'examine', 'test', 'researchers', 'academic', 'problems', 'primary', 'fidelity', 'motor', 'access', 'delivery', 'delivered', 'week', 'increasing', 'adolescents', 'digital', 'instructional', 'improvement', 'conclusions', 'condition', 'science', 'improving', 'feasibility', 'home', 'changes', 'low', 'treatments', 'need', 'overall', 'completed', 'setting', 'family', 'paper', 'caregiver', 'attention', 'classroom', 'mobile', 'service', 'preference', 'educational', 'pre', 'living', 'pandemic', 'play', 'new', 'participated', 'independent', 'life', 'challenging', 'addition', 'responses', 'designs', 'function', 'mathematics', 'secondary', 'knowledge', 'monitoring', 'identified', 'observed', 'improvements', 'disorder', 'higher', 'families', 'making', 'analyses', 'package', 'variables', 'focused', 'assess', 'work', 'phases', 'word', 'protocol', 'stimuli', 'developed', 'psychological', 'moderate', 'stimulus', 'important', 'presented', 'challenges', '12', 'peer', 'needed', 'ability', 'trials', 'background', 'criteria', 'mental', 'fluency', 'alternating', 'tablet', 'rate', 'interactions', 'risk', 'experience', 'strategy', 'context', 'difficulties', 'symptoms', 'determine', 'severe', 'programs', 'interaction', 'aphasia', 'large', 'acceptability', 'investigate', 'total', 'implement', 'information', 'spectrum', 'designed', 'complex', 'regarding', 'person', 'patient', 'did', 'staff', 'aged', 'limitations', 'diagnosed', 'tool', 'technologies', 'tasks', 'mixed', 'verbal', 'objective', 'help', 'preliminary', 'practitioners', 'assessments', 'small', 'remote', 'associated', 'words', 'brain', 'rehabilitation', 'music', 'conclusion', 'community', 'received', 'developing', 'various', 'size', 'taught', 'al', 'session', 'et', 'population', 'outcome', 'differences', 'measured', 'previous', 'period', 'significantly', 'novel', 'items', 'text', 'investigated', 'additional', 'field', 'appropriate', 'vocabulary', 'public', 'provides', 'meta', 'direct', 'step', 'analysts', 'scores', 'approaches', 'face', 'device', 'providing', 'year', 'bst', 'barriers', 'emotional', 'frequency', 'aimed', 'depression', 'ipad', 'aims', 'randomized', 'writing', 'sample', 'indicate', 'collected', 'id', 'promote', 'procedure', 'chronic', 'professionals', 'general', 'stress', 'targeted', 'devices', 'analyzed', 'identify', 'groups', 'contingency', 'exercise', 'available', 'models', 'required', 'characteristics', 'solving', 'components', 'article', 'enhance', 'goal', 'address', 'qualitative', 'augmented', 'evaluating', 'analytic', 'measure', 'scale', 'methodology', 'tau', 'relation', 'old', 'tools', 'responding', 'reduce', 'mean', 'sced', 'mediated', 'months', 'explore', 'choice', 'participation', 'supporting', 'assistive', 'comprehension', 'leisure', 'telepractice', 'combined', 'concurrent', 'smartphone', 'interviews', 'brief', 'satisfaction', 'questions', 'sleep', 'inclusion', 'include', 'preferred', 'schedules', 'media', 'intensity', 'revealed', 'elementary', 'professional', 'therapeutic', 'mastery', 'functioning', 'injury', 'framework', 'robot', 'recommendations', 'vr', 'published', 'controlled', 'opportunities', 'real', 'employed', 'peers', 'english', 'content', 'type', 'preschool', 'supported', 'environment', 'involved', 'subjects', 'performed', 'weekly', 'goals', 'seven', 'discussion', 'negative', 'comparison', 'youth', 'supports', 'trained', 'adapted', 'grade', 'prompts', 'adult', 'relationship', 'gains', 'behaviour', 'human', 'series', 'awareness', 'met', 'syndrome', 'average', 'factors', 'alternative', 'greater', 'materials', 'assisted', 'stimulation', 'correct', 'decision', 'term', 'role', 'report', 'act', 'selected', 'additionally', 'perceived', 'discrete', 'body', 'vocal', 'shown', 'repeated', 'experiences', 'delay', 'applications', 'supervision', 'areas', 'long', 'aided', 'progress', 'techniques', 'led', 'acquired', '15', 'stroke', 'embedded', 'lack', 'despite', 'understanding', 'quantitative', 'reducing', 'safety', 'demonstrate', 'extended', 'pilot', 'range', 'medical', 'therapists', 'compare', 'enhanced', 'vocational', 'disruptive', 'intensive', 'cbt', 'relevant', 'percentage', 'lower', 'naturalistic', 'statistical', 'collection', 'types', 'structured', 'picture', 'functions', 'decreased', 'targets', 'features', 'speaking', 'develop', 'survey', 'learners', 'reviewed', 'replicated', 'involving', 'month', 'dependent', 'increases', 'therapist', 'make', 'web', 'recent', 'focus', 'socially', 'modelling', 'software', 'idd', 'better', 'systems', 'adherence', 'nick', 'terms', 'standards', 'replication', 'followed', 'decrease', 'efficiency', 'probes', 'rates', 'instructions', 'exposure', 'given', 'criterion', 'electronic', 'gbg', 'independently', 'engaged', 'acceptance', 'component', 'learned', 'contingent', 'assessing', 'comparing', 'common', 'impairment', 'benefits', 'interactive', 'generalized', 'duration', 'differential', 'learn', 'similar', 'steps', 'promising', 'promoting', 'aim', 'considered', 'variable', 'specifically', 'efficient', '11', 'methodological', 'objectives', 'experienced', 'experiment', 'initial', 'vm', 'machine', 'active', 'second', 'internet', 'schedule', 'articles', 'good', 'oral', 'set', 'eye', 'disease', 'stereotypy', '20', 'imitation', 'expressive', 'independence', 'able', 'naming', 'employment', 'times', 'procedural', '30', 'suggested', 'cases', 'hours', 'according', 'complete', 'engage', 'min', 'acceptable', 'described', 'feasible', 'contexts', 'patterns', 'statistically', 'power', 'dyads', 'reduction', 'combination', 'sizes', 'math', 'memory', 'utilized', 'prior', 'manipulatives', 'ai', 'traditional', 'end', 'best', 'particularly', 'typically', 'class', 'successful', 'individualized', 'resulted', 'days', 'variability', 'introduction', 'games', 'standard', 'clinicians', 'diagnosis', 'implementing', 'completion', 'events', 'automatically', 'guidance', 'healthcare', 'literacy', 'enhancing', 'graphs', '95', 'adaptive', 'concerns', 'main', 'practical', 'user', 'comprehensive', 'university', 'receiving', 'trend', 'apps', 'commonly', 'collaborative', 'critical', 'production', 'curriculum', 'members', 'search', 'questionnaires', 'generating', 'questionnaire', 'order', 'value', 'course', 'movement', 'proposed', 'highly', 'little', 'auditory', '14', 'result', 'educators', 'incorporating', 'directions', 'modified', 'withdrawal', 'working', 'board', 'videos', 'form', 'integrity', '13', 'inclusive', 'area', 'usability', 'providers', 'modalities', 'voice', 'facilitate', 'perceptions', 'effectively', 'emotion', 'existing', 'necessary', 'occupational', 'known', 'childhood', 'schools', 'strong', 'observation', 'importance', '18', 'guidelines', 'day', 'integrated', 'therapies', 'format', 'obtained', 'natural', 'reduced', 'hearing', 'environments', 'conversation', 'furthermore', 'trauma', 'college', 'successfully', 'ratings', 'suggestions', 'behavioural', 'transfer', 'basic', 'tracking', 'relations', 'mobility', 'contingencies', 'ethical', 'testing', 'communicative', 'classrooms', 'dementia', 'sound', 'key', 'discuss', 'continued', 'established', '16', 'errors', 'smart', 'influence', '2020', 'recognition', 'valid', 'investigation', 'consistent', 'examining', 'joint', 'gender', 'commitment', 'points', 'reviews', 'personal', 'interview', 'way', 'short', 'rated', 'reversal', 'systematically', 'shared', 'difficulty', 'ci', 'cost', 'affect', 'partners', 'cultural', 'utility', 'aid', 'benefit', 'abilities', '17', 'transition', 'inspection', 'tech', 'pecs', 'state', 'executive', 'minimally', 'mood', '25', 'issues', 'variety', 'conduct', 'palsy', 'essential', 'sensory', 'repetitive', 'cerebral', 'parental', 'stories', 'majority', 'complexity', 'perspectives', 'programming', 'success', 'observational', '100', 'mathematical', 'preschoolers', 'train', 'technique', 'classes', 'especially', 'flexibility', 'global', 'rural', 'competing', 'varied', 'adhd', 'bias', 'traumatic', 'reach', 'difference', 'older', 'offer', 'authors', 'applying', 'plus', 'center', 'explored', 'values', 'imagery', 'processes', 'require', 'equivalence', 'identifying', 'administered', 'possible', 'open', 'platform', 'client', 'clinically', 'consisted', 'consider', 'confidence', 'versus', 'generally', 'robots', 'utilizing', 'principles', 'scientific', 'ar', 'frequently', 'occurred', 'resources', 'item', 'create', 'immediate', 'recorded', 'linear', 'tests', 'motivation', 'upper', 'reports', 'automatic', 'ethics', 'synchronous', 'prompt', 'involves', 'read', 'emerging', 'analyze', 'limb', 'adolescent', 'produced', 'like', 'hallucinations', 'score', 'checklist', 'recruited', 'everyday', 'concept', 'head', 'motion', '2021', 'combining', 'line', 'consistency', 'question', 'middle', 'descriptive', 'artificial', 'theory', 'behaviours', 'matrix', 'clients', 'accurate', 'affected', 'larger', 'compliance', 'suggests', 'assigned', 'hygiene', 'preferences', 'randomly', 'interface', 'lead', 'deficits', 'mothers', 'technological', 'live', 'experiments', 'project', 'thinking', 'dynamic', 'databases', 'display', 'personalized', 'experiencing', 'elements', 'tact', 'likely', 'resource', 'perform', 'presents', 'guided', 'ages', 'building', 'consisting', 'exploring', 'guide', 'meet', 'recovery', 'point', 'regulation', 'concepts', 'gaze', 'targeting', 'telerehabilitation', 'impacts', 'hand', 'diverse', 'exchange', 'index', 'aspects', 'minutes', 'action', 'directly', 'world', 'wide', 'modules', 'mild', 'female', 'directed', 'receptive', 'contribute', 'untrained', 'achieved', '001', '40', 'persons', 'relationships', 'assist', 'intelligence', 'severity', 'neurodevelopmental', 'linguistic', 'culturally', 'useful', 'ways', 'positively', 'job', 'multi', 'expected', 'simple', 'local', 'indicating', 'partner', 'input', 'growing', 'parenting', 'requesting', 'gait', 'collaboration', 'gap', 'extend', 'addressing', 'measurement', 'explicit', 'mhealth', '50', 'understand', 'reporting', 'domains', 'users', 'cancer', 'accessible', 'simultaneous', 'centered', 'speed', 'vp', 'team', 'scoping', 'empirical', 'china', 'electrical', 'topic', 'integration', 'phonological', 'created', 'synthesis', 'carried', 'creating', 'respond', 'policy', 'meditation', 'reliability', 'suggesting', 'situations', 'dissemination', 'distress', 'compassionate', 'informed', 'automated', 'conversational', 'maintain', 'asynchronous', 'displays', 'changing', 'mindfulness', 'error', 'perception', 'states', 'maintaining', 'yielded', 'cp', 'deliver', 'feature', 'walking', 'sight', 'talk', 'sets', 'works', 'women', 'male', 'designing', 'widely', 'healthy', 'ebi', 'promise', 'sgd', 'preparation', 'pairs', 'recommended', 'final', 'rating', 'minute', 'produce', 'unique', 'particular', 'tested', 'includes', 'movements', 'dance', 'selection', 'conducting', 'praise', 'capacity', 'substantial', 'enrolled', 'increasingly', 'written', 'impairments', 'module', 'standardized', 'reinforced', 'meaningful', 'fa', 'having', 'tutorial', 'story', 'nonconcurrent', 'reinforcer', 'kindergarten', 'diagnostic', 'abstract', 'shows', 'matching', 'prevention', 'countries', 'offers', 'insights', 'cohort', 'challenge', 'modality', 'interventionists', 'respectively', 'potentially', 'relative', 'right', 'programme', 'finally', 'physiotherapy', 'varying', 'coding', 'version', 'reliable', 'currently', 'difficult', '2022', 'network', 'pd', 'sequence', 'extensive', '21', 'minimal', 'vs', 'wearable', 'continue', 'beneficial', 'learner', 'ratio', 'masking', 'place', 'periods', 'sd', 'engaging', 'base', 'onset', 'phrase', 'focuses', 'forms', 'agreement', 'sentence', '2023', 'mand', 'diabetes', 'coping', 'calculated', '60', 'sceds', 'simulation', 'compassion', 'means', 'establish', 'plans', 'crucial', 'google', 'recess', 'hybrid', 'previously', 'analysed', 'planning', 'foreign', 'samples', 'dtt', 'began', 'demonstrating', 'options', 'longer', 'preservice', 'cross', 'just', 'prevalence', 'emt', 'multilevel', 'mechanisms', 'food', 'thematic', 'experts', 'paired', 'organizations', 'trends', 'examines', 'delivering', 'surveys', 'national', 'discrimination', 'valuable', 'serve', 'addressed', 'balance', 'half', 'males', 'tele', 'strength', 'homes', '29', 'treating', 'interpretation', 'athletes', 'extension', 'pa', 'blended', 'motivational', 'manipulative', 'identification', 'consultation', 'indicators', 'muscle', 'sars', 'feeding', 'toddlers', 'exploratory', 'core', 'populations', 'posttest', 'dual', 'decisions', 'adopted', 'processing', 'statements', 'medicine', 'subsequent', 'reductions', 'request', 'allow', 'apply', 'recording', '33', 'categories', 'antecedent', 'introduced', 'oriented', 'methodologies', 'extent', 'structure', 'participating', 'organization', 'meeting', 'intervals', 'correctly', 'solution', 'united', 'opinions', 'visually', '80', 'sufficient', 'topics', 'heart', 'multimedia', 'derived', 'determined', 'multistep', 'depressive', 'actions', 'achieve', 'ab', 'lecture', 'observations', 'clear', 'calls', 'objects', 'history', 'clinic', 'card', 'responsive', 'accessibility', 'remaining', 'overlap', 'paraeducators', 'scd', 'factor', 'does', 'remain', 'concrete', 'algebra', 'displayed', 'tutoring', 'analyst', 'determination', 'pediatric', 'adaptations', 'examples', 'consequences', 'vsds', 'messages', 'fatigue', 'taking', 'prosthetic', 'usage', 'weight', 'supplemental', 'inform', 'emerged', 'primarily', 'highlights', 'answer', 'hyperactivity', 'statistics', 'typical', 'issue', 'pictures', 'demonstrates', 'ongoing', 'random', 'perspective', 'cm', 'phrases', 'constant', 'expressed', 'indicates', 'conceptual', 'regular', 'offered', '2019', '81', 'output', 'responded', 'describes', 'cognition', 'took', '24', 'protocols', 'progressive', 'augmentative', 'ecological', 'count', 'consecutive', 'material', 'completing', 'contributes', 'baselines', 'tbi', 'verb', 'symbols', 'investigating', 'exhibited', 'continuous', 'researcher', 'lessons', 'subtraction', 'generalize', 'decreasing', 'psychotherapy', 'driven', 'start', 'examination', '90', 'allows', 'controls', 'stem', 'coach', 'videoconferencing', 'unit', 'insomnia', 'precision', 'avoidance', 'replicate', 'financial', 'wearing', 'teams', 'nonverbal', 'estimation', 'sexual', 'measurements', 'poor', 'color', 'example', 'tablets', 'postural', '27', 'considering', 'robust', 'regression', 'initially', 'script', 'mother', 'trunk', 'loss', 'falling', 'sought', 'mastered', 'seeking', 'narrative', 'themes', 'communicate', 'receive', 'meaning', 'called', '36', 'past', 'playing', 'hour', 'advanced', 'requests', '2018', 'distance', 'accessing', 'remains', 'contact', 'hospital', 'certified', 'personality', 'major', 'gamification', 'proficiency', 'wwc', 'degree', 'exercises', 'sampling', 'initiated', 'organizational', 'players', 'resulting', 'cook', 'sustained', 'ensure', 'pairing', 'studied', 'audio', 'courses', 'adapting', 'turns', 'fact', 'solve', 'efficacious', 'burnout', 'gain', 'multimodal', 'cards', 'medication', 'scene', 'registration', 'spoken', 'manual', 'simulated', 'recruitment', 'stage', 'adverse', 'account', 'tm', 'internal', 'advocacy', 'missing', 'sustainability', 'matched', 'correlation', 'arrangement', 'opportunity', 'burden', '66', '01', 'parameters', 'solutions', 'graduate', 'uses', 'reciprocal', 'struggling', 'rapid', 'sport', 'vocalizations', 'option', 'recently', '42', 'stages', 'comfort', 'coded', 'turn', 'posttreatment', 'instructor', 'relatively', 'retention', 'presence', 'income', 'orientation', '45', 'notes', 'spinal', 'abab', 'monitor', 'instructors', 'formats', 'spelling', 'rigor', 'incorporated', 'routine', 'agents', 'graphing', 'tailored', 'american', 'book', 'interpersonal', 'easy', 'coordination', 'ii', 'trainers', 'vivo', 'adequate', 'subtypes', 'determining', 'near', 'provision', 'routines', 'semi', 'multielement', 'excel', 'sense', 'decline', 'symptom', 'significance', 'innovative', 'banging', 'ml', 'habit', 'breathing', 'semantic', 'safe', 'reached', 'socio', 'map', 'technical', 'desired', 'nursing', 'fully', 'length', 'fct', 'efforts', 'modification', 'sports', 'viable', 'aggression', 'extinction', 'injurious', 'rett', 'frequent', 'highlighted', 'showing', 'usual', 'accurately', 'integrating', 'acquire', 'variations', 'leading', 'interval', 'dro', 'boy', 'predict', 'cord', 'boys', 'japanese', 'incentives', 'prevent', 'graphical', 'manage', 'randomization', 'pica', 'sgds', 'shortly', 'nap', 'trainees', 'psychosis', 'object', 'validated', 'starting', 'note', 'demand', 'view', 'scored', 'treat', 'surgery', 'impacted', 'considerations', 'later', 'flashcards', 'sensitivity', 'environmental', 'nature', 'represent', '26', 'clinician', 'journals', 'occur', 'remained', 'bcbas', 'free', 'labeling', 'dyslexia', 'indices', 'estimate', 'asleep', 'clearinghouse', 'videoconference', 'unknown', 'explores', 'fewer', 'date', 'tens', 'prospective', 'standing', 'residential', 'check', 'added', 'retrieval', 'animated', 'moderator', 'detailed', 'scenarios', 'analyzing', 'mode', 'fear', 'evaluations', 'bayesian', 'match', 'hrv', 'likelihood', 'retrospective', 'screening', 'situation', 'animation', 'certification', 'stakeholders', 'beliefs', 'combines', 'dyad', '75', 'requirements', 'recognized', 'sharing', 'db', 'served', 'verbally', 'generalisation', 'supervisors', 'exists', 'pivotal', 'spent', 'focusing', 'conventional', '2017', 'email', 'centers', 'seen', 'highest', '38', 'bsp', 'vsm', 'exist', 'enabled', 'token', 'graph', 'occupation', 'taken', 'pubmed', 'cov', 'deficit', 'storytelling', 'shift', 'plan', 'smoking', 'subjective', 'innovation', 'warranted', 'stability', 'pencil', 'choices', 'idbt', 'chain', 'presenting', 'appraisal', 'sources', 'computerized', 'vnest', 'add', 'combinations', 'adoption', 'measuring', 'registered', 'infant', 'redirection', 'load', 'stuttering', 'demonstration', 'spatial', 'widespread', 'delayed', 'elevated', 'fine', 'construction', 'proportion', 'representations', 'inflammatory', 'cai', 'achievement', 'arm', 'delays', 'recall', 'improves', 'strengths', 'fourth', 'metabolic', 'helped', 'unclear', 'responsiveness', 'musculoskeletal', 'respect', 'effort', 'provider', 'locations', 'spontaneous', 'operant', '2015', 'basis', 'handwriting', 'lives', 'noncontingent', 'contextual', 'light', 'undergraduate', 'parkinson', 'flashcard', 'collect', 'pressure', 'highlight', 'code', 'meal', 'dental', 'presentation', 'dosage', 'dd', 'mbs', 'technicians', 'generated', 'autonomy', 'achieving', 'intraverbal', 'csa', 'paraeducator', 'managing', 'listener', 'emergence', 'competence', 'screen', 'insight', 'modifications', 'chains', 'randomised', 'worry', 'psychology', 'approximately', 'defined', 'actual', 'infants', 'resilience', 'race', 'plays', 'scales', 'helping', 'utilization', 'seating', 'workers', 'communities', 'prediction', 'record', 'cochlear', 'gross', 'fraction', 'symbolic', 'economy', 'regardless', 'prt', 'corrective', 'animal', 'microsoft', 'psychosocial', 'translational', 'recommend', 'addiction', 'rules', 'utilizes', 'tdcs', 'fifth', 'searched', 'run', 'conferencing', '32', 'stt', 'considerable', 'society', 'interdependent', 'genetic', '70', 'conditional', 'blocks', 'tangible', 'proof', 'journal', 'corresponding', 'fit', 'detect', 'accelerometer', 'adulthood', 'facilitating', 'listening', 'far', 'document', '31', 'foster', 'formulation', 'urban', 'prepared', '2016', 'remotely', 'scope', 'ebd', 'algorithms', 'close', 'attend', 'programmed', 'original', 'concluded', 'parkour', 'economic', 'repetition', 'flexible', 'spaces', 'climbing', 'pretest', 'leads', 'perceptual', 'manualized', 'absence', 'ptsd', 'confirmed', 'status', 'treated', 'private', 'friendly', 'adding', 'capture', 'trust', 'cues', 'ict', 'tootling', 'robotic', 'skin', 'prolonged', 'performing', 'build', 'enable', 'postsecondary', '22', 'extracted', 'restricted', '93', '85', 'hierarchical', 'empathy', 'equally', 'blood', 'slightly', 'cochrane', 'facial', 'https', 'connect', 'immediately', 'physically', 'rule', 'ansa', 'hs', 'magnetic', 'drawing', 'pose', 'pdc', 'spanish', 'dimensions', 'maps', 'momentary', 'dataset', 'replications', 'sam', 'expect', 'adaptation', 'passive', 'march', 'fractions', 'satisfied', 'contributed', 'engineering', 'mass', 'siblings', 'tom', 'yoga', 'observer', 'certain', 'divided', 'style', 'interteaching', 'creativity', 'negatively', 'avatar', 'medium', 'rare', 'edible', 'failed', 'soccer', 'asked', 'disparities', 'underlying', 'observing', 'instrument', 'lasting', 'pediatrician', 'situ', 'emotions', 'problematic', 'happiness', 'relapse', 'strengthening', '35', 'slow', 'helpful', 'decreases', 'letter', 'surface', 'participate', 'affects', 'black', 'impaired', 'practitioner', 'advantages', 'sciences', 'graphic', 'january', 'conversations', 'validate', 'normal', '28', 'maximum', 'interruption', 'knee', 'comparisons', 'menstrual', 'longitudinal', 'physician', 'exploration', 'cortisol', 'art', 'investigations', 'withdrawn', 'struggle', 'follows', 'suitable', 'representational', 'ld', 'ms', 'finding', 'referred', 'switch', 'projects', 'easily', 'extraction', 'domain', 'museum', 'sign', 'grief', 'influenced', 'synthesize', 'eating', 'substantially', 'central', 'sitting', 'beginning', 'texts', 'formal', 'multidisciplinary', 'highlighting', 'median', 'infection', 'stand', 'minimum', 'prepare', 'encourage', 'grid', 'books', 'quasi', 'incremental', 'causal', 'establishing', 'virtually', 'comprised', 'vbi', 'toothbrushing', 'identity', 'units', 'correspondence', 'coronavirus', 'kinect', 'messaging', 'creation', 'contributions', 'ranging', 'substance', 'fluent', 'international', 'chinese', 'distinct', 'gaming', 'involvement', 'microprocessor', 'datasets', 'gov', 'expression', 'powr', 'postpartum', 'sequential', 'postintervention', 'outside', 'adjustments', 'pedagogical', 'reference', 'neurotypical', 'cooperative', '00', 'estimates', 'exclusion', 'asking', '3d', 'packages', 'classification', 'validation', 'native', 'ultimately', 'incorporates', 'subtype', 'consideration', 'sensors', 'initiations', 'encouraged', 'requiring', 'association', 'talking', 'reaching', 'intensified', 'mands', 'selecting', 'predictive', 'productive', 'located', 'speakers', 'alpha', 'enabling', 'windows', 'utilize', 'telephone', 'augment', 'rumination', 'similarly', 'workshop', 'reinforcers', 'appears', 'transitioned', 'phone', 'diversity', 'expanding', 'expand', 'extremity', 'sensitive', 'esteem', 'summer', 'profound', 'waiting', 'reciprocity', 'choose', 'skinner', 'inconsistent', 'descriptions', 'structures', 'sentences', 'planned', 'empirically', 'rrb', 'latency', 'pay', 'answering', 'bariatric', 'lexical', 'recreational', 'interpreted', 'sequences', 'designers', 'modes', 'quantity', 'facilitated', 'telemedicine', 'wisdom', 'india', '34', 'pwd', 'image', 'characterized', 'nonoverlap', 'fields', 'database', 'comparable', 'variance', '05', '37', 'storybook', 'tier', 'abstinence', 'favorable', 'milieu', 'formation', 'pursuit', 'velocity', 'psychiatric', 'plp', 'multicomponent', 'pitch', 'relevance', '83', 'involve', 'representing', 'cause', 'ca', 'employing', 'originality', 'contributing', 'clinicaltrials', 'interested', '23', 'occurring', 'discourse', 'suspected', 'dystonic', 'stimulating', 'creative', 'fidget', 'ed', 'incorporate', 'ema', 'sustainable', 'blocking', 'scoring', 'helps', 'usefulness', 'appear', 'adds', 'habits', 'reflection', 'interpret', 'proxy', 'ha', 'trainer', 'dysregulation', 'serving', 'associations', 'inquiry', 'pe', 'improvised', 'noted', 'intrusive', 'migraine', 'temporal', 'linked', 'graduated', 'investigates', 'alm', 'twice', 'survivors', 'underwent', 'popular', 'injuries', 'list', 'sld', 'modest', '64', 'played', 'touching', 'propose', 'pnd', 'spd', 'description', 'institutions', 'broad', 'supplement', 'mind', 'disfluencies', 'expert', 'musical', 'demands', 'critically', 'faster', 'practicing', 'styles', 'heterogeneous', 'persistent', 'pt', 'rely', 'tacts', 'aids', 'contrast', 'publication', 'pattern', 'phonemic', 'define', 'cumulative', 'vaping', 'verbs', 'prosocial', 'comparative', 'intended', 'rcts', 'sequencing', 'bidirectional', 'pharmacological', '68', 'running', 'ecoaching', 'pcr', 'hip', 'exposed', 'graded', 'apraxia', 'workplace', 'prototype', 'ranged', '76', 'respondents', 'commercial', 'room', 'zoom', '82', 'overlapping', 'hands', 'broader', 'moderators', 'lateropulsion', 'fast', 'antidepressants', 'caused', 'repertoire', 'conjunction', 'interprofessional', 'respiratory', 'vigorous', 'assistants', 'antipsychotic', 'platforms', 'specialized', 'moderately', 'concerning', '63', 'relational', 'external', 'displaying', 'consistently', 'wheeled', 'coached', 'evaluates', 'theoretical', 'prevalent', 'backgrounds', 'experiential', 'approved', 'resultsthe', 'reward', 'supplemented', 'requires', 'interpreting', 'subsequently', 'documented', 'mitigate', 'consumer', 'electroencephalogram', 'insufficient', 'dysphagia', 'aware', '41', 'synthesized', 'searches', 'left', 'minimize', 'williams', 'restrictions', 'concern', 'protection', 'great', 'risks', 'females', 'diary', 'rehearsal', 'depth', 'exhibit', 'incidence', 'transitioning', 'foundation', 'nearly', 'removed', 'overview', 'volunteers', 'consensus', 'pragmatic', 'fixed', 'echo', 'acquiring', 'facilitators', 'advances', 'costs', 'evaluative', 'attentional', 'alongside', 'organized', 'gold', 'mask', 'rsas', '62', 'experimenter', 'cadence', 'growth', 'sen', 'tweets', 'availability', 'estimated', 'reveal', 'equity', 'cooking', 'authentic', 'numbers', 'statement', 'prisma', 'law', 'percent', 'interests', 'cas', 'sib', 'expectations', 'forward', 'yield', 'answers', 'qol', 'construct', 'fitness', 'traits', 'existed', 'hypothesis', 'failure', 'message', 'crisis', 'competitive', 'computers', 'gaps', 'rd', 'dbt', 'ensuring', 'generic', 'org', 'phobia', 'turning', '86', '84', 'enhancement', 'sleeping', 'externalizing', 'physiological', 'dysfunction', 'pb', 'makes', 'possibility', '88', 'dressing', 'tinnitus', 'supportive', 'assistance', 'visits', 'pst', 'assistant', 'calculate', 'sounds', 'abduction', 'pedagogy', 'offering', 'calculations', 'posture', 'faced', 'moving', 'accelerometers', 'regions', 'rr', 'receives', 'proximity', 'comprising', 'summarized', 'categorized', '87', 'started', 'company', 'memories', 'bug', 'ear', 'master', 'frame', 'corrected', 'obsessive', 'contained', 'cbm', 'detection', 'metrics', 'doi', 'loneliness', '89', 'evolutionary', 'trajectory', 'equivalent', 'es', 'fsp', 'element', 'lures', 'paradigm', 'views', 'expressions', 'fu', 'ended', 'reasons', 'diseases', 'pathologists', 'distributed', 'stigma', 'hypothesized', 'markers', 'sites', 'release', 'dynamics', 'frameworks', 'thought', 'evolution', 'representative', 'green', 'attending', '48', 'theraplay', 'deviation', 'geometry', 'captured', 'interventionist', 'tutors', 'ocd', 'searching', 'manner', 'universal', 'allowing', 'position', 'neuromuscular', 'inter', 'escape', 'mealtime', 'st', 'navigate', 'proved', 'dyslexic', 'represented', 'differ', 'iv', 'constructed', 'microlearning', 'watch', 'endurance', 'powerpoint', 'op', 'brian', 'dialogic', 'explanation', 'publications', 'summarize', 'site', 'buprenorphine', 'describing', 'fundamental', 'largely', 'author', 'partnership', 'interference', 'medications', 'incidental', '99', 'decades', 'acupuncture', 'urine', 'evidenced', 'aatd', 'individually', 'ndbi', 'correction', 'untreated', 'appeared', 'korean', 'monitored', 'competency', 'entire', 'unsafe', 'generation', 'sheets', 'obe', 'sar', 'isolation', 'reddit', 'shorter', '96', 'market', 'scopus', 'panel', 'purposes', 'centred', 'late', 'carlo', 'cardiac', 'incarcerated', 'interrater', 'discusses', 'producing', 'multiplication', 'money', 'away', 'reflect', 'acid', '2014', 'eligible', 'lacking', 'zero', 'bcba', 'esdm', 'manipulation', 'resonance', 'efl', 'vf', 'regurgitation', 'category', 'cooperation', '65', 'inventory', 'antecedents', 'neuropathic', 'acts', 'encouraging', 'smartphones', 'alleviate', 'proposes', 'block', 'cbc', 'b12', 'lumbar', 'imaging', 'dilated', 'perivascular', 'organic', 'chromosomal', 'gathered', 'acids', 'ketosis', 'vitamin', 'parametric', 'ssrds', 'gamified', 'animals', 'accessed', 'collecting', 'anomia', 'discussions', 'digit', 'event', 'explain', 'psycinfo', 'disruptions', 'strengthen', 'fearful', 'stabilizing', 'steroids', 'immunotherapy', 'instances', 'inference', 'chosen', 'prompted', 'scalable', 'guiding', 'physiotherapist', 'volunteer', 'candidates', 'ndbis', 'electromyography', 'coaches', 'insurance', 'girl', 'rac', 'dilemmas', 'turkish', 'largest', 'initiatives', 'readers', 'induced', 'worldwide', 'nutrition', 'commenting', 'doing', 'renewal', 'faculty', 'aiming', 'dearth', 'nonparametric', 'foundational', 'select', 'bacb', 'fading', 'posting', 'direction', 'initiation', 'instant', 'assignment', 'leveraging', 'ct', 'competition', 'rater', 'interact', 'vbis', 'emergent', 'depending', 'bilingual', 'facts', 'details', 'contribution', 'profoundly', 'inpatient', '46', 'iterative', 'counseling', 'assisting', 'diaphragmatic', 'biofeedback', 'affecting', 'steam', 'exceptionality', 'undertaken', 'explicitly', 'transformative', 'computational', 'deposit', 'false', 'logbook', 'attended', 'shifts', 'standardised', 'emergency', 'geographic', 'collateral', 'teletherapy', 'revised', 'touch', 'inappropriate', 'poses', 'conflict', 'gradual', 'location', 'protective', 'lectures', 'detected', 'abi', '92', 'metacognitive', 'recurrence', 'isolated', 'npos', 'tutor', 'pair', 'immersive', 'lesson', 'causes', 'influencing', 'roles', 'voluntary', 'rigorous', 'informal', 'summary', 'observers', 'bridge', 'mrehab', '56', 'portion', 'degrees', 'introducing', 'reaches', 'applicability', 'toileting', 'actors', 'thyroid', 'abla', 'homework', 'screened', 'tactile', 'beta', 'reliably', 'regularly', 'conscious', 'authenticity', 'monte', 'compulsive', 'interfaces', 'minor', 'childbirth', 'intelligibility', 'reverse', 'equipment', 'copm', 'underserved', '57', '52', 'implant', 'ebp', 'shame', 'sm', 'optimal', 'telesupervision', 'mandarin', 'applicable', 'thrashing', 'puncture', 'awake', 'belief', 'microarray', 'fragile', 'exome', 'lactic', 'antinuclear', 'antibody', 'generalizability', 'rct', 'extends', 'tagteach', 'pcit', 'images', 'indirect', 'confirm', 'anova', 'pfe', 'outpatient', 'rird', 'cessation', 'proposal', 'makey', 'psychologists', 'overcome', 'trialed', 'ego', 'printed', 'vividly', 'obesity', 'absent', 'reinforce', 'accompanied', 'interrupted', 'specialists', 'encountered', 'favorably', 'prerequisite', 'rob', 'picking', 'utilising', 'sedentary', 'cinahl', 'dose', '49', 'vulvodynia', 'fun', 'formative', 'innovations'</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>207</v>
+      </c>
+      <c r="E7" t="n">
+        <v>433</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1511</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.276483050847458</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.970568999345978</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.376230128690386</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.826719576719577</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.74963412084466</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17.62666436105827</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.864719004971168</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.800446887258514</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12.03813602890815</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21.6327751624043</v>
+      </c>
+      <c r="F9" t="n">
+        <v>61.83731533275075</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.99277253865486</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.34819296219609</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.500339181392611</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.599483873444695</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.220325998376923</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12.51424867829706</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.97469157403105</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kurt</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>46.17321095884201</v>
+      </c>
+      <c r="C11" t="n">
+        <v>37.99852422875433</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79.0457710603057</v>
+      </c>
+      <c r="E11" t="n">
+        <v>115.1084782814069</v>
+      </c>
+      <c r="F11" t="n">
+        <v>207.4533340897165</v>
+      </c>
+      <c r="G11" t="n">
+        <v>273.7433156945392</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Distinct Word Count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>944</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1529</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3963</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5292</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9566</v>
+      </c>
+      <c r="G12" t="n">
         <v>11566</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>['erosion', 'generalisability', 'bourque', 'listened', 'humanizing', 'assimilation', 'alertness', 'aneurodegenerative', 'interconnectivity', 'digitalized', 'syllabus', 'cocare', 'abcaa', 'empatica', 'attempting', 'landslide', 'thiemann', 'decentralised', 'bob', 'e4', 'initiator', 'internationally', 'uae', 'bicultural', 'tangibles', 'conferenced', 'indications', 'illuminate', 'sayeski', 'organisers', 'organiser', 'robint', 'looks', 'reuse', 'consort', 'appreciate', 'distinctive', 'leaves', 'delinquency', 'pianists', 'nces', 'curfews', 'pedestrian', 'efficiencies', 'unexpectedly', 'gazes', 'sustainment', 'deliverables', 'organisational', 'scalability', 'mongolian', '25th', 'musicians', '149', 'engendering', 'arabic', 'imbrications', 'exposition', 'miscues', 'fsq', 'stuck', 'criticisms', 'intervenes', 'manikin', 'stai', 'fss', 'mantras', 'dismantle', 'kratochwill', 'generator', 'conversely', 'objectivity', 'descriptives', 'supplements', '906', 'champ', 'quarterly', 'totals', '885', 'consulted', 'digging', '109', 'partly', 'akadema', 'atademix', 'bilge', 'neighborhoods', 'rectal', 'enacted', 'voted', '2025', 'succeeded', 'bands', 'singers', '266', 'finland', 'elaborates', 'reversibility', 'prioritizes', 'boundaries', 'relearning', 'export', 'pave', 'gis', '3138', 'suffer', 'mapped', 'acknowledgement', 'doubling', 'infrequent', 'disasters', 'techno', 'echolalia', 'adoptation', 'presumed', 'wolf', 'gainful', 'risley', 'impeding', 'planted', 'correspondingly', 'montes', 'generalisationonly', 'leds', 'spouse', 'toilet', 'conductivity', 'usb', 'microswitch', 'cluster', 'backgroundself', 'headset', 'persisting', 'oblige', 'selfmodeling', 'immersed', 'dictation', 'depicting', 'entail', 'approximation', 'unedited', 'ccds', 'keys', 'youtube', 'files', 'musician', '320', 'noninjurious', 'eu', 'inequitable', 'obligated', 'impulse', 'neurobehavioral', 'postschool', 'clerk', 'courtesy', 'associates', '3661', 'nomination', 'rehabilitative', 'viewer', 'genital', 'dttc', 'birds', 'try', 'nonhuman', 'untapped', 'outgrowth', 'autonomus', 'empowers', 'parrot', 'safeguards', 'admissions', 'postdisaster', 'ttct', 'commboard', 'disabled', 'disconnect', '933', 'remember', 'imagine', 'trying', 'chance', 'conformed', 'attach', 'inevitably', 'trap', 'furthering', 'shooting', 'envisioned', 'parametrically', 'p4p', 'assume', 'familial', 'combinatorial', 'mbl', 'beverage', 'entitled', 'conceptualizing', 'throught', 'outages', 'characterised', 'managment', 'vulval', 'cit', 'forgetfulness', 'quebec', 'collective', 'tab', '2modifier', 'yearold', 'translates', 'likewise', 'underscored', 'popcorn', 'irregular', 'fresh', 'juice', 'ecrit', 'eveil', 'langage', 'declines', 'engagements', 'andragogy', 'soutien', 'pratiques', 'individualize', 'steep', 'coherent', 'pictorially', 'multistate', 'multisystem', '746', 'passionate', 'concussion', 'striking', '6477', 'seedling', 'sprinkled', 'tribute', 'pausing', '979', 'programa', 'implementar', '222', 'cholesterol', '046', 'robustness', 'ears', 'contagious', 'easons', '392', 'redistribution', 'opic', 'rite', 'cons', 'weigh', 'rganize', 'occasion', 'taping', 'copious', 'regimens', 'biserial', 'preferably', 'pow', 'escalation', 'transcribed', 'constituents', 'minimized', 'onse', 'epas', 'pick', 'toolkit', 'apartment', 'curvilinear', 'serendipitously', 'reject', 'soda', 'unrest', 'psychotropic', 'undertaking', 'thesuperbetter', 'pros', 'tape', 'referrers', 'underresearched', 'adhesive', 'mbsced', 'incidents', '16915663', 'avert', 'certifiied', 'parametrize', 'anddestressify', 'hri', 'matures', 'thermoregulation', 'worsen', 'stereotyped', 'implantation', 'hanen', 'manifestation', 'buffalo', 'prelingually', 'nominated', 'nonindependent', 'cooler', 'loosened', 'recreation', 'permissibility', 'underneath', 'exploit', 'moral', 'thermodynamics', 'spilled', 'postoperative', 'reprimands', 'userfriendlyscience', 'fundamentally', 'devised', 'accounts', 'formación', 'avian', 'interspecies', 'upset', 'hris', 'activated', 'backing', 'cluttering', 'prospectively', 'dcs', 'intersections', '234', 'entropy', 'stands', '102', 'sma', 'purposeful', 'augmentation', 'multiclass', 'vienna', 'doc2vec', 'germany', 'overburdens', 'abandoned', 'communicates', 'hypothesize', 'pipelines', 'regulative', 'grille', 'systematics', '028', '027', 'intimate', 'coincidental', 'undecided', 'liwc', 'pressures', 'producer', 'scheme', '948', 'artistic', '16734532', 'emergencies', 'ordered', 'electrodermal', '2582', 'asserts', 'sociopolitical', 'stone', 'throughmturk', 'austria', 'peculiarities', 'vague', 'simulacra', 'wcag', 'refusals', 'aprogress', 'enthusiastic', 'sociology', 'thinned', 'explains', 'oscillation', 'iciq', 'cleveland', 'cariveau', 'capital', 'transperineal', 'ultrasound', 'nashville', 'hoffman', 'mcs', 'enduring', '76190', 'cultivation', 'aptitude', 'startle', 'studio', 'edwards', 'fixations', 'figures', 'feldmiller', 'experimentation', 'transported', 'durable', 'negligible', 'johner', 'outlets', 'persists', 'hammering', 'ppvt', 'eowpvt', 'repeating', '041', 'intravaginal', 'verifying', 'uncoordinated', 'rte', 'quick', 'hypotonia', 'dynamometric', 'gynecological', 'survivorship', 'frampton', '02381', 'congenital', 'alterations', 'rapp', 'acquisitions', '7th', 'th', 'demonstation', 'eggs', 'columns', 'fecal', 'inputted', 'assets', 'segmenting', 'slimmer', 'bandung', 'pronouncing', 'ncrease', 'bart', 'unpredictable', '20th', 'egg', 'treading', 'unchartered', 'welk', 'miscommunication', 'reemerged', 'scanpath', '1modifier', 'antisaccades', 'microsaccades', 'surroundings', 'enculturated', 'beverages', 'verification', 'e33555', 'separating', 'outings', 'selfinstruction', 'pennsylvania', 'nding', 'xplain', 'complimentary', 'funny', 'waiter', 'quantifies', 'accommodation', 'hallmark', 'schulze', 'generalizationprobe', '526', 'murcia', 'compulsory', 'rosales', 'ref', 'pract', 'childh', 'snacks', 'broderick', 'bounds', 'tying', 'tenets', 'ladson', 'productively', 'billings', '1995a', '1995b', 'gradients', 'exhibitions', 'populate', 'leastto', 'cyprus', 'approximated', 'jennyo_csueb', 'meredith', 'nicosia', 'curated', 'barber', 'throughs', 'undertake', 'digcomporg', 'nonchallenging', 'ofthe', 'incompatibility', 'tied', 'ignore', 'aspires', 'fitzgerald', 'relegated', 'contemplated', 'pushups', 'frank_o_ely', '461', 'organisations', 'overwhelming', 'multicultural', 'surprise', 'uninvestigated', 'undergirding', 'resembled', 'speaks', 'digitized', 'domestic', 'surpassed', 'adaption', 'saber', '935', '361', 'spanning', 'vive', 'ga', 'ceased', 'sella', 'consortium', 'lunches', 'sized', 'unsystematic', 'casting', 'liu', 'doubt', 'masochistic', 'stereotypes', 'postpone', 'illinois', 'subcomponent', 'disproportionally', 'speeches', 'compelled', 'forest', 'revolutionizing', 'carrot', 'milestone', 'scr', 'cope', 'ineffectiveness', 'htc', 'unsubstantiated', 'fad', 'touchscreen', 'housed', 'monoxide', 'carbon', 'gatherings', 'differentially', 'unproven', '237', '332', 'applicants', 'mails', 'tabriz', '347', 'gars', 'stochastic', 'caring', 'assq', 'essentially', 'rehearsals', 'boutot', 'intraindividual', 'decided', 'counselors', 'sociodemographic', 'cpst', 'trustworthy', 'assistedreading', 'pertinent', 'revenue', 'volumes', 'forecasted', 'anonymously', 'director', 'oregon', 'oases', 'phd', 'ofexceptional', 'editor', 'emeritus', 'milestones', 'scholarly', 'j4', 'flowchart', 'unger', 'kirkbride', 'adolesc', 'peck', '635', 'sadness', '1016', 'jaac', 'pretherapy', 'conversion', 'projective', 'nonintensive', 'writings', 'simplifies', '646', 'fronto', 'default', 'extinguished', 'boundary', 'intrusions', 'kaye', 'allegiance', 'surveying', 'merged', 'psychol', 'sch', 'mccurdy', 'lunchrooms', 'neighbors', 'nearest', 'descent', 'instability', 'ri', 'ucla', 'resourcing', 'angeles', 'golf', 'clicker', 'los', 'ipg', 'smn', 'deceased', 'compellingness', 'kasari', 'winter', 'rld', 'rlds', 'acad', 'alters', 'handstands', 'trip', 'gee', 'rmcorr', 'belongs', 'detached', 'pigeon', 'executing', 'workplaces', 'mention', 'confound', 'procrastinate', '157', 'suicide', 'shake', 'hypothalamic', 'shoulder', 'outweigh', 'unassisted', 'voiced', 'detracted', 'tissue', 'safely', 'regulates', 'waned', 'discouraging', 'occasionally', 'tantrums', 'confluence', 'hydroxyzine', 'incrementally', 'clonidine', 'regimen', 'coalesced', 'waxed', 'thirds', 'locally', 'workloads', 'teleoperation', 'attracted', 'integers', '125', 'cheek', 'integer', 'addictive', 'newsfeed', 'mindlessly', 'billion', 'surfaces', 'climbers', 'mindfully', 'tarantula', 'pituitary', 'adrenal', 'concentrate', 'alleviation', 'clarify', 'headband', 'nonintrusive', 'unfolding', 'dystonia', 'palette', 'augments', 'intense', 'unorthodox', 'proposition', 'iisca', 'hyperkinetic', 'impending', 'nonsimulated', 'haemorrhage', 'subarachnoid', 'dorsiflexion', 'lidcombe', 'ashworth', 'syrup', 'kuningan', 'truly', 'matches', 'considerably', 'phonetic', 'neighborhood', 'onsite', 'ascending', 'galbraith', 'detergent', 'dense', 'compensating', 'correctives', 'dvd', 'carers', 'debit', 'reloadable', 'kinematic', 'exhausting', 'exploits', 'arrays', 'saturation', 'oxyhemoglobin', 'angell', 'stoner', 'daczewitz', 'flexors', 'advertisement', 'acronyms', 'pushing', 'contraversive', 'sided', 'smell', 'clearing', 'debugging', 'normand', 'mechling', 'phonemes', 'blend', 'rime', 'disappeared', 'moves', 'passively', 'electric', 'ieps', 'soap', 'oil', 'suggestion', 'larson', 'recesses', 'bdi', 'sad', '587', 'coneff', 'preschools', 'theorists', 'footprints', 'reproduced', 'inserted', 'sniff', 'absolute', 'squares', '275', 'finger', 'fractionated', 'pronation', 'supination', 'complementarily', 'partitioning', '2sd', 'triggering', 'viral', 'residual', 'mainstay', 'risky', 'printing', 'dexterity', '104', 'gec', 'footage', 'impair', 'nonmotor', 'webinar', 'informally', '089', 'simpler', 'transiently', 'pretesting', 'doorknob', 'bowl', 'mug', 'visuals', 'ipad2', 'retain', '483', '555', 'prehensile', 'financially', 'verbalization', 'dissensus', 'regurgitatians', 'gut', 'octopus', 'breaking', 'came', 'abovementioned', 'hayden', 'rigour', 'scribe', 'stewart', 'glossophobia', 'catastrophic', 'phobic', 'purposefully', 'conform', 'misses', 'hpc', 'versame', 'consumed', 'classbadges', 'classdojo', 'coherence', 'greeting', 'nonexclusionary', 'unappealing', 'hygienically', 'cumbersome', 'augmentals', 'booklets', 'augmental', 'coworkers', 'nonmatched', 'doors', 'reopening', 'usedandthe', 'wrong', 'theirs', 'regulators', 'complicate', 'undertreated', 'establisheda', 'feasibilitysuccess', 'armband', 'myo', 'forearm', 'inertial', 'pinching', 'asfeasible', 'contradictory', 'overeating', 'burn', 'supervisee', 'midwestern', 'dewiele', 'underpinning', 'trade', 'precautions', 'momentarily', 'ingrained', 'hamper', 'rhetoric', 'splitting', 'solvent', 'urgency', 'exempt', 'conclusionsthere', 'tracker', 'finalized', 'positivity', 'kuwaiti', 'truax', 'jacobson', 'download', 'participationmeasures', 'preacademic', 'covaries', 'expressing', 'fromjabainto', 'window', 'launching', 'analysisis', 'thejournal', 'adventitiously', 'foractivities', 'functionoutcome', 'priori', 'destressify', 'prohibitive', 'obviously', 'ids', 'prework', 'instantly', 'routeam', 'slayer', 'colleges', 'iowa', 'navigates', 'hydrotherapy', 'conductive', '17319', 'nation', 'tess', 'webpage', 'eased', 'minecraft', 'allocations', 'pdd', 'damaged', 'detention', 'recycle', 'extraneous', 'critiquing', 'ofaba', 'esl', 'colored', 'elective', 'moran', 'sort', 'electroencephalographic', 'allotted', 'reproduce', 'swim', 'confers', 'onsets', 'anecdotally', 'nairobi', 'referent', 'fictitious', 'thalamus', 'sydney', 'committees', 'multisymbol', 'interviewees', '647', 'doses', 'extraordinary', 'classical', 'representativeness', 'wings', 'reinvigorate', 'inapplicable', 'disuse', 'neurogenic', 'blanket', 'jurisdiction', 'opened', 'lovaas', 'versatile', 'overburdened', 'suspend', 'deems', 'richness', 'coexisting', 'caseloads', 'succeed', 'stocco', 'appl', 'purposeto', 'behav', 'anal', 'assurance', 'tradition', 'poar', 'reap', '510', 'vista', 'accommodate', 'agitation', 'jaba', 'fallen', 'pitcher', 'infield', 'leagues', 'worse', 'predicts', '600', 'myriad', 'multiday', 'b5', 'pck', 'skip', '108', 'mere', 'downstream', 'ingredient', 'corners', 'c5', 'birrs', 'coordinating', 'postsession', 'denoting', 'informing', 'louder', 'alarmingly', 'batters', 'meditations', 'league', 'metadata', 'rgbd', 'rgb', '3000', 'playdates', 'descriptor', 'guilt', 'birthplace', 'tackles', 'headers', 'noncompliance', '1997', 'bowman', 'threat', 'hsq', 'b4', 'binder', 'aminobutyric', 'excludes', 'gamma', 'thalamic', 'plausible', 'powers', 'divert', 'lua', 'moon', 'isrctn15312724', 'categorised', 'isrctn', 'arises', 'inadvertent', 'marks', 'depositing', 'receptively', 'substantive', 'c3', 'b3', 'c4', 'checkpoints', 'fitbits', 'earning', 'neutralized', 'redirecting', 'lessen', 'interchange', 'dros', 'crime', 'lisa', 'edgington', 'succeeds', 'preteaching', 'occluding', 'reinforcements', 'vocally', 'asymmetries', 'annul', 'speechgenerating', 'organizers', 'rain', 'cigarettes', 'combustible', 'safer', 'rehabilatation', 'angular', 'cleaned', 'implementations', 'exceptions', 'kst', 'uptakes', 'escalating', 'submitting', 'greet', '2004', 'chin', 'kurtz', 'nct02906956', 'substantiates', 'abe', 'spectra', 'inflammation', 'predilection', 'reminiscence', '1000', 'continent', 'vue', 'susceptibility', 'cerebrospinal', 'omitted', 'beget', '307', 'desirability', 'nlysql', 'wearer', 'pop', '1984', 'nct06219122', 'childless', 'erroneous', 'cbcl', 'surviving', 'spectre', 'conception', 'affection', 'railway', 'standalone', 'gamifying', 'retrieve', 'maranhao', 'professors', 'attain', 'biopsychosocial', 'warming', 'easing', 'prescription', 'insurmountable', 'concede', 'ovid', 'chapter', 'optimise', 'safeguard', 'spot', 'counselor', 'manager', 'rehabdata', 'fluidity', 'volatile', 'thirdly', 'districts', 'rmsea', 'offices', '059', 'srmr', 'symptomology', '071', 'dosing', 'therapeutical', 'hci', 'rubbing', 'electrically', 'akin', 'currents', 'pulsed', 'elaborated', 'delaying', 'multifactorial', 'andriod', 'interconnectedness', 'interconnected', 'gamm', 'estonia', 'tonal', 'deltas', 'complements', 'ofremote', '796', 'jaramillo', 'supervisionand', 'amplitude', 'saliva', 'alere', '290', 'precluded', 'languageplus', 'commencement', 'existent', 'crd42020147669', 'communicable', 'diversify', 'reciprocally', 'dialectic', 'didtas', 'spontaneity', 'rtc', 'reinforces', 'paralleled', 'unlimited', 'geriatrics', 'learnings', 'clearer', 'il', 'exploited', 'modulate', 'nepali', 'khmer', 'connects', 'hmong', 'worthy', 'psf', '3gi', 'conner', 'achenbach', 'seqex', 'polin', 'jews', 'osteoarthritis', 'spoke', 'commuting', 'capacities', 'impedance', 'wideband', 'combiner', 'cancelation', 'centralized', 'tnf', 'edit', 'camtasia', 'ipec', 'silent', 'restructure', 'visitor', '024', 'deictic', 'entrance', 'reversely', 'misrepresented', 'ntd', 'dispel', 'approve', 'exhibition', 'disapproved', '14977605', 'disapprove', 'openly', 'onour', 'glance', 'laptops', 'prepost', 'lockdown', 'indian', '897', 'globalizing', 'ruhr', 'confronted', 'transformations', 'paralysed', 'paralleling', 'liberation', 'democratization', 'portray', 'employable', 'steeper', '205', 'theoretic', 'arthroplasty', 'supplementing', 'compromised', 'attaches', 'ideals', 'encouragingly', 'mbti', 'terminals', 'gyms', 'pays', 'mmics', 'microwave', 'realization', 'tradeoff', 'childen', 'linearity', 'coupling', 'peak', '2clte', 'leakage', 'outstanding', 'monolithic', 'interactional', '0027', 'hibernate', 'deandre', '0018', 'zion', 'disparate', 'hairdressing', 'programmatic', 'pause', 'researchkit', 'converges', 'irp', '0343', '6775', 'malik', 'licensing', 'kodak', 'ross', 'paediatric', 'kmet', 'carefully', 'lsf', 'fellowship', 'achieves', 'artifact', 'addictions', 'semiconductor', 'oxide', 'metal', 'diffused', 'laterally', 'drain', 'cihr', '10clte', 'obo', 'determines', 'dbm', 'instantaneous', 'candy', '345', 'scaled', 'clements', 'mmic', 'rf', 'compact', 'mature', 'dpas', 'gan', '8clte', 'manualization', 'escapement', 'erred', 'storing', 'fassnacht', 'lechermeier', 'alvero', 'corley', 'gravina', '896', 'timeout', 'pellecchia', 'attenuate', 'dev', 'repurposed', 'discreet', 'watches', 'reprimand', '441', 'boosts', 'ecology', 'awkward', 'navarro', 'irregularities', 'dt', 'bear', 'slowed', 'depended', 'aimsweb', 'punishing', 'hypothetically', 'boyd', 'mcdonald', 'bimonthly', 'lapses', 'strive', 'assign', 'flourishing', 'belong', 'nontreatment', 'grundfos', 'baseof', 'mathematic', 'disord', '1975', 'crossed', 'villages', 'kenyan', 'pump', 'unravel', 'ant', 'designating', 'surpass', 'popliteal', 'fossa', 'deafblind', 'pointed', 'sacrum', 'tackled', 'curbing', 'statistician', 'stacked', 'obtrusiveness', 'assessor', 'transmit', '230', 'wendt', 'schlosser', 'titled', '1hr', 'naturalness', 'sophisticated', 'kanjuruhan', 'let', 'topography', 'volunteering', 'knot', 'disorde', 'transferability', 'timeliness', 'resides', 'hoped', 'taipei', 'indulge', 'lot', 'thing', 'hurt', 'github', 'unhooked', 'accountable', 'texas', 'knees', 'nmpk', 'mpk', 'walkway', 'contrived', 'instagram', 'unhooks', 'alleviates', 'nets', 'pmis', 'amounts', '221', 'circumference', 'stride', 'simplification', 'empathetic', 'attendant', 'credentials', 'aggressiveness', '1223', 'krippendorff', 'uncovered', 'thoughtfulness', 'guarantee', 'equality', 'asset', 'resolves', 'purchase', '876', 'ageing', 'themself', 'broadened', 'annoyance', 'phasing', 'ruizvja', 'rdarbs', 'inexperienced', '758', 'sessment', 'credentialed', 'boxers', 'punches', 'reactivity', '2917', 'sufferers', 'resembles', 'comprehensiveness', '2927', 'differentiate', 'athletics', 'confusing', 'dwelling', 'unblinded', 'horseback', 'terminal', 'resetting', 'deploys', 'christy', 'charlop', 'ird', 'prominently', 'formalized', 'securing', 'danger', '242', 'daneshvar', 'hanewicz', 'compromises', 'francis', 'johnson', 'river', 'bridging', 'ra', 'obese', 'prentice', 'cooper', 'abacad', '40th', '8211', 'uwer', 'hayward', 'eikeseth', 'saddle', 'collaborating', 'conveying', 'cairo', 'audiovisual', 'clock', 'weather', 'comprehensible', '186', 'suspicion', 'elapse', 'cymatics', '908', 'graphics', 'hc200199', 'tli', 'resolving', 'cfi', '846', 'detract', 'shea', 'analgesia', 'cooling', 'referencing', 'perspecitves', 'copies', 'videotape', 'banjarmasin', 'intercoder', 'recalculated', 'accomplish', 'wondered', 'convection', 'distracted', 'footwork', 'intracoder', 'oftentimes', 'cinah', 'allred', 'ingesting', 'ps', 'inductively', 'iphone', 'platt', 'complicates', 'shredding', 'copying', 'postprogram', 'advertisements', 'intergroup', 'fab', 'unaltered', 'chores', 'smokers', '414', 'reverting', 'lifelink', 'reverted', 'counterparts', '1989', 'eductaion', 'fitbit', 'flex', 'seemingly', '246', 'sss', 'narrated', '1481', 'psyinfo', 'gresham', 'noun', 'nondiagonal', 'unreliably', 'springer', 'ieee', 'poisoning', '65yrs', 'ghq30', '43yrs', 'intermediate', 'guw6h', 'trego', '287', 'assemble', 'slovak', 'scenes', 'osf', 'caprice', 'boxing', 'ex', 'badminton', 'ont', 'relaxation', 'accumulate', 'mitteer', 'choking', 'ingestion', 'alarming', 'pass', 'enviornment', '257', '253', 'leblanc', 'caps', 'counterbalancing', 'malott', 'policymaking', 'circumscribed', 'reintegration', 'shakers', 'pepper', 'salt', 'lounge', 'tendencies', 'wallis', 'kruskal', 'rehabilitationtechnology', 'conclusionteachers', 'silverware', 'cleaning', 'sal', 'rever', 'modular', 'methodsan', 'cast', 'election', 'casts', 'provinces', 'metacontingencies', 'opportune', 'legislators', 'successes', 'conclusionswith', 'beginners', 'objectivesmeditation', 'brisk', 'jogging', 'wandering', 'meditators', 'resultsbody', 'methodusing', '1953', 'cyberchondria', 'unraveling', 'transparent', 'flipped', 'edge', 'portability', 'concluding', 'mall', 'effector', 'subclinical', 'optimising', 'anthropomorphic', 'thique', '2021070', 'personnes', 'vaior', 'universit', 'humains', 'tres', 'debated', 'mu', 'modulations', 'erd', 'desynchronization', 'cz', 'rolling', 'catching', 'palms', 'restoration', 'fingers', 'adjuvant', 'approaching', 'mcgill', 'premise', 'msbi', 'discernible', 'flavor', 'jbi', 'accident', 'istanbul', 'optimizes', '6760', 'scrimmages', 'presses', 'awaits', 'reweightings', 'opacity', 'citizen', 'collectively', 'infarct', 'cerebellar', 'medullary', 'really', 'favour', 'unlocking', 'ceti', 'bnt', 'modulated', 'bathroom', 'substitute', 'dichotomous', 'sesame', 'multiplicative', 'multiculturism', 'cohesion', 'chapters', 'occupations', 'addict', 'deviated', 'mediolateral', 'rubber', 'reactionary', 'dialog', 'sparks', 'scrimmage', 'neglected', 'mcar', 'massachusetts', 'arizona', 'mandates', 'showcased', 'lobbyist', 'toolkits', 'semantics', 'morphology', 'boston', 'proceduresfour', 'scarfv2', 'vkcsites', 'ebip', 'votes', 'polls', 'citizens', 'ibcs', 'governmental', 'pieces', 'wab', '1844', 'nih', 'coincides', 'foci', 'standardisation', 'accumulating', 'conclusionsevidence', 'nightly', 'delve', 'formed', 'irlssg', 'pharmaceuticals', 'pharmaceutical', 'anemia', 'iron', 'hemodialysis', 'plms', 'subpopulations', 'desensitisation', 'hypertension', 'heating', 'nct05593302', '0922', 'ti', 'atlas', 'artwork', 'ecirc', 'rosenberg', 'prominence', 'opiate', 'atlantic', 'nurture', 'hints', 'crafted', 'emi', 'nonclinical', 'referrer', 'recounting', 'insecurity', 'disjuncture', 'loops', 'colleague', 'coordinate', 'suture', 'acoustical', 'beck', '017', 'registrationclinicaltrials', 'offline', '509', '719', '400', 'subgroup', 'multicentre', 'prepandemic', 'violent', 'interplay', 'mg', 'overdose', 'methadone', 'opens', 'intuitive', 'functionality', 'pool', 'reprioritization', 'craving', 'measuresprimary', 'cam2038', 'sichuan', 'chengdu', 'nvivo', 'cravings', 'worst', 'spontaneously', 'nonprescribed', 'contrasting', 'perpetually', 'nonexperimental', 'southwest', 'nigerian', 'alphabet', 'microlearn', 'streaming', '1501', 'particle', '633', 'ibm', '0098', 'neuropsychology', 'nct03958487', 'multisensor', 'capturing', 'gyroscope', 'atmospheric', 'receiver', '913', '808', '789', '891', '767', '962', 'kidscreen', 'lays', 'truth', 'ground', 'holistically', 'deteriorate', 'autoshaping', 'moved', 'invention', 'inquisitive', 'pioneer', 'bathing', 'les', 'avec', 'recherche', '294', 'cer', 'egrave', 'rivi', 'trois', '895', 'bec', 'qu', 'discussionthis', 'introductionlingotalk', 'xgboost', 'ensemble', 'boosted', 'intensities', '811', 'agrave', 'nct03699007', 'nct01974791', 'avoided', 'narrowing', 'incentivized', 'intubation', 'endotracheal', 'cents', 'darkness', 'stationary', 'aimwriting', 'brainingcamp', 'chromebook', 'sdnn', 'rmssd', 'tries', 'asperger', 'synergy', 'bike', 'sturgeon', 'lake', 'sidman', 'fish', 'siamese', 'garry', 'coauthored', 'keller', 'losing', 'psychoeducational', 'sweden', 'asynchronously', 'telecoaching', 'tentatively', 'climates', 'discarding', 'nonsocial', 'asssessment', 'advertising', 'ambiguous', '1176', '1170', 'wilder', 'audiology', 'psych', '165', 'mandate', 'backward', 'misaligned', 'crianças', 'vocabulário', 'aumento', 'contibuindo', 'ensino', 'executi', 'sti', 'auti', 'mtss', 'mutation', 'reproduction', 'darwinian', '1978', 'resultsthirty', 'resultsfifteen', 'animate', 'videogaming', 'varieties', '728', 'associate', 'meyer', 'specificities', 'lumiar', 'paco', 'undermine', 'nestled', 'arisen', 'literal', 'purchased', 'conclusionsit', 'frt', 'mexican', 'portfolio', 'resort', 'stigmatized', 'unconscious', 'tled', 'shaming', 'dirty', 'dinner', 'soup', 'smoothly', 'camouflaging', 'roots', 'societies', '260', 'camouflage', 'enti', 'cle', 'arti', 'autista', 'crucially', 'objectifying', 'clusters', 'specifications', 'bought', 'lobato', 'monteiro', 'aee', 'gaia', 'benign', 'constellations', 'methodfor', 'certainly', '214', 've', 'centrally', 'results92', 'accrediting', 'permission', 'dm', 'methodsto', 'converging', 'philosophies', 'info', 'neurologists', 'anxieties', 'biosensors', 'neurodevelopment', 'floortime', 'dir', 'revolutions', 'embrace', 'quietly', 'discussiontwo', 'nct05893914', '2023p000931', 'brigham', 'publically', 'sexuality', 'learns', 'optimizer', 'adam', 'numeric', 'rhythmicity', 'conclusionimplementing', 'resultsno', 'purposetelehealth', 'existence', 'controversial', 'peripherally', 'amplify', 'nprs', 'optimizers', 'honors', 'collapsed', 'methodschildren', 'rican', 'costa', 'backgroundworldwide', 'privately', 'reichow', 'tolerating', 'sourced', 'comorbidity', 'pervades', 'pts', 'comparably', 'bca', 'vocation', 'inclusionary', 'surprising', 'overly', '0011', 'bespoke', '1986', 'isi', 'nonlinear', 'skeptic', 'opposing', 'file', 'respects', 'undergraduates', 'broadening', 'diagnostics', 'introductionrecent', 'renaissance', 'ripe', 'covid19', 'layered', 'dignity', 'hermeneutic', 'accomplishments', 'staged', 'mastering', 'inquiries', 'arrive', 'piwi', 'phi', 'indirectly', 'analytically', 'implicationsgiven', 'macro', 'hayes', 'hotel', '305', 'garners', 'subordinate', 'powerless', 'recognise', 'piqued', 'expansive', 'presentationwe', 'dividing', 'conservation', 'elucidating', 'burgeoning', 'valuethis', 'scrutiny', 'recover', 'pretests', 'keyboards', 'container', 'consultants', 'trailers', 'conversed', 'introductionfollowing', 'nct04778423', 'ct2', 'hospitality', 'burns', 'cuts', 'stings', 'insect', 'needing', 'soliciting', '106', 'depersonalization', 'inner', 'jd', 'flaws', 'unreliable', 'thrived', 'extroversion', 'legibility', 'misspelled', 'vacation', 'luiselli', '118', 'hiring', 'missoula', 'character', 'selections', 'a1ba2', 'tales', 'captivated', 'ohio', 'spear', '1990', 'smokejumpers', 'malevolence', 'omnipotence', 'critiques', 'cassette', 'war', 'situating', 'alouds', 'guest', 'hiding', 'alienation', 'teased', 'shamed', 'intersectional', 'anonymous', 'facebook', 'fuel', 'incarceration', 'cisgender', 'traumas', 'selves', 'associating', 'perceptibility', 'latitudes', 'multicolor', 'subfields', 'fails', 'overrepresentation', 'pc', 'dishwasher', 'dishes', 'rooms', 'targetted', 'hammersmith', 'nct03264339', 'obstetric', 'hurting', 'roane', 'compile', 'clustering', 'extensions', 'pressuring', 'visibility', 'unconsciously', 'consciously', 'suppressing', 'labor', 'toothpastes', 'toothbrushes', 'leaflets', 'bunny', 'toothpaste', 'spit', '227', '331', 'complaint', 'equivalently', 'correctional', 'stretching', 'bending', 'honor', 'predictable', 'chasing', 'rex', '2021a', 'underpin', '218', 'fmc', 'pdms2', 'reproducibility', 'differently', 'backgroundchildcare', 'curves', 'percentiles', 'childsmile', 'gmc', 'hygienist', 'streamed', 'unemployed', 'inequitably', 'hired', 'agenda', 'hygienists', 'dentition', 'hai', 'goalsetting', 'subdomain', 'ues', 'relaying', 'competitor', 'elevate', 'cena', 'tio', 'exchanged', 'eng', 'bot', 'ings', 'ry', 'su', 'collector', 'merges', 'employability', 'objectivesto', 'om', 'contender', 'extrinsic', 'intrinsic', 'confounding', 'hashtags', '492', '408', '911', 'averages', 'capitalized', 'feminization', 'afternoon', 'diets', 'videoed', 'transwomen', 'acoustics', 'ritualistic', 'evolves', '119', 'latina', 'español', 'teachings', 'vocalizing', 'dounavi', 'daly', 'latino', 'conclusionsvm', 'collate', 'objectivespeople', 'resultshalf', 'objectiveschildren', 'fills', 'resultsduring', 'interspersed', 'optic', '191', '172', 'carryover', 'egms', 'exclusive', 'abundance', 'backgroundvideo', 'analysissearch', 'criteriaall', 'grey', 'repositories', 'elicitations', 'concert', 'mapper', 'identical', 'reviewer', 'consequated', 'undifferentiated', 'mbsi', 'weakened', 'unsupported', 'methodssearches', 'clinictrials', 'proceduresa', 'understandings', 'stigmaand', 'conclusionsvnest', 'endpoint', 'quadriceps', 'contractions', 'widening', 'jesson', 'wilson', 'subreddit', 'attacks', 'malicious', 'sociocultural', 'engender', 'inf', 'cyberbehaviors', 'cells', 'pember', 'overlook', 'myokine', 'nct05822297', 'derivation', 'candyland', 'derivatives', 'framing', 'nct05152979', 'iatrogenic', 'networking', 'comprehending', 'hole', 'gardener', 'dig', 'backgroundverb', 'metalinguistic', 'maori', 'derivative', 'conclusionsin', 'objectivesemployment', 'nct03949959', 'registrationthe', 'backgroundphysical', 'conclusionsrelatively', 'resultsnineteen', 'confounders', 'cyberspace', 'expertise', 'taxing', 'assured', 'methodsthirteen', 'uc', 'injections', 'conclusionsour', 'appliedbehavioranalysis', 'behavioranalysis', 'inservice', 'businesses', 'conclusiondespite', 'dropouts', 'unreachable', 'ineligible', 'resultsamong', 'thrice', 'oromotor', 'cv', 'activ', 'bari', 'certificants', 'cwpm', 'founded', 'overarching', 'predecessors', 'enforceable', 'iskur', 'respiration', 'pod', 'fosters', 'magenis', 'smith', 'umin000048677', 'invaders', 'candidate', 'rescheduling', '238', 'gameboard', 'screenings', 'selectively', 'contributionthe', 'methodssix', 'aimsto', 'born', 'backgroundthe', 'prone', 'kunze', '387', '371', 'harnesses', 'affinity', 'unengagement', 'simulating', '546', 'nonresponders', 'intermountain', 'unprogrammed', 'cats', 'nuances', 'hint', '004', '346', '350', '535', '357', 'decrements', 'inherently', 'strokes', 'demanding', 'evaluator', 'rve', 'mo', 'mos', 'locate', 'counselling', 'interparticipant', 'intraparticipant', 'afforded', 'smiles', 'destination', 'intermixing', 'entailing', 'teller', 'samagalas', 'substantiate', 'underrepresented', 'conclusionsthree', 'webgazer', 'familiarizations', 'maximises', 'ja', 'substantiated', 'lite', 'disfigurement', 'imitated', 'utilises', 'precious', 'assuming', 'pp', 'totally', 'emit', 'intelligible', 'justifies', 'tensorflow', 'equipping', 'decide', 'justifications', 'enriches', 'shedding', 'edtech', 'addsimplications', 'timepoints', '464', 'redistribute', 'silhouette', 'bookended', 'vulnerabilities', 'counterintuitive', 'thinness', 'neutralizing', 'evenly', 'picturebook', 'superseded', 'vms', 'king', 'gevarter', 'cleary', 'barnett', 'hume', 'undergo', 'finds', 'demystifying', 'laughing', 'heavily', 'streamline', 'impetus', 'topicwhat', 'noteswhat', '136', 'internally', 'aspiring', 'minds', 'punctuation', 'heis', 'technologically', 'interpretivist', 'circle', 'endorsing', 'nationally', 'utilities', 'culminating', 'strives', 'childrens', 'unscripted', '208', '259', 'assembled', 'atlanta', 'datafinch', '512', '263', 'uncoached', 'wholistic', 'acrossbehaviors', 'purposethere', 'son', 'lord', 'positionality', 'plain', 'meaningfulness', 'bullying', 'waving', 'flapping', '393', 'scaffolded', 'argumentative', 'dire', 'bypassing', 'practise', 'thinning', 'nct05610982', 'devote', 'depiction', 'editorial', 'thoroughness', 'teleconsultation', 'pitfalls', 'professionalization', 'knowlden', 'precisely', 'rankings', 'munich', 'revisions', 'earthquakes', 'unadapted', 'applicationrecorded', '235', 'susceptible', 'hone', 'medial', 'biceps', 'rectus', 'mentee', 'resiliencethemed', 'atrisk', '25464064', '25799935', 'evidencebased', 'resilient', 'burst', 'pseudorandom', 'citing', 'solicited', '288', 'vigilant', '203', '449', 'preto', 'conclusionsleveraging', 'objectivesmany', 'calm', 'paliperidone', 'risperidone', 'monohydrate', 'subtests', 'additions', 'phenomenology', 'resists', 'massively', 'cultures', 'stabilized', 'myocardial', 'playsets', 'joy', 'playfulness', 'proportionally', 'imaginative', 'methodan', 'unaddressed', 'jeopardize', 'backgroundfeeding', 'participator', 'logbooks', 'climate', 'lmics', 'latine', 'collaborate', 'neglecting', 'spoon', 'tends', 'innovate', 'formalize', 'preliminarily', 'changemaker', 'diploma', 'dublin', 'multisensorial', 'microscale', 'accreditation', 'stabilised', 'embeds', 'graduates', 'elaborating', 'audiences', 'gastrocnemius', 'utilisation', 't12', 't11', 't10', 'stimulated', 'incomplete', 'locomotor', 'eurasian', 'cater', 'polytechnic', 'nonepileptic', 'carrying', 'hampered', 'intends', 'excited', 'regency', 'mantova', 'spazio', 'epilepsy', 'senctds', 'ctsas', 'chats', 'precursor', 'reform', 'quickening', 'backend', 'layout', 'alternations', 'dispersed', 'establishment', 'stems', 'staffmembers', 'studycommenced', 'thecovid', 'relatedtraumatic', 'hesitation', 'deliveredwith', 'retards', 'ofintrusive', 'guidedimagery', 'nonstigmatizing', 'posttraumaticstress', 'sensorimotor', '130', 'ajay', 'derek', 'tibialis', 'feasibilityand', 'salient', 'creativecommons', 'attribution', 'commons', 'linguistics', 'chatbots', 'licenses', 'workshopping', 'disclosure', 'firstadministered', 'wherethe', 'ambulance', 'theintensive', 'releasing', 'pandemicand', 'apotential', 'interventionwas', 'uncovering', 'memoriesfrom', 'possession', 'forensic', 'testimony', 'zone', 'summaries', 'essays', '192', 'meuc', 'spill', 'hematological', 'invasive', 'conclusionsa', 'purposeenvironmental', '1970s', 'branch', 'eline', 'bas', 'apy', 'restoring', 'mitigates', 'allogeneic', 'autologous', 'orf', '</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Count (Once)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>573</v>
+      </c>
+      <c r="C13" t="n">
+        <v>801</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1617</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3219</v>
+      </c>
+      <c r="G13" t="n">
         <v>4054</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>['intervention', 'study', 'design', 'participants', 'children', 'training', 'students', 'asd', 'skills', 'based', 'research', 'behavior', 'single', 'using', 'results', 'case', 'treatment', 'social', 'aba', 'use', 'analysis', 'used', 'video', 'effects', 'data', 'baseline', 'learning', 'multiple', 'autism', 'studies', 'interventions', 'behavioral', 'self', 'communication', 'technology', 'teaching', 'disabilities', 'instruction', 'effective', 'therapy', 'individuals', 'support', 'effect', 'intellectual', 'outcomes', 'performance', 'experimental', 'telehealth', 'effectiveness', 'reading', 'functional', 'education', 'behaviors', 'evidence', 'visual', 'time', 'findings', 'parent', 'high', 'parents', 'methods', 'child', 'language', 'practice', 'review', 'aac', 'program', 'modeling', 'sessions', 'school', 'significant', 'assessment', 'group', 'health', 'showed', 'activity', 'purpose', 'feedback', 'online', 'speech', 'positive', 'developmental', 'future', 'subject', 'improve', 'method', 'teachers', 'approach', 'model', 'virtual', 'included', 'disability', 'physical', 'increase', 'conducted', 'strategies', 'autistic', 'increased', 'quality', 'evaluate', 'current', 'teach', 'implementation', 'efficacy', 'participant', 'adults', 'care', 'people', 'phase', 'systematic', 'development', 'cognitive', 'demonstrated', 'evaluated', 'engagement', 'related', 'clinical', 'student', 'daily', 'implications', 'coaching', 'activities', 'provide', 'reinforcement', 'task', 'services', 'implemented', 'management', 'post', 'discussed', 'patients', 'level', 'needs', 'reported', 'game', 'impact', 'control', 'following', '19', 'application', 'compared', 'measures', 'prompting', 'response', 'caregivers', 'levels', 'indicated', 'including', 'years', 'generalization', 'literature', 'follow', 'potential', 'improved', 'validity', 'different', 'number', 'trial', 'accuracy', 'specific', 'pain', 'early', 'skill', 'problem', 'conditions', 'app', 'acquisition', 'change', 'procedures', 'present', 'target', 'probe', 'teacher', 'individual', 'applied', 'special', 'covid', 'weeks', 'practices', 'examined', 'non', 'evaluation', 'young', 'computer', 'assessed', 'suggest', 'settings', 'disorders', 'provided', 'limited', 'reality', '10', 'age', 'maintained', 'anxiety', 'process', 'maintenance', 'examine', 'test', 'researchers', 'academic', 'problems', 'primary', 'fidelity', 'motor', 'access', 'delivery', 'delivered', 'week', 'increasing', 'adolescents', 'digital', 'instructional', 'improvement', 'conclusions', 'condition', 'science', 'improving', 'feasibility', 'home', 'changes', 'low', 'treatments', 'need', 'overall', 'completed', 'setting', 'family', 'paper', 'caregiver', 'attention', 'classroom', 'mobile', 'service', 'preference', 'educational', 'pre', 'living', 'pandemic', 'play', 'new', 'participated', 'independent', 'life', 'challenging', 'addition', 'responses', 'designs', 'function', 'mathematics', 'secondary', 'knowledge', 'monitoring', 'identified', 'observed', 'improvements', 'disorder', 'higher', 'families', 'making', 'analyses', 'package', 'variables', 'focused', 'assess', 'work', 'phases', 'word', 'protocol', 'stimuli', 'developed', 'psychological', 'moderate', 'stimulus', 'important', 'presented', 'challenges', '12', 'peer', 'needed', 'ability', 'trials', 'background', 'criteria', 'mental', 'fluency', 'alternating', 'tablet', 'rate', 'interactions', 'risk', 'experience', 'strategy', 'context', 'difficulties', 'symptoms', 'determine', 'severe', 'programs', 'interaction', 'aphasia', 'large', 'acceptability', 'investigate', 'total', 'implement', 'information', 'spectrum', 'designed', 'complex', 'regarding', 'person', 'patient', 'did', 'staff', 'aged', 'limitations', 'diagnosed', 'tool', 'technologies', 'tasks', 'mixed', 'verbal', 'objective', 'help', 'preliminary', 'practitioners', 'assessments', 'small', 'remote', 'associated', 'words', 'brain', 'rehabilitation', 'music', 'conclusion', 'community', 'received', 'developing', 'various', 'size', 'taught', 'al', 'session', 'et', 'population', 'outcome', 'differences', 'measured', 'previous', 'period', 'significantly', 'novel', 'items', 'text', 'investigated', 'additional', 'field', 'appropriate', 'vocabulary', 'public', 'provides', 'meta', 'direct', 'step', 'analysts', 'scores', 'approaches', 'face', 'device', 'providing', 'year', 'bst', 'barriers', 'emotional', 'frequency', 'aimed', 'depression', 'ipad', 'aims', 'randomized', 'writing', 'sample', 'indicate', 'collected', 'id', 'promote', 'procedure', 'chronic', 'professionals', 'general', 'stress', 'targeted', 'devices', 'analyzed', 'identify', 'groups', 'contingency', 'exercise', 'available', 'models', 'required', 'characteristics', 'solving', 'components', 'article', 'enhance', 'goal', 'address', 'qualitative', 'augmented', 'evaluating', 'analytic', 'measure', 'scale', 'methodology', 'tau', 'relation', 'old', 'tools', 'responding', 'reduce', 'mean', 'sced', 'mediated', 'months', 'explore', 'choice', 'participation', 'supporting', 'assistive', 'comprehension', 'leisure', 'telepractice', 'combined', 'concurrent', 'smartphone', 'interviews', 'brief', 'satisfaction', 'questions', 'sleep', 'inclusion', 'include', 'preferred', 'schedules', 'media', 'intensity', 'revealed', 'elementary', 'professional', 'therapeutic', 'mastery', 'functioning', 'injury', 'framework', 'robot', 'recommendations', 'vr', 'published', 'controlled', 'opportunities', 'real', 'employed', 'peers', 'english', 'content', 'type', 'preschool', 'supported', 'environment', 'involved', 'subjects', 'performed', 'weekly', 'goals', 'seven', 'discussion', 'negative', 'comparison', 'youth', 'supports', 'trained', 'adapted', 'grade', 'prompts', 'adult', 'relationship', 'gains', 'behaviour', 'human', 'series', 'awareness', 'met', 'syndrome', 'average', 'factors', 'alternative', 'greater', 'materials', 'assisted', 'stimulation', 'correct', 'decision', 'term', 'role', 'report', 'act', 'selected', 'additionally', 'perceived', 'discrete', 'body', 'vocal', 'shown', 'repeated', 'experiences', 'delay', 'applications', 'supervision', 'areas', 'long', 'aided', 'progress', 'techniques', 'led', 'acquired', '15', 'stroke', 'embedded', 'lack', 'despite', 'understanding', 'quantitative', 'reducing', 'safety', 'demonstrate', 'extended', 'pilot', 'range', 'medical', 'therapists', 'compare', 'enhanced', 'vocational', 'disruptive', 'intensive', 'cbt', 'relevant', 'percentage', 'lower', 'naturalistic', 'statistical', 'collection', 'types', 'structured', 'picture', 'functions', 'decreased', 'targets', 'features', 'speaking', 'develop', 'survey', 'learners', 'reviewed', 'replicated', 'involving', 'month', 'dependent', 'increases', 'therapist', 'make', 'web', 'recent', 'focus', 'socially', 'modelling', 'software', 'idd', 'better', 'systems', 'adherence', 'nick', 'terms', 'standards', 'replication', 'followed', 'decrease', 'efficiency', 'probes', 'rates', 'instructions', 'exposure', 'given', 'criterion', 'electronic', 'gbg', 'independently', 'engaged', 'acceptance', 'component', 'learned', 'contingent', 'assessing', 'comparing', 'common', 'impairment', 'benefits', 'interactive', 'generalized', 'duration', 'differential', 'learn', 'similar', 'steps', 'promising', 'promoting', 'aim', 'considered', 'variable', 'specifically', 'efficient', '11', 'methodological', 'objectives', 'experienced', 'experiment', 'initial', 'vm', 'machine', 'active', 'second', 'internet', 'schedule', 'articles', 'good', 'oral', 'set', 'eye', 'disease', 'stereotypy', '20', 'imitation', 'expressive', 'independence', 'able', 'naming', 'employment', 'times', 'procedural', '30', 'suggested', 'cases', 'hours', 'according', 'complete', 'engage', 'min', 'acceptable', 'described', 'feasible', 'contexts', 'patterns', 'statistically', 'power', 'dyads', 'reduction', 'combination', 'sizes', 'math', 'memory', 'utilized', 'prior', 'manipulatives', 'ai', 'traditional', 'end', 'best', 'particularly', 'typically', 'class', 'successful', 'individualized', 'resulted', 'days', 'variability', 'introduction', 'games', 'standard', 'clinicians', 'diagnosis', 'implementing', 'completion', 'events', 'automatically', 'guidance', 'healthcare', 'literacy', 'enhancing', 'graphs', '95', 'adaptive', 'concerns', 'main', 'practical', 'user', 'comprehensive', 'university', 'receiving', 'trend', 'apps', 'commonly', 'collaborative', 'critical', 'production', 'curriculum', 'members', 'search', 'questionnaires', 'generating', 'questionnaire', 'order', 'value', 'course', 'movement', 'proposed', 'highly', 'little', 'auditory', '14', 'result', 'educators', 'incorporating', 'directions', 'modified', 'withdrawal', 'working', 'board', 'videos', 'form', 'integrity', '13', 'inclusive', 'area', 'usability', 'providers', 'modalities', 'voice', 'facilitate', 'perceptions', 'effectively', 'emotion', 'existing', 'necessary', 'occupational', 'known', 'childhood', 'schools', 'strong', 'observation', 'importance', '18', 'guidelines', 'day', 'integrated', 'therapies', 'format', 'obtained', 'natural', 'reduced', 'hearing', 'environments', 'conversation', 'furthermore', 'trauma', 'college', 'successfully', 'ratings', 'suggestions', 'behavioural', 'transfer', 'basic', 'tracking', 'relations', 'mobility', 'contingencies', 'ethical', 'testing', 'communicative', 'classrooms', 'dementia', 'sound', 'key', 'discuss', 'continued', 'established', '16', 'errors', 'smart', 'influence', '2020', 'recognition', 'valid', 'investigation', 'consistent', 'examining', 'joint', 'gender', 'commitment', 'points', 'reviews', 'personal', 'interview', 'way', 'short', 'rated', 'reversal', 'systematically', 'shared', 'difficulty', 'ci', 'cost', 'affect', 'partners', 'cultural', 'utility', 'aid', 'benefit', 'abilities', '17', 'transition', 'inspection', 'tech', 'pecs', 'state', 'executive', 'minimally', 'mood', '25', 'issues', 'variety', 'conduct', 'palsy', 'essential', 'sensory', 'repetitive', 'cerebral', 'parental', 'stories', 'majority', 'complexity', 'perspectives', 'programming', 'success', 'observational', '100', 'mathematical', 'preschoolers', 'train', 'technique', 'classes', 'especially', 'flexibility', 'global', 'rural', 'competing', 'varied', 'adhd', 'bias', 'traumatic', 'reach', 'difference', 'older', 'offer', 'authors', 'applying', 'plus', 'center', 'explored', 'values', 'imagery', 'processes', 'require', 'equivalence', 'identifying', 'administered', 'possible', 'open', 'platform', 'client', 'clinically', 'consisted', 'consider', 'confidence', 'versus', 'generally', 'robots', 'utilizing', 'principles', 'scientific', 'ar', 'frequently', 'occurred', 'resources', 'item', 'create', 'immediate', 'recorded', 'linear', 'tests', 'motivation', 'upper', 'reports', 'automatic', 'ethics', 'synchronous', 'prompt', 'involves', 'read', 'emerging', 'analyze', 'limb', 'adolescent', 'produced', 'like', 'hallucinations', 'score', 'checklist', 'recruited', 'everyday', 'concept', 'head', 'motion', '2021', 'combining', 'line', 'consistency', 'question', 'middle', 'descriptive', 'artificial', 'theory', 'behaviours', 'matrix', 'clients', 'accurate', 'affected', 'larger', 'compliance', 'suggests', 'assigned', 'hygiene', 'preferences', 'randomly', 'interface', 'lead', 'deficits', 'mothers', 'technological', 'live', 'experiments', 'project', 'thinking', 'dynamic', 'databases', 'display', 'personalized', 'experiencing', 'elements', 'tact', 'likely', 'resource', 'perform', 'presents', 'guided', 'ages', 'building', 'consisting', 'exploring', 'guide', 'meet', 'recovery', 'point', 'regulation', 'concepts', 'gaze', 'targeting', 'telerehabilitation', 'impacts', 'hand', 'diverse', 'exchange', 'index', 'aspects', 'minutes', 'action', 'directly', 'world', 'wide', 'modules', 'mild', 'female', 'directed', 'receptive', 'contribute', 'untrained', 'achieved', '001', '40', 'persons', 'relationships', 'assist', 'intelligence', 'severity', 'neurodevelopmental', 'linguistic', 'culturally', 'useful', 'ways', 'positively', 'job', 'multi', 'expected', 'simple', 'local', 'indicating', 'partner', 'input', 'growing', 'parenting', 'requesting', 'gait', 'collaboration', 'gap', 'extend', 'addressing', 'measurement', 'explicit', 'mhealth', '50', 'understand', 'reporting', 'domains', 'users', 'cancer', 'accessible', 'simultaneous', 'centered', 'speed', 'vp', 'team', 'scoping', 'empirical', 'china', 'electrical', 'topic', 'integration', 'phonological', 'created', 'synthesis', 'carried', 'creating', 'respond', 'policy', 'meditation', 'reliability', 'suggesting', 'situations', 'dissemination', 'distress', 'compassionate', 'informed', 'automated', 'conversational', 'maintain', 'asynchronous', 'displays', 'changing', 'mindfulness', 'error', 'perception', 'states', 'maintaining', 'yielded', 'cp', 'deliver', 'feature', 'walking', 'sight', 'talk', 'sets', 'works', 'women', 'male', 'designing', 'widely', 'healthy', 'ebi', 'promise', 'sgd', 'preparation', 'pairs', 'recommended', 'final', 'rating', 'minute', 'produce', 'unique', 'particular', 'tested', 'includes', 'movements', 'dance', 'selection', 'conducting', 'praise', 'capacity', 'substantial', 'enrolled', 'increasingly', 'written', 'impairments', 'module', 'standardized', 'reinforced', 'meaningful', 'fa', 'having', 'tutorial', 'story', 'nonconcurrent', 'reinforcer', 'kindergarten', 'diagnostic', 'abstract', 'shows', 'matching', 'prevention', 'countries', 'offers', 'insights', 'cohort', 'challenge', 'modality', 'interventionists', 'respectively', 'potentially', 'relative', 'right', 'programme', 'finally', 'physiotherapy', 'varying', 'coding', 'version', 'reliable', 'currently', 'difficult', '2022', 'network', 'pd', 'sequence', 'extensive', '21', 'minimal', 'vs', 'wearable', 'continue', 'beneficial', 'learner', 'ratio', 'masking', 'place', 'periods', 'sd', 'engaging', 'base', 'onset', 'phrase', 'focuses', 'forms', 'agreement', 'sentence', '2023', 'mand', 'diabetes', 'coping', 'calculated', '60', 'sceds', 'simulation', 'compassion', 'means', 'establish', 'plans', 'crucial', 'google', 'recess', 'hybrid', 'previously', 'analysed', 'planning', 'foreign', 'samples', 'dtt', 'began', 'demonstrating', 'options', 'longer', 'preservice', 'cross', 'just', 'prevalence', 'emt', 'multilevel', 'mechanisms', 'food', 'thematic', 'experts', 'paired', 'organizations', 'trends', 'examines', 'delivering', 'surveys', 'national', 'discrimination', 'valuable', 'serve', 'addressed', 'balance', 'half', 'males', 'tele', 'strength', 'homes', '29', 'treating', 'interpretation', 'athletes', 'extension', 'pa', 'blended', 'motivational', 'manipulative', 'identification', 'consultation', 'indicators', 'muscle', 'sars', 'feeding', 'toddlers', 'exploratory', 'core', 'populations', 'posttest', 'dual', 'decisions', 'adopted', 'processing', 'statements', 'medicine', 'subsequent', 'reductions', 'request', 'allow', 'apply', 'recording', '33', 'categories', 'antecedent', 'introduced', 'oriented', 'methodologies', 'extent', 'structure', 'participating', 'organization', 'meeting', 'intervals', 'correctly', 'solution', 'united', 'opinions', 'visually', '80', 'sufficient', 'topics', 'heart', 'multimedia', 'derived', 'determined', 'multistep', 'depressive', 'actions', 'achieve', 'ab', 'lecture', 'observations', 'clear', 'calls', 'objects', 'history', 'clinic', 'card', 'responsive', 'accessibility', 'remaining', 'overlap', 'paraeducators', 'scd', 'factor', 'does', 'remain', 'concrete', 'algebra', 'displayed', 'tutoring', 'analyst', 'determination', 'pediatric', 'adaptations', 'examples', 'consequences', 'vsds', 'messages', 'fatigue', 'taking', 'prosthetic', 'usage', 'weight', 'supplemental', 'inform', 'emerged', 'primarily', 'highlights', 'answer', 'hyperactivity', 'statistics', 'typical', 'issue', 'pictures', 'demonstrates', 'ongoing', 'random', 'perspective', 'cm', 'phrases', 'constant', 'expressed', 'indicates', 'conceptual', 'regular', 'offered', '2019', '81', 'output', 'responded', 'describes', 'cognition', 'took', '24', 'protocols', 'progressive', 'augmentative', 'ecological', 'count', 'consecutive', 'material', 'completing', 'contributes', 'baselines', 'tbi', 'verb', 'symbols', 'investigating', 'exhibited', 'continuous', 'researcher', 'lessons', 'subtraction', 'generalize', 'decreasing', 'psychotherapy', 'driven', 'start', 'examination', '90', 'allows', 'controls', 'stem', 'coach', 'videoconferencing', 'unit', 'insomnia', 'precision', 'avoidance', 'replicate', 'financial', 'wearing', 'teams', 'nonverbal', 'estimation', 'sexual', 'measurements', 'poor', 'color', 'example', 'tablets', 'postural', '27', 'considering', 'robust', 'regression', 'initially', 'script', 'mother', 'trunk', 'loss', 'falling', 'sought', 'mastered', 'seeking', 'narrative', 'themes', 'communicate', 'receive', 'meaning', 'called', '36', 'past', 'playing', 'hour', 'advanced', 'requests', '2018', 'distance', 'accessing', 'remains', 'contact', 'hospital', 'certified', 'personality', 'major', 'gamification', 'proficiency', 'wwc', 'degree', 'exercises', 'sampling', 'initiated', 'organizational', 'players', 'resulting', 'cook', 'sustained', 'ensure', 'pairing', 'studied', 'audio', 'courses', 'adapting', 'turns', 'fact', 'solve', 'efficacious', 'burnout', 'gain', 'multimodal', 'cards', 'medication', 'scene', 'registration', 'spoken', 'manual', 'simulated', 'recruitment', 'stage', 'adverse', 'account', 'tm', 'internal', 'advocacy', 'missing', 'sustainability', 'matched', 'correlation', 'arrangement', 'opportunity', 'burden', '66', '01', 'parameters', 'solutions', 'graduate', 'uses', 'reciprocal', 'struggling', 'rapid', 'sport', 'vocalizations', 'option', 'recently', '42', 'stages', 'comfort', 'coded', 'turn', 'posttreatment', 'instructor', 'relatively', 'retention', 'presence', 'income', 'orientation', '45', 'notes', 'spinal', 'abab', 'monitor', 'instructors', 'formats', 'spelling', 'rigor', 'incorporated', 'routine', 'agents', 'graphing', 'tailored', 'american', 'book', 'interpersonal', 'easy', 'coordination', 'ii', 'trainers', 'vivo', 'adequate', 'subtypes', 'determining', 'near', 'provision', 'routines', 'semi', 'multielement', 'excel', 'sense', 'decline', 'symptom', 'significance', 'innovative', 'banging', 'ml', 'habit', 'breathing', 'semantic', 'safe', 'reached', 'socio', 'map', 'technical', 'desired', 'nursing', 'fully', 'length', 'fct', 'efforts', 'modification', 'sports', 'viable', 'aggression', 'extinction', 'injurious', 'rett', 'frequent', 'highlighted', 'showing', 'usual', 'accurately', 'integrating', 'acquire', 'variations', 'leading', 'interval', 'dro', 'boy', 'predict', 'cord', 'boys', 'japanese', 'incentives', 'prevent', 'graphical', 'manage', 'randomization', 'pica', 'sgds', 'shortly', 'nap', 'trainees', 'psychosis', 'object', 'validated', 'starting', 'note', 'demand', 'view', 'scored', 'treat', 'surgery', 'impacted', 'considerations', 'later', 'flashcards', 'sensitivity', 'environmental', 'nature', 'represent', '26', 'clinician', 'journals', 'occur', 'remained', 'bcbas', 'free', 'labeling', 'dyslexia', 'indices', 'estimate', 'asleep', 'clearinghouse', 'videoconference', 'unknown', 'explores', 'fewer', 'date', 'tens', 'prospective', 'standing', 'residential', 'check', 'added', 'retrieval', 'animated', 'moderator', 'detailed', 'scenarios', 'analyzing', 'mode', 'fear', 'evaluations', 'bayesian', 'match', 'hrv', 'likelihood', 'retrospective', 'screening', 'situation', 'animation', 'certification', 'stakeholders', 'beliefs', 'combines', 'dyad', '75', 'requirements', 'recognized', 'sharing', 'db', 'served', 'verbally', 'generalisation', 'supervisors', 'exists', 'pivotal', 'spent', 'focusing', 'conventional', '2017', 'email', 'centers', 'seen', 'highest', '38', 'bsp', 'vsm', 'exist', 'enabled', 'token', 'graph', 'occupation', 'taken', 'pubmed', 'cov', 'deficit', 'storytelling', 'shift', 'plan', 'smoking', 'subjective', 'innovation', 'warranted', 'stability', 'pencil', 'choices', 'idbt', 'chain', 'presenting', 'appraisal', 'sources', 'computerized', 'vnest', 'add', 'combinations', 'adoption', 'measuring', 'registered', 'infant', 'redirection', 'load', 'stuttering', 'demonstration', 'spatial', 'widespread', 'delayed', 'elevated', 'fine', 'construction', 'proportion', 'representations', 'inflammatory', 'cai', 'achievement', 'arm', 'delays', 'recall', 'improves', 'strengths', 'fourth', 'metabolic', 'helped', 'unclear', 'responsiveness', 'musculoskeletal', 'respect', 'effort', 'provider', 'locations', 'spontaneous', 'operant', '2015', 'basis', 'handwriting', 'lives', 'noncontingent', 'contextual', 'light', 'undergraduate', 'parkinson', 'flashcard', 'collect', 'pressure', 'highlight', 'code', 'meal', 'dental', 'presentation', 'dosage', 'dd', 'mbs', 'technicians', 'generated', 'autonomy', 'achieving', 'intraverbal', 'csa', 'paraeducator', 'managing', 'listener', 'emergence', 'competence', 'screen', 'insight', 'modifications', 'chains', 'randomised', 'worry', 'psychology', 'approximately', 'defined', 'actual', 'infants', 'resilience', 'race', 'plays', 'scales', 'helping', 'utilization', 'seating', 'workers', 'communities', 'prediction', 'record', 'cochlear', 'gross', 'fraction', 'symbolic', 'economy', 'regardless', 'prt', 'corrective', 'animal', 'microsoft', 'psychosocial', 'translational', 'recommend', 'addiction', 'rules', 'utilizes', 'tdcs', 'fifth', 'searched', 'run', 'conferencing', '32', 'stt', 'considerable', 'society', 'interdependent', 'genetic', '70', 'conditional', 'blocks', 'tangible', 'proof', 'journal', 'corresponding', 'fit', 'detect', 'accelerometer', 'adulthood', 'facilitating', 'listening', 'far', 'document', '31', 'foster', 'formulation', 'urban', 'prepared', '2016', 'remotely', 'scope', 'ebd', 'algorithms', 'close', 'attend', 'programmed', 'original', 'concluded', 'parkour', 'economic', 'repetition', 'flexible', 'spaces', 'climbing', 'pretest', 'leads', 'perceptual', 'manualized', 'absence', 'ptsd', 'confirmed', 'status', 'treated', 'private', 'friendly', 'adding', 'capture', 'trust', 'cues', 'ict', 'tootling', 'robotic', 'skin', 'prolonged', 'performing', 'build', 'enable', 'postsecondary', '22', 'extracted', 'restricted', '93', '85', 'hierarchical', 'empathy', 'equally', 'blood', 'slightly', 'cochrane', 'facial', 'https', 'connect', 'immediately', 'physically', 'rule', 'ansa', 'hs', 'magnetic', 'drawing', 'pose', 'pdc', 'spanish', 'dimensions', 'maps', 'momentary', 'dataset', 'replications', 'sam', 'expect', 'adaptation', 'passive', 'march', 'fractions', 'satisfied', 'contributed', 'engineering', 'mass', 'siblings', 'tom', 'yoga', 'observer', 'certain', 'divided', 'style', 'interteaching', 'creativity', 'negatively', 'avatar', 'medium', 'rare', 'edible', 'failed', 'soccer', 'asked', 'disparities', 'underlying', 'observing', 'instrument', 'lasting', 'pediatrician', 'situ', 'emotions', 'problematic', 'happiness', 'relapse', 'strengthening', '35', 'slow', 'helpful', 'decreases', 'letter', 'surface', 'participate', 'affects', 'black', 'impaired', 'practitioner', 'advantages', 'sciences', 'graphic', 'january', 'conversations', 'validate', 'normal', '28', 'maximum', 'interruption', 'knee', 'comparisons', 'menstrual', 'longitudinal', 'physician', 'exploration', 'cortisol', 'art', 'investigations', 'withdrawn', 'struggle', 'follows', 'suitable', 'representational', 'ld', 'ms', 'finding', 'referred', 'switch', 'projects', 'easily', 'extraction', 'domain', 'museum', 'sign', 'grief', 'influenced', 'synthesize', 'eating', 'substantially', 'central', 'sitting', 'beginning', 'texts', 'formal', 'multidisciplinary', 'highlighting', 'median', 'infection', 'stand', 'minimum', 'prepare', 'encourage', 'grid', 'books', 'quasi', 'incremental', 'causal', 'establishing', 'virtually', 'comprised', 'vbi', 'toothbrushing', 'identity', 'units', 'correspondence', 'coronavirus', 'kinect', 'messaging', 'creation', 'contributions', 'ranging', 'substance', 'fluent', 'international', 'chinese', 'distinct', 'gaming', 'involvement', 'microprocessor', 'datasets', 'gov', 'expression', 'powr', 'postpartum', 'sequential', 'postintervention', 'outside', 'adjustments', 'pedagogical', 'reference', 'neurotypical', 'cooperative', '00', 'estimates', 'exclusion', 'asking', '3d', 'packages', 'classification', 'validation', 'native', 'ultimately', 'incorporates', 'subtype', 'consideration', 'sensors', 'initiations', 'encouraged', 'requiring', 'association', 'talking', 'reaching', 'intensified', 'mands', 'selecting', 'predictive', 'productive', 'located', 'speakers', 'alpha', 'enabling', 'windows', 'utilize', 'telephone', 'augment', 'rumination', 'similarly', 'workshop', 'reinforcers', 'appears', 'transitioned', 'phone', 'diversity', 'expanding', 'expand', 'extremity', 'sensitive', 'esteem', 'summer', 'profound', 'waiting', 'reciprocity', 'choose', 'skinner', 'inconsistent', 'descriptions', 'structures', 'sentences', 'planned', 'empirically', 'rrb', 'latency', 'pay', 'answering', 'bariatric', 'lexical', 'recreational', 'interpreted', 'sequences', 'designers', 'modes', 'quantity', 'facilitated', 'telemedicine', 'wisdom', 'india', '34', 'pwd', 'image', 'characterized', 'nonoverlap', 'fields', 'database', 'comparable', 'variance', '05', '37', 'storybook', 'tier', 'abstinence', 'favorable', 'milieu', 'formation', 'pursuit', 'velocity', 'psychiatric', 'plp', 'multicomponent', 'pitch', 'relevance', '83', 'involve', 'representing', 'cause', 'ca', 'employing', 'originality', 'contributing', 'clinicaltrials', 'interested', '23', 'occurring', 'discourse', 'suspected', 'dystonic', 'stimulating', 'creative', 'fidget', 'ed', 'incorporate', 'ema', 'sustainable', 'blocking', 'scoring', 'helps', 'usefulness', 'appear', 'adds', 'habits', 'reflection', 'interpret', 'proxy', 'ha', 'trainer', 'dysregulation', 'serving', 'associations', 'inquiry', 'pe', 'improvised', 'noted', 'intrusive', 'migraine', 'temporal', 'linked', 'graduated', 'investigates', 'alm', 'twice', 'survivors', 'underwent', 'popular', 'injuries', 'list', 'sld', 'modest', '64', 'played', 'touching', 'propose', 'pnd', 'spd', 'description', 'institutions', 'broad', 'supplement', 'mind', 'disfluencies', 'expert', 'musical', 'demands', 'critically', 'faster', 'practicing', 'styles', 'heterogeneous', 'persistent', 'pt', 'rely', 'tacts', 'aids', 'contrast', 'publication', 'pattern', 'phonemic', 'define', 'cumulative', 'vaping', 'verbs', 'prosocial', 'comparative', 'intended', 'rcts', 'sequencing', 'bidirectional', 'pharmacological', '68', 'running', 'ecoaching', 'pcr', 'hip', 'exposed', 'graded', 'apraxia', 'workplace', 'prototype', 'ranged', '76', 'respondents', 'commercial', 'room', 'zoom', '82', 'overlapping', 'hands', 'broader', 'moderators', 'lateropulsion', 'fast', 'antidepressants', 'caused', 'repertoire', 'conjunction', 'interprofessional', 'respiratory', 'vigorous', 'assistants', 'antipsychotic', 'platforms', 'specialized', 'moderately', 'concerning', '63', 'relational', 'external', 'displaying', 'consistently', 'wheeled', 'coached', 'evaluates', 'theoretical', 'prevalent', 'backgrounds', 'experiential', 'approved', 'resultsthe', 'reward', 'supplemented', 'requires', 'interpreting', 'subsequently', 'documented', 'mitigate', 'consumer', 'electroencephalogram', 'insufficient', 'dysphagia', 'aware', '41', 'synthesized', 'searches', 'left', 'minimize', 'williams', 'restrictions', 'concern', 'protection', 'great', 'risks', 'females', 'diary', 'rehearsal', 'depth', 'exhibit', 'incidence', 'transitioning', 'foundation', 'nearly', 'removed', 'overview', 'volunteers', 'consensus', 'pragmatic', 'fixed', 'echo', 'acquiring', 'facilitators', 'advances', 'costs', 'evaluative', 'attentional', 'alongside', 'organized', 'gold', 'mask', 'rsas', '62', 'experimenter', 'cadence', 'growth', 'sen', 'tweets', 'availability', 'estimated', 'reveal', 'equity', 'cooking', 'authentic', 'numbers', 'statement', 'prisma', 'law', 'percent', 'interests', 'cas', 'sib', 'expectations', 'forward', 'yield', 'answers', 'qol', 'construct', 'fitness', 'traits', 'existed', 'hypothesis', 'failure', 'message', 'crisis', 'competitive', 'computers', 'gaps', 'rd', 'dbt', 'ensuring', 'generic', 'org', 'phobia', 'turning', '86', '84', 'enhancement', 'sleeping', 'externalizing', 'physiological', 'dysfunction', 'pb', 'makes', 'possibility', '88', 'dressing', 'tinnitus', 'supportive', 'assistance', 'visits', 'pst', 'assistant', 'calculate', 'sounds', 'abduction', 'pedagogy', 'offering', 'calculations', 'posture', 'faced', 'moving', 'accelerometers', 'regions', 'rr', 'receives', 'proximity', 'comprising', 'summarized', 'categorized', '87', 'started', 'company', 'memories', 'bug', 'ear', 'master', 'frame', 'corrected', 'obsessive', 'contained', 'cbm', 'detection', 'metrics', 'doi', 'loneliness', '89', 'evolutionary', 'trajectory', 'equivalent', 'es', 'fsp', 'element', 'lures', 'paradigm', 'views', 'expressions', 'fu', 'ended', 'reasons', 'diseases', 'pathologists', 'distributed', 'stigma', 'hypothesized', 'markers', 'sites', 'release', 'dynamics', 'frameworks', 'thought', 'evolution', 'representative', 'green', 'attending', '48', 'theraplay', 'deviation', 'geometry', 'captured', 'interventionist', 'tutors', 'ocd', 'searching', 'manner', 'universal', 'allowing', 'position', 'neuromuscular', 'inter', 'escape', 'mealtime', 'st', 'navigate', 'proved', 'dyslexic', 'represented', 'differ', 'iv', 'constructed', 'microlearning', 'watch', 'endurance', 'powerpoint', 'op', 'brian', 'dialogic', 'explanation', 'publications', 'summarize', 'site', 'buprenorphine', 'describing', 'fundamental', 'largely', 'author', 'partnership', 'interference', 'medications', 'incidental', '99', 'decades', 'acupuncture', 'urine', 'evidenced', 'aatd', 'individually', 'ndbi', 'correction', 'untreated', 'appeared', 'korean', 'monitored', 'competency', 'entire', 'unsafe', 'generation', 'sheets', 'obe', 'sar', 'isolation', 'reddit', 'shorter', '96', 'market', 'scopus', 'panel', 'purposes', 'centred', 'late', 'carlo', 'cardiac', 'incarcerated', 'interrater', 'discusses', 'producing', 'multiplication', 'money', 'away', 'reflect', 'acid', '2014', 'eligible', 'lacking', 'zero', 'bcba', 'esdm', 'manipulation', 'resonance', 'efl', 'vf', 'regurgitation', 'category', 'cooperation', '65', 'inventory', 'antecedents', 'neuropathic', 'acts', 'encouraging', 'smartphones', 'alleviate', 'proposes', 'block', 'cbc', 'b12', 'lumbar', 'imaging', 'dilated', 'perivascular', 'organic', 'chromosomal', 'gathered', 'acids', 'ketosis', 'vitamin', 'parametric', 'ssrds', 'gamified', 'animals', 'accessed', 'collecting', 'anomia', 'discussions', 'digit', 'event', 'explain', 'psycinfo', 'disruptions', 'strengthen', 'fearful', 'stabilizing', 'steroids', 'immunotherapy', 'instances', 'inference', 'chosen', 'prompted', 'scalable', 'guiding', 'physiotherapist', 'volunteer', 'candidates', 'ndbis', 'electromyography', 'coaches', 'insurance', 'girl', 'rac', 'dilemmas', 'turkish', 'largest', 'initiatives', 'readers', 'induced', 'worldwide', 'nutrition', 'commenting', 'doing', 'renewal', 'faculty', 'aiming', 'dearth', 'nonparametric', 'foundational', 'select', 'bacb', 'fading', 'posting', 'direction', 'initiation', 'instant', 'assignment', 'leveraging', 'ct', 'competition', 'rater', 'interact', 'vbis', 'emergent', 'depending', 'bilingual', 'facts', 'details', 'contribution', 'profoundly', 'inpatient', '46', 'iterative', 'counseling', 'assisting', 'diaphragmatic', 'biofeedback', 'affecting', 'steam', 'exceptionality', 'undertaken', 'explicitly', 'transformative', 'computational', 'deposit', 'false', 'logbook', 'attended', 'shifts', 'standardised', 'emergency', 'geographic', 'collateral', 'teletherapy', 'revised', 'touch', 'inappropriate', 'poses', 'conflict', 'gradual', 'location', 'protective', 'lectures', 'detected', 'abi', '92', 'metacognitive', 'recurrence', 'isolated', 'npos', 'tutor', 'pair', 'immersive', 'lesson', 'causes', 'influencing', 'roles', 'voluntary', 'rigorous', 'informal', 'summary', 'observers', 'bridge', 'mrehab', '56', 'portion', 'degrees', 'introducing', 'reaches', 'applicability', 'toileting', 'actors', 'thyroid', 'abla', 'homework', 'screened', 'tactile', 'beta', 'reliably', 'regularly', 'conscious', 'authenticity', 'monte', 'compulsive', 'interfaces', 'minor', 'childbirth', 'intelligibility', 'reverse', 'equipment', 'copm', 'underserved', '57', '52', 'implant', 'ebp', 'shame', 'sm', 'optimal', 'telesupervision', 'mandarin', 'applicable', 'thrashing', 'puncture', 'awake', 'belief', 'microarray', 'fragile', 'exome', 'lactic', 'antinuclear', 'antibody', 'generalizability', 'rct', 'extends', 'tagteach', 'pcit', 'images', 'indirect', 'confirm', 'anova', 'pfe', 'outpatient', 'rird', 'cessation', 'proposal', 'makey', 'psychologists', 'overcome', 'trialed', 'ego', 'printed', 'vividly', 'obesity', 'absent', 'reinforce', 'accompanied', 'interrupted', 'specialists', 'encountered', 'favorably', 'prerequisite', 'rob', 'picking', 'utilising', 'sedentary', 'cinahl', 'dose', '49', 'vulvodynia', 'fun', 'formative', 'innovations'</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Count (&gt;1 Time)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>371</v>
+      </c>
+      <c r="C14" t="n">
+        <v>728</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2346</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3304</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6347</v>
+      </c>
+      <c r="G14" t="n">
         <v>7512</v>
       </c>
-      <c r="G7" t="n">
-        <v>203870</v>
-      </c>
-      <c r="H7" t="n">
-        <v>11566</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2214</v>
-      </c>
-      <c r="N7" t="n">
-        <v>17.62666436105827</v>
-      </c>
-      <c r="O7" t="n">
-        <v>73.99277253865486</v>
-      </c>
-      <c r="P7" t="n">
-        <v>13.97469157403105</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>273.7433156945392</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Reused Word Count</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>497</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2858</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4816</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Top 10 Reused Words</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>behavior, subjects, children, training, design, behavioral, treatment, generalization, baseline, self</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>behavior, study, treatment, design, results, children, self, training, social, effects</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>children, study, design, behavior, treatment, results, video, participants, training, effects</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>intervention, study, design, children, participants, results, students, video, based, training</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>intervention, study, design, participants, children, training, students, asd, skills, based</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>New Word Count Per Decade</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>944</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2658</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2434</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Top 10 New Words</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>behavior, self, children, training, ss, treatment, procedures, baseline, assessment, sensory</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>performance, community, treatments, restraint, coaching, cognitive, conditions, severe, casts, reducing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>autism, matching, delay, developmental, object, participant, spelling, injury, second, reduced</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>symbol, pecs, stories, asd, protocol, spectrum, seating, slot, discrete, blending</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ipad, gbg, fidelity, app, scribe, id, tau, tech, expressions, emotions</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>covid, pandemic, nick, hallucinations, asynchronous, compassion, emt, certified, insomnia, burnout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>New Word Per Topic Per Decade Count</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1328</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7981</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10152</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22695</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20397</v>
       </c>
     </row>
   </sheetData>

--- a/evolution/unigrams_concat.xlsx
+++ b/evolution/unigrams_concat.xlsx
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1328</v>
+        <v>1314</v>
       </c>
       <c r="C19" t="n">
-        <v>2210</v>
+        <v>2158</v>
       </c>
       <c r="D19" t="n">
-        <v>7981</v>
+        <v>7293</v>
       </c>
       <c r="E19" t="n">
-        <v>10152</v>
+        <v>9094</v>
       </c>
       <c r="F19" t="n">
-        <v>22695</v>
+        <v>19793</v>
       </c>
       <c r="G19" t="n">
-        <v>20397</v>
+        <v>18220</v>
       </c>
     </row>
   </sheetData>

--- a/evolution/unigrams_concat.xlsx
+++ b/evolution/unigrams_concat.xlsx
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="C19" t="n">
-        <v>2158</v>
+        <v>2143</v>
       </c>
       <c r="D19" t="n">
-        <v>7293</v>
+        <v>7086</v>
       </c>
       <c r="E19" t="n">
-        <v>9094</v>
+        <v>8891</v>
       </c>
       <c r="F19" t="n">
-        <v>19793</v>
+        <v>19138</v>
       </c>
       <c r="G19" t="n">
-        <v>18220</v>
+        <v>17716</v>
       </c>
     </row>
   </sheetData>
